--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -7,8 +7,13 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12600"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="System" sheetId="1" r:id="rId1"/>
+    <sheet name="Items" sheetId="2" r:id="rId2"/>
+    <sheet name="Enemies" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_1" localSheetId="0">System!$A$6:$C$249</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -18,8 +23,22 @@
 </workbook>
 </file>
 
+<file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <connection id="1" name="1" type="6" refreshedVersion="6" background="1" saveData="1">
+    <textPr codePage="65001" sourceFile="C:\Users\liufengming\Desktop\1.txt">
+      <textFields count="3">
+        <textField/>
+        <textField/>
+        <textField/>
+      </textFields>
+    </textPr>
+  </connection>
+</connections>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="771">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -150,6 +169,2257 @@
   </si>
   <si>
     <t>KEY_Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRINT</t>
+  </si>
+  <si>
+    <t>Print message in the game console.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以在游戏控制台输出打印的信息。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRINT_DESC</t>
+  </si>
+  <si>
+    <t>Print Message</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>打印信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EXEC</t>
+  </si>
+  <si>
+    <t>EXEC_DESC</t>
+  </si>
+  <si>
+    <t>执行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Execute</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Execute a Python script</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行一段Python脚本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IF</t>
+  </si>
+  <si>
+    <t>If</t>
+  </si>
+  <si>
+    <t>条件分支</t>
+  </si>
+  <si>
+    <t>IF_DESC</t>
+  </si>
+  <si>
+    <t>Select the True or False branch by condition.</t>
+  </si>
+  <si>
+    <t>根据条件选择 True 或 False 分支。</t>
+  </si>
+  <si>
+    <t>SET_LOCAL_VALUE</t>
+  </si>
+  <si>
+    <t>Set Local Value</t>
+  </si>
+  <si>
+    <t>设置本地变量</t>
+  </si>
+  <si>
+    <t>SET_LOCAL_VALUE_DESC</t>
+  </si>
+  <si>
+    <t>Set a graph local value by name.</t>
+  </si>
+  <si>
+    <t>按名称设置图的本地变量值。</t>
+  </si>
+  <si>
+    <t>GET_LOCAL_VALUE</t>
+  </si>
+  <si>
+    <t>Get Local Value</t>
+  </si>
+  <si>
+    <t>获取本地变量</t>
+  </si>
+  <si>
+    <t>GET_LOCAL_VALUE_DESC</t>
+  </si>
+  <si>
+    <t>Get a graph local value by name, with default.</t>
+  </si>
+  <si>
+    <t>按名称获取图的本地变量值，支持默认值。</t>
+  </si>
+  <si>
+    <t>GET_LOCAL_VALUE_REF</t>
+  </si>
+  <si>
+    <t>Get Local Value Ref</t>
+  </si>
+  <si>
+    <t>获取本地变量引用</t>
+  </si>
+  <si>
+    <t>GET_LOCAL_VALUE_REF_DESC</t>
+  </si>
+  <si>
+    <t>Get a readable/writable reference to a local value.</t>
+  </si>
+  <si>
+    <t>获取一个可读写的本地变量引用。</t>
+  </si>
+  <si>
+    <t>ADD_ANIM</t>
+  </si>
+  <si>
+    <t>Add Animation</t>
+  </si>
+  <si>
+    <t>添加动画</t>
+  </si>
+  <si>
+    <t>ADD_ANIM_DESC</t>
+  </si>
+  <si>
+    <t>Create and add an animation sprite to the scene.</t>
+  </si>
+  <si>
+    <t>在场景中创建并播放一个动画精灵。</t>
+  </si>
+  <si>
+    <t>GET_ANIM_LENGTH</t>
+  </si>
+  <si>
+    <t>Get Animation Length</t>
+  </si>
+  <si>
+    <t>获取动画时长</t>
+  </si>
+  <si>
+    <t>GET_ANIM_LENGTH_DESC</t>
+  </si>
+  <si>
+    <t>Get the duration of an animation (seconds).</t>
+  </si>
+  <si>
+    <t>获取指定动画的持续时间（秒）。</t>
+  </si>
+  <si>
+    <t>SUPER</t>
+  </si>
+  <si>
+    <t>Call Super</t>
+  </si>
+  <si>
+    <t>调用父类</t>
+  </si>
+  <si>
+    <t>SUPER_DESC</t>
+  </si>
+  <si>
+    <t>Call the parent implementation for the current method.</t>
+  </si>
+  <si>
+    <t>在蓝图/生成类中调用父类同名方法。</t>
+  </si>
+  <si>
+    <t>SELF</t>
+  </si>
+  <si>
+    <t>Self</t>
+  </si>
+  <si>
+    <t>自身对象</t>
+  </si>
+  <si>
+    <t>SELF_DESC</t>
+  </si>
+  <si>
+    <t>Get the object instance that owns the current graph.</t>
+  </si>
+  <si>
+    <t>获取当前图所属的对象实例。</t>
+  </si>
+  <si>
+    <t>GET_ATTR_REF</t>
+  </si>
+  <si>
+    <t>Get Attribute Ref</t>
+  </si>
+  <si>
+    <t>获取属性引用</t>
+  </si>
+  <si>
+    <t>GET_ATTR_REF_DESC</t>
+  </si>
+  <si>
+    <t>Get a readable/writable reference to an object attribute.</t>
+  </si>
+  <si>
+    <t>获取一个可读写的对象属性引用。</t>
+  </si>
+  <si>
+    <t>GET_ATTR</t>
+  </si>
+  <si>
+    <t>Get Attribute</t>
+  </si>
+  <si>
+    <t>获取属性</t>
+  </si>
+  <si>
+    <t>GET_ATTR_DESC</t>
+  </si>
+  <si>
+    <t>Read an attribute value from an object.</t>
+  </si>
+  <si>
+    <t>读取对象的指定属性值。</t>
+  </si>
+  <si>
+    <t>SET_ATTR</t>
+  </si>
+  <si>
+    <t>Set Attribute</t>
+  </si>
+  <si>
+    <t>设置属性</t>
+  </si>
+  <si>
+    <t>SET_ATTR_DESC</t>
+  </si>
+  <si>
+    <t>Set an attribute value on an object.</t>
+  </si>
+  <si>
+    <t>设置对象的指定属性值。</t>
+  </si>
+  <si>
+    <t>GET_SCENE</t>
+  </si>
+  <si>
+    <t>Get Scene</t>
+  </si>
+  <si>
+    <t>获取场景</t>
+  </si>
+  <si>
+    <t>GET_SCENE_DESC</t>
+  </si>
+  <si>
+    <t>Get the current running scene.</t>
+  </si>
+  <si>
+    <t>获取当前运行中的场景对象。</t>
+  </si>
+  <si>
+    <t>IS_VALID_VALUE</t>
+  </si>
+  <si>
+    <t>Is Valid Value</t>
+  </si>
+  <si>
+    <t>值有效</t>
+  </si>
+  <si>
+    <t>IS_VALID_VALUE_DESC</t>
+  </si>
+  <si>
+    <t>Check whether the value is not None.</t>
+  </si>
+  <si>
+    <t>判断值是否为非空（None）。</t>
+  </si>
+  <si>
+    <t>RUN_COMMON_FUNCTION</t>
+  </si>
+  <si>
+    <t>Run Common Function</t>
+  </si>
+  <si>
+    <t>运行公共函数</t>
+  </si>
+  <si>
+    <t>RUN_COMMON_FUNCTION_DESC</t>
+  </si>
+  <si>
+    <t>Execute a common function graph by name.</t>
+  </si>
+  <si>
+    <t>执行指定名称的公共函数图。</t>
+  </si>
+  <si>
+    <t>DICT_GET</t>
+  </si>
+  <si>
+    <t>Dict Get</t>
+  </si>
+  <si>
+    <t>字典获取</t>
+  </si>
+  <si>
+    <t>DICT_GET_DESC</t>
+  </si>
+  <si>
+    <t>Get a value from a dict by key.</t>
+  </si>
+  <si>
+    <t>按 key 获取字典中的 value。</t>
+  </si>
+  <si>
+    <t>DICT_ADD</t>
+  </si>
+  <si>
+    <t>Dict Set</t>
+  </si>
+  <si>
+    <t>字典设置</t>
+  </si>
+  <si>
+    <t>DICT_ADD_DESC</t>
+  </si>
+  <si>
+    <t>Set a dict value by key.</t>
+  </si>
+  <si>
+    <t>按 key 写入字典的 value。</t>
+  </si>
+  <si>
+    <t>DICT_REMOVE</t>
+  </si>
+  <si>
+    <t>Dict Remove</t>
+  </si>
+  <si>
+    <t>字典移除</t>
+  </si>
+  <si>
+    <t>DICT_REMOVE_DESC</t>
+  </si>
+  <si>
+    <t>Remove a key from a dict.</t>
+  </si>
+  <si>
+    <t>移除字典中的指定 key。</t>
+  </si>
+  <si>
+    <t>DICT_CLEAR</t>
+  </si>
+  <si>
+    <t>Dict Clear</t>
+  </si>
+  <si>
+    <t>字典清空</t>
+  </si>
+  <si>
+    <t>DICT_CLEAR_DESC</t>
+  </si>
+  <si>
+    <t>Clear all entries in a dict.</t>
+  </si>
+  <si>
+    <t>清空字典的所有内容。</t>
+  </si>
+  <si>
+    <t>DICT_CONTAINS</t>
+  </si>
+  <si>
+    <t>Dict Contains</t>
+  </si>
+  <si>
+    <t>字典包含</t>
+  </si>
+  <si>
+    <t>DICT_CONTAINS_DESC</t>
+  </si>
+  <si>
+    <t>Check whether a dict contains a key.</t>
+  </si>
+  <si>
+    <t>判断字典是否包含指定 key。</t>
+  </si>
+  <si>
+    <t>LIST_GET</t>
+  </si>
+  <si>
+    <t>List Get</t>
+  </si>
+  <si>
+    <t>列表获取</t>
+  </si>
+  <si>
+    <t>LIST_GET_DESC</t>
+  </si>
+  <si>
+    <t>Get a list item by index.</t>
+  </si>
+  <si>
+    <t>按索引获取列表元素。</t>
+  </si>
+  <si>
+    <t>LIST_APPEND</t>
+  </si>
+  <si>
+    <t>List Append</t>
+  </si>
+  <si>
+    <t>列表追加</t>
+  </si>
+  <si>
+    <t>LIST_APPEND_DESC</t>
+  </si>
+  <si>
+    <t>Append an item to a list.</t>
+  </si>
+  <si>
+    <t>向列表尾部追加一个元素。</t>
+  </si>
+  <si>
+    <t>LIST_REMOVE</t>
+  </si>
+  <si>
+    <t>List Remove</t>
+  </si>
+  <si>
+    <t>列表移除</t>
+  </si>
+  <si>
+    <t>LIST_REMOVE_DESC</t>
+  </si>
+  <si>
+    <t>Remove a list item by index.</t>
+  </si>
+  <si>
+    <t>按索引移除列表元素。</t>
+  </si>
+  <si>
+    <t>LIST_FIND</t>
+  </si>
+  <si>
+    <t>List Find</t>
+  </si>
+  <si>
+    <t>列表查找</t>
+  </si>
+  <si>
+    <t>LIST_FIND_DESC</t>
+  </si>
+  <si>
+    <t>Find the index of a value in a list.</t>
+  </si>
+  <si>
+    <t>查找元素在列表中的索引。</t>
+  </si>
+  <si>
+    <t>LIST_CLEAR</t>
+  </si>
+  <si>
+    <t>List Clear</t>
+  </si>
+  <si>
+    <t>列表清空</t>
+  </si>
+  <si>
+    <t>LIST_CLEAR_DESC</t>
+  </si>
+  <si>
+    <t>Clear all items in a list.</t>
+  </si>
+  <si>
+    <t>清空列表的所有元素。</t>
+  </si>
+  <si>
+    <t>LIST_CONTAINS</t>
+  </si>
+  <si>
+    <t>List Contains</t>
+  </si>
+  <si>
+    <t>列表包含</t>
+  </si>
+  <si>
+    <t>LIST_CONTAINS_DESC</t>
+  </si>
+  <si>
+    <t>Check whether a list contains a value.</t>
+  </si>
+  <si>
+    <t>判断列表是否包含指定元素。</t>
+  </si>
+  <si>
+    <t>TO_STRING</t>
+  </si>
+  <si>
+    <t>To String</t>
+  </si>
+  <si>
+    <t>转字符串</t>
+  </si>
+  <si>
+    <t>TO_STRING_DESC</t>
+  </si>
+  <si>
+    <t>Convert a value to string.</t>
+  </si>
+  <si>
+    <t>将任意值转换为字符串。</t>
+  </si>
+  <si>
+    <t>GET_INT_FROM_STR</t>
+  </si>
+  <si>
+    <t>String To Int</t>
+  </si>
+  <si>
+    <t>字符串转整数</t>
+  </si>
+  <si>
+    <t>GET_INT_FROM_STR_DESC</t>
+  </si>
+  <si>
+    <t>Parse a string as int.</t>
+  </si>
+  <si>
+    <t>将字符串解析为整数。</t>
+  </si>
+  <si>
+    <t>GET_FLOAT_FROM_STR</t>
+  </si>
+  <si>
+    <t>String To Float</t>
+  </si>
+  <si>
+    <t>字符串转浮点</t>
+  </si>
+  <si>
+    <t>GET_FLOAT_FROM_STR_DESC</t>
+  </si>
+  <si>
+    <t>Parse a string as float.</t>
+  </si>
+  <si>
+    <t>将字符串解析为浮点数。</t>
+  </si>
+  <si>
+    <t>STRING_CONCAT</t>
+  </si>
+  <si>
+    <t>String Concat</t>
+  </si>
+  <si>
+    <t>字符串拼接</t>
+  </si>
+  <si>
+    <t>STRING_CONCAT_DESC</t>
+  </si>
+  <si>
+    <t>Concatenate two strings.</t>
+  </si>
+  <si>
+    <t>拼接两个字符串。</t>
+  </si>
+  <si>
+    <t>STRING_CONTAINS</t>
+  </si>
+  <si>
+    <t>String Contains</t>
+  </si>
+  <si>
+    <t>字符串包含</t>
+  </si>
+  <si>
+    <t>STRING_CONTAINS_DESC</t>
+  </si>
+  <si>
+    <t>Check whether a string contains a substring.</t>
+  </si>
+  <si>
+    <t>判断字符串是否包含子串。</t>
+  </si>
+  <si>
+    <t>STRING_LENGTH</t>
+  </si>
+  <si>
+    <t>String Length</t>
+  </si>
+  <si>
+    <t>字符串长度</t>
+  </si>
+  <si>
+    <t>STRING_LENGTH_DESC</t>
+  </si>
+  <si>
+    <t>Get string length.</t>
+  </si>
+  <si>
+    <t>获取字符串长度。</t>
+  </si>
+  <si>
+    <t>STRING_FIND</t>
+  </si>
+  <si>
+    <t>String Find</t>
+  </si>
+  <si>
+    <t>字符串查找</t>
+  </si>
+  <si>
+    <t>STRING_FIND_DESC</t>
+  </si>
+  <si>
+    <t>Find the first occurrence index of a substring.</t>
+  </si>
+  <si>
+    <t>查找子串首次出现的位置。</t>
+  </si>
+  <si>
+    <t>STRING_REPLACE</t>
+  </si>
+  <si>
+    <t>String Replace</t>
+  </si>
+  <si>
+    <t>字符串替换</t>
+  </si>
+  <si>
+    <t>STRING_REPLACE_DESC</t>
+  </si>
+  <si>
+    <t>Replace occurrences of a substring.</t>
+  </si>
+  <si>
+    <t>将子串替换为新字符串。</t>
+  </si>
+  <si>
+    <t>STRING_SPLIT</t>
+  </si>
+  <si>
+    <t>String Split</t>
+  </si>
+  <si>
+    <t>字符串分割</t>
+  </si>
+  <si>
+    <t>STRING_SPLIT_DESC</t>
+  </si>
+  <si>
+    <t>Split a string by delimiter.</t>
+  </si>
+  <si>
+    <t>按分隔符拆分字符串。</t>
+  </si>
+  <si>
+    <t>STRING_SUBSTRING</t>
+  </si>
+  <si>
+    <t>Substring</t>
+  </si>
+  <si>
+    <t>字符串截取</t>
+  </si>
+  <si>
+    <t>STRING_SUBSTRING_DESC</t>
+  </si>
+  <si>
+    <t>Get a substring by start/end indices.</t>
+  </si>
+  <si>
+    <t>按起止索引截取子串。</t>
+  </si>
+  <si>
+    <t>STRING_TO_LOWER</t>
+  </si>
+  <si>
+    <t>To Lower</t>
+  </si>
+  <si>
+    <t>转小写</t>
+  </si>
+  <si>
+    <t>STRING_TO_LOWER_DESC</t>
+  </si>
+  <si>
+    <t>Convert a string to lowercase.</t>
+  </si>
+  <si>
+    <t>将字符串转换为小写。</t>
+  </si>
+  <si>
+    <t>STRING_TO_UPPER</t>
+  </si>
+  <si>
+    <t>To Upper</t>
+  </si>
+  <si>
+    <t>转大写</t>
+  </si>
+  <si>
+    <t>STRING_TO_UPPER_DESC</t>
+  </si>
+  <si>
+    <t>Convert a string to uppercase.</t>
+  </si>
+  <si>
+    <t>将字符串转换为大写。</t>
+  </si>
+  <si>
+    <t>STRING_STRIP</t>
+  </si>
+  <si>
+    <t>Trim</t>
+  </si>
+  <si>
+    <t>去首尾空白</t>
+  </si>
+  <si>
+    <t>STRING_STRIP_DESC</t>
+  </si>
+  <si>
+    <t>Trim leading/trailing whitespace.</t>
+  </si>
+  <si>
+    <t>移除字符串首尾空白字符。</t>
+  </si>
+  <si>
+    <t>EDIT_SOUND_FILTER</t>
+  </si>
+  <si>
+    <t>Edit Sound Filter</t>
+  </si>
+  <si>
+    <t>编辑音效滤镜</t>
+  </si>
+  <si>
+    <t>EDIT_SOUND_FILTER_DESC</t>
+  </si>
+  <si>
+    <t>Set a property on the sound filter.</t>
+  </si>
+  <si>
+    <t>设置音效滤镜的指定属性。</t>
+  </si>
+  <si>
+    <t>EDIT_MUSIC_FILTER</t>
+  </si>
+  <si>
+    <t>Edit Music Filter</t>
+  </si>
+  <si>
+    <t>编辑音乐滤镜</t>
+  </si>
+  <si>
+    <t>EDIT_MUSIC_FILTER_DESC</t>
+  </si>
+  <si>
+    <t>Set a property on the music filter.</t>
+  </si>
+  <si>
+    <t>设置音乐滤镜的指定属性。</t>
+  </si>
+  <si>
+    <t>PLAY_SOUND</t>
+  </si>
+  <si>
+    <t>Play Sound</t>
+  </si>
+  <si>
+    <t>播放音效</t>
+  </si>
+  <si>
+    <t>PLAY_SOUND_DESC</t>
+  </si>
+  <si>
+    <t>Play a sound effect, optionally with filter.</t>
+  </si>
+  <si>
+    <t>播放音效，可选择是否应用滤镜。</t>
+  </si>
+  <si>
+    <t>PLAY_MUSIC</t>
+  </si>
+  <si>
+    <t>Play Music</t>
+  </si>
+  <si>
+    <t>播放音乐</t>
+  </si>
+  <si>
+    <t>PLAY_MUSIC_DESC</t>
+  </si>
+  <si>
+    <t>Play background music, optionally with filter.</t>
+  </si>
+  <si>
+    <t>播放背景音乐，可选择是否应用滤镜。</t>
+  </si>
+  <si>
+    <t>PLAY_VIDEO</t>
+  </si>
+  <si>
+    <t>Play Video</t>
+  </si>
+  <si>
+    <t>播放视频</t>
+  </si>
+  <si>
+    <t>PLAY_VIDEO_DESC</t>
+  </si>
+  <si>
+    <t>Play a video file with mute and skippable options.</t>
+  </si>
+  <si>
+    <t>播放视频文件，可设置静音与可跳过。</t>
+  </si>
+  <si>
+    <t>BUILD_VECTOR2F</t>
+  </si>
+  <si>
+    <t>Build Vector2f</t>
+  </si>
+  <si>
+    <t>构建 Vector2f</t>
+  </si>
+  <si>
+    <t>BUILD_VECTOR2F_DESC</t>
+  </si>
+  <si>
+    <t>Build a Vector2f from x and y.</t>
+  </si>
+  <si>
+    <t>从 x、y 构建 Vector2f。</t>
+  </si>
+  <si>
+    <t>BUILD_VECTOR2I</t>
+  </si>
+  <si>
+    <t>Build Vector2i</t>
+  </si>
+  <si>
+    <t>构建 Vector2i</t>
+  </si>
+  <si>
+    <t>BUILD_VECTOR2I_DESC</t>
+  </si>
+  <si>
+    <t>Build a Vector2i from x and y.</t>
+  </si>
+  <si>
+    <t>从 x、y 构建 Vector2i。</t>
+  </si>
+  <si>
+    <t>BUILD_VECTOR2U</t>
+  </si>
+  <si>
+    <t>Build Vector2u</t>
+  </si>
+  <si>
+    <t>构建 Vector2u</t>
+  </si>
+  <si>
+    <t>BUILD_VECTOR2U_DESC</t>
+  </si>
+  <si>
+    <t>Build a Vector2u from x and y.</t>
+  </si>
+  <si>
+    <t>从 x、y 构建 Vector2u。</t>
+  </si>
+  <si>
+    <t>BUILD_VECTOR3F</t>
+  </si>
+  <si>
+    <t>Build Vector3f</t>
+  </si>
+  <si>
+    <t>构建 Vector3f</t>
+  </si>
+  <si>
+    <t>BUILD_VECTOR3F_DESC</t>
+  </si>
+  <si>
+    <t>Build a Vector3f from x, y, z.</t>
+  </si>
+  <si>
+    <t>从 x、y、z 构建 Vector3f。</t>
+  </si>
+  <si>
+    <t>BUILD_VECTOR3I</t>
+  </si>
+  <si>
+    <t>Build Vector3i</t>
+  </si>
+  <si>
+    <t>构建 Vector3i</t>
+  </si>
+  <si>
+    <t>BUILD_VECTOR3I_DESC</t>
+  </si>
+  <si>
+    <t>Build a Vector3i from x, y, z.</t>
+  </si>
+  <si>
+    <t>从 x、y、z 构建 Vector3i。</t>
+  </si>
+  <si>
+    <t>IS_NEAR_ZERO</t>
+  </si>
+  <si>
+    <t>Is Near Zero</t>
+  </si>
+  <si>
+    <t>IS_NEAR_ZERO_DESC</t>
+  </si>
+  <si>
+    <t>Check whether a number is near 0 (epsilon).</t>
+  </si>
+  <si>
+    <t>判断数值是否接近 0（epsilon）。</t>
+  </si>
+  <si>
+    <t>IS_VECTOR2_NEAR_ZERO</t>
+  </si>
+  <si>
+    <t>Is Vector2 Near Zero</t>
+  </si>
+  <si>
+    <t>二维向量接近零</t>
+  </si>
+  <si>
+    <t>IS_VECTOR2_NEAR_ZERO_DESC</t>
+  </si>
+  <si>
+    <t>Check whether a Vector2 is near zero (epsilon).</t>
+  </si>
+  <si>
+    <t>判断 Vector2 是否接近零向量（epsilon）。</t>
+  </si>
+  <si>
+    <t>IS_VECTOR3_NEAR_ZERO</t>
+  </si>
+  <si>
+    <t>Is Vector3 Near Zero</t>
+  </si>
+  <si>
+    <t>三维向量接近零</t>
+  </si>
+  <si>
+    <t>IS_VECTOR3_NEAR_ZERO_DESC</t>
+  </si>
+  <si>
+    <t>Check whether a Vector3 is near zero (epsilon).</t>
+  </si>
+  <si>
+    <t>判断 Vector3 是否接近零向量（epsilon）。</t>
+  </si>
+  <si>
+    <t>VECTOR2F_ROUND</t>
+  </si>
+  <si>
+    <t>Vector2 Round</t>
+  </si>
+  <si>
+    <t>二维向量四舍五入</t>
+  </si>
+  <si>
+    <t>VECTOR2F_ROUND_DESC</t>
+  </si>
+  <si>
+    <t>Round each component of a Vector2.</t>
+  </si>
+  <si>
+    <t>对 Vector2 的各分量进行四舍五入。</t>
+  </si>
+  <si>
+    <t>VECTOR2F_FLOOR</t>
+  </si>
+  <si>
+    <t>Vector2 Floor</t>
+  </si>
+  <si>
+    <t>二维向量向下取整</t>
+  </si>
+  <si>
+    <t>VECTOR2F_FLOOR_DESC</t>
+  </si>
+  <si>
+    <t>Floor each component of a Vector2.</t>
+  </si>
+  <si>
+    <t>对 Vector2 的各分量向下取整。</t>
+  </si>
+  <si>
+    <t>VECTOR2F_CEIL</t>
+  </si>
+  <si>
+    <t>Vector2 Ceil</t>
+  </si>
+  <si>
+    <t>二维向量向上取整</t>
+  </si>
+  <si>
+    <t>VECTOR2F_CEIL_DESC</t>
+  </si>
+  <si>
+    <t>Ceil each component of a Vector2.</t>
+  </si>
+  <si>
+    <t>对 Vector2 的各分量向上取整。</t>
+  </si>
+  <si>
+    <t>TO_VECTOR2F</t>
+  </si>
+  <si>
+    <t>To Vector2f</t>
+  </si>
+  <si>
+    <t>转 Vector2f</t>
+  </si>
+  <si>
+    <t>TO_VECTOR2F_DESC</t>
+  </si>
+  <si>
+    <t>Convert Vector2i/Vector2u to Vector2f.</t>
+  </si>
+  <si>
+    <t>将 Vector2i/Vector2u 转换为 Vector2f。</t>
+  </si>
+  <si>
+    <t>TO_VECTOR2I</t>
+  </si>
+  <si>
+    <t>To Vector2i</t>
+  </si>
+  <si>
+    <t>转 Vector2i</t>
+  </si>
+  <si>
+    <t>TO_VECTOR2I_DESC</t>
+  </si>
+  <si>
+    <t>Convert Vector2f/Vector2u to Vector2i.</t>
+  </si>
+  <si>
+    <t>将 Vector2f/Vector2u 转换为 Vector2i。</t>
+  </si>
+  <si>
+    <t>TO_VECTOR2U</t>
+  </si>
+  <si>
+    <t>To Vector2u</t>
+  </si>
+  <si>
+    <t>转 Vector2u</t>
+  </si>
+  <si>
+    <t>TO_VECTOR2U_DESC</t>
+  </si>
+  <si>
+    <t>Convert Vector2f/Vector2i to Vector2u.</t>
+  </si>
+  <si>
+    <t>将 Vector2f/Vector2i 转换为 Vector2u。</t>
+  </si>
+  <si>
+    <t>TO_VECTOR3F</t>
+  </si>
+  <si>
+    <t>To Vector3f</t>
+  </si>
+  <si>
+    <t>转 Vector3f</t>
+  </si>
+  <si>
+    <t>TO_VECTOR3F_DESC</t>
+  </si>
+  <si>
+    <t>Convert Vector3i to Vector3f.</t>
+  </si>
+  <si>
+    <t>将 Vector3i 转换为 Vector3f。</t>
+  </si>
+  <si>
+    <t>TO_VECTOR3I</t>
+  </si>
+  <si>
+    <t>To Vector3i</t>
+  </si>
+  <si>
+    <t>转 Vector3i</t>
+  </si>
+  <si>
+    <t>TO_VECTOR3I_DESC</t>
+  </si>
+  <si>
+    <t>Convert Vector3f to Vector3i.</t>
+  </si>
+  <si>
+    <t>将 Vector3f 转换为 Vector3i。</t>
+  </si>
+  <si>
+    <t>TO_INT_RECT</t>
+  </si>
+  <si>
+    <t>Build IntRect</t>
+  </si>
+  <si>
+    <t>构建 IntRect</t>
+  </si>
+  <si>
+    <t>TO_INT_RECT_DESC</t>
+  </si>
+  <si>
+    <t>Build an IntRect from x, y, width, height.</t>
+  </si>
+  <si>
+    <t>从 x、y、width、height 构建 IntRect。</t>
+  </si>
+  <si>
+    <t>TO_FLOAT_RECT</t>
+  </si>
+  <si>
+    <t>Build FloatRect</t>
+  </si>
+  <si>
+    <t>构建 FloatRect</t>
+  </si>
+  <si>
+    <t>TO_FLOAT_RECT_DESC</t>
+  </si>
+  <si>
+    <t>Build a FloatRect from x, y, width, height.</t>
+  </si>
+  <si>
+    <t>从 x、y、width、height 构建 FloatRect。</t>
+  </si>
+  <si>
+    <t>CLAMP</t>
+  </si>
+  <si>
+    <t>Clamp</t>
+  </si>
+  <si>
+    <t>限制范围</t>
+  </si>
+  <si>
+    <t>CLAMP_DESC</t>
+  </si>
+  <si>
+    <t>Clamp a value between min and max.</t>
+  </si>
+  <si>
+    <t>将值限制在最小值与最大值之间。</t>
+  </si>
+  <si>
+    <t>LERP</t>
+  </si>
+  <si>
+    <t>Lerp</t>
+  </si>
+  <si>
+    <t>线性插值</t>
+  </si>
+  <si>
+    <t>LERP_DESC</t>
+  </si>
+  <si>
+    <t>Linear interpolation between a and b by t.</t>
+  </si>
+  <si>
+    <t>在 a 与 b 之间进行线性插值（t）。</t>
+  </si>
+  <si>
+    <t>ABS</t>
+  </si>
+  <si>
+    <t>Abs</t>
+  </si>
+  <si>
+    <t>绝对值</t>
+  </si>
+  <si>
+    <t>ABS_DESC</t>
+  </si>
+  <si>
+    <t>Get the absolute value.</t>
+  </si>
+  <si>
+    <t>返回数值的绝对值。</t>
+  </si>
+  <si>
+    <t>TO_INT</t>
+  </si>
+  <si>
+    <t>To Int</t>
+  </si>
+  <si>
+    <t>转整数</t>
+  </si>
+  <si>
+    <t>TO_INT_DESC</t>
+  </si>
+  <si>
+    <t>Convert a number to int.</t>
+  </si>
+  <si>
+    <t>将数值转换为整数。</t>
+  </si>
+  <si>
+    <t>TO_FLOAT</t>
+  </si>
+  <si>
+    <t>To Float</t>
+  </si>
+  <si>
+    <t>转浮点</t>
+  </si>
+  <si>
+    <t>TO_FLOAT_DESC</t>
+  </si>
+  <si>
+    <t>Convert a number to float.</t>
+  </si>
+  <si>
+    <t>将数值转换为浮点数。</t>
+  </si>
+  <si>
+    <t>MAX</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>最大值</t>
+  </si>
+  <si>
+    <t>MAX_DESC</t>
+  </si>
+  <si>
+    <t>Get the maximum value in a list.</t>
+  </si>
+  <si>
+    <t>返回列表中的最大值。</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>最小值</t>
+  </si>
+  <si>
+    <t>MIN_DESC</t>
+  </si>
+  <si>
+    <t>Get the minimum value in a list.</t>
+  </si>
+  <si>
+    <t>返回列表中的最小值。</t>
+  </si>
+  <si>
+    <t>SQRT</t>
+  </si>
+  <si>
+    <t>Sqrt</t>
+  </si>
+  <si>
+    <t>平方根</t>
+  </si>
+  <si>
+    <t>SQRT_DESC</t>
+  </si>
+  <si>
+    <t>Compute the square root.</t>
+  </si>
+  <si>
+    <t>计算平方根。</t>
+  </si>
+  <si>
+    <t>POW</t>
+  </si>
+  <si>
+    <t>Pow</t>
+  </si>
+  <si>
+    <t>幂运算</t>
+  </si>
+  <si>
+    <t>POW_DESC</t>
+  </si>
+  <si>
+    <t>Compute base raised to exp.</t>
+  </si>
+  <si>
+    <t>计算 base 的 exp 次幂。</t>
+  </si>
+  <si>
+    <t>VECTOR2_DISTANCE</t>
+  </si>
+  <si>
+    <t>Vector2 Distance</t>
+  </si>
+  <si>
+    <t>二维距离</t>
+  </si>
+  <si>
+    <t>VECTOR2_DISTANCE_DESC</t>
+  </si>
+  <si>
+    <t>Compute distance between two 2D vectors.</t>
+  </si>
+  <si>
+    <t>计算两个二维向量之间的距离。</t>
+  </si>
+  <si>
+    <t>VECTOR3_DISTANCE</t>
+  </si>
+  <si>
+    <t>Vector3 Distance</t>
+  </si>
+  <si>
+    <t>三维距离</t>
+  </si>
+  <si>
+    <t>VECTOR3_DISTANCE_DESC</t>
+  </si>
+  <si>
+    <t>Compute distance between two 3D vectors.</t>
+  </si>
+  <si>
+    <t>计算两个三维向量之间的距离。</t>
+  </si>
+  <si>
+    <t>VECTOR2_DOT</t>
+  </si>
+  <si>
+    <t>Vector2 Dot</t>
+  </si>
+  <si>
+    <t>二维点积</t>
+  </si>
+  <si>
+    <t>VECTOR2_DOT_DESC</t>
+  </si>
+  <si>
+    <t>Compute dot product for 2D vectors.</t>
+  </si>
+  <si>
+    <t>计算二维向量点积。</t>
+  </si>
+  <si>
+    <t>VECTOR3_DOT</t>
+  </si>
+  <si>
+    <t>Vector3 Dot</t>
+  </si>
+  <si>
+    <t>三维点积</t>
+  </si>
+  <si>
+    <t>VECTOR3_DOT_DESC</t>
+  </si>
+  <si>
+    <t>Compute dot product for 3D vectors.</t>
+  </si>
+  <si>
+    <t>计算三维向量点积。</t>
+  </si>
+  <si>
+    <t>VECTOR2_CROSS</t>
+  </si>
+  <si>
+    <t>Vector2 Cross</t>
+  </si>
+  <si>
+    <t>二维叉积</t>
+  </si>
+  <si>
+    <t>VECTOR2_CROSS_DESC</t>
+  </si>
+  <si>
+    <t>Compute cross product for 2D vectors.</t>
+  </si>
+  <si>
+    <t>计算二维向量叉积。</t>
+  </si>
+  <si>
+    <t>VECTOR3_CROSS</t>
+  </si>
+  <si>
+    <t>Vector3 Cross</t>
+  </si>
+  <si>
+    <t>三维叉积</t>
+  </si>
+  <si>
+    <t>VECTOR3_CROSS_DESC</t>
+  </si>
+  <si>
+    <t>Compute cross product for 3D vectors.</t>
+  </si>
+  <si>
+    <t>计算三维向量叉积。</t>
+  </si>
+  <si>
+    <t>VECTOR2_LENGTH</t>
+  </si>
+  <si>
+    <t>Vector2 Length</t>
+  </si>
+  <si>
+    <t>二维长度</t>
+  </si>
+  <si>
+    <t>VECTOR2_LENGTH_DESC</t>
+  </si>
+  <si>
+    <t>Compute length of a 2D vector.</t>
+  </si>
+  <si>
+    <t>计算二维向量长度。</t>
+  </si>
+  <si>
+    <t>VECTOR3_LENGTH</t>
+  </si>
+  <si>
+    <t>Vector3 Length</t>
+  </si>
+  <si>
+    <t>三维长度</t>
+  </si>
+  <si>
+    <t>VECTOR3_LENGTH_DESC</t>
+  </si>
+  <si>
+    <t>Compute length of a 3D vector.</t>
+  </si>
+  <si>
+    <t>计算三维向量长度。</t>
+  </si>
+  <si>
+    <t>VECTOR2_LENGTH_SQUARED</t>
+  </si>
+  <si>
+    <t>Vector2 Length Squared</t>
+  </si>
+  <si>
+    <t>二维长度平方</t>
+  </si>
+  <si>
+    <t>VECTOR2_LENGTH_SQUARED_DESC</t>
+  </si>
+  <si>
+    <t>Compute squared length of a 2D vector.</t>
+  </si>
+  <si>
+    <t>计算二维向量长度的平方。</t>
+  </si>
+  <si>
+    <t>VECTOR3_LENGTH_SQUARED</t>
+  </si>
+  <si>
+    <t>Vector3 Length Squared</t>
+  </si>
+  <si>
+    <t>三维长度平方</t>
+  </si>
+  <si>
+    <t>VECTOR3_LENGTH_SQUARED_DESC</t>
+  </si>
+  <si>
+    <t>Compute squared length of a 3D vector.</t>
+  </si>
+  <si>
+    <t>计算三维向量长度的平方。</t>
+  </si>
+  <si>
+    <t>VECTOR2_NORMALIZED</t>
+  </si>
+  <si>
+    <t>Vector2 Normalize</t>
+  </si>
+  <si>
+    <t>二维归一化</t>
+  </si>
+  <si>
+    <t>VECTOR2_NORMALIZED_DESC</t>
+  </si>
+  <si>
+    <t>Normalize a 2D vector.</t>
+  </si>
+  <si>
+    <t>将二维向量归一化。</t>
+  </si>
+  <si>
+    <t>VECTOR3_NORMALIZED</t>
+  </si>
+  <si>
+    <t>Vector3 Normalize</t>
+  </si>
+  <si>
+    <t>三维归一化</t>
+  </si>
+  <si>
+    <t>VECTOR3_NORMALIZED_DESC</t>
+  </si>
+  <si>
+    <t>Normalize a 3D vector.</t>
+  </si>
+  <si>
+    <t>将三维向量归一化。</t>
+  </si>
+  <si>
+    <t>GET_ANGLE</t>
+  </si>
+  <si>
+    <t>Get Angle</t>
+  </si>
+  <si>
+    <t>获取角度</t>
+  </si>
+  <si>
+    <t>GET_ANGLE_DESC</t>
+  </si>
+  <si>
+    <t>Get the angle of a 2D vector.</t>
+  </si>
+  <si>
+    <t>获取二维向量的角度。</t>
+  </si>
+  <si>
+    <t>GET_ANGLE_TO</t>
+  </si>
+  <si>
+    <t>Get Angle To</t>
+  </si>
+  <si>
+    <t>获取指向角度</t>
+  </si>
+  <si>
+    <t>GET_ANGLE_TO_DESC</t>
+  </si>
+  <si>
+    <t>Get the angle from v1 to v2.</t>
+  </si>
+  <si>
+    <t>获取从 v1 指向 v2 的角度。</t>
+  </si>
+  <si>
+    <t>AS_DEGREES</t>
+  </si>
+  <si>
+    <t>As Degrees</t>
+  </si>
+  <si>
+    <t>角度转度</t>
+  </si>
+  <si>
+    <t>AS_DEGREES_DESC</t>
+  </si>
+  <si>
+    <t>Convert an Angle to degrees.</t>
+  </si>
+  <si>
+    <t>将角度对象转换为度数值。</t>
+  </si>
+  <si>
+    <t>AS_RADIANS</t>
+  </si>
+  <si>
+    <t>As Radians</t>
+  </si>
+  <si>
+    <t>角度转弧度</t>
+  </si>
+  <si>
+    <t>AS_RADIANS_DESC</t>
+  </si>
+  <si>
+    <t>Convert an Angle to radians.</t>
+  </si>
+  <si>
+    <t>将角度对象转换为弧度值。</t>
+  </si>
+  <si>
+    <t>VECTOR2_COMPONENT_WISE_DIV</t>
+  </si>
+  <si>
+    <t>Component-wise Div</t>
+  </si>
+  <si>
+    <t>按分量相除</t>
+  </si>
+  <si>
+    <t>VECTOR2_COMPONENT_WISE_DIV_DESC</t>
+  </si>
+  <si>
+    <t>Divide vectors component-wise.</t>
+  </si>
+  <si>
+    <t>对向量的每个分量分别相除。</t>
+  </si>
+  <si>
+    <t>VECTOR2_COMPONENT_WISE_MUL</t>
+  </si>
+  <si>
+    <t>Component-wise Mul</t>
+  </si>
+  <si>
+    <t>按分量相乘</t>
+  </si>
+  <si>
+    <t>VECTOR2_COMPONENT_WISE_MUL_DESC</t>
+  </si>
+  <si>
+    <t>Multiply vectors component-wise.</t>
+  </si>
+  <si>
+    <t>对向量的每个分量分别相乘。</t>
+  </si>
+  <si>
+    <t>VECTOR2_PERPENDICULAR</t>
+  </si>
+  <si>
+    <t>Perpendicular</t>
+  </si>
+  <si>
+    <t>垂直向量</t>
+  </si>
+  <si>
+    <t>VECTOR2_PERPENDICULAR_DESC</t>
+  </si>
+  <si>
+    <t>Get a perpendicular vector.</t>
+  </si>
+  <si>
+    <t>获取与二维向量垂直的向量。</t>
+  </si>
+  <si>
+    <t>VECTOR2_PROJECTED_ONTO</t>
+  </si>
+  <si>
+    <t>Project Onto</t>
+  </si>
+  <si>
+    <t>投影到轴</t>
+  </si>
+  <si>
+    <t>VECTOR2_PROJECTED_ONTO_DESC</t>
+  </si>
+  <si>
+    <t>Project a vector onto an axis.</t>
+  </si>
+  <si>
+    <t>将二维向量投影到指定轴向量上。</t>
+  </si>
+  <si>
+    <t>VECTOR2_ROTATED_BY</t>
+  </si>
+  <si>
+    <t>Rotate Vector</t>
+  </si>
+  <si>
+    <t>旋转向量</t>
+  </si>
+  <si>
+    <t>VECTOR2_ROTATED_BY_DESC</t>
+  </si>
+  <si>
+    <t>Rotate a 2D vector by an angle.</t>
+  </si>
+  <si>
+    <t>按指定角度旋转二维向量。</t>
+  </si>
+  <si>
+    <t>DEGREES_TO_ANGLE</t>
+  </si>
+  <si>
+    <t>Degrees To Angle</t>
+  </si>
+  <si>
+    <t>度转角度对象</t>
+  </si>
+  <si>
+    <t>DEGREES_TO_ANGLE_DESC</t>
+  </si>
+  <si>
+    <t>Convert degrees value to Angle.</t>
+  </si>
+  <si>
+    <t>将度数值转换为 Angle。</t>
+  </si>
+  <si>
+    <t>RADIANS_TO_ANGLE</t>
+  </si>
+  <si>
+    <t>Radians To Angle</t>
+  </si>
+  <si>
+    <t>弧度转角度对象</t>
+  </si>
+  <si>
+    <t>RADIANS_TO_ANGLE_DESC</t>
+  </si>
+  <si>
+    <t>Convert radians value to Angle.</t>
+  </si>
+  <si>
+    <t>将弧度值转换为 Angle。</t>
+  </si>
+  <si>
+    <t>RANDOM_INT</t>
+  </si>
+  <si>
+    <t>Random Int</t>
+  </si>
+  <si>
+    <t>随机整数</t>
+  </si>
+  <si>
+    <t>RANDOM_INT_DESC</t>
+  </si>
+  <si>
+    <t>Generate a random int in range.</t>
+  </si>
+  <si>
+    <t>生成指定范围内的随机整数。</t>
+  </si>
+  <si>
+    <t>RANDOM_FLOAT</t>
+  </si>
+  <si>
+    <t>Random Float</t>
+  </si>
+  <si>
+    <t>随机浮点</t>
+  </si>
+  <si>
+    <t>RANDOM_FLOAT_DESC</t>
+  </si>
+  <si>
+    <t>Generate a random float in range.</t>
+  </si>
+  <si>
+    <t>生成指定范围内的随机浮点数。</t>
+  </si>
+  <si>
+    <t>GCD</t>
+  </si>
+  <si>
+    <t>最大公约数</t>
+  </si>
+  <si>
+    <t>GCD_DESC</t>
+  </si>
+  <si>
+    <t>Compute greatest common divisor.</t>
+  </si>
+  <si>
+    <t>计算最大公约数。</t>
+  </si>
+  <si>
+    <t>LCM</t>
+  </si>
+  <si>
+    <t>最小公倍数</t>
+  </si>
+  <si>
+    <t>LCM_DESC</t>
+  </si>
+  <si>
+    <t>Compute least common multiple.</t>
+  </si>
+  <si>
+    <t>计算最小公倍数。</t>
+  </si>
+  <si>
+    <t>ADD</t>
+  </si>
+  <si>
+    <t>ADD_DESC</t>
+  </si>
+  <si>
+    <t>Compute a + b.</t>
+  </si>
+  <si>
+    <t>计算 a + b。</t>
+  </si>
+  <si>
+    <t>SUB</t>
+  </si>
+  <si>
+    <t>SUB_DESC</t>
+  </si>
+  <si>
+    <t>Compute a - b.</t>
+  </si>
+  <si>
+    <t>计算 a - b。</t>
+  </si>
+  <si>
+    <t>MUL</t>
+  </si>
+  <si>
+    <t>MUL_DESC</t>
+  </si>
+  <si>
+    <t>Compute a * b.</t>
+  </si>
+  <si>
+    <t>计算 a * b。</t>
+  </si>
+  <si>
+    <t>DIV</t>
+  </si>
+  <si>
+    <t>DIV_DESC</t>
+  </si>
+  <si>
+    <t>Compute a / b.</t>
+  </si>
+  <si>
+    <t>计算 a / b。</t>
+  </si>
+  <si>
+    <t>MOD</t>
+  </si>
+  <si>
+    <t>Modulo</t>
+  </si>
+  <si>
+    <t>取模</t>
+  </si>
+  <si>
+    <t>MOD_DESC</t>
+  </si>
+  <si>
+    <t>Compute a % b.</t>
+  </si>
+  <si>
+    <t>计算 a % b。</t>
+  </si>
+  <si>
+    <t>POW_OP</t>
+  </si>
+  <si>
+    <t>POW_OP_DESC</t>
+  </si>
+  <si>
+    <t>Compute a ** b.</t>
+  </si>
+  <si>
+    <t>计算 a ** b。</t>
+  </si>
+  <si>
+    <t>EQUALS</t>
+  </si>
+  <si>
+    <t>EQUALS_DESC</t>
+  </si>
+  <si>
+    <t>Check whether a equals b.</t>
+  </si>
+  <si>
+    <t>判断 a 是否等于 b。</t>
+  </si>
+  <si>
+    <t>NOT_EQUALS</t>
+  </si>
+  <si>
+    <t>NOT_EQUALS_DESC</t>
+  </si>
+  <si>
+    <t>Check whether a does not equal b.</t>
+  </si>
+  <si>
+    <t>判断 a 是否不等于 b。</t>
+  </si>
+  <si>
+    <t>LESS</t>
+  </si>
+  <si>
+    <t>LESS_DESC</t>
+  </si>
+  <si>
+    <t>Check whether a is less than b.</t>
+  </si>
+  <si>
+    <t>判断 a 是否小于 b。</t>
+  </si>
+  <si>
+    <t>LESS_EQUALS</t>
+  </si>
+  <si>
+    <t>LESS_EQUALS_DESC</t>
+  </si>
+  <si>
+    <t>Check whether a is less than or equal to b.</t>
+  </si>
+  <si>
+    <t>判断 a 是否小于等于 b。</t>
+  </si>
+  <si>
+    <t>GREATER</t>
+  </si>
+  <si>
+    <t>GREATER_DESC</t>
+  </si>
+  <si>
+    <t>Check whether a is greater than b.</t>
+  </si>
+  <si>
+    <t>判断 a 是否大于 b。</t>
+  </si>
+  <si>
+    <t>GREATER_EQUALS</t>
+  </si>
+  <si>
+    <t>GREATER_EQUALS_DESC</t>
+  </si>
+  <si>
+    <t>Check whether a is greater than or equal to b.</t>
+  </si>
+  <si>
+    <t>判断 a 是否大于等于 b。</t>
+  </si>
+  <si>
+    <t>AND</t>
+  </si>
+  <si>
+    <t>And</t>
+  </si>
+  <si>
+    <t>与</t>
+  </si>
+  <si>
+    <t>AND_DESC</t>
+  </si>
+  <si>
+    <t>Boolean AND.</t>
+  </si>
+  <si>
+    <t>布尔与运算。</t>
+  </si>
+  <si>
+    <t>OR</t>
+  </si>
+  <si>
+    <t>Or</t>
+  </si>
+  <si>
+    <t>或</t>
+  </si>
+  <si>
+    <t>OR_DESC</t>
+  </si>
+  <si>
+    <t>Boolean OR.</t>
+  </si>
+  <si>
+    <t>布尔或运算。</t>
+  </si>
+  <si>
+    <t>NOT</t>
+  </si>
+  <si>
+    <t>Not</t>
+  </si>
+  <si>
+    <t>非</t>
+  </si>
+  <si>
+    <t>NOT_DESC</t>
+  </si>
+  <si>
+    <t>Boolean NOT.</t>
+  </si>
+  <si>
+    <t>布尔非运算。</t>
+  </si>
+  <si>
+    <t>XOR</t>
+  </si>
+  <si>
+    <t>Xor</t>
+  </si>
+  <si>
+    <t>异或</t>
+  </si>
+  <si>
+    <t>XOR_DESC</t>
+  </si>
+  <si>
+    <t>Boolean XOR.</t>
+  </si>
+  <si>
+    <t>布尔异或运算。</t>
+  </si>
+  <si>
+    <t>NAND</t>
+  </si>
+  <si>
+    <t>Nand</t>
+  </si>
+  <si>
+    <t>与非</t>
+  </si>
+  <si>
+    <t>NAND_DESC</t>
+  </si>
+  <si>
+    <t>Boolean NAND.</t>
+  </si>
+  <si>
+    <t>布尔与非运算。</t>
+  </si>
+  <si>
+    <t>NOR</t>
+  </si>
+  <si>
+    <t>Nor</t>
+  </si>
+  <si>
+    <t>或非</t>
+  </si>
+  <si>
+    <t>NOR_DESC</t>
+  </si>
+  <si>
+    <t>Boolean NOR.</t>
+  </si>
+  <si>
+    <t>布尔或非运算。</t>
+  </si>
+  <si>
+    <t>XNOR</t>
+  </si>
+  <si>
+    <t>Xnor</t>
+  </si>
+  <si>
+    <t>同或</t>
+  </si>
+  <si>
+    <t>XNOR_DESC</t>
+  </si>
+  <si>
+    <t>Boolean XNOR.</t>
+  </si>
+  <si>
+    <t>布尔同或运算。</t>
+  </si>
+  <si>
+    <t>IADD</t>
+  </si>
+  <si>
+    <t>IADD_DESC</t>
+  </si>
+  <si>
+    <t>Apply += to a reference/variable.</t>
+  </si>
+  <si>
+    <t>对引用/变量执行 += 运算。</t>
+  </si>
+  <si>
+    <t>ISUB</t>
+  </si>
+  <si>
+    <t>ISUB_DESC</t>
+  </si>
+  <si>
+    <t>Apply -= to a reference/variable.</t>
+  </si>
+  <si>
+    <t>对引用/变量执行 -= 运算。</t>
+  </si>
+  <si>
+    <t>IMUL</t>
+  </si>
+  <si>
+    <t>IMUL_DESC</t>
+  </si>
+  <si>
+    <t>Apply *= to a reference/variable.</t>
+  </si>
+  <si>
+    <t>对引用/变量执行 *= 运算。</t>
+  </si>
+  <si>
+    <t>IDIV</t>
+  </si>
+  <si>
+    <t>IDIV_DESC</t>
+  </si>
+  <si>
+    <t>Apply /= to a reference/variable.</t>
+  </si>
+  <si>
+    <t>对引用/变量执行 /= 运算。</t>
+  </si>
+  <si>
+    <t>IMOD</t>
+  </si>
+  <si>
+    <t>Mod Assign</t>
+  </si>
+  <si>
+    <t>取模并赋值</t>
+  </si>
+  <si>
+    <t>IMOD_DESC</t>
+  </si>
+  <si>
+    <t>Apply %= to a reference/variable.</t>
+  </si>
+  <si>
+    <t>对引用/变量执行 %= 运算。</t>
+  </si>
+  <si>
+    <t>IPOW</t>
+  </si>
+  <si>
+    <t>IPOW_DESC</t>
+  </si>
+  <si>
+    <t>Apply **= to a reference/variable.</t>
+  </si>
+  <si>
+    <t>对引用/变量执行 **= 运算。</t>
+  </si>
+  <si>
+    <t>是否接近零</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>**</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>==</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>==</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!=</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!=</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;=</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;=</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;=</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>+=</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>+=</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-=</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*=</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*=</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/=</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>**=</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>**=</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -173,12 +2443,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -193,8 +2469,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -210,6 +2488,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="1" connectionId="1" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -475,133 +2757,2751 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C249"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="34.625" customWidth="1"/>
-    <col min="2" max="2" width="54.875" customWidth="1"/>
-    <col min="3" max="3" width="59.875" customWidth="1"/>
+    <col min="1" max="1" width="38.75" customWidth="1"/>
+    <col min="2" max="2" width="61.875" customWidth="1"/>
+    <col min="3" max="3" width="52.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18" t="s">
+        <v>82</v>
+      </c>
+      <c r="C18" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>84</v>
+      </c>
+      <c r="B19" t="s">
+        <v>85</v>
+      </c>
+      <c r="C19" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>90</v>
+      </c>
+      <c r="B21" t="s">
+        <v>91</v>
+      </c>
+      <c r="C21" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>93</v>
+      </c>
+      <c r="B22" t="s">
+        <v>94</v>
+      </c>
+      <c r="C22" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>96</v>
+      </c>
+      <c r="B23" t="s">
+        <v>97</v>
+      </c>
+      <c r="C23" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>99</v>
+      </c>
+      <c r="B24" t="s">
+        <v>100</v>
+      </c>
+      <c r="C24" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>102</v>
+      </c>
+      <c r="B25" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>105</v>
+      </c>
+      <c r="B26" t="s">
+        <v>106</v>
+      </c>
+      <c r="C26" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>108</v>
+      </c>
+      <c r="B27" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>111</v>
+      </c>
+      <c r="B28" t="s">
+        <v>112</v>
+      </c>
+      <c r="C28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>114</v>
+      </c>
+      <c r="B29" t="s">
+        <v>115</v>
+      </c>
+      <c r="C29" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>117</v>
+      </c>
+      <c r="B30" t="s">
+        <v>118</v>
+      </c>
+      <c r="C30" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>120</v>
+      </c>
+      <c r="B31" t="s">
+        <v>121</v>
+      </c>
+      <c r="C31" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>123</v>
+      </c>
+      <c r="B32" t="s">
+        <v>124</v>
+      </c>
+      <c r="C32" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>126</v>
+      </c>
+      <c r="B33" t="s">
+        <v>127</v>
+      </c>
+      <c r="C33" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>129</v>
+      </c>
+      <c r="B34" t="s">
+        <v>130</v>
+      </c>
+      <c r="C34" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>132</v>
+      </c>
+      <c r="B35" t="s">
+        <v>133</v>
+      </c>
+      <c r="C35" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>135</v>
+      </c>
+      <c r="B36" t="s">
+        <v>136</v>
+      </c>
+      <c r="C36" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>138</v>
+      </c>
+      <c r="B37" t="s">
+        <v>139</v>
+      </c>
+      <c r="C37" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>141</v>
+      </c>
+      <c r="B38" t="s">
+        <v>142</v>
+      </c>
+      <c r="C38" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>144</v>
+      </c>
+      <c r="B39" t="s">
+        <v>145</v>
+      </c>
+      <c r="C39" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>147</v>
+      </c>
+      <c r="B40" t="s">
+        <v>148</v>
+      </c>
+      <c r="C40" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>150</v>
+      </c>
+      <c r="B41" t="s">
+        <v>151</v>
+      </c>
+      <c r="C41" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>153</v>
+      </c>
+      <c r="B42" t="s">
+        <v>154</v>
+      </c>
+      <c r="C42" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>156</v>
+      </c>
+      <c r="B43" t="s">
+        <v>157</v>
+      </c>
+      <c r="C43" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>159</v>
+      </c>
+      <c r="B44" t="s">
+        <v>160</v>
+      </c>
+      <c r="C44" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>162</v>
+      </c>
+      <c r="B45" t="s">
+        <v>163</v>
+      </c>
+      <c r="C45" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>165</v>
+      </c>
+      <c r="B46" t="s">
+        <v>166</v>
+      </c>
+      <c r="C46" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>168</v>
+      </c>
+      <c r="B47" t="s">
+        <v>169</v>
+      </c>
+      <c r="C47" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>171</v>
+      </c>
+      <c r="B48" t="s">
+        <v>172</v>
+      </c>
+      <c r="C48" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>174</v>
+      </c>
+      <c r="B49" t="s">
+        <v>175</v>
+      </c>
+      <c r="C49" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>177</v>
+      </c>
+      <c r="B50" t="s">
+        <v>178</v>
+      </c>
+      <c r="C50" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>180</v>
+      </c>
+      <c r="B51" t="s">
+        <v>181</v>
+      </c>
+      <c r="C51" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>183</v>
+      </c>
+      <c r="B52" t="s">
+        <v>184</v>
+      </c>
+      <c r="C52" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>186</v>
+      </c>
+      <c r="B53" t="s">
+        <v>187</v>
+      </c>
+      <c r="C53" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>189</v>
+      </c>
+      <c r="B54" t="s">
+        <v>190</v>
+      </c>
+      <c r="C54" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>192</v>
+      </c>
+      <c r="B55" t="s">
+        <v>193</v>
+      </c>
+      <c r="C55" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>195</v>
+      </c>
+      <c r="B56" t="s">
+        <v>196</v>
+      </c>
+      <c r="C56" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>198</v>
+      </c>
+      <c r="B57" t="s">
+        <v>199</v>
+      </c>
+      <c r="C57" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>201</v>
+      </c>
+      <c r="B58" t="s">
+        <v>202</v>
+      </c>
+      <c r="C58" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>204</v>
+      </c>
+      <c r="B59" t="s">
+        <v>205</v>
+      </c>
+      <c r="C59" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>207</v>
+      </c>
+      <c r="B60" t="s">
+        <v>208</v>
+      </c>
+      <c r="C60" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>210</v>
+      </c>
+      <c r="B61" t="s">
+        <v>211</v>
+      </c>
+      <c r="C61" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>213</v>
+      </c>
+      <c r="B62" t="s">
+        <v>214</v>
+      </c>
+      <c r="C62" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>216</v>
+      </c>
+      <c r="B63" t="s">
+        <v>217</v>
+      </c>
+      <c r="C63" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>219</v>
+      </c>
+      <c r="B64" t="s">
+        <v>220</v>
+      </c>
+      <c r="C64" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>222</v>
+      </c>
+      <c r="B65" t="s">
+        <v>223</v>
+      </c>
+      <c r="C65" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>225</v>
+      </c>
+      <c r="B66" t="s">
+        <v>226</v>
+      </c>
+      <c r="C66" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>228</v>
+      </c>
+      <c r="B67" t="s">
+        <v>229</v>
+      </c>
+      <c r="C67" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>231</v>
+      </c>
+      <c r="B68" t="s">
+        <v>232</v>
+      </c>
+      <c r="C68" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>234</v>
+      </c>
+      <c r="B69" t="s">
+        <v>235</v>
+      </c>
+      <c r="C69" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>237</v>
+      </c>
+      <c r="B70" t="s">
+        <v>238</v>
+      </c>
+      <c r="C70" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>240</v>
+      </c>
+      <c r="B71" t="s">
+        <v>241</v>
+      </c>
+      <c r="C71" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>243</v>
+      </c>
+      <c r="B72" t="s">
+        <v>244</v>
+      </c>
+      <c r="C72" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>246</v>
+      </c>
+      <c r="B73" t="s">
+        <v>247</v>
+      </c>
+      <c r="C73" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>249</v>
+      </c>
+      <c r="B74" t="s">
+        <v>250</v>
+      </c>
+      <c r="C74" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>252</v>
+      </c>
+      <c r="B75" t="s">
+        <v>253</v>
+      </c>
+      <c r="C75" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>255</v>
+      </c>
+      <c r="B76" t="s">
+        <v>256</v>
+      </c>
+      <c r="C76" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>258</v>
+      </c>
+      <c r="B77" t="s">
+        <v>259</v>
+      </c>
+      <c r="C77" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>261</v>
+      </c>
+      <c r="B78" t="s">
+        <v>262</v>
+      </c>
+      <c r="C78" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>264</v>
+      </c>
+      <c r="B79" t="s">
+        <v>265</v>
+      </c>
+      <c r="C79" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>267</v>
+      </c>
+      <c r="B80" t="s">
+        <v>268</v>
+      </c>
+      <c r="C80" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>270</v>
+      </c>
+      <c r="B81" t="s">
+        <v>271</v>
+      </c>
+      <c r="C81" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>273</v>
+      </c>
+      <c r="B82" t="s">
+        <v>274</v>
+      </c>
+      <c r="C82" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>276</v>
+      </c>
+      <c r="B83" t="s">
+        <v>277</v>
+      </c>
+      <c r="C83" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>279</v>
+      </c>
+      <c r="B84" t="s">
+        <v>280</v>
+      </c>
+      <c r="C84" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>282</v>
+      </c>
+      <c r="B85" t="s">
+        <v>283</v>
+      </c>
+      <c r="C85" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>285</v>
+      </c>
+      <c r="B86" t="s">
+        <v>286</v>
+      </c>
+      <c r="C86" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>288</v>
+      </c>
+      <c r="B87" t="s">
+        <v>289</v>
+      </c>
+      <c r="C87" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>291</v>
+      </c>
+      <c r="B88" t="s">
+        <v>292</v>
+      </c>
+      <c r="C88" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>294</v>
+      </c>
+      <c r="B89" t="s">
+        <v>295</v>
+      </c>
+      <c r="C89" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>297</v>
+      </c>
+      <c r="B90" t="s">
+        <v>298</v>
+      </c>
+      <c r="C90" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>300</v>
+      </c>
+      <c r="B91" t="s">
+        <v>301</v>
+      </c>
+      <c r="C91" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>303</v>
+      </c>
+      <c r="B92" t="s">
+        <v>304</v>
+      </c>
+      <c r="C92" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>306</v>
+      </c>
+      <c r="B93" t="s">
+        <v>307</v>
+      </c>
+      <c r="C93" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>309</v>
+      </c>
+      <c r="B94" t="s">
+        <v>310</v>
+      </c>
+      <c r="C94" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>312</v>
+      </c>
+      <c r="B95" t="s">
+        <v>313</v>
+      </c>
+      <c r="C95" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>315</v>
+      </c>
+      <c r="B96" t="s">
+        <v>316</v>
+      </c>
+      <c r="C96" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>318</v>
+      </c>
+      <c r="B97" t="s">
+        <v>319</v>
+      </c>
+      <c r="C97" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>321</v>
+      </c>
+      <c r="B98" t="s">
+        <v>322</v>
+      </c>
+      <c r="C98" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>324</v>
+      </c>
+      <c r="B99" t="s">
+        <v>325</v>
+      </c>
+      <c r="C99" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>327</v>
+      </c>
+      <c r="B100" t="s">
+        <v>328</v>
+      </c>
+      <c r="C100" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>330</v>
+      </c>
+      <c r="B101" t="s">
+        <v>331</v>
+      </c>
+      <c r="C101" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>333</v>
+      </c>
+      <c r="B102" t="s">
+        <v>334</v>
+      </c>
+      <c r="C102" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>335</v>
+      </c>
+      <c r="B103" t="s">
+        <v>336</v>
+      </c>
+      <c r="C103" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>338</v>
+      </c>
+      <c r="B104" t="s">
+        <v>339</v>
+      </c>
+      <c r="C104" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>341</v>
+      </c>
+      <c r="B105" t="s">
+        <v>342</v>
+      </c>
+      <c r="C105" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>344</v>
+      </c>
+      <c r="B106" t="s">
+        <v>345</v>
+      </c>
+      <c r="C106" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>347</v>
+      </c>
+      <c r="B107" t="s">
+        <v>348</v>
+      </c>
+      <c r="C107" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>350</v>
+      </c>
+      <c r="B108" t="s">
+        <v>351</v>
+      </c>
+      <c r="C108" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>353</v>
+      </c>
+      <c r="B109" t="s">
+        <v>354</v>
+      </c>
+      <c r="C109" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>356</v>
+      </c>
+      <c r="B110" t="s">
+        <v>357</v>
+      </c>
+      <c r="C110" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>359</v>
+      </c>
+      <c r="B111" t="s">
+        <v>360</v>
+      </c>
+      <c r="C111" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>362</v>
+      </c>
+      <c r="B112" t="s">
+        <v>363</v>
+      </c>
+      <c r="C112" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>365</v>
+      </c>
+      <c r="B113" t="s">
+        <v>366</v>
+      </c>
+      <c r="C113" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>368</v>
+      </c>
+      <c r="B114" t="s">
+        <v>369</v>
+      </c>
+      <c r="C114" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>371</v>
+      </c>
+      <c r="B115" t="s">
+        <v>372</v>
+      </c>
+      <c r="C115" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>374</v>
+      </c>
+      <c r="B116" t="s">
+        <v>375</v>
+      </c>
+      <c r="C116" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>377</v>
+      </c>
+      <c r="B117" t="s">
+        <v>378</v>
+      </c>
+      <c r="C117" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>380</v>
+      </c>
+      <c r="B118" t="s">
+        <v>381</v>
+      </c>
+      <c r="C118" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>383</v>
+      </c>
+      <c r="B119" t="s">
+        <v>384</v>
+      </c>
+      <c r="C119" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>386</v>
+      </c>
+      <c r="B120" t="s">
+        <v>387</v>
+      </c>
+      <c r="C120" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>389</v>
+      </c>
+      <c r="B121" t="s">
+        <v>390</v>
+      </c>
+      <c r="C121" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>392</v>
+      </c>
+      <c r="B122" t="s">
+        <v>393</v>
+      </c>
+      <c r="C122" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>395</v>
+      </c>
+      <c r="B123" t="s">
+        <v>396</v>
+      </c>
+      <c r="C123" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>398</v>
+      </c>
+      <c r="B124" t="s">
+        <v>399</v>
+      </c>
+      <c r="C124" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>401</v>
+      </c>
+      <c r="B125" t="s">
+        <v>402</v>
+      </c>
+      <c r="C125" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>404</v>
+      </c>
+      <c r="B126" t="s">
+        <v>405</v>
+      </c>
+      <c r="C126" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>407</v>
+      </c>
+      <c r="B127" t="s">
+        <v>408</v>
+      </c>
+      <c r="C127" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>410</v>
+      </c>
+      <c r="B128" t="s">
+        <v>411</v>
+      </c>
+      <c r="C128" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>413</v>
+      </c>
+      <c r="B129" t="s">
+        <v>414</v>
+      </c>
+      <c r="C129" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>416</v>
+      </c>
+      <c r="B130" t="s">
+        <v>417</v>
+      </c>
+      <c r="C130" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>419</v>
+      </c>
+      <c r="B131" t="s">
+        <v>420</v>
+      </c>
+      <c r="C131" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>422</v>
+      </c>
+      <c r="B132" t="s">
+        <v>423</v>
+      </c>
+      <c r="C132" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>425</v>
+      </c>
+      <c r="B133" t="s">
+        <v>426</v>
+      </c>
+      <c r="C133" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>428</v>
+      </c>
+      <c r="B134" t="s">
+        <v>429</v>
+      </c>
+      <c r="C134" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
+        <v>431</v>
+      </c>
+      <c r="B135" t="s">
+        <v>432</v>
+      </c>
+      <c r="C135" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>434</v>
+      </c>
+      <c r="B136" t="s">
+        <v>435</v>
+      </c>
+      <c r="C136" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
+        <v>437</v>
+      </c>
+      <c r="B137" t="s">
+        <v>438</v>
+      </c>
+      <c r="C137" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
+        <v>440</v>
+      </c>
+      <c r="B138" t="s">
+        <v>441</v>
+      </c>
+      <c r="C138" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
+        <v>443</v>
+      </c>
+      <c r="B139" t="s">
+        <v>444</v>
+      </c>
+      <c r="C139" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
+        <v>446</v>
+      </c>
+      <c r="B140" t="s">
+        <v>447</v>
+      </c>
+      <c r="C140" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
+        <v>449</v>
+      </c>
+      <c r="B141" t="s">
+        <v>450</v>
+      </c>
+      <c r="C141" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>452</v>
+      </c>
+      <c r="B142" t="s">
+        <v>453</v>
+      </c>
+      <c r="C142" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>455</v>
+      </c>
+      <c r="B143" t="s">
+        <v>456</v>
+      </c>
+      <c r="C143" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
+        <v>458</v>
+      </c>
+      <c r="B144" t="s">
+        <v>459</v>
+      </c>
+      <c r="C144" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
+        <v>461</v>
+      </c>
+      <c r="B145" t="s">
+        <v>462</v>
+      </c>
+      <c r="C145" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
+        <v>464</v>
+      </c>
+      <c r="B146" t="s">
+        <v>465</v>
+      </c>
+      <c r="C146" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A147" t="s">
+        <v>467</v>
+      </c>
+      <c r="B147" t="s">
+        <v>468</v>
+      </c>
+      <c r="C147" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A148" t="s">
+        <v>470</v>
+      </c>
+      <c r="B148" t="s">
+        <v>471</v>
+      </c>
+      <c r="C148" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A149" t="s">
+        <v>473</v>
+      </c>
+      <c r="B149" t="s">
+        <v>474</v>
+      </c>
+      <c r="C149" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A150" t="s">
+        <v>476</v>
+      </c>
+      <c r="B150" t="s">
+        <v>477</v>
+      </c>
+      <c r="C150" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A151" t="s">
+        <v>479</v>
+      </c>
+      <c r="B151" t="s">
+        <v>480</v>
+      </c>
+      <c r="C151" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A152" t="s">
+        <v>482</v>
+      </c>
+      <c r="B152" t="s">
+        <v>483</v>
+      </c>
+      <c r="C152" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A153" t="s">
+        <v>485</v>
+      </c>
+      <c r="B153" t="s">
+        <v>486</v>
+      </c>
+      <c r="C153" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A154" t="s">
+        <v>488</v>
+      </c>
+      <c r="B154" t="s">
+        <v>489</v>
+      </c>
+      <c r="C154" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A155" t="s">
+        <v>491</v>
+      </c>
+      <c r="B155" t="s">
+        <v>492</v>
+      </c>
+      <c r="C155" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A156" t="s">
+        <v>494</v>
+      </c>
+      <c r="B156" t="s">
+        <v>495</v>
+      </c>
+      <c r="C156" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A157" t="s">
+        <v>497</v>
+      </c>
+      <c r="B157" t="s">
+        <v>498</v>
+      </c>
+      <c r="C157" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A158" t="s">
+        <v>500</v>
+      </c>
+      <c r="B158" t="s">
+        <v>501</v>
+      </c>
+      <c r="C158" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A159" t="s">
+        <v>503</v>
+      </c>
+      <c r="B159" t="s">
+        <v>504</v>
+      </c>
+      <c r="C159" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A160" t="s">
+        <v>506</v>
+      </c>
+      <c r="B160" t="s">
+        <v>507</v>
+      </c>
+      <c r="C160" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A161" t="s">
+        <v>509</v>
+      </c>
+      <c r="B161" t="s">
+        <v>510</v>
+      </c>
+      <c r="C161" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A162" t="s">
+        <v>512</v>
+      </c>
+      <c r="B162" t="s">
+        <v>513</v>
+      </c>
+      <c r="C162" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A163" t="s">
+        <v>515</v>
+      </c>
+      <c r="B163" t="s">
+        <v>516</v>
+      </c>
+      <c r="C163" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A164" t="s">
+        <v>518</v>
+      </c>
+      <c r="B164" t="s">
+        <v>519</v>
+      </c>
+      <c r="C164" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A165" t="s">
+        <v>521</v>
+      </c>
+      <c r="B165" t="s">
+        <v>522</v>
+      </c>
+      <c r="C165" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A166" t="s">
+        <v>524</v>
+      </c>
+      <c r="B166" t="s">
+        <v>525</v>
+      </c>
+      <c r="C166" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A167" t="s">
+        <v>527</v>
+      </c>
+      <c r="B167" t="s">
+        <v>528</v>
+      </c>
+      <c r="C167" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A168" t="s">
+        <v>530</v>
+      </c>
+      <c r="B168" t="s">
+        <v>531</v>
+      </c>
+      <c r="C168" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A169" t="s">
+        <v>533</v>
+      </c>
+      <c r="B169" t="s">
+        <v>534</v>
+      </c>
+      <c r="C169" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A170" t="s">
+        <v>536</v>
+      </c>
+      <c r="B170" t="s">
+        <v>537</v>
+      </c>
+      <c r="C170" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A171" t="s">
+        <v>539</v>
+      </c>
+      <c r="B171" t="s">
+        <v>540</v>
+      </c>
+      <c r="C171" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A172" t="s">
+        <v>542</v>
+      </c>
+      <c r="B172" t="s">
+        <v>543</v>
+      </c>
+      <c r="C172" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A173" t="s">
+        <v>545</v>
+      </c>
+      <c r="B173" t="s">
+        <v>546</v>
+      </c>
+      <c r="C173" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A174" t="s">
+        <v>548</v>
+      </c>
+      <c r="B174" t="s">
+        <v>549</v>
+      </c>
+      <c r="C174" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A175" t="s">
+        <v>551</v>
+      </c>
+      <c r="B175" t="s">
+        <v>552</v>
+      </c>
+      <c r="C175" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A176" t="s">
+        <v>554</v>
+      </c>
+      <c r="B176" t="s">
+        <v>555</v>
+      </c>
+      <c r="C176" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A177" t="s">
+        <v>557</v>
+      </c>
+      <c r="B177" t="s">
+        <v>558</v>
+      </c>
+      <c r="C177" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A178" t="s">
+        <v>560</v>
+      </c>
+      <c r="B178" t="s">
+        <v>561</v>
+      </c>
+      <c r="C178" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A179" t="s">
+        <v>563</v>
+      </c>
+      <c r="B179" t="s">
+        <v>564</v>
+      </c>
+      <c r="C179" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A180" t="s">
+        <v>566</v>
+      </c>
+      <c r="B180" t="s">
+        <v>567</v>
+      </c>
+      <c r="C180" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A181" t="s">
+        <v>569</v>
+      </c>
+      <c r="B181" t="s">
+        <v>570</v>
+      </c>
+      <c r="C181" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A182" t="s">
+        <v>572</v>
+      </c>
+      <c r="B182" t="s">
+        <v>573</v>
+      </c>
+      <c r="C182" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A183" t="s">
+        <v>575</v>
+      </c>
+      <c r="B183" t="s">
+        <v>576</v>
+      </c>
+      <c r="C183" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A184" t="s">
+        <v>578</v>
+      </c>
+      <c r="B184" t="s">
+        <v>579</v>
+      </c>
+      <c r="C184" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A185" t="s">
+        <v>581</v>
+      </c>
+      <c r="B185" t="s">
+        <v>582</v>
+      </c>
+      <c r="C185" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A186" t="s">
+        <v>584</v>
+      </c>
+      <c r="B186" t="s">
+        <v>585</v>
+      </c>
+      <c r="C186" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A187" t="s">
+        <v>587</v>
+      </c>
+      <c r="B187" t="s">
+        <v>588</v>
+      </c>
+      <c r="C187" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A188" t="s">
+        <v>590</v>
+      </c>
+      <c r="B188" t="s">
+        <v>591</v>
+      </c>
+      <c r="C188" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A189" t="s">
+        <v>593</v>
+      </c>
+      <c r="B189" t="s">
+        <v>594</v>
+      </c>
+      <c r="C189" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A190" t="s">
+        <v>596</v>
+      </c>
+      <c r="B190" t="s">
+        <v>597</v>
+      </c>
+      <c r="C190" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A191" t="s">
+        <v>599</v>
+      </c>
+      <c r="B191" t="s">
+        <v>600</v>
+      </c>
+      <c r="C191" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A192" t="s">
+        <v>602</v>
+      </c>
+      <c r="B192" t="s">
+        <v>603</v>
+      </c>
+      <c r="C192" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A193" t="s">
+        <v>605</v>
+      </c>
+      <c r="B193" t="s">
+        <v>606</v>
+      </c>
+      <c r="C193" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A194" t="s">
+        <v>608</v>
+      </c>
+      <c r="B194" t="s">
+        <v>609</v>
+      </c>
+      <c r="C194" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A195" t="s">
+        <v>611</v>
+      </c>
+      <c r="B195" t="s">
+        <v>612</v>
+      </c>
+      <c r="C195" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A196" t="s">
+        <v>614</v>
+      </c>
+      <c r="B196" t="s">
+        <v>614</v>
+      </c>
+      <c r="C196" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A197" t="s">
+        <v>616</v>
+      </c>
+      <c r="B197" t="s">
+        <v>617</v>
+      </c>
+      <c r="C197" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A198" t="s">
+        <v>619</v>
+      </c>
+      <c r="B198" t="s">
+        <v>619</v>
+      </c>
+      <c r="C198" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A199" t="s">
+        <v>621</v>
+      </c>
+      <c r="B199" t="s">
+        <v>622</v>
+      </c>
+      <c r="C199" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A200" t="s">
+        <v>624</v>
+      </c>
+      <c r="B200" t="s">
+        <v>743</v>
+      </c>
+      <c r="C200" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A201" t="s">
+        <v>625</v>
+      </c>
+      <c r="B201" t="s">
+        <v>626</v>
+      </c>
+      <c r="C201" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A202" t="s">
+        <v>628</v>
+      </c>
+      <c r="B202" t="s">
+        <v>745</v>
+      </c>
+      <c r="C202" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A203" t="s">
+        <v>629</v>
+      </c>
+      <c r="B203" t="s">
+        <v>630</v>
+      </c>
+      <c r="C203" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A204" t="s">
+        <v>632</v>
+      </c>
+      <c r="B204" t="s">
+        <v>747</v>
+      </c>
+      <c r="C204" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A205" t="s">
+        <v>633</v>
+      </c>
+      <c r="B205" t="s">
+        <v>634</v>
+      </c>
+      <c r="C205" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A206" t="s">
+        <v>636</v>
+      </c>
+      <c r="B206" t="s">
+        <v>749</v>
+      </c>
+      <c r="C206" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A207" t="s">
+        <v>637</v>
+      </c>
+      <c r="B207" t="s">
+        <v>638</v>
+      </c>
+      <c r="C207" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A208" t="s">
+        <v>640</v>
+      </c>
+      <c r="B208" t="s">
+        <v>641</v>
+      </c>
+      <c r="C208" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A209" t="s">
+        <v>643</v>
+      </c>
+      <c r="B209" t="s">
+        <v>644</v>
+      </c>
+      <c r="C209" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A210" t="s">
+        <v>646</v>
+      </c>
+      <c r="B210" t="s">
+        <v>751</v>
+      </c>
+      <c r="C210" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A211" t="s">
+        <v>647</v>
+      </c>
+      <c r="B211" t="s">
+        <v>648</v>
+      </c>
+      <c r="C211" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A212" t="s">
+        <v>650</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A213" t="s">
+        <v>651</v>
+      </c>
+      <c r="B213" t="s">
+        <v>652</v>
+      </c>
+      <c r="C213" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A214" t="s">
+        <v>654</v>
+      </c>
+      <c r="B214" t="s">
+        <v>754</v>
+      </c>
+      <c r="C214" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A215" t="s">
+        <v>655</v>
+      </c>
+      <c r="B215" t="s">
+        <v>656</v>
+      </c>
+      <c r="C215" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A216" t="s">
+        <v>658</v>
+      </c>
+      <c r="B216" t="s">
+        <v>756</v>
+      </c>
+      <c r="C216" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A217" t="s">
+        <v>659</v>
+      </c>
+      <c r="B217" t="s">
+        <v>660</v>
+      </c>
+      <c r="C217" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A218" t="s">
+        <v>662</v>
+      </c>
+      <c r="B218" t="s">
+        <v>758</v>
+      </c>
+      <c r="C218" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A219" t="s">
+        <v>663</v>
+      </c>
+      <c r="B219" t="s">
+        <v>664</v>
+      </c>
+      <c r="C219" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A220" t="s">
+        <v>666</v>
+      </c>
+      <c r="B220" t="s">
+        <v>760</v>
+      </c>
+      <c r="C220" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A221" t="s">
+        <v>667</v>
+      </c>
+      <c r="B221" t="s">
+        <v>668</v>
+      </c>
+      <c r="C221" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A222" t="s">
+        <v>670</v>
+      </c>
+      <c r="B222" t="s">
+        <v>762</v>
+      </c>
+      <c r="C222" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A223" t="s">
+        <v>671</v>
+      </c>
+      <c r="B223" t="s">
+        <v>672</v>
+      </c>
+      <c r="C223" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A224" t="s">
+        <v>674</v>
+      </c>
+      <c r="B224" t="s">
+        <v>675</v>
+      </c>
+      <c r="C224" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A225" t="s">
+        <v>677</v>
+      </c>
+      <c r="B225" t="s">
+        <v>678</v>
+      </c>
+      <c r="C225" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A226" t="s">
+        <v>680</v>
+      </c>
+      <c r="B226" t="s">
+        <v>681</v>
+      </c>
+      <c r="C226" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A227" t="s">
+        <v>683</v>
+      </c>
+      <c r="B227" t="s">
+        <v>684</v>
+      </c>
+      <c r="C227" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A228" t="s">
+        <v>686</v>
+      </c>
+      <c r="B228" t="s">
+        <v>687</v>
+      </c>
+      <c r="C228" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A229" t="s">
+        <v>689</v>
+      </c>
+      <c r="B229" t="s">
+        <v>690</v>
+      </c>
+      <c r="C229" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A230" t="s">
+        <v>692</v>
+      </c>
+      <c r="B230" t="s">
+        <v>693</v>
+      </c>
+      <c r="C230" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A231" t="s">
+        <v>695</v>
+      </c>
+      <c r="B231" t="s">
+        <v>696</v>
+      </c>
+      <c r="C231" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A232" t="s">
+        <v>698</v>
+      </c>
+      <c r="B232" t="s">
+        <v>699</v>
+      </c>
+      <c r="C232" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A233" t="s">
+        <v>701</v>
+      </c>
+      <c r="B233" t="s">
+        <v>702</v>
+      </c>
+      <c r="C233" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A234" t="s">
+        <v>704</v>
+      </c>
+      <c r="B234" t="s">
+        <v>705</v>
+      </c>
+      <c r="C234" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A235" t="s">
+        <v>707</v>
+      </c>
+      <c r="B235" t="s">
+        <v>708</v>
+      </c>
+      <c r="C235" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A236" t="s">
+        <v>710</v>
+      </c>
+      <c r="B236" t="s">
+        <v>711</v>
+      </c>
+      <c r="C236" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A237" t="s">
+        <v>713</v>
+      </c>
+      <c r="B237" t="s">
+        <v>714</v>
+      </c>
+      <c r="C237" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A238" t="s">
+        <v>716</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A239" t="s">
+        <v>717</v>
+      </c>
+      <c r="B239" t="s">
+        <v>718</v>
+      </c>
+      <c r="C239" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A240" t="s">
+        <v>720</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A241" t="s">
+        <v>721</v>
+      </c>
+      <c r="B241" t="s">
+        <v>722</v>
+      </c>
+      <c r="C241" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A242" t="s">
+        <v>724</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A243" t="s">
+        <v>725</v>
+      </c>
+      <c r="B243" t="s">
+        <v>726</v>
+      </c>
+      <c r="C243" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A244" t="s">
+        <v>728</v>
+      </c>
+      <c r="B244" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A245" t="s">
+        <v>729</v>
+      </c>
+      <c r="B245" t="s">
+        <v>730</v>
+      </c>
+      <c r="C245" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A246" t="s">
+        <v>732</v>
+      </c>
+      <c r="B246" t="s">
+        <v>733</v>
+      </c>
+      <c r="C246" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A247" t="s">
+        <v>735</v>
+      </c>
+      <c r="B247" t="s">
+        <v>736</v>
+      </c>
+      <c r="C247" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A248" t="s">
+        <v>738</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A249" t="s">
+        <v>739</v>
+      </c>
+      <c r="B249" t="s">
+        <v>740</v>
+      </c>
+      <c r="C249" t="s">
+        <v>741</v>
       </c>
     </row>
   </sheetData>
@@ -609,4 +5509,169 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="25.75" customWidth="1"/>
+    <col min="2" max="2" width="29" customWidth="1"/>
+    <col min="3" max="3" width="24.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="29.625" customWidth="1"/>
+    <col min="2" max="2" width="29" customWidth="1"/>
+    <col min="3" max="3" width="32.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BFD7A62-CC9B-45C3-A6C5-15DD9ACA4D59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12600"/>
+    <workbookView xWindow="1780" yWindow="2090" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="System" sheetId="1" r:id="rId1"/>
@@ -24,8 +25,8 @@
 </file>
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <connection id="1" name="1" type="6" refreshedVersion="6" background="1" saveData="1">
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
+  <connection id="1" xr16:uid="{00000000-0015-0000-FFFF-FFFF00000000}" name="1" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="65001" sourceFile="C:\Users\liufengming\Desktop\1.txt">
       <textFields count="3">
         <textField/>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="771">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="777">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2420,13 +2421,37 @@
   </si>
   <si>
     <t>**=</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BACK_TO_TITLE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回到标题界面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BACK_TO_TITLE_DESC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>After this command, you will get back to the title scene.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本次操作后，将会回到标题界面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Go Back To Title</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2491,7 +2516,7 @@
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="1" connectionId="1" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="1" connectionId="1" xr16:uid="{00000000-0016-0000-0000-000000000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2756,16 +2781,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C249"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C251"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38.75" customWidth="1"/>
-    <col min="2" max="2" width="61.875" customWidth="1"/>
-    <col min="3" max="3" width="52.375" customWidth="1"/>
+    <col min="2" max="2" width="61.83203125" customWidth="1"/>
+    <col min="3" max="3" width="52.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2776,7 +2801,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -2787,7 +2812,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>36</v>
       </c>
@@ -2798,7 +2823,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -2809,7 +2834,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -2820,7 +2845,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>45</v>
       </c>
@@ -2831,7 +2856,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>48</v>
       </c>
@@ -2842,7 +2867,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>51</v>
       </c>
@@ -2853,7 +2878,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>54</v>
       </c>
@@ -2864,7 +2889,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>57</v>
       </c>
@@ -2875,7 +2900,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>60</v>
       </c>
@@ -2886,7 +2911,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -2897,7 +2922,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>66</v>
       </c>
@@ -2908,7 +2933,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>69</v>
       </c>
@@ -2919,7 +2944,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>72</v>
       </c>
@@ -2930,7 +2955,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>75</v>
       </c>
@@ -2941,7 +2966,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>78</v>
       </c>
@@ -2952,7 +2977,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>81</v>
       </c>
@@ -2963,7 +2988,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>84</v>
       </c>
@@ -2974,7 +2999,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>87</v>
       </c>
@@ -2985,7 +3010,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>90</v>
       </c>
@@ -2996,7 +3021,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>93</v>
       </c>
@@ -3007,7 +3032,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>96</v>
       </c>
@@ -3018,7 +3043,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>99</v>
       </c>
@@ -3029,7 +3054,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>102</v>
       </c>
@@ -3040,7 +3065,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>105</v>
       </c>
@@ -3051,7 +3076,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>108</v>
       </c>
@@ -3062,7 +3087,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>111</v>
       </c>
@@ -3073,7 +3098,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>114</v>
       </c>
@@ -3084,7 +3109,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>117</v>
       </c>
@@ -3095,7 +3120,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>120</v>
       </c>
@@ -3106,7 +3131,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>123</v>
       </c>
@@ -3117,7 +3142,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>126</v>
       </c>
@@ -3128,7 +3153,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>129</v>
       </c>
@@ -3139,7 +3164,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>132</v>
       </c>
@@ -3150,7 +3175,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>135</v>
       </c>
@@ -3161,7 +3186,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>138</v>
       </c>
@@ -3172,7 +3197,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>141</v>
       </c>
@@ -3183,7 +3208,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>144</v>
       </c>
@@ -3194,7 +3219,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>147</v>
       </c>
@@ -3205,7 +3230,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>150</v>
       </c>
@@ -3216,7 +3241,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>153</v>
       </c>
@@ -3227,7 +3252,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>156</v>
       </c>
@@ -3238,7 +3263,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>159</v>
       </c>
@@ -3249,7 +3274,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>162</v>
       </c>
@@ -3260,7 +3285,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>165</v>
       </c>
@@ -3271,7 +3296,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>168</v>
       </c>
@@ -3282,7 +3307,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>171</v>
       </c>
@@ -3293,7 +3318,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>174</v>
       </c>
@@ -3304,7 +3329,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>177</v>
       </c>
@@ -3315,7 +3340,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>180</v>
       </c>
@@ -3326,7 +3351,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>183</v>
       </c>
@@ -3337,7 +3362,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>186</v>
       </c>
@@ -3348,7 +3373,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>189</v>
       </c>
@@ -3359,7 +3384,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>192</v>
       </c>
@@ -3370,7 +3395,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>195</v>
       </c>
@@ -3381,7 +3406,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>198</v>
       </c>
@@ -3392,7 +3417,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>201</v>
       </c>
@@ -3403,7 +3428,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>204</v>
       </c>
@@ -3414,7 +3439,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>207</v>
       </c>
@@ -3425,7 +3450,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>210</v>
       </c>
@@ -3436,7 +3461,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>213</v>
       </c>
@@ -3447,7 +3472,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>216</v>
       </c>
@@ -3458,7 +3483,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>219</v>
       </c>
@@ -3469,7 +3494,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>222</v>
       </c>
@@ -3480,7 +3505,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>225</v>
       </c>
@@ -3491,7 +3516,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>228</v>
       </c>
@@ -3502,7 +3527,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>231</v>
       </c>
@@ -3513,7 +3538,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>234</v>
       </c>
@@ -3524,7 +3549,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>237</v>
       </c>
@@ -3535,7 +3560,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>240</v>
       </c>
@@ -3546,7 +3571,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>243</v>
       </c>
@@ -3557,7 +3582,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>246</v>
       </c>
@@ -3568,7 +3593,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>249</v>
       </c>
@@ -3579,7 +3604,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>252</v>
       </c>
@@ -3590,7 +3615,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>255</v>
       </c>
@@ -3601,7 +3626,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>258</v>
       </c>
@@ -3612,7 +3637,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>261</v>
       </c>
@@ -3623,7 +3648,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>264</v>
       </c>
@@ -3634,7 +3659,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>267</v>
       </c>
@@ -3645,7 +3670,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>270</v>
       </c>
@@ -3656,7 +3681,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>273</v>
       </c>
@@ -3667,7 +3692,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>276</v>
       </c>
@@ -3678,7 +3703,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>279</v>
       </c>
@@ -3689,7 +3714,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>282</v>
       </c>
@@ -3700,7 +3725,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>285</v>
       </c>
@@ -3711,7 +3736,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>288</v>
       </c>
@@ -3722,7 +3747,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>291</v>
       </c>
@@ -3733,7 +3758,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>294</v>
       </c>
@@ -3744,7 +3769,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>297</v>
       </c>
@@ -3755,7 +3780,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>300</v>
       </c>
@@ -3766,7 +3791,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>303</v>
       </c>
@@ -3777,7 +3802,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>306</v>
       </c>
@@ -3788,7 +3813,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>309</v>
       </c>
@@ -3799,7 +3824,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>312</v>
       </c>
@@ -3810,7 +3835,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>315</v>
       </c>
@@ -3821,7 +3846,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>318</v>
       </c>
@@ -3832,7 +3857,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>321</v>
       </c>
@@ -3843,7 +3868,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>324</v>
       </c>
@@ -3854,7 +3879,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>327</v>
       </c>
@@ -3865,7 +3890,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>330</v>
       </c>
@@ -3876,7 +3901,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>333</v>
       </c>
@@ -3887,7 +3912,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>335</v>
       </c>
@@ -3898,7 +3923,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>338</v>
       </c>
@@ -3909,7 +3934,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>341</v>
       </c>
@@ -3920,7 +3945,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>344</v>
       </c>
@@ -3931,7 +3956,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>347</v>
       </c>
@@ -3942,7 +3967,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>350</v>
       </c>
@@ -3953,7 +3978,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>353</v>
       </c>
@@ -3964,7 +3989,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>356</v>
       </c>
@@ -3975,7 +4000,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>359</v>
       </c>
@@ -3986,7 +4011,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>362</v>
       </c>
@@ -3997,7 +4022,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>365</v>
       </c>
@@ -4008,7 +4033,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>368</v>
       </c>
@@ -4019,7 +4044,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>371</v>
       </c>
@@ -4030,7 +4055,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>374</v>
       </c>
@@ -4041,7 +4066,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>377</v>
       </c>
@@ -4052,7 +4077,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>380</v>
       </c>
@@ -4063,7 +4088,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>383</v>
       </c>
@@ -4074,7 +4099,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>386</v>
       </c>
@@ -4085,7 +4110,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>389</v>
       </c>
@@ -4096,7 +4121,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>392</v>
       </c>
@@ -4107,7 +4132,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>395</v>
       </c>
@@ -4118,7 +4143,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>398</v>
       </c>
@@ -4129,7 +4154,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>401</v>
       </c>
@@ -4140,7 +4165,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>404</v>
       </c>
@@ -4151,7 +4176,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>407</v>
       </c>
@@ -4162,7 +4187,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>410</v>
       </c>
@@ -4173,7 +4198,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>413</v>
       </c>
@@ -4184,7 +4209,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>416</v>
       </c>
@@ -4195,7 +4220,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>419</v>
       </c>
@@ -4206,7 +4231,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>422</v>
       </c>
@@ -4217,7 +4242,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>425</v>
       </c>
@@ -4228,7 +4253,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>428</v>
       </c>
@@ -4239,7 +4264,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>431</v>
       </c>
@@ -4250,7 +4275,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>434</v>
       </c>
@@ -4261,7 +4286,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>437</v>
       </c>
@@ -4272,7 +4297,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>440</v>
       </c>
@@ -4283,7 +4308,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>443</v>
       </c>
@@ -4294,7 +4319,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>446</v>
       </c>
@@ -4305,7 +4330,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>449</v>
       </c>
@@ -4316,7 +4341,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>452</v>
       </c>
@@ -4327,7 +4352,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>455</v>
       </c>
@@ -4338,7 +4363,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>458</v>
       </c>
@@ -4349,7 +4374,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>461</v>
       </c>
@@ -4360,7 +4385,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>464</v>
       </c>
@@ -4371,7 +4396,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>467</v>
       </c>
@@ -4382,7 +4407,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>470</v>
       </c>
@@ -4393,7 +4418,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>473</v>
       </c>
@@ -4404,7 +4429,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>476</v>
       </c>
@@ -4415,7 +4440,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>479</v>
       </c>
@@ -4426,7 +4451,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>482</v>
       </c>
@@ -4437,7 +4462,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>485</v>
       </c>
@@ -4448,7 +4473,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>488</v>
       </c>
@@ -4459,7 +4484,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>491</v>
       </c>
@@ -4470,7 +4495,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>494</v>
       </c>
@@ -4481,7 +4506,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>497</v>
       </c>
@@ -4492,7 +4517,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>500</v>
       </c>
@@ -4503,7 +4528,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>503</v>
       </c>
@@ -4514,7 +4539,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>506</v>
       </c>
@@ -4525,7 +4550,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>509</v>
       </c>
@@ -4536,7 +4561,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>512</v>
       </c>
@@ -4547,7 +4572,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>515</v>
       </c>
@@ -4558,7 +4583,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>518</v>
       </c>
@@ -4569,7 +4594,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>521</v>
       </c>
@@ -4580,7 +4605,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>524</v>
       </c>
@@ -4591,7 +4616,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>527</v>
       </c>
@@ -4602,7 +4627,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>530</v>
       </c>
@@ -4613,7 +4638,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>533</v>
       </c>
@@ -4624,7 +4649,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>536</v>
       </c>
@@ -4635,7 +4660,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>539</v>
       </c>
@@ -4646,7 +4671,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>542</v>
       </c>
@@ -4657,7 +4682,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>545</v>
       </c>
@@ -4668,7 +4693,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>548</v>
       </c>
@@ -4679,7 +4704,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>551</v>
       </c>
@@ -4690,7 +4715,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>554</v>
       </c>
@@ -4701,7 +4726,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>557</v>
       </c>
@@ -4712,7 +4737,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>560</v>
       </c>
@@ -4723,7 +4748,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>563</v>
       </c>
@@ -4734,7 +4759,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>566</v>
       </c>
@@ -4745,7 +4770,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>569</v>
       </c>
@@ -4756,7 +4781,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>572</v>
       </c>
@@ -4767,7 +4792,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>575</v>
       </c>
@@ -4778,7 +4803,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>578</v>
       </c>
@@ -4789,7 +4814,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>581</v>
       </c>
@@ -4800,7 +4825,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>584</v>
       </c>
@@ -4811,7 +4836,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>587</v>
       </c>
@@ -4822,7 +4847,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>590</v>
       </c>
@@ -4833,7 +4858,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>593</v>
       </c>
@@ -4844,7 +4869,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>596</v>
       </c>
@@ -4855,7 +4880,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>599</v>
       </c>
@@ -4866,7 +4891,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>602</v>
       </c>
@@ -4877,7 +4902,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>605</v>
       </c>
@@ -4888,7 +4913,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>608</v>
       </c>
@@ -4899,7 +4924,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>611</v>
       </c>
@@ -4910,7 +4935,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>614</v>
       </c>
@@ -4921,7 +4946,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>616</v>
       </c>
@@ -4932,7 +4957,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>619</v>
       </c>
@@ -4943,7 +4968,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>621</v>
       </c>
@@ -4954,7 +4979,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>624</v>
       </c>
@@ -4965,7 +4990,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>625</v>
       </c>
@@ -4976,7 +5001,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>628</v>
       </c>
@@ -4987,7 +5012,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>629</v>
       </c>
@@ -4998,7 +5023,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>632</v>
       </c>
@@ -5009,7 +5034,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>633</v>
       </c>
@@ -5020,7 +5045,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>636</v>
       </c>
@@ -5031,7 +5056,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>637</v>
       </c>
@@ -5042,7 +5067,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>640</v>
       </c>
@@ -5053,7 +5078,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>643</v>
       </c>
@@ -5064,7 +5089,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>646</v>
       </c>
@@ -5075,7 +5100,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>647</v>
       </c>
@@ -5086,7 +5111,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>650</v>
       </c>
@@ -5097,7 +5122,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>651</v>
       </c>
@@ -5108,7 +5133,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>654</v>
       </c>
@@ -5119,7 +5144,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>655</v>
       </c>
@@ -5130,7 +5155,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>658</v>
       </c>
@@ -5141,7 +5166,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>659</v>
       </c>
@@ -5152,7 +5177,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>662</v>
       </c>
@@ -5163,7 +5188,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>663</v>
       </c>
@@ -5174,7 +5199,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>666</v>
       </c>
@@ -5185,7 +5210,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>667</v>
       </c>
@@ -5196,7 +5221,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>670</v>
       </c>
@@ -5207,7 +5232,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>671</v>
       </c>
@@ -5218,7 +5243,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>674</v>
       </c>
@@ -5229,7 +5254,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>677</v>
       </c>
@@ -5240,7 +5265,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>680</v>
       </c>
@@ -5251,7 +5276,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>683</v>
       </c>
@@ -5262,7 +5287,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>686</v>
       </c>
@@ -5273,7 +5298,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>689</v>
       </c>
@@ -5284,7 +5309,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>692</v>
       </c>
@@ -5295,7 +5320,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>695</v>
       </c>
@@ -5306,7 +5331,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>698</v>
       </c>
@@ -5317,7 +5342,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>701</v>
       </c>
@@ -5328,7 +5353,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>704</v>
       </c>
@@ -5339,7 +5364,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>707</v>
       </c>
@@ -5350,7 +5375,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>710</v>
       </c>
@@ -5361,7 +5386,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>713</v>
       </c>
@@ -5372,7 +5397,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>716</v>
       </c>
@@ -5383,7 +5408,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>717</v>
       </c>
@@ -5394,7 +5419,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>720</v>
       </c>
@@ -5405,7 +5430,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>721</v>
       </c>
@@ -5416,7 +5441,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>724</v>
       </c>
@@ -5427,7 +5452,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>725</v>
       </c>
@@ -5438,7 +5463,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>728</v>
       </c>
@@ -5449,7 +5474,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>729</v>
       </c>
@@ -5460,7 +5485,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>732</v>
       </c>
@@ -5471,7 +5496,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>735</v>
       </c>
@@ -5482,7 +5507,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>738</v>
       </c>
@@ -5493,7 +5518,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>739</v>
       </c>
@@ -5502,6 +5527,28 @@
       </c>
       <c r="C249" t="s">
         <v>741</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A250" t="s">
+        <v>771</v>
+      </c>
+      <c r="B250" t="s">
+        <v>776</v>
+      </c>
+      <c r="C250" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A251" t="s">
+        <v>773</v>
+      </c>
+      <c r="B251" t="s">
+        <v>774</v>
+      </c>
+      <c r="C251" t="s">
+        <v>775</v>
       </c>
     </row>
   </sheetData>
@@ -5512,16 +5559,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.75" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="3" max="3" width="24.875" customWidth="1"/>
+    <col min="3" max="3" width="24.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5532,7 +5579,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -5543,7 +5590,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -5554,7 +5601,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -5565,7 +5612,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -5576,7 +5623,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -5587,7 +5634,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -5606,16 +5653,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.625" customWidth="1"/>
+    <col min="1" max="1" width="29.58203125" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="3" max="3" width="32.375" customWidth="1"/>
+    <col min="3" max="3" width="32.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5626,7 +5673,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -5637,7 +5684,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -5648,7 +5695,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -5659,7 +5706,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>20</v>
       </c>

--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Other\Ludork\Sample\Data\Locale\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DE0D9E8-D3D9-4378-B72D-29D5FB278C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42DCD8BD-002D-4E8F-B3CB-4A357603568D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10070" yWindow="3030" windowWidth="28800" windowHeight="15370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9600" yWindow="3030" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="System" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="857">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="860">
   <si>
     <t>ID</t>
   </si>
@@ -2622,6 +2622,18 @@
   </si>
   <si>
     <t>Config</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ITEM_NEW</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Got {name}!\n{desc}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得了{name}！\n{desc}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2955,7 +2967,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C273"/>
+  <dimension ref="A1:C274"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38.75" customWidth="1"/>
@@ -5964,6 +5976,17 @@
       </c>
       <c r="C273" t="s">
         <v>800</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A274" t="s">
+        <v>857</v>
+      </c>
+      <c r="B274" t="s">
+        <v>858</v>
+      </c>
+      <c r="C274" t="s">
+        <v>859</v>
       </c>
     </row>
   </sheetData>

--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Other\Ludork\Sample\Data\Locale\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\Ludork\Sample\Data\Locale\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42DCD8BD-002D-4E8F-B3CB-4A357603568D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F0E867-15CD-4532-8441-B581C170FE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9600" yWindow="3030" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="System" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="860">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="866">
   <si>
     <t>ID</t>
   </si>
@@ -2634,6 +2634,30 @@
   </si>
   <si>
     <t>获得了{name}！\n{desc}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ENEMY_BOOK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ENEMY_BOOK_DESC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>持有后可以查看敌人信息（快捷键D）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>You can view the info of enemies with it(Hotkey: D).</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy Book</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>怪物手册</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6124,7 +6148,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.75" customWidth="1"/>
@@ -6207,6 +6231,28 @@
       </c>
       <c r="C7" t="s">
         <v>818</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>860</v>
+      </c>
+      <c r="B8" t="s">
+        <v>864</v>
+      </c>
+      <c r="C8" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>861</v>
+      </c>
+      <c r="B9" t="s">
+        <v>863</v>
+      </c>
+      <c r="C9" t="s">
+        <v>862</v>
       </c>
     </row>
   </sheetData>

--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\Ludork\Sample\Data\Locale\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F0E867-15CD-4532-8441-B581C170FE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ED621E0-3945-4F03-8FFE-FA9B3116FB32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="System" sheetId="1" r:id="rId1"/>
-    <sheet name="UI" sheetId="4" r:id="rId2"/>
-    <sheet name="Items" sheetId="2" r:id="rId3"/>
-    <sheet name="Enemies" sheetId="3" r:id="rId4"/>
+    <sheet name="UI" sheetId="2" r:id="rId2"/>
+    <sheet name="Items" sheetId="3" r:id="rId3"/>
+    <sheet name="Enemies" sheetId="4" r:id="rId4"/>
+    <sheet name="Equips" sheetId="5" r:id="rId5"/>
+    <sheet name="Classes" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_1" localSheetId="0">System!$A$6:$C$249</definedName>
@@ -26,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="866">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1059" uniqueCount="1025">
   <si>
     <t>ID</t>
   </si>
@@ -37,6 +39,507 @@
     <t>zh_CN</t>
   </si>
   <si>
+    <t>TITLE_START</t>
+  </si>
+  <si>
+    <t>Start Game</t>
+  </si>
+  <si>
+    <t>开始游戏</t>
+  </si>
+  <si>
+    <t>TITLE_CONTINUE</t>
+  </si>
+  <si>
+    <t>Continue</t>
+  </si>
+  <si>
+    <t>继续游戏</t>
+  </si>
+  <si>
+    <t>TITLE_CONFIG</t>
+  </si>
+  <si>
+    <t>Config</t>
+  </si>
+  <si>
+    <t>设置</t>
+  </si>
+  <si>
+    <t>TITLE_EXIT</t>
+  </si>
+  <si>
+    <t>Exit Game</t>
+  </si>
+  <si>
+    <t>退出游戏</t>
+  </si>
+  <si>
+    <t>MENU_ITEM</t>
+  </si>
+  <si>
+    <t>Items</t>
+  </si>
+  <si>
+    <t>物品道具</t>
+  </si>
+  <si>
+    <t>MENU_EQUIP</t>
+  </si>
+  <si>
+    <t>Equipments</t>
+  </si>
+  <si>
+    <t>装备</t>
+  </si>
+  <si>
+    <t>MENU_SAVE</t>
+  </si>
+  <si>
+    <t>Save File</t>
+  </si>
+  <si>
+    <t>存档</t>
+  </si>
+  <si>
+    <t>MENU_LOAD</t>
+  </si>
+  <si>
+    <t>Load File</t>
+  </si>
+  <si>
+    <t>读档</t>
+  </si>
+  <si>
+    <t>MENU_EXIT</t>
+  </si>
+  <si>
+    <t>回到标题</t>
+  </si>
+  <si>
+    <t>DIALOGUE_BOOK</t>
+  </si>
+  <si>
+    <t>Dialogue Book</t>
+  </si>
+  <si>
+    <t>对话手册</t>
+  </si>
+  <si>
+    <t>DIALOGUE_BOOK_DESC</t>
+  </si>
+  <si>
+    <t>You can review the dialogues that you've met with it.</t>
+  </si>
+  <si>
+    <t>持有后可以查看经历过的对话内容。</t>
+  </si>
+  <si>
+    <t>EQUIP_UNEQUIPPED</t>
+  </si>
+  <si>
+    <t>[Unequipped]</t>
+  </si>
+  <si>
+    <t>[未装备]</t>
+  </si>
+  <si>
+    <t>EQUIP_UNEQUIP</t>
+  </si>
+  <si>
+    <t>Unequip</t>
+  </si>
+  <si>
+    <t>卸下</t>
+  </si>
+  <si>
+    <t>EQUIP_UNEQUIP_DESC</t>
+  </si>
+  <si>
+    <t>Remove equipment from this slot.</t>
+  </si>
+  <si>
+    <t>卸下当前槽位的装备。</t>
+  </si>
+  <si>
+    <t>GET_PLAYER</t>
+  </si>
+  <si>
+    <t>Get Player</t>
+  </si>
+  <si>
+    <t>获取玩家</t>
+  </si>
+  <si>
+    <t>GET_PLAYER_DESC</t>
+  </si>
+  <si>
+    <t>Get the primary player from the current scene.</t>
+  </si>
+  <si>
+    <t>获取当前场景的主角实例</t>
+  </si>
+  <si>
+    <t>ADD_ITEM</t>
+  </si>
+  <si>
+    <t>Add Item</t>
+  </si>
+  <si>
+    <t>添加道具</t>
+  </si>
+  <si>
+    <t>ADD_ITEM_DESC</t>
+  </si>
+  <si>
+    <t>Add item(s) to the player inventory.</t>
+  </si>
+  <si>
+    <t>将道具添加到玩家背包</t>
+  </si>
+  <si>
+    <t>REMOVE_ITEM</t>
+  </si>
+  <si>
+    <t>Remove Item</t>
+  </si>
+  <si>
+    <t>移除道具</t>
+  </si>
+  <si>
+    <t>REMOVE_ITEM_DESC</t>
+  </si>
+  <si>
+    <t>Remove item(s) from the player inventory. Fails if count is insufficient.</t>
+  </si>
+  <si>
+    <t>从玩家背包移除道具，数量不足则失败</t>
+  </si>
+  <si>
+    <t>HAS_ITEM</t>
+  </si>
+  <si>
+    <t>Has Item</t>
+  </si>
+  <si>
+    <t>是否持有道具</t>
+  </si>
+  <si>
+    <t>HAS_ITEM_DESC</t>
+  </si>
+  <si>
+    <t>Check whether the player owns at least one of the specified item.</t>
+  </si>
+  <si>
+    <t>检查玩家是否持有至少一个指定道具</t>
+  </si>
+  <si>
+    <t>GET_ITEM_COUNT</t>
+  </si>
+  <si>
+    <t>Get Item Count</t>
+  </si>
+  <si>
+    <t>获取道具数量</t>
+  </si>
+  <si>
+    <t>GET_ITEM_COUNT_DESC</t>
+  </si>
+  <si>
+    <t>Get the quantity of a specific item in the player inventory.</t>
+  </si>
+  <si>
+    <t>获取玩家背包中指定道具的数量</t>
+  </si>
+  <si>
+    <t>ADD_EQUIP</t>
+  </si>
+  <si>
+    <t>Add Equip</t>
+  </si>
+  <si>
+    <t>添加装备</t>
+  </si>
+  <si>
+    <t>ADD_EQUIP_DESC</t>
+  </si>
+  <si>
+    <t>Add equip(s) to the player equipment bag.</t>
+  </si>
+  <si>
+    <t>将装备添加到玩家装备包</t>
+  </si>
+  <si>
+    <t>REMOVE_EQUIP</t>
+  </si>
+  <si>
+    <t>Remove Equip</t>
+  </si>
+  <si>
+    <t>移除装备</t>
+  </si>
+  <si>
+    <t>REMOVE_EQUIP_DESC</t>
+  </si>
+  <si>
+    <t>Remove equip(s) from the player equipment bag. Fails if count is insufficient.</t>
+  </si>
+  <si>
+    <t>从玩家装备包移除装备，数量不足则失败</t>
+  </si>
+  <si>
+    <t>HAS_EQUIP</t>
+  </si>
+  <si>
+    <t>Has Equip</t>
+  </si>
+  <si>
+    <t>是否持有装备</t>
+  </si>
+  <si>
+    <t>HAS_EQUIP_DESC</t>
+  </si>
+  <si>
+    <t>Check whether the player owns at least one of the specified equip.</t>
+  </si>
+  <si>
+    <t>检查玩家是否持有至少一个指定装备</t>
+  </si>
+  <si>
+    <t>EQUIP_ITEM</t>
+  </si>
+  <si>
+    <t>Equip Item</t>
+  </si>
+  <si>
+    <t>装备物品</t>
+  </si>
+  <si>
+    <t>EQUIP_ITEM_DESC</t>
+  </si>
+  <si>
+    <t>Equip a piece of equipment onto the player.</t>
+  </si>
+  <si>
+    <t>将装备穿戴到玩家身上</t>
+  </si>
+  <si>
+    <t>UNEQUIP_SLOT</t>
+  </si>
+  <si>
+    <t>Unequip Slot</t>
+  </si>
+  <si>
+    <t>卸下装备栏</t>
+  </si>
+  <si>
+    <t>UNEQUIP_SLOT_DESC</t>
+  </si>
+  <si>
+    <t>Unequip the item occupying the given equipment slot.</t>
+  </si>
+  <si>
+    <t>卸下指定装备栏中的装备</t>
+  </si>
+  <si>
+    <t>GET_EQUIP_IN_SLOT</t>
+  </si>
+  <si>
+    <t>Get Equip In Slot</t>
+  </si>
+  <si>
+    <t>获取装备栏中的装备</t>
+  </si>
+  <si>
+    <t>GET_EQUIP_IN_SLOT_DESC</t>
+  </si>
+  <si>
+    <t>Get the equip ID in the specified slot, or empty string if the slot is empty.</t>
+  </si>
+  <si>
+    <t>获取指定装备栏中当前装备的ID，空栏返回空字符串</t>
+  </si>
+  <si>
+    <t>GET_PLAYER_ATTR</t>
+  </si>
+  <si>
+    <t>Get Player Attribute</t>
+  </si>
+  <si>
+    <t>获取玩家属性</t>
+  </si>
+  <si>
+    <t>GET_PLAYER_ATTR_DESC</t>
+  </si>
+  <si>
+    <t>Get a named attribute from the player (e.g. HP, MAXHP, ATK, DEF, GOLD, EXP, LEVEL).</t>
+  </si>
+  <si>
+    <t>获取玩家指定属性值（如 HP/MAXHP/ATK/DEF/GOLD/EXP/LEVEL）</t>
+  </si>
+  <si>
+    <t>SET_PLAYER_ATTR</t>
+  </si>
+  <si>
+    <t>Set Player Attribute</t>
+  </si>
+  <si>
+    <t>设置玩家属性</t>
+  </si>
+  <si>
+    <t>SET_PLAYER_ATTR_DESC</t>
+  </si>
+  <si>
+    <t>Set a named attribute on the player (e.g. HP, MAXHP, ATK, DEF, GOLD, EXP, LEVEL).</t>
+  </si>
+  <si>
+    <t>设置玩家指定属性值（如 HP/MAXHP/ATK/DEF/GOLD/EXP/LEVEL）</t>
+  </si>
+  <si>
+    <t>HEAL_PLAYER</t>
+  </si>
+  <si>
+    <t>Heal Player</t>
+  </si>
+  <si>
+    <t>回复玩家HP</t>
+  </si>
+  <si>
+    <t>HEAL_PLAYER_DESC</t>
+  </si>
+  <si>
+    <t>Restore HP to the player, capped at MAXHP.</t>
+  </si>
+  <si>
+    <t>恢复玩家生命值，上限为最大生命值</t>
+  </si>
+  <si>
+    <t>DAMAGE_PLAYER</t>
+  </si>
+  <si>
+    <t>Damage Player</t>
+  </si>
+  <si>
+    <t>对玩家造成伤害</t>
+  </si>
+  <si>
+    <t>DAMAGE_PLAYER_DESC</t>
+  </si>
+  <si>
+    <t>Deal damage to the player, floored at 0.</t>
+  </si>
+  <si>
+    <t>减少玩家生命值，下限为0</t>
+  </si>
+  <si>
+    <t>ADD_GOLD</t>
+  </si>
+  <si>
+    <t>Add Gold</t>
+  </si>
+  <si>
+    <t>增加金币</t>
+  </si>
+  <si>
+    <t>ADD_GOLD_DESC</t>
+  </si>
+  <si>
+    <t>Add gold to the player (can be negative to subtract).</t>
+  </si>
+  <si>
+    <t>为玩家增加（或减少）金币</t>
+  </si>
+  <si>
+    <t>ADD_EXP</t>
+  </si>
+  <si>
+    <t>Add EXP</t>
+  </si>
+  <si>
+    <t>增加经验值</t>
+  </si>
+  <si>
+    <t>ADD_EXP_DESC</t>
+  </si>
+  <si>
+    <t>Add experience points to the player.</t>
+  </si>
+  <si>
+    <t>为玩家增加经验值</t>
+  </si>
+  <si>
+    <t>SAVE_GAME</t>
+  </si>
+  <si>
+    <t>Save Game</t>
+  </si>
+  <si>
+    <t>保存游戏</t>
+  </si>
+  <si>
+    <t>SAVE_GAME_DESC</t>
+  </si>
+  <si>
+    <t>Save the current game state to a file (.json or .dat).</t>
+  </si>
+  <si>
+    <t>将当前游戏状态保存至文件（.json 或 .dat）</t>
+  </si>
+  <si>
+    <t>LOAD_GAME</t>
+  </si>
+  <si>
+    <t>Load Game</t>
+  </si>
+  <si>
+    <t>读取游戏</t>
+  </si>
+  <si>
+    <t>LOAD_GAME_DESC</t>
+  </si>
+  <si>
+    <t>Load game state from a file and apply it to the current scene.</t>
+  </si>
+  <si>
+    <t>从文件读取游戏状态并应用到当前场景</t>
+  </si>
+  <si>
+    <t>GET_SAVE_PATH</t>
+  </si>
+  <si>
+    <t>Get Save Path</t>
+  </si>
+  <si>
+    <t>获取存档路径</t>
+  </si>
+  <si>
+    <t>GET_SAVE_PATH_DESC</t>
+  </si>
+  <si>
+    <t>Get the platform-specific save file path for a given slot.</t>
+  </si>
+  <si>
+    <t>获取指定存档槽的平台存储路径</t>
+  </si>
+  <si>
+    <t>GOTO_MAP</t>
+  </si>
+  <si>
+    <t>Go to Map</t>
+  </si>
+  <si>
+    <t>跳转地图</t>
+  </si>
+  <si>
+    <t>GOTO_MAP_DESC</t>
+  </si>
+  <si>
+    <t>Transition to a map and optionally place the player at (x, y).</t>
+  </si>
+  <si>
+    <t>切换到指定地图，并可选择设置玩家位置</t>
+  </si>
+  <si>
     <t>PRINT</t>
   </si>
   <si>
@@ -2431,6 +2934,15 @@
     <t>立即停止正在进行的画面抖动效果。</t>
   </si>
   <si>
+    <t>ITEM_NEW</t>
+  </si>
+  <si>
+    <t>Got #FFD966#{name}#default#!\n{desc}</t>
+  </si>
+  <si>
+    <t>获得了#FFD966#{name}#default#！\n{desc}</t>
+  </si>
+  <si>
     <t>KEY_Y</t>
   </si>
   <si>
@@ -2485,6 +2997,24 @@
     <t>可以打开一扇红门</t>
   </si>
   <si>
+    <t>ENEMY_BOOK</t>
+  </si>
+  <si>
+    <t>Enemy Book</t>
+  </si>
+  <si>
+    <t>怪物手册</t>
+  </si>
+  <si>
+    <t>ENEMY_BOOK_DESC</t>
+  </si>
+  <si>
+    <t>You can view the info of enemies with it(Hotkey: D).</t>
+  </si>
+  <si>
+    <t>持有后可以查看敌人信息（快捷键D）</t>
+  </si>
+  <si>
     <t>SKELETON_SODIER</t>
   </si>
   <si>
@@ -2521,144 +3051,58 @@
     <t>这是一个史莱姆</t>
   </si>
   <si>
-    <t>MENU_ITEM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Items</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>物品道具</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MENU_EQUIP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equipments</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>装备</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MENU_SAVE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>存档</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Save File</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>读档</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回到标题</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MENU_LOAD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Load File</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MENU_EXIT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Exit Game</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TITLE_START</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TITLE_CONTINUE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TITLE_CONFIG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TITLE_EXIT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Start Game</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>开始游戏</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>继续游戏</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>设置</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>退出游戏</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Continue</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Config</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ITEM_NEW</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Got {name}!\n{desc}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得了{name}！\n{desc}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ENEMY_BOOK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ENEMY_BOOK_DESC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>持有后可以查看敌人信息（快捷键D）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>You can view the info of enemies with it(Hotkey: D).</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enemy Book</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>怪物手册</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>SWORD_A</t>
+  </si>
+  <si>
+    <t>Ironic Sword</t>
+  </si>
+  <si>
+    <t>铁剑</t>
+  </si>
+  <si>
+    <t>SWORD_A_DESC</t>
+  </si>
+  <si>
+    <t>A sword made by iron, it could bring 10 ATK when it's equipped.</t>
+  </si>
+  <si>
+    <t>铁制造的剑，装备后可提升10攻击力</t>
+  </si>
+  <si>
+    <t>SHIELD_A</t>
+  </si>
+  <si>
+    <t>Ironic Shield</t>
+  </si>
+  <si>
+    <t>铁盾</t>
+  </si>
+  <si>
+    <t>SHIELD_A_DESC</t>
+  </si>
+  <si>
+    <t>A shield made by iron, it could bring 10 DEF when it's equipped.</t>
+  </si>
+  <si>
+    <t>铁制造的盾，装备后可提升10防御力</t>
+  </si>
+  <si>
+    <t>WARRIOR</t>
+  </si>
+  <si>
+    <t>Warrior</t>
+  </si>
+  <si>
+    <t>战士</t>
+  </si>
+  <si>
+    <t>WARRIOR_DESC</t>
+  </si>
+  <si>
+    <t>A brave warrior with relatively balanced abilities.</t>
+  </si>
+  <si>
+    <t>勇猛的战士，具有比较均衡的能力</t>
   </si>
 </sst>
 </file>
@@ -2991,7 +3435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C274"/>
+  <dimension ref="A1:C316"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38.75" customWidth="1"/>
@@ -3012,3005 +3456,3467 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>170</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>171</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>173</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>174</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>176</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>177</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>179</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>180</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>182</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>183</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>185</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>186</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>188</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>189</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>191</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>192</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>194</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>195</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>197</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>198</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>200</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>201</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>203</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>204</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>206</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>207</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>209</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>210</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>211</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>45</v>
+        <v>212</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>213</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>214</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>215</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>216</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>217</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>218</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>219</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>220</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>221</v>
       </c>
       <c r="B19" t="s">
-        <v>55</v>
+        <v>222</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>57</v>
+        <v>224</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>225</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
+        <v>226</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>60</v>
+        <v>227</v>
       </c>
       <c r="B21" t="s">
-        <v>61</v>
+        <v>228</v>
       </c>
       <c r="C21" t="s">
-        <v>62</v>
+        <v>229</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>63</v>
+        <v>230</v>
       </c>
       <c r="B22" t="s">
-        <v>64</v>
+        <v>231</v>
       </c>
       <c r="C22" t="s">
-        <v>65</v>
+        <v>232</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>66</v>
+        <v>233</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>234</v>
       </c>
       <c r="C23" t="s">
-        <v>68</v>
+        <v>235</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>69</v>
+        <v>236</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>237</v>
       </c>
       <c r="C24" t="s">
-        <v>71</v>
+        <v>238</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>72</v>
+        <v>239</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
+        <v>240</v>
       </c>
       <c r="C25" t="s">
-        <v>74</v>
+        <v>241</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>75</v>
+        <v>242</v>
       </c>
       <c r="B26" t="s">
-        <v>76</v>
+        <v>243</v>
       </c>
       <c r="C26" t="s">
-        <v>77</v>
+        <v>244</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>78</v>
+        <v>245</v>
       </c>
       <c r="B27" t="s">
-        <v>79</v>
+        <v>246</v>
       </c>
       <c r="C27" t="s">
-        <v>80</v>
+        <v>247</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>81</v>
+        <v>248</v>
       </c>
       <c r="B28" t="s">
-        <v>82</v>
+        <v>249</v>
       </c>
       <c r="C28" t="s">
-        <v>83</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>84</v>
+        <v>251</v>
       </c>
       <c r="B29" t="s">
-        <v>85</v>
+        <v>252</v>
       </c>
       <c r="C29" t="s">
-        <v>86</v>
+        <v>253</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>87</v>
+        <v>254</v>
       </c>
       <c r="B30" t="s">
-        <v>88</v>
+        <v>255</v>
       </c>
       <c r="C30" t="s">
-        <v>89</v>
+        <v>256</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>90</v>
+        <v>257</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>258</v>
       </c>
       <c r="C31" t="s">
-        <v>92</v>
+        <v>259</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>93</v>
+        <v>260</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>261</v>
       </c>
       <c r="C32" t="s">
-        <v>95</v>
+        <v>262</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>96</v>
+        <v>263</v>
       </c>
       <c r="B33" t="s">
-        <v>97</v>
+        <v>264</v>
       </c>
       <c r="C33" t="s">
-        <v>98</v>
+        <v>265</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>99</v>
+        <v>266</v>
       </c>
       <c r="B34" t="s">
-        <v>100</v>
+        <v>267</v>
       </c>
       <c r="C34" t="s">
-        <v>101</v>
+        <v>268</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>102</v>
+        <v>269</v>
       </c>
       <c r="B35" t="s">
-        <v>103</v>
+        <v>270</v>
       </c>
       <c r="C35" t="s">
-        <v>104</v>
+        <v>271</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>105</v>
+        <v>272</v>
       </c>
       <c r="B36" t="s">
-        <v>106</v>
+        <v>273</v>
       </c>
       <c r="C36" t="s">
-        <v>107</v>
+        <v>274</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>108</v>
+        <v>275</v>
       </c>
       <c r="B37" t="s">
-        <v>109</v>
+        <v>276</v>
       </c>
       <c r="C37" t="s">
-        <v>110</v>
+        <v>277</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>111</v>
+        <v>278</v>
       </c>
       <c r="B38" t="s">
-        <v>112</v>
+        <v>279</v>
       </c>
       <c r="C38" t="s">
-        <v>113</v>
+        <v>280</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>114</v>
+        <v>281</v>
       </c>
       <c r="B39" t="s">
-        <v>115</v>
+        <v>282</v>
       </c>
       <c r="C39" t="s">
-        <v>116</v>
+        <v>283</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>117</v>
+        <v>284</v>
       </c>
       <c r="B40" t="s">
-        <v>118</v>
+        <v>285</v>
       </c>
       <c r="C40" t="s">
-        <v>119</v>
+        <v>286</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>120</v>
+        <v>287</v>
       </c>
       <c r="B41" t="s">
-        <v>121</v>
+        <v>288</v>
       </c>
       <c r="C41" t="s">
-        <v>122</v>
+        <v>289</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>123</v>
+        <v>290</v>
       </c>
       <c r="B42" t="s">
-        <v>124</v>
+        <v>291</v>
       </c>
       <c r="C42" t="s">
-        <v>125</v>
+        <v>292</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>126</v>
+        <v>293</v>
       </c>
       <c r="B43" t="s">
-        <v>127</v>
+        <v>294</v>
       </c>
       <c r="C43" t="s">
-        <v>128</v>
+        <v>295</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>129</v>
+        <v>296</v>
       </c>
       <c r="B44" t="s">
-        <v>130</v>
+        <v>297</v>
       </c>
       <c r="C44" t="s">
-        <v>131</v>
+        <v>298</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>132</v>
+        <v>299</v>
       </c>
       <c r="B45" t="s">
-        <v>133</v>
+        <v>300</v>
       </c>
       <c r="C45" t="s">
-        <v>134</v>
+        <v>301</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>135</v>
+        <v>302</v>
       </c>
       <c r="B46" t="s">
-        <v>136</v>
+        <v>303</v>
       </c>
       <c r="C46" t="s">
-        <v>137</v>
+        <v>304</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>138</v>
+        <v>305</v>
       </c>
       <c r="B47" t="s">
-        <v>139</v>
+        <v>306</v>
       </c>
       <c r="C47" t="s">
-        <v>140</v>
+        <v>307</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>141</v>
+        <v>308</v>
       </c>
       <c r="B48" t="s">
-        <v>142</v>
+        <v>309</v>
       </c>
       <c r="C48" t="s">
-        <v>143</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>144</v>
+        <v>311</v>
       </c>
       <c r="B49" t="s">
-        <v>145</v>
+        <v>312</v>
       </c>
       <c r="C49" t="s">
-        <v>146</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>147</v>
+        <v>314</v>
       </c>
       <c r="B50" t="s">
-        <v>148</v>
+        <v>315</v>
       </c>
       <c r="C50" t="s">
-        <v>149</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>150</v>
+        <v>317</v>
       </c>
       <c r="B51" t="s">
-        <v>151</v>
+        <v>318</v>
       </c>
       <c r="C51" t="s">
-        <v>152</v>
+        <v>319</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>153</v>
+        <v>320</v>
       </c>
       <c r="B52" t="s">
-        <v>154</v>
+        <v>321</v>
       </c>
       <c r="C52" t="s">
-        <v>155</v>
+        <v>322</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>156</v>
+        <v>323</v>
       </c>
       <c r="B53" t="s">
-        <v>157</v>
+        <v>324</v>
       </c>
       <c r="C53" t="s">
-        <v>158</v>
+        <v>325</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>159</v>
+        <v>326</v>
       </c>
       <c r="B54" t="s">
-        <v>160</v>
+        <v>327</v>
       </c>
       <c r="C54" t="s">
-        <v>161</v>
+        <v>328</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>162</v>
+        <v>329</v>
       </c>
       <c r="B55" t="s">
-        <v>163</v>
+        <v>330</v>
       </c>
       <c r="C55" t="s">
-        <v>164</v>
+        <v>331</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>165</v>
+        <v>332</v>
       </c>
       <c r="B56" t="s">
-        <v>166</v>
+        <v>333</v>
       </c>
       <c r="C56" t="s">
-        <v>167</v>
+        <v>334</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>168</v>
+        <v>335</v>
       </c>
       <c r="B57" t="s">
-        <v>169</v>
+        <v>336</v>
       </c>
       <c r="C57" t="s">
-        <v>170</v>
+        <v>337</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>171</v>
+        <v>338</v>
       </c>
       <c r="B58" t="s">
-        <v>172</v>
+        <v>339</v>
       </c>
       <c r="C58" t="s">
-        <v>173</v>
+        <v>340</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>174</v>
+        <v>341</v>
       </c>
       <c r="B59" t="s">
-        <v>175</v>
+        <v>342</v>
       </c>
       <c r="C59" t="s">
-        <v>176</v>
+        <v>343</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>177</v>
+        <v>344</v>
       </c>
       <c r="B60" t="s">
-        <v>178</v>
+        <v>345</v>
       </c>
       <c r="C60" t="s">
-        <v>179</v>
+        <v>346</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>180</v>
+        <v>347</v>
       </c>
       <c r="B61" t="s">
-        <v>181</v>
+        <v>348</v>
       </c>
       <c r="C61" t="s">
-        <v>182</v>
+        <v>349</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>183</v>
+        <v>350</v>
       </c>
       <c r="B62" t="s">
-        <v>184</v>
+        <v>351</v>
       </c>
       <c r="C62" t="s">
-        <v>185</v>
+        <v>352</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>186</v>
+        <v>353</v>
       </c>
       <c r="B63" t="s">
-        <v>187</v>
+        <v>354</v>
       </c>
       <c r="C63" t="s">
-        <v>188</v>
+        <v>355</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>189</v>
+        <v>356</v>
       </c>
       <c r="B64" t="s">
-        <v>190</v>
+        <v>357</v>
       </c>
       <c r="C64" t="s">
-        <v>191</v>
+        <v>358</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>192</v>
+        <v>359</v>
       </c>
       <c r="B65" t="s">
-        <v>193</v>
+        <v>360</v>
       </c>
       <c r="C65" t="s">
-        <v>194</v>
+        <v>361</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>195</v>
+        <v>362</v>
       </c>
       <c r="B66" t="s">
-        <v>196</v>
+        <v>363</v>
       </c>
       <c r="C66" t="s">
-        <v>197</v>
+        <v>364</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>198</v>
+        <v>365</v>
       </c>
       <c r="B67" t="s">
-        <v>199</v>
+        <v>366</v>
       </c>
       <c r="C67" t="s">
-        <v>200</v>
+        <v>367</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>201</v>
+        <v>368</v>
       </c>
       <c r="B68" t="s">
-        <v>202</v>
+        <v>369</v>
       </c>
       <c r="C68" t="s">
-        <v>203</v>
+        <v>370</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>204</v>
+        <v>371</v>
       </c>
       <c r="B69" t="s">
-        <v>205</v>
+        <v>372</v>
       </c>
       <c r="C69" t="s">
-        <v>206</v>
+        <v>373</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>207</v>
+        <v>374</v>
       </c>
       <c r="B70" t="s">
-        <v>208</v>
+        <v>375</v>
       </c>
       <c r="C70" t="s">
-        <v>209</v>
+        <v>376</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>210</v>
+        <v>377</v>
       </c>
       <c r="B71" t="s">
-        <v>211</v>
+        <v>378</v>
       </c>
       <c r="C71" t="s">
-        <v>212</v>
+        <v>379</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>213</v>
+        <v>380</v>
       </c>
       <c r="B72" t="s">
-        <v>214</v>
+        <v>381</v>
       </c>
       <c r="C72" t="s">
-        <v>215</v>
+        <v>382</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>216</v>
+        <v>383</v>
       </c>
       <c r="B73" t="s">
-        <v>217</v>
+        <v>384</v>
       </c>
       <c r="C73" t="s">
-        <v>218</v>
+        <v>385</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>219</v>
+        <v>386</v>
       </c>
       <c r="B74" t="s">
-        <v>220</v>
+        <v>387</v>
       </c>
       <c r="C74" t="s">
-        <v>221</v>
+        <v>388</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>222</v>
+        <v>389</v>
       </c>
       <c r="B75" t="s">
-        <v>223</v>
+        <v>390</v>
       </c>
       <c r="C75" t="s">
-        <v>224</v>
+        <v>391</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>225</v>
+        <v>392</v>
       </c>
       <c r="B76" t="s">
-        <v>226</v>
+        <v>393</v>
       </c>
       <c r="C76" t="s">
-        <v>227</v>
+        <v>394</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>228</v>
+        <v>395</v>
       </c>
       <c r="B77" t="s">
-        <v>229</v>
+        <v>396</v>
       </c>
       <c r="C77" t="s">
-        <v>230</v>
+        <v>397</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>231</v>
+        <v>398</v>
       </c>
       <c r="B78" t="s">
-        <v>232</v>
+        <v>399</v>
       </c>
       <c r="C78" t="s">
-        <v>233</v>
+        <v>400</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>234</v>
+        <v>401</v>
       </c>
       <c r="B79" t="s">
-        <v>235</v>
+        <v>402</v>
       </c>
       <c r="C79" t="s">
-        <v>236</v>
+        <v>403</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>237</v>
+        <v>404</v>
       </c>
       <c r="B80" t="s">
-        <v>238</v>
+        <v>405</v>
       </c>
       <c r="C80" t="s">
-        <v>239</v>
+        <v>406</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>240</v>
+        <v>407</v>
       </c>
       <c r="B81" t="s">
-        <v>241</v>
+        <v>408</v>
       </c>
       <c r="C81" t="s">
-        <v>242</v>
+        <v>409</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>243</v>
+        <v>410</v>
       </c>
       <c r="B82" t="s">
-        <v>244</v>
+        <v>411</v>
       </c>
       <c r="C82" t="s">
-        <v>245</v>
+        <v>412</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>246</v>
+        <v>413</v>
       </c>
       <c r="B83" t="s">
-        <v>247</v>
+        <v>414</v>
       </c>
       <c r="C83" t="s">
-        <v>248</v>
+        <v>415</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>249</v>
+        <v>416</v>
       </c>
       <c r="B84" t="s">
-        <v>250</v>
+        <v>417</v>
       </c>
       <c r="C84" t="s">
-        <v>251</v>
+        <v>418</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>252</v>
+        <v>419</v>
       </c>
       <c r="B85" t="s">
-        <v>253</v>
+        <v>420</v>
       </c>
       <c r="C85" t="s">
-        <v>254</v>
+        <v>421</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>255</v>
+        <v>422</v>
       </c>
       <c r="B86" t="s">
-        <v>256</v>
+        <v>423</v>
       </c>
       <c r="C86" t="s">
-        <v>257</v>
+        <v>424</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>258</v>
+        <v>425</v>
       </c>
       <c r="B87" t="s">
-        <v>259</v>
+        <v>426</v>
       </c>
       <c r="C87" t="s">
-        <v>260</v>
+        <v>427</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>261</v>
+        <v>428</v>
       </c>
       <c r="B88" t="s">
-        <v>262</v>
+        <v>429</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>430</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>264</v>
+        <v>431</v>
       </c>
       <c r="B89" t="s">
-        <v>265</v>
+        <v>432</v>
       </c>
       <c r="C89" t="s">
-        <v>266</v>
+        <v>433</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>267</v>
+        <v>434</v>
       </c>
       <c r="B90" t="s">
-        <v>268</v>
+        <v>435</v>
       </c>
       <c r="C90" t="s">
-        <v>269</v>
+        <v>436</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>270</v>
+        <v>437</v>
       </c>
       <c r="B91" t="s">
-        <v>271</v>
+        <v>438</v>
       </c>
       <c r="C91" t="s">
-        <v>272</v>
+        <v>439</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>273</v>
+        <v>440</v>
       </c>
       <c r="B92" t="s">
-        <v>274</v>
+        <v>441</v>
       </c>
       <c r="C92" t="s">
-        <v>275</v>
+        <v>442</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>276</v>
+        <v>443</v>
       </c>
       <c r="B93" t="s">
-        <v>277</v>
+        <v>444</v>
       </c>
       <c r="C93" t="s">
-        <v>278</v>
+        <v>445</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>279</v>
+        <v>446</v>
       </c>
       <c r="B94" t="s">
-        <v>280</v>
+        <v>447</v>
       </c>
       <c r="C94" t="s">
-        <v>281</v>
+        <v>448</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>282</v>
+        <v>449</v>
       </c>
       <c r="B95" t="s">
-        <v>283</v>
+        <v>450</v>
       </c>
       <c r="C95" t="s">
-        <v>284</v>
+        <v>451</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>285</v>
+        <v>452</v>
       </c>
       <c r="B96" t="s">
-        <v>286</v>
+        <v>453</v>
       </c>
       <c r="C96" t="s">
-        <v>287</v>
+        <v>454</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>288</v>
+        <v>455</v>
       </c>
       <c r="B97" t="s">
-        <v>289</v>
+        <v>456</v>
       </c>
       <c r="C97" t="s">
-        <v>290</v>
+        <v>457</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>291</v>
+        <v>458</v>
       </c>
       <c r="B98" t="s">
-        <v>292</v>
+        <v>459</v>
       </c>
       <c r="C98" t="s">
-        <v>293</v>
+        <v>460</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>294</v>
+        <v>461</v>
       </c>
       <c r="B99" t="s">
-        <v>295</v>
+        <v>462</v>
       </c>
       <c r="C99" t="s">
-        <v>296</v>
+        <v>463</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>297</v>
+        <v>464</v>
       </c>
       <c r="B100" t="s">
-        <v>298</v>
+        <v>465</v>
       </c>
       <c r="C100" t="s">
-        <v>299</v>
+        <v>466</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>300</v>
+        <v>467</v>
       </c>
       <c r="B101" t="s">
-        <v>301</v>
+        <v>468</v>
       </c>
       <c r="C101" t="s">
-        <v>302</v>
+        <v>469</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>303</v>
+        <v>470</v>
       </c>
       <c r="B102" t="s">
-        <v>304</v>
+        <v>471</v>
       </c>
       <c r="C102" t="s">
-        <v>305</v>
+        <v>472</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>306</v>
+        <v>473</v>
       </c>
       <c r="B103" t="s">
-        <v>307</v>
+        <v>474</v>
       </c>
       <c r="C103" t="s">
-        <v>308</v>
+        <v>475</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>309</v>
+        <v>476</v>
       </c>
       <c r="B104" t="s">
-        <v>310</v>
+        <v>477</v>
       </c>
       <c r="C104" t="s">
-        <v>311</v>
+        <v>478</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>312</v>
+        <v>479</v>
       </c>
       <c r="B105" t="s">
-        <v>313</v>
+        <v>480</v>
       </c>
       <c r="C105" t="s">
-        <v>314</v>
+        <v>481</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>315</v>
+        <v>482</v>
       </c>
       <c r="B106" t="s">
-        <v>316</v>
+        <v>483</v>
       </c>
       <c r="C106" t="s">
-        <v>317</v>
+        <v>484</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>318</v>
+        <v>485</v>
       </c>
       <c r="B107" t="s">
-        <v>319</v>
+        <v>486</v>
       </c>
       <c r="C107" t="s">
-        <v>320</v>
+        <v>487</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>321</v>
+        <v>488</v>
       </c>
       <c r="B108" t="s">
-        <v>322</v>
+        <v>489</v>
       </c>
       <c r="C108" t="s">
-        <v>323</v>
+        <v>490</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>324</v>
+        <v>491</v>
       </c>
       <c r="B109" t="s">
-        <v>325</v>
+        <v>492</v>
       </c>
       <c r="C109" t="s">
-        <v>326</v>
+        <v>493</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>327</v>
+        <v>494</v>
       </c>
       <c r="B110" t="s">
-        <v>328</v>
+        <v>495</v>
       </c>
       <c r="C110" t="s">
-        <v>329</v>
+        <v>496</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>330</v>
+        <v>497</v>
       </c>
       <c r="B111" t="s">
-        <v>331</v>
+        <v>498</v>
       </c>
       <c r="C111" t="s">
-        <v>332</v>
+        <v>499</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>333</v>
+        <v>500</v>
       </c>
       <c r="B112" t="s">
-        <v>334</v>
+        <v>501</v>
       </c>
       <c r="C112" t="s">
-        <v>335</v>
+        <v>502</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>336</v>
+        <v>503</v>
       </c>
       <c r="B113" t="s">
-        <v>337</v>
+        <v>504</v>
       </c>
       <c r="C113" t="s">
-        <v>338</v>
+        <v>505</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>339</v>
+        <v>506</v>
       </c>
       <c r="B114" t="s">
-        <v>340</v>
+        <v>507</v>
       </c>
       <c r="C114" t="s">
-        <v>341</v>
+        <v>508</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>342</v>
+        <v>509</v>
       </c>
       <c r="B115" t="s">
-        <v>343</v>
+        <v>510</v>
       </c>
       <c r="C115" t="s">
-        <v>344</v>
+        <v>511</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>345</v>
+        <v>512</v>
       </c>
       <c r="B116" t="s">
-        <v>346</v>
+        <v>513</v>
       </c>
       <c r="C116" t="s">
-        <v>347</v>
+        <v>514</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>348</v>
+        <v>515</v>
       </c>
       <c r="B117" t="s">
-        <v>349</v>
+        <v>516</v>
       </c>
       <c r="C117" t="s">
-        <v>350</v>
+        <v>517</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>351</v>
+        <v>518</v>
       </c>
       <c r="B118" t="s">
-        <v>352</v>
+        <v>519</v>
       </c>
       <c r="C118" t="s">
-        <v>353</v>
+        <v>520</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>354</v>
+        <v>521</v>
       </c>
       <c r="B119" t="s">
-        <v>355</v>
+        <v>522</v>
       </c>
       <c r="C119" t="s">
-        <v>356</v>
+        <v>523</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>357</v>
+        <v>524</v>
       </c>
       <c r="B120" t="s">
-        <v>358</v>
+        <v>525</v>
       </c>
       <c r="C120" t="s">
-        <v>359</v>
+        <v>526</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>360</v>
+        <v>527</v>
       </c>
       <c r="B121" t="s">
-        <v>361</v>
+        <v>528</v>
       </c>
       <c r="C121" t="s">
-        <v>362</v>
+        <v>529</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>363</v>
+        <v>530</v>
       </c>
       <c r="B122" t="s">
-        <v>364</v>
+        <v>531</v>
       </c>
       <c r="C122" t="s">
-        <v>365</v>
+        <v>532</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>366</v>
+        <v>533</v>
       </c>
       <c r="B123" t="s">
-        <v>367</v>
+        <v>534</v>
       </c>
       <c r="C123" t="s">
-        <v>368</v>
+        <v>535</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>369</v>
+        <v>536</v>
       </c>
       <c r="B124" t="s">
-        <v>370</v>
+        <v>537</v>
       </c>
       <c r="C124" t="s">
-        <v>371</v>
+        <v>538</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>372</v>
+        <v>539</v>
       </c>
       <c r="B125" t="s">
-        <v>373</v>
+        <v>540</v>
       </c>
       <c r="C125" t="s">
-        <v>374</v>
+        <v>541</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>375</v>
+        <v>542</v>
       </c>
       <c r="B126" t="s">
-        <v>376</v>
+        <v>543</v>
       </c>
       <c r="C126" t="s">
-        <v>377</v>
+        <v>544</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>378</v>
+        <v>545</v>
       </c>
       <c r="B127" t="s">
-        <v>379</v>
+        <v>546</v>
       </c>
       <c r="C127" t="s">
-        <v>380</v>
+        <v>547</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>381</v>
+        <v>548</v>
       </c>
       <c r="B128" t="s">
-        <v>382</v>
+        <v>549</v>
       </c>
       <c r="C128" t="s">
-        <v>383</v>
+        <v>550</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>384</v>
+        <v>551</v>
       </c>
       <c r="B129" t="s">
-        <v>385</v>
+        <v>552</v>
       </c>
       <c r="C129" t="s">
-        <v>386</v>
+        <v>553</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>387</v>
+        <v>554</v>
       </c>
       <c r="B130" t="s">
-        <v>388</v>
+        <v>555</v>
       </c>
       <c r="C130" t="s">
-        <v>389</v>
+        <v>556</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>390</v>
+        <v>557</v>
       </c>
       <c r="B131" t="s">
-        <v>391</v>
+        <v>558</v>
       </c>
       <c r="C131" t="s">
-        <v>392</v>
+        <v>559</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>393</v>
+        <v>560</v>
       </c>
       <c r="B132" t="s">
-        <v>394</v>
+        <v>561</v>
       </c>
       <c r="C132" t="s">
-        <v>395</v>
+        <v>562</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>396</v>
+        <v>563</v>
       </c>
       <c r="B133" t="s">
-        <v>397</v>
+        <v>564</v>
       </c>
       <c r="C133" t="s">
-        <v>398</v>
+        <v>565</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>399</v>
+        <v>566</v>
       </c>
       <c r="B134" t="s">
-        <v>400</v>
+        <v>567</v>
       </c>
       <c r="C134" t="s">
-        <v>401</v>
+        <v>568</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>402</v>
+        <v>569</v>
       </c>
       <c r="B135" t="s">
-        <v>403</v>
+        <v>570</v>
       </c>
       <c r="C135" t="s">
-        <v>404</v>
+        <v>571</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>405</v>
+        <v>572</v>
       </c>
       <c r="B136" t="s">
-        <v>406</v>
+        <v>573</v>
       </c>
       <c r="C136" t="s">
-        <v>407</v>
+        <v>574</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>408</v>
+        <v>575</v>
       </c>
       <c r="B137" t="s">
-        <v>409</v>
+        <v>576</v>
       </c>
       <c r="C137" t="s">
-        <v>410</v>
+        <v>577</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>411</v>
+        <v>578</v>
       </c>
       <c r="B138" t="s">
-        <v>412</v>
+        <v>579</v>
       </c>
       <c r="C138" t="s">
-        <v>413</v>
+        <v>580</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>414</v>
+        <v>581</v>
       </c>
       <c r="B139" t="s">
-        <v>415</v>
+        <v>582</v>
       </c>
       <c r="C139" t="s">
-        <v>416</v>
+        <v>583</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>417</v>
+        <v>584</v>
       </c>
       <c r="B140" t="s">
-        <v>418</v>
+        <v>585</v>
       </c>
       <c r="C140" t="s">
-        <v>419</v>
+        <v>586</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>420</v>
+        <v>587</v>
       </c>
       <c r="B141" t="s">
-        <v>421</v>
+        <v>588</v>
       </c>
       <c r="C141" t="s">
-        <v>422</v>
+        <v>589</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>423</v>
+        <v>590</v>
       </c>
       <c r="B142" t="s">
-        <v>424</v>
+        <v>591</v>
       </c>
       <c r="C142" t="s">
-        <v>425</v>
+        <v>592</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>426</v>
+        <v>593</v>
       </c>
       <c r="B143" t="s">
-        <v>427</v>
+        <v>594</v>
       </c>
       <c r="C143" t="s">
-        <v>428</v>
+        <v>595</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>429</v>
+        <v>596</v>
       </c>
       <c r="B144" t="s">
-        <v>430</v>
+        <v>597</v>
       </c>
       <c r="C144" t="s">
-        <v>431</v>
+        <v>598</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>432</v>
+        <v>599</v>
       </c>
       <c r="B145" t="s">
-        <v>433</v>
+        <v>600</v>
       </c>
       <c r="C145" t="s">
-        <v>434</v>
+        <v>601</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>435</v>
+        <v>602</v>
       </c>
       <c r="B146" t="s">
-        <v>436</v>
+        <v>603</v>
       </c>
       <c r="C146" t="s">
-        <v>437</v>
+        <v>604</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>438</v>
+        <v>605</v>
       </c>
       <c r="B147" t="s">
-        <v>439</v>
+        <v>606</v>
       </c>
       <c r="C147" t="s">
-        <v>440</v>
+        <v>607</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>441</v>
+        <v>608</v>
       </c>
       <c r="B148" t="s">
-        <v>442</v>
+        <v>609</v>
       </c>
       <c r="C148" t="s">
-        <v>443</v>
+        <v>610</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>444</v>
+        <v>611</v>
       </c>
       <c r="B149" t="s">
-        <v>445</v>
+        <v>612</v>
       </c>
       <c r="C149" t="s">
-        <v>446</v>
+        <v>613</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>447</v>
+        <v>614</v>
       </c>
       <c r="B150" t="s">
-        <v>448</v>
+        <v>615</v>
       </c>
       <c r="C150" t="s">
-        <v>449</v>
+        <v>616</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>450</v>
+        <v>617</v>
       </c>
       <c r="B151" t="s">
-        <v>451</v>
+        <v>618</v>
       </c>
       <c r="C151" t="s">
-        <v>452</v>
+        <v>619</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>453</v>
+        <v>620</v>
       </c>
       <c r="B152" t="s">
-        <v>454</v>
+        <v>621</v>
       </c>
       <c r="C152" t="s">
-        <v>455</v>
+        <v>622</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>456</v>
+        <v>623</v>
       </c>
       <c r="B153" t="s">
-        <v>457</v>
+        <v>624</v>
       </c>
       <c r="C153" t="s">
-        <v>458</v>
+        <v>625</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>459</v>
+        <v>626</v>
       </c>
       <c r="B154" t="s">
-        <v>460</v>
+        <v>627</v>
       </c>
       <c r="C154" t="s">
-        <v>461</v>
+        <v>628</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>462</v>
+        <v>629</v>
       </c>
       <c r="B155" t="s">
-        <v>463</v>
+        <v>630</v>
       </c>
       <c r="C155" t="s">
-        <v>464</v>
+        <v>631</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>465</v>
+        <v>632</v>
       </c>
       <c r="B156" t="s">
-        <v>466</v>
+        <v>633</v>
       </c>
       <c r="C156" t="s">
-        <v>467</v>
+        <v>634</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>468</v>
+        <v>635</v>
       </c>
       <c r="B157" t="s">
-        <v>469</v>
+        <v>636</v>
       </c>
       <c r="C157" t="s">
-        <v>470</v>
+        <v>637</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>471</v>
+        <v>638</v>
       </c>
       <c r="B158" t="s">
-        <v>472</v>
+        <v>639</v>
       </c>
       <c r="C158" t="s">
-        <v>473</v>
+        <v>640</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>474</v>
+        <v>641</v>
       </c>
       <c r="B159" t="s">
-        <v>475</v>
+        <v>642</v>
       </c>
       <c r="C159" t="s">
-        <v>476</v>
+        <v>643</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>477</v>
+        <v>644</v>
       </c>
       <c r="B160" t="s">
-        <v>478</v>
+        <v>645</v>
       </c>
       <c r="C160" t="s">
-        <v>479</v>
+        <v>646</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>480</v>
+        <v>647</v>
       </c>
       <c r="B161" t="s">
-        <v>481</v>
+        <v>648</v>
       </c>
       <c r="C161" t="s">
-        <v>482</v>
+        <v>649</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>483</v>
+        <v>650</v>
       </c>
       <c r="B162" t="s">
-        <v>484</v>
+        <v>651</v>
       </c>
       <c r="C162" t="s">
-        <v>485</v>
+        <v>652</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>486</v>
+        <v>653</v>
       </c>
       <c r="B163" t="s">
-        <v>487</v>
+        <v>654</v>
       </c>
       <c r="C163" t="s">
-        <v>488</v>
+        <v>655</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>489</v>
+        <v>656</v>
       </c>
       <c r="B164" t="s">
-        <v>490</v>
+        <v>657</v>
       </c>
       <c r="C164" t="s">
-        <v>491</v>
+        <v>658</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>492</v>
+        <v>659</v>
       </c>
       <c r="B165" t="s">
-        <v>493</v>
+        <v>660</v>
       </c>
       <c r="C165" t="s">
-        <v>494</v>
+        <v>661</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>495</v>
+        <v>662</v>
       </c>
       <c r="B166" t="s">
-        <v>496</v>
+        <v>663</v>
       </c>
       <c r="C166" t="s">
-        <v>497</v>
+        <v>664</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>498</v>
+        <v>665</v>
       </c>
       <c r="B167" t="s">
-        <v>499</v>
+        <v>666</v>
       </c>
       <c r="C167" t="s">
-        <v>500</v>
+        <v>667</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>501</v>
+        <v>668</v>
       </c>
       <c r="B168" t="s">
-        <v>502</v>
+        <v>669</v>
       </c>
       <c r="C168" t="s">
-        <v>503</v>
+        <v>670</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>504</v>
+        <v>671</v>
       </c>
       <c r="B169" t="s">
-        <v>505</v>
+        <v>672</v>
       </c>
       <c r="C169" t="s">
-        <v>506</v>
+        <v>673</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>507</v>
+        <v>674</v>
       </c>
       <c r="B170" t="s">
-        <v>508</v>
+        <v>675</v>
       </c>
       <c r="C170" t="s">
-        <v>509</v>
+        <v>676</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>510</v>
+        <v>677</v>
       </c>
       <c r="B171" t="s">
-        <v>511</v>
+        <v>678</v>
       </c>
       <c r="C171" t="s">
-        <v>512</v>
+        <v>679</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>513</v>
+        <v>680</v>
       </c>
       <c r="B172" t="s">
-        <v>514</v>
+        <v>681</v>
       </c>
       <c r="C172" t="s">
-        <v>515</v>
+        <v>682</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>516</v>
+        <v>683</v>
       </c>
       <c r="B173" t="s">
-        <v>517</v>
+        <v>684</v>
       </c>
       <c r="C173" t="s">
-        <v>518</v>
+        <v>685</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>519</v>
+        <v>686</v>
       </c>
       <c r="B174" t="s">
-        <v>520</v>
+        <v>687</v>
       </c>
       <c r="C174" t="s">
-        <v>521</v>
+        <v>688</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>522</v>
+        <v>689</v>
       </c>
       <c r="B175" t="s">
-        <v>523</v>
+        <v>690</v>
       </c>
       <c r="C175" t="s">
-        <v>524</v>
+        <v>691</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>525</v>
+        <v>692</v>
       </c>
       <c r="B176" t="s">
-        <v>526</v>
+        <v>693</v>
       </c>
       <c r="C176" t="s">
-        <v>527</v>
+        <v>694</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>528</v>
+        <v>695</v>
       </c>
       <c r="B177" t="s">
-        <v>529</v>
+        <v>696</v>
       </c>
       <c r="C177" t="s">
-        <v>530</v>
+        <v>697</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>531</v>
+        <v>698</v>
       </c>
       <c r="B178" t="s">
-        <v>532</v>
+        <v>699</v>
       </c>
       <c r="C178" t="s">
-        <v>533</v>
+        <v>700</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>534</v>
+        <v>701</v>
       </c>
       <c r="B179" t="s">
-        <v>535</v>
+        <v>702</v>
       </c>
       <c r="C179" t="s">
-        <v>536</v>
+        <v>703</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>537</v>
+        <v>704</v>
       </c>
       <c r="B180" t="s">
-        <v>538</v>
+        <v>705</v>
       </c>
       <c r="C180" t="s">
-        <v>539</v>
+        <v>706</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>540</v>
+        <v>707</v>
       </c>
       <c r="B181" t="s">
-        <v>541</v>
+        <v>708</v>
       </c>
       <c r="C181" t="s">
-        <v>542</v>
+        <v>709</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>543</v>
+        <v>710</v>
       </c>
       <c r="B182" t="s">
-        <v>544</v>
+        <v>711</v>
       </c>
       <c r="C182" t="s">
-        <v>545</v>
+        <v>712</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>546</v>
+        <v>713</v>
       </c>
       <c r="B183" t="s">
-        <v>547</v>
+        <v>714</v>
       </c>
       <c r="C183" t="s">
-        <v>548</v>
+        <v>715</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>549</v>
+        <v>716</v>
       </c>
       <c r="B184" t="s">
-        <v>550</v>
+        <v>717</v>
       </c>
       <c r="C184" t="s">
-        <v>551</v>
+        <v>718</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>552</v>
+        <v>719</v>
       </c>
       <c r="B185" t="s">
-        <v>553</v>
+        <v>720</v>
       </c>
       <c r="C185" t="s">
-        <v>554</v>
+        <v>721</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>555</v>
+        <v>722</v>
       </c>
       <c r="B186" t="s">
-        <v>556</v>
+        <v>723</v>
       </c>
       <c r="C186" t="s">
-        <v>557</v>
+        <v>724</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>558</v>
+        <v>725</v>
       </c>
       <c r="B187" t="s">
-        <v>559</v>
+        <v>726</v>
       </c>
       <c r="C187" t="s">
-        <v>560</v>
+        <v>727</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>561</v>
+        <v>728</v>
       </c>
       <c r="B188" t="s">
-        <v>562</v>
+        <v>729</v>
       </c>
       <c r="C188" t="s">
-        <v>563</v>
+        <v>730</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>564</v>
+        <v>731</v>
       </c>
       <c r="B189" t="s">
-        <v>565</v>
+        <v>732</v>
       </c>
       <c r="C189" t="s">
-        <v>566</v>
+        <v>733</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>567</v>
+        <v>734</v>
       </c>
       <c r="B190" t="s">
-        <v>568</v>
+        <v>735</v>
       </c>
       <c r="C190" t="s">
-        <v>569</v>
+        <v>736</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>570</v>
+        <v>737</v>
       </c>
       <c r="B191" t="s">
-        <v>571</v>
+        <v>738</v>
       </c>
       <c r="C191" t="s">
-        <v>572</v>
+        <v>739</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>573</v>
+        <v>740</v>
       </c>
       <c r="B192" t="s">
-        <v>574</v>
+        <v>741</v>
       </c>
       <c r="C192" t="s">
-        <v>575</v>
+        <v>742</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>576</v>
+        <v>743</v>
       </c>
       <c r="B193" t="s">
-        <v>577</v>
+        <v>744</v>
       </c>
       <c r="C193" t="s">
-        <v>578</v>
+        <v>745</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>579</v>
+        <v>746</v>
       </c>
       <c r="B194" t="s">
-        <v>580</v>
+        <v>747</v>
       </c>
       <c r="C194" t="s">
-        <v>581</v>
+        <v>748</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>582</v>
+        <v>749</v>
       </c>
       <c r="B195" t="s">
-        <v>583</v>
+        <v>750</v>
       </c>
       <c r="C195" t="s">
-        <v>584</v>
+        <v>751</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>585</v>
+        <v>752</v>
       </c>
       <c r="B196" t="s">
-        <v>585</v>
+        <v>752</v>
       </c>
       <c r="C196" t="s">
-        <v>586</v>
+        <v>753</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>587</v>
+        <v>754</v>
       </c>
       <c r="B197" t="s">
-        <v>588</v>
+        <v>755</v>
       </c>
       <c r="C197" t="s">
-        <v>589</v>
+        <v>756</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>590</v>
+        <v>757</v>
       </c>
       <c r="B198" t="s">
-        <v>590</v>
+        <v>757</v>
       </c>
       <c r="C198" t="s">
-        <v>591</v>
+        <v>758</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>592</v>
+        <v>759</v>
       </c>
       <c r="B199" t="s">
-        <v>593</v>
+        <v>760</v>
       </c>
       <c r="C199" t="s">
-        <v>594</v>
+        <v>761</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>595</v>
+        <v>762</v>
       </c>
       <c r="B200" t="s">
-        <v>596</v>
+        <v>763</v>
       </c>
       <c r="C200" t="s">
-        <v>596</v>
+        <v>763</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>597</v>
+        <v>764</v>
       </c>
       <c r="B201" t="s">
-        <v>598</v>
+        <v>765</v>
       </c>
       <c r="C201" t="s">
-        <v>599</v>
+        <v>766</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>600</v>
+        <v>767</v>
       </c>
       <c r="B202" t="s">
-        <v>601</v>
+        <v>768</v>
       </c>
       <c r="C202" t="s">
-        <v>601</v>
+        <v>768</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>602</v>
+        <v>769</v>
       </c>
       <c r="B203" t="s">
-        <v>603</v>
+        <v>770</v>
       </c>
       <c r="C203" t="s">
-        <v>604</v>
+        <v>771</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>605</v>
+        <v>772</v>
       </c>
       <c r="B204" t="s">
-        <v>606</v>
+        <v>773</v>
       </c>
       <c r="C204" t="s">
-        <v>606</v>
+        <v>773</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>607</v>
+        <v>774</v>
       </c>
       <c r="B205" t="s">
-        <v>608</v>
+        <v>775</v>
       </c>
       <c r="C205" t="s">
-        <v>609</v>
+        <v>776</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>610</v>
+        <v>777</v>
       </c>
       <c r="B206" t="s">
-        <v>611</v>
+        <v>778</v>
       </c>
       <c r="C206" t="s">
-        <v>611</v>
+        <v>778</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>612</v>
+        <v>779</v>
       </c>
       <c r="B207" t="s">
-        <v>613</v>
+        <v>780</v>
       </c>
       <c r="C207" t="s">
-        <v>614</v>
+        <v>781</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>615</v>
+        <v>782</v>
       </c>
       <c r="B208" t="s">
-        <v>616</v>
+        <v>783</v>
       </c>
       <c r="C208" t="s">
-        <v>617</v>
+        <v>784</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>618</v>
+        <v>785</v>
       </c>
       <c r="B209" t="s">
-        <v>619</v>
+        <v>786</v>
       </c>
       <c r="C209" t="s">
-        <v>620</v>
+        <v>787</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>621</v>
+        <v>788</v>
       </c>
       <c r="B210" t="s">
-        <v>622</v>
+        <v>789</v>
       </c>
       <c r="C210" t="s">
-        <v>622</v>
+        <v>789</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>623</v>
+        <v>790</v>
       </c>
       <c r="B211" t="s">
-        <v>624</v>
+        <v>791</v>
       </c>
       <c r="C211" t="s">
-        <v>625</v>
+        <v>792</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>626</v>
+        <v>793</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>627</v>
+        <v>794</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>627</v>
+        <v>794</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>628</v>
+        <v>795</v>
       </c>
       <c r="B213" t="s">
-        <v>629</v>
+        <v>796</v>
       </c>
       <c r="C213" t="s">
-        <v>630</v>
+        <v>797</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>631</v>
+        <v>798</v>
       </c>
       <c r="B214" t="s">
-        <v>632</v>
+        <v>799</v>
       </c>
       <c r="C214" t="s">
-        <v>632</v>
+        <v>799</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>633</v>
+        <v>800</v>
       </c>
       <c r="B215" t="s">
-        <v>634</v>
+        <v>801</v>
       </c>
       <c r="C215" t="s">
-        <v>635</v>
+        <v>802</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>636</v>
+        <v>803</v>
       </c>
       <c r="B216" t="s">
-        <v>637</v>
+        <v>804</v>
       </c>
       <c r="C216" t="s">
-        <v>637</v>
+        <v>804</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>638</v>
+        <v>805</v>
       </c>
       <c r="B217" t="s">
-        <v>639</v>
+        <v>806</v>
       </c>
       <c r="C217" t="s">
-        <v>640</v>
+        <v>807</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>641</v>
+        <v>808</v>
       </c>
       <c r="B218" t="s">
-        <v>642</v>
+        <v>809</v>
       </c>
       <c r="C218" t="s">
-        <v>642</v>
+        <v>809</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>643</v>
+        <v>810</v>
       </c>
       <c r="B219" t="s">
-        <v>644</v>
+        <v>811</v>
       </c>
       <c r="C219" t="s">
-        <v>645</v>
+        <v>812</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>646</v>
+        <v>813</v>
       </c>
       <c r="B220" t="s">
-        <v>647</v>
+        <v>814</v>
       </c>
       <c r="C220" t="s">
-        <v>647</v>
+        <v>814</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>648</v>
+        <v>815</v>
       </c>
       <c r="B221" t="s">
-        <v>649</v>
+        <v>816</v>
       </c>
       <c r="C221" t="s">
-        <v>650</v>
+        <v>817</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>651</v>
+        <v>818</v>
       </c>
       <c r="B222" t="s">
-        <v>652</v>
+        <v>819</v>
       </c>
       <c r="C222" t="s">
-        <v>652</v>
+        <v>819</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>653</v>
+        <v>820</v>
       </c>
       <c r="B223" t="s">
-        <v>654</v>
+        <v>821</v>
       </c>
       <c r="C223" t="s">
-        <v>655</v>
+        <v>822</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>656</v>
+        <v>823</v>
       </c>
       <c r="B224" t="s">
-        <v>657</v>
+        <v>824</v>
       </c>
       <c r="C224" t="s">
-        <v>658</v>
+        <v>825</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>659</v>
+        <v>826</v>
       </c>
       <c r="B225" t="s">
-        <v>660</v>
+        <v>827</v>
       </c>
       <c r="C225" t="s">
-        <v>661</v>
+        <v>828</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>662</v>
+        <v>829</v>
       </c>
       <c r="B226" t="s">
-        <v>663</v>
+        <v>830</v>
       </c>
       <c r="C226" t="s">
-        <v>664</v>
+        <v>831</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>665</v>
+        <v>832</v>
       </c>
       <c r="B227" t="s">
-        <v>666</v>
+        <v>833</v>
       </c>
       <c r="C227" t="s">
-        <v>667</v>
+        <v>834</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>668</v>
+        <v>835</v>
       </c>
       <c r="B228" t="s">
-        <v>669</v>
+        <v>836</v>
       </c>
       <c r="C228" t="s">
-        <v>670</v>
+        <v>837</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>671</v>
+        <v>838</v>
       </c>
       <c r="B229" t="s">
-        <v>672</v>
+        <v>839</v>
       </c>
       <c r="C229" t="s">
-        <v>673</v>
+        <v>840</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>674</v>
+        <v>841</v>
       </c>
       <c r="B230" t="s">
-        <v>675</v>
+        <v>842</v>
       </c>
       <c r="C230" t="s">
-        <v>676</v>
+        <v>843</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>677</v>
+        <v>844</v>
       </c>
       <c r="B231" t="s">
-        <v>678</v>
+        <v>845</v>
       </c>
       <c r="C231" t="s">
-        <v>679</v>
+        <v>846</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>680</v>
+        <v>847</v>
       </c>
       <c r="B232" t="s">
-        <v>681</v>
+        <v>848</v>
       </c>
       <c r="C232" t="s">
-        <v>682</v>
+        <v>849</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>683</v>
+        <v>850</v>
       </c>
       <c r="B233" t="s">
-        <v>684</v>
+        <v>851</v>
       </c>
       <c r="C233" t="s">
-        <v>685</v>
+        <v>852</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>686</v>
+        <v>853</v>
       </c>
       <c r="B234" t="s">
-        <v>687</v>
+        <v>854</v>
       </c>
       <c r="C234" t="s">
-        <v>688</v>
+        <v>855</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>689</v>
+        <v>856</v>
       </c>
       <c r="B235" t="s">
-        <v>690</v>
+        <v>857</v>
       </c>
       <c r="C235" t="s">
-        <v>691</v>
+        <v>858</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>692</v>
+        <v>859</v>
       </c>
       <c r="B236" t="s">
-        <v>693</v>
+        <v>860</v>
       </c>
       <c r="C236" t="s">
-        <v>694</v>
+        <v>861</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>695</v>
+        <v>862</v>
       </c>
       <c r="B237" t="s">
-        <v>696</v>
+        <v>863</v>
       </c>
       <c r="C237" t="s">
-        <v>697</v>
+        <v>864</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>698</v>
+        <v>865</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>699</v>
+        <v>866</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>699</v>
+        <v>866</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>700</v>
+        <v>867</v>
       </c>
       <c r="B239" t="s">
-        <v>701</v>
+        <v>868</v>
       </c>
       <c r="C239" t="s">
-        <v>702</v>
+        <v>869</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>703</v>
+        <v>870</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>704</v>
+        <v>871</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>704</v>
+        <v>871</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>705</v>
+        <v>872</v>
       </c>
       <c r="B241" t="s">
-        <v>706</v>
+        <v>873</v>
       </c>
       <c r="C241" t="s">
-        <v>707</v>
+        <v>874</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>708</v>
+        <v>875</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>709</v>
+        <v>876</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>709</v>
+        <v>876</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>710</v>
+        <v>877</v>
       </c>
       <c r="B243" t="s">
-        <v>711</v>
+        <v>878</v>
       </c>
       <c r="C243" t="s">
-        <v>712</v>
+        <v>879</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>713</v>
+        <v>880</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>714</v>
+        <v>881</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>714</v>
+        <v>881</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>715</v>
+        <v>882</v>
       </c>
       <c r="B245" t="s">
-        <v>716</v>
+        <v>883</v>
       </c>
       <c r="C245" t="s">
-        <v>717</v>
+        <v>884</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>718</v>
+        <v>885</v>
       </c>
       <c r="B246" t="s">
-        <v>719</v>
+        <v>886</v>
       </c>
       <c r="C246" t="s">
-        <v>720</v>
+        <v>887</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>721</v>
+        <v>888</v>
       </c>
       <c r="B247" t="s">
-        <v>722</v>
+        <v>889</v>
       </c>
       <c r="C247" t="s">
-        <v>723</v>
+        <v>890</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>724</v>
+        <v>891</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>725</v>
+        <v>892</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>725</v>
+        <v>892</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>726</v>
+        <v>893</v>
       </c>
       <c r="B249" t="s">
-        <v>727</v>
+        <v>894</v>
       </c>
       <c r="C249" t="s">
-        <v>728</v>
+        <v>895</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>729</v>
+        <v>896</v>
       </c>
       <c r="B250" t="s">
-        <v>730</v>
+        <v>897</v>
       </c>
       <c r="C250" t="s">
-        <v>731</v>
+        <v>898</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>732</v>
+        <v>899</v>
       </c>
       <c r="B251" t="s">
-        <v>733</v>
+        <v>900</v>
       </c>
       <c r="C251" t="s">
-        <v>734</v>
+        <v>901</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>735</v>
+        <v>902</v>
       </c>
       <c r="B252" t="s">
-        <v>736</v>
+        <v>903</v>
       </c>
       <c r="C252" t="s">
-        <v>737</v>
+        <v>904</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>738</v>
+        <v>905</v>
       </c>
       <c r="B253" t="s">
-        <v>739</v>
+        <v>906</v>
       </c>
       <c r="C253" t="s">
-        <v>740</v>
+        <v>907</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>741</v>
+        <v>908</v>
       </c>
       <c r="B254" t="s">
-        <v>742</v>
+        <v>909</v>
       </c>
       <c r="C254" t="s">
-        <v>743</v>
+        <v>910</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>744</v>
+        <v>911</v>
       </c>
       <c r="B255" t="s">
-        <v>745</v>
+        <v>912</v>
       </c>
       <c r="C255" t="s">
-        <v>746</v>
+        <v>913</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>747</v>
+        <v>914</v>
       </c>
       <c r="B256" t="s">
-        <v>748</v>
+        <v>915</v>
       </c>
       <c r="C256" t="s">
-        <v>749</v>
+        <v>916</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>750</v>
+        <v>917</v>
       </c>
       <c r="B257" t="s">
-        <v>751</v>
+        <v>918</v>
       </c>
       <c r="C257" t="s">
-        <v>752</v>
+        <v>919</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>753</v>
+        <v>920</v>
       </c>
       <c r="B258" t="s">
-        <v>754</v>
+        <v>921</v>
       </c>
       <c r="C258" t="s">
-        <v>755</v>
+        <v>922</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>756</v>
+        <v>923</v>
       </c>
       <c r="B259" t="s">
-        <v>757</v>
+        <v>924</v>
       </c>
       <c r="C259" t="s">
-        <v>758</v>
+        <v>925</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>759</v>
+        <v>926</v>
       </c>
       <c r="B260" t="s">
-        <v>760</v>
+        <v>927</v>
       </c>
       <c r="C260" t="s">
-        <v>761</v>
+        <v>928</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>762</v>
+        <v>929</v>
       </c>
       <c r="B261" t="s">
-        <v>763</v>
+        <v>930</v>
       </c>
       <c r="C261" t="s">
-        <v>764</v>
+        <v>931</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>765</v>
+        <v>932</v>
       </c>
       <c r="B262" t="s">
-        <v>766</v>
+        <v>933</v>
       </c>
       <c r="C262" t="s">
-        <v>767</v>
+        <v>934</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>768</v>
+        <v>935</v>
       </c>
       <c r="B263" t="s">
-        <v>769</v>
+        <v>936</v>
       </c>
       <c r="C263" t="s">
-        <v>770</v>
+        <v>937</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>771</v>
+        <v>938</v>
       </c>
       <c r="B264" t="s">
-        <v>772</v>
+        <v>939</v>
       </c>
       <c r="C264" t="s">
-        <v>773</v>
+        <v>940</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>774</v>
+        <v>941</v>
       </c>
       <c r="B265" t="s">
-        <v>775</v>
+        <v>942</v>
       </c>
       <c r="C265" t="s">
-        <v>776</v>
+        <v>943</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>777</v>
+        <v>944</v>
       </c>
       <c r="B266" t="s">
-        <v>778</v>
+        <v>945</v>
       </c>
       <c r="C266" t="s">
-        <v>779</v>
+        <v>946</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>780</v>
+        <v>947</v>
       </c>
       <c r="B267" t="s">
-        <v>781</v>
+        <v>948</v>
       </c>
       <c r="C267" t="s">
-        <v>782</v>
+        <v>949</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>783</v>
+        <v>950</v>
       </c>
       <c r="B268" t="s">
-        <v>784</v>
+        <v>951</v>
       </c>
       <c r="C268" t="s">
-        <v>785</v>
+        <v>952</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>786</v>
+        <v>953</v>
       </c>
       <c r="B269" t="s">
-        <v>787</v>
+        <v>954</v>
       </c>
       <c r="C269" t="s">
-        <v>788</v>
+        <v>955</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>789</v>
+        <v>956</v>
       </c>
       <c r="B270" t="s">
-        <v>790</v>
+        <v>957</v>
       </c>
       <c r="C270" t="s">
-        <v>791</v>
+        <v>958</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>792</v>
+        <v>959</v>
       </c>
       <c r="B271" t="s">
-        <v>793</v>
+        <v>960</v>
       </c>
       <c r="C271" t="s">
-        <v>794</v>
+        <v>961</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>795</v>
+        <v>962</v>
       </c>
       <c r="B272" t="s">
-        <v>796</v>
+        <v>963</v>
       </c>
       <c r="C272" t="s">
-        <v>797</v>
+        <v>964</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>798</v>
+        <v>965</v>
       </c>
       <c r="B273" t="s">
-        <v>799</v>
+        <v>966</v>
       </c>
       <c r="C273" t="s">
-        <v>800</v>
+        <v>967</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>857</v>
+        <v>968</v>
       </c>
       <c r="B274" t="s">
-        <v>858</v>
+        <v>969</v>
       </c>
       <c r="C274" t="s">
-        <v>859</v>
+        <v>970</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A275" t="s">
+        <v>44</v>
+      </c>
+      <c r="B275" t="s">
+        <v>45</v>
+      </c>
+      <c r="C275" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A276" t="s">
+        <v>47</v>
+      </c>
+      <c r="B276" t="s">
+        <v>48</v>
+      </c>
+      <c r="C276" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A277" t="s">
+        <v>50</v>
+      </c>
+      <c r="B277" t="s">
+        <v>51</v>
+      </c>
+      <c r="C277" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A278" t="s">
+        <v>53</v>
+      </c>
+      <c r="B278" t="s">
+        <v>54</v>
+      </c>
+      <c r="C278" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A279" t="s">
+        <v>56</v>
+      </c>
+      <c r="B279" t="s">
+        <v>57</v>
+      </c>
+      <c r="C279" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A280" t="s">
+        <v>59</v>
+      </c>
+      <c r="B280" t="s">
+        <v>60</v>
+      </c>
+      <c r="C280" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A281" t="s">
+        <v>62</v>
+      </c>
+      <c r="B281" t="s">
+        <v>63</v>
+      </c>
+      <c r="C281" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A282" t="s">
+        <v>65</v>
+      </c>
+      <c r="B282" t="s">
+        <v>66</v>
+      </c>
+      <c r="C282" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A283" t="s">
+        <v>68</v>
+      </c>
+      <c r="B283" t="s">
+        <v>69</v>
+      </c>
+      <c r="C283" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A284" t="s">
+        <v>71</v>
+      </c>
+      <c r="B284" t="s">
+        <v>72</v>
+      </c>
+      <c r="C284" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A285" t="s">
+        <v>74</v>
+      </c>
+      <c r="B285" t="s">
+        <v>75</v>
+      </c>
+      <c r="C285" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A286" t="s">
+        <v>77</v>
+      </c>
+      <c r="B286" t="s">
+        <v>78</v>
+      </c>
+      <c r="C286" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A287" t="s">
+        <v>80</v>
+      </c>
+      <c r="B287" t="s">
+        <v>81</v>
+      </c>
+      <c r="C287" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A288" t="s">
+        <v>83</v>
+      </c>
+      <c r="B288" t="s">
+        <v>84</v>
+      </c>
+      <c r="C288" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A289" t="s">
+        <v>86</v>
+      </c>
+      <c r="B289" t="s">
+        <v>87</v>
+      </c>
+      <c r="C289" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A290" t="s">
+        <v>89</v>
+      </c>
+      <c r="B290" t="s">
+        <v>90</v>
+      </c>
+      <c r="C290" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A291" t="s">
+        <v>92</v>
+      </c>
+      <c r="B291" t="s">
+        <v>93</v>
+      </c>
+      <c r="C291" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A292" t="s">
+        <v>95</v>
+      </c>
+      <c r="B292" t="s">
+        <v>96</v>
+      </c>
+      <c r="C292" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A293" t="s">
+        <v>98</v>
+      </c>
+      <c r="B293" t="s">
+        <v>99</v>
+      </c>
+      <c r="C293" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A294" t="s">
+        <v>101</v>
+      </c>
+      <c r="B294" t="s">
+        <v>102</v>
+      </c>
+      <c r="C294" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A295" t="s">
+        <v>104</v>
+      </c>
+      <c r="B295" t="s">
+        <v>105</v>
+      </c>
+      <c r="C295" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A296" t="s">
+        <v>107</v>
+      </c>
+      <c r="B296" t="s">
+        <v>108</v>
+      </c>
+      <c r="C296" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A297" t="s">
+        <v>110</v>
+      </c>
+      <c r="B297" t="s">
+        <v>111</v>
+      </c>
+      <c r="C297" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A298" t="s">
+        <v>113</v>
+      </c>
+      <c r="B298" t="s">
+        <v>114</v>
+      </c>
+      <c r="C298" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A299" t="s">
+        <v>116</v>
+      </c>
+      <c r="B299" t="s">
+        <v>117</v>
+      </c>
+      <c r="C299" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A300" t="s">
+        <v>119</v>
+      </c>
+      <c r="B300" t="s">
+        <v>120</v>
+      </c>
+      <c r="C300" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A301" t="s">
+        <v>122</v>
+      </c>
+      <c r="B301" t="s">
+        <v>123</v>
+      </c>
+      <c r="C301" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A302" t="s">
+        <v>125</v>
+      </c>
+      <c r="B302" t="s">
+        <v>126</v>
+      </c>
+      <c r="C302" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A303" t="s">
+        <v>128</v>
+      </c>
+      <c r="B303" t="s">
+        <v>129</v>
+      </c>
+      <c r="C303" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A304" t="s">
+        <v>131</v>
+      </c>
+      <c r="B304" t="s">
+        <v>132</v>
+      </c>
+      <c r="C304" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A305" t="s">
+        <v>134</v>
+      </c>
+      <c r="B305" t="s">
+        <v>135</v>
+      </c>
+      <c r="C305" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A306" t="s">
+        <v>137</v>
+      </c>
+      <c r="B306" t="s">
+        <v>138</v>
+      </c>
+      <c r="C306" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A307" t="s">
+        <v>140</v>
+      </c>
+      <c r="B307" t="s">
+        <v>141</v>
+      </c>
+      <c r="C307" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A308" t="s">
+        <v>143</v>
+      </c>
+      <c r="B308" t="s">
+        <v>144</v>
+      </c>
+      <c r="C308" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A309" t="s">
+        <v>146</v>
+      </c>
+      <c r="B309" t="s">
+        <v>147</v>
+      </c>
+      <c r="C309" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A310" t="s">
+        <v>149</v>
+      </c>
+      <c r="B310" t="s">
+        <v>150</v>
+      </c>
+      <c r="C310" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A311" t="s">
+        <v>152</v>
+      </c>
+      <c r="B311" t="s">
+        <v>153</v>
+      </c>
+      <c r="C311" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A312" t="s">
+        <v>155</v>
+      </c>
+      <c r="B312" t="s">
+        <v>156</v>
+      </c>
+      <c r="C312" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A313" t="s">
+        <v>158</v>
+      </c>
+      <c r="B313" t="s">
+        <v>159</v>
+      </c>
+      <c r="C313" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A314" t="s">
+        <v>161</v>
+      </c>
+      <c r="B314" t="s">
+        <v>162</v>
+      </c>
+      <c r="C314" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A315" t="s">
+        <v>164</v>
+      </c>
+      <c r="B315" t="s">
+        <v>165</v>
+      </c>
+      <c r="C315" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A316" t="s">
+        <v>167</v>
+      </c>
+      <c r="B316" t="s">
+        <v>168</v>
+      </c>
+      <c r="C316" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -6021,8 +6927,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B27CD3B9-76BC-4867-974C-73F739555344}">
-  <dimension ref="A1:C10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.4140625" customWidth="1"/>
@@ -6043,101 +6949,156 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>846</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>850</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>851</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>847</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>855</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>852</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>848</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>856</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>853</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>849</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>845</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>854</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>831</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>832</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>833</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>834</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>835</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>836</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>837</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>839</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>838</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>842</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>843</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>840</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>844</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>845</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>841</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -6147,7 +7108,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6169,90 +7130,90 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>801</v>
+        <v>971</v>
       </c>
       <c r="B2" t="s">
-        <v>802</v>
+        <v>972</v>
       </c>
       <c r="C2" t="s">
-        <v>803</v>
+        <v>973</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>804</v>
+        <v>974</v>
       </c>
       <c r="B3" t="s">
-        <v>805</v>
+        <v>975</v>
       </c>
       <c r="C3" t="s">
-        <v>806</v>
+        <v>976</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>807</v>
+        <v>977</v>
       </c>
       <c r="B4" t="s">
-        <v>808</v>
+        <v>978</v>
       </c>
       <c r="C4" t="s">
-        <v>809</v>
+        <v>979</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>810</v>
+        <v>980</v>
       </c>
       <c r="B5" t="s">
-        <v>811</v>
+        <v>981</v>
       </c>
       <c r="C5" t="s">
-        <v>812</v>
+        <v>982</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>813</v>
+        <v>983</v>
       </c>
       <c r="B6" t="s">
-        <v>814</v>
+        <v>984</v>
       </c>
       <c r="C6" t="s">
-        <v>815</v>
+        <v>985</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>816</v>
+        <v>986</v>
       </c>
       <c r="B7" t="s">
-        <v>817</v>
+        <v>987</v>
       </c>
       <c r="C7" t="s">
-        <v>818</v>
+        <v>988</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>860</v>
+        <v>989</v>
       </c>
       <c r="B8" t="s">
-        <v>864</v>
+        <v>990</v>
       </c>
       <c r="C8" t="s">
-        <v>865</v>
+        <v>991</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>861</v>
+        <v>992</v>
       </c>
       <c r="B9" t="s">
-        <v>863</v>
+        <v>993</v>
       </c>
       <c r="C9" t="s">
-        <v>862</v>
+        <v>994</v>
       </c>
     </row>
   </sheetData>
@@ -6263,7 +7224,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6285,50 +7246,160 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>819</v>
+        <v>995</v>
       </c>
       <c r="B2" t="s">
-        <v>820</v>
+        <v>996</v>
       </c>
       <c r="C2" t="s">
-        <v>821</v>
+        <v>997</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>822</v>
+        <v>998</v>
       </c>
       <c r="B3" t="s">
-        <v>823</v>
+        <v>999</v>
       </c>
       <c r="C3" t="s">
-        <v>824</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>825</v>
+        <v>1001</v>
       </c>
       <c r="B4" t="s">
-        <v>826</v>
+        <v>1002</v>
       </c>
       <c r="C4" t="s">
-        <v>827</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>828</v>
+        <v>1004</v>
       </c>
       <c r="B5" t="s">
-        <v>829</v>
+        <v>1005</v>
       </c>
       <c r="C5" t="s">
-        <v>830</v>
+        <v>1006</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Enemies" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Equips" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Classes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="States" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_1" localSheetId="0">System!$A$6:$C$249</definedName>
@@ -5940,7 +5941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="17.4140625" customWidth="1" min="1" max="1"/>
@@ -6070,12 +6071,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MENU_SAVE</t>
+          <t>MENU_SAVE_FILE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Save File</t>
+          <t>Files</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -6087,119 +6088,153 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MENU_LOAD</t>
+          <t>MENU_EXIT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Load File</t>
+          <t>Exit Game</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>读档</t>
+          <t>回到标题</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MENU_EXIT</t>
+          <t>DIALOGUE_BOOK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Exit Game</t>
+          <t>Dialogue Book</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>回到标题</t>
+          <t>对话手册</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DIALOGUE_BOOK</t>
+          <t>DIALOGUE_BOOK_DESC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dialogue Book</t>
+          <t>You can review the dialogues that you've met with it.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>对话手册</t>
+          <t>持有后可以查看经历过的对话内容。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DIALOGUE_BOOK_DESC</t>
+          <t>EQUIP_UNEQUIPPED</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>You can review the dialogues that you've met with it.</t>
+          <t>[Unequipped]</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>持有后可以查看经历过的对话内容。</t>
+          <t>[未装备]</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EQUIP_UNEQUIPPED</t>
+          <t>EQUIP_UNEQUIP</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[Unequipped]</t>
+          <t>Unequip</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[未装备]</t>
+          <t>卸下</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EQUIP_UNEQUIP</t>
+          <t>EQUIP_UNEQUIP_DESC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Unequip</t>
+          <t>Remove equipment from this slot.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>卸下</t>
+          <t>卸下当前槽位的装备。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EQUIP_UNEQUIP_DESC</t>
+          <t>MENU_SAVE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Remove equipment from this slot.</t>
+          <t>Save File</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>卸下当前槽位的装备。</t>
+          <t>存档</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MENU_LOAD</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Load File</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>读档</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MENU_LOAD</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Load File</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>读档</t>
         </is>
       </c>
     </row>
@@ -6647,4 +6682,69 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>en_GB</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>zh_CN</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>POISONED</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Poisoned</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>中毒</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>POISONED_DESC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Once afflicted with the Poisoned status, the affected entity loses additional HP equal to the number of Poison stacks at the end of each turn.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>陷入中毒状态后每回合会多损失中毒层数数值的生命值</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C324"/>
+  <dimension ref="A1:C350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="38.75" customWidth="1" min="1" max="1"/>
@@ -5926,6 +5926,448 @@
       <c r="C324" t="inlineStr">
         <is>
           <t>雪</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>GET_STATE_OWNER</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Get State Owner</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>获取状态宿主</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>GET_STATE_OWNER_DESC</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Return the battler currently hosting this state.</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>返回当前承载该状态的战斗者。</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>GET_EVENT_ARG</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Get Event Arg</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>获取事件参数</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>GET_EVENT_ARG_DESC</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Read a keyword argument injected into the current blueprint event (e.g. battler, context, opponent, won).</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>读取注入到当前蓝图事件的关键字参数（如 battler、context、opponent、won 等）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>GET_DAMAGE_CONTEXT</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Get Damage Context</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>获取伤害上下文</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>GET_DAMAGE_CONTEXT_DESC</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Get the active DamageContext for the current event.</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>获取当前事件下活动的 DamageContext。</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>GET_CTX_FIELD</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Get Ctx Field</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>读取上下文字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>GET_CTX_FIELD_DESC</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Read a field from a DamageContext (atk, deF, damagePerRound, rounds, totalDamage, …).</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>从 DamageContext 读取字段（atk、deF、damagePerRound、rounds、totalDamage 等）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>SET_CTX_FIELD</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Set Ctx Field</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>写入上下文字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>SET_CTX_FIELD_DESC</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Write a field on a DamageContext to alter damage resolution.</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>向 DamageContext 写入字段以影响伤害结算。</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>ADD_CTX_FIELD</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Add Ctx Field</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>累加上下文字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>ADD_CTX_FIELD_DESC</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Add a numeric delta to a field on the DamageContext (totalDamage, damagePerRound, atk, deF, …).</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>在 DamageContext 字段上累加数值（totalDamage、damagePerRound、atk、deF 等）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>GET_BATTLER_ATTR</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Get Battler Attr</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>读取战斗者属性</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>GET_BATTLER_ATTR_DESC</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Read a named attribute from any battler (HP, MAXHP, ATK, DEF, …).</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>从任意战斗者读取命名属性（HP、MAXHP、ATK、DEF 等）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>SET_BATTLER_ATTR</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Set Battler Attr</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>写入战斗者属性</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>SET_BATTLER_ATTR_DESC</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Write a named attribute on any battler.</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>向任意战斗者写入命名属性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>DAMAGE_BATTLER</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Damage Battler</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>扣除战斗者血量</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>DAMAGE_BATTLER_DESC</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Subtract HP from any battler (floored at 0).</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>从任意战斗者扣除生命值（下限为 0）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>HEAL_BATTLER</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Heal Battler</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>治疗战斗者</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>HEAL_BATTLER_DESC</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Restore HP on any battler (capped at MAXHP).</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>为任意战斗者恢复生命值（上限为 MAXHP）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>BATTLER_HAS_STATE</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Battler Has State</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>战斗者是否拥有状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>BATTLER_HAS_STATE_DESC</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Check whether a battler currently carries the given state ID.</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>检查战斗者当前是否拥有指定状态 ID。</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>ADD_STATE_TO</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Add State To</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>为战斗者添加状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>ADD_STATE_TO_DESC</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Apply a state (by ID) to any battler, firing its onAdd blueprint.</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>通过 ID 给任意战斗者添加状态，并触发其 onAdd 蓝图。</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>REMOVE_STATE_FROM</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Remove State From</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>从战斗者移除状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>REMOVE_STATE_FROM_DESC</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Remove a state (by ID) from any battler, firing its onRemove blueprint.</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>通过 ID 从任意战斗者移除状态，并触发其 onRemove 蓝图。</t>
         </is>
       </c>
     </row>

--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="280" yWindow="4710" windowWidth="28800" windowHeight="15370" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="280" yWindow="4710" windowWidth="28800" windowHeight="15370" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="System" sheetId="1" state="visible" r:id="rId1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C350"/>
+  <dimension ref="A1:C362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="38.75" customWidth="1" min="1" max="1"/>
@@ -6368,6 +6368,210 @@
       <c r="C350" t="inlineStr">
         <is>
           <t>通过 ID 从任意战斗者移除状态，并触发其 onRemove 蓝图。</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>OPEN_SHOP</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Open Shop</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>打开商店</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>OPEN_SHOP_DESC</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Open the map shop with purchasable item IDs and whether selling is allowed.</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>打开地图场景商店，参数为可购买道具ID数组和是否允许出售。</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>RECORD_TELEPOINT</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Record Telepoint</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>记录传送点</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>RECORD_TELEPOINT_DESC</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Record a telepoint for a map so it can be used by teleport items.</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>记录地图传送点，供传送道具使用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>OPEN_MONSTER_BOOK</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Open Monster Book</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>打开怪物手册</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>OPEN_MONSTER_BOOK_DESC</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Open the monster handbook for the current map.</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>打开当前地图的怪物手册。</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>GET_CURRENT_REGION</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Get Current Region</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>获取当前区域</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>GET_CURRENT_REGION_DESC</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Get the current mota region name.</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>获取当前魔塔区域名。</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>SET_CURRENT_REGION</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Set Current Region</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>设置当前区域</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>SET_CURRENT_REGION_DESC</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Set the current mota region name.</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>设置当前魔塔区域名。</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>OPEN_FLOOR_TELEPORTER</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Open Floor Teleporter</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>打开楼层传送器</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>OPEN_FLOOR_TELEPORTER_DESC</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Open the visited-floor teleporter preview window.</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>打开已去过楼层的传送器预览窗口。</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="17.4140625" customWidth="1" min="1" max="1"/>
@@ -6728,40 +6932,6 @@
       <c r="C20" t="inlineStr">
         <is>
           <t>出售</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>OPEN_SHOP</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Open Shop</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>打开商店</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>OPEN_SHOP_DESC</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Open the map shop with purchasable item IDs and whether selling is allowed.</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>打开地图场景商店，参数为可购买道具ID数组和是否允许出售。</t>
         </is>
       </c>
     </row>
@@ -6776,7 +6946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="25.75" customWidth="1" min="1" max="1"/>
@@ -6934,6 +7104,40 @@
       <c r="C9" t="inlineStr">
         <is>
           <t>持有后可以查看敌人信息（快捷键D）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FLY_FLOOR</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Teleporter</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>地图传送器</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FLY_FLOOR_DESC</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>You can teleport to the map you had been to with it(Hotkey: F).</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>持有后可以在前往过的传送点（快捷键F）</t>
         </is>
       </c>
     </row>

--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="280" yWindow="4710" windowWidth="28800" windowHeight="15370" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="280" yWindow="4710" windowWidth="28800" windowHeight="15370" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="System" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,6 +13,7 @@
     <sheet name="Equips" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Classes" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="States" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="MapNames" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_1" localSheetId="0">System!$A$6:$C$249</definedName>
@@ -4014,15 +4015,13 @@
           <t>EQUALS</t>
         </is>
       </c>
-      <c r="B212" s="1" t="inlineStr">
-        <is>
-          <t>==</t>
-        </is>
-      </c>
-      <c r="C212" s="1" t="inlineStr">
-        <is>
-          <t>==</t>
-        </is>
+      <c r="B212" s="1">
+        <f>=</f>
+        <v/>
+      </c>
+      <c r="C212" s="1">
+        <f>=</f>
+        <v/>
       </c>
     </row>
     <row r="213">
@@ -6587,7 +6586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="17.4140625" customWidth="1" min="1" max="1"/>
@@ -6932,6 +6931,23 @@
       <c r="C20" t="inlineStr">
         <is>
           <t>出售</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>POINT</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>P {index}</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>点位 {index}</t>
         </is>
       </c>
     </row>
@@ -7478,4 +7494,69 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>en_GB</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>zh_CN</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MAP_01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Tower G</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>魔塔 0 层</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MAP_02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Tower 1F</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>魔塔 1 层</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C362"/>
+  <dimension ref="A1:C372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="38.75" customWidth="1" min="1" max="1"/>
@@ -6571,6 +6571,176 @@
       <c r="C362" t="inlineStr">
         <is>
           <t>打开已去过楼层的传送器预览窗口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>DESTROY_TERRAIN</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Destroy Terrain</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>破坏地形</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>DESTROY_TERRAIN_DESC</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Replace one tile on a layer of the current map with the specified tile ID.</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>将当前地图指定图层上的一个格子替换为指定 tileID。</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>GET_TERRAIN_TILE</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Get Terrain Tile</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>获取地形 Tile</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>GET_TERRAIN_TILE_DESC</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Get the tile ID at a layer position on the current map.</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>获取当前地图指定图层和坐标上的 tileID。</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>GET_PLAYER_FRONT_POSITION</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Get Player Front Position</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>获取玩家面前坐标</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>GET_PLAYER_FRONT_POSITION_DESC</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Get the tile coordinate in front of the player based on the current facing direction.</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>根据玩家当前朝向获取面前一格的地图坐标。</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>DESTROY_TERRAIN_LIST</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Destroy Terrain List</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>批量破坏地形</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>DESTROY_TERRAIN_LIST_DESC</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Replace multiple tiles on a layer of the current map with the specified tile ID.</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>将当前地图指定图层上的多个格子替换为指定 tileID。</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>GET_TERRAIN_TILE_POSITIONS</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Get Terrain Tile Positions</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>获取地形 Tile 坐标列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>GET_TERRAIN_TILE_POSITIONS_DESC</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Get all coordinates matching a tile ID on a layer of the current map.</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>获取当前地图指定图层中所有匹配 tileID 的坐标。</t>
         </is>
       </c>
     </row>
@@ -6962,7 +7132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="25.75" customWidth="1" min="1" max="1"/>
@@ -7154,6 +7324,74 @@
       <c r="C11" t="inlineStr">
         <is>
           <t>持有后可以在前往过的传送点（快捷键F）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BREAK_WALL</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pickaxe</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>镐</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BREAK_WALL_DESC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>You can use it to destroy a wall in front of you.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>可以破坏面前的一堵墙壁</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CLEAR_WALL</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Earthquake Scroll</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>地震卷轴</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CLEAR_WALL_DESC</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>You can use this to remove all walls on the current map.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>可以清除当前地图所有墙壁</t>
         </is>
       </c>
     </row>

--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="280" yWindow="4710" windowWidth="28800" windowHeight="15370" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="System" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="UI" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Items" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Enemies" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Equips" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Classes" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="States" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="MapNames" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Items" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemies" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equips" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="States" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MapNames" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_1" localSheetId="0">System!$A$6:$C$249</definedName>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C372"/>
+  <dimension ref="A1:C380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="38.75" customWidth="1" min="1" max="1"/>
@@ -6741,6 +6741,142 @@
       <c r="C372" t="inlineStr">
         <is>
           <t>获取当前地图指定图层中所有匹配 tileID 的坐标。</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>SET_MOVE_ROUTE</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Set Move Route</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>设置移动路线</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>SET_MOVE_ROUTE_DESC</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Set an actor movement route. Started continues immediately; Finished continues after movement ends.</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>设置 actor 的移动路线。Started 立即继续，Finished 在移动结束后继续。</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>SET_AUTO_PATH_TO_DESTINATION</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Set Auto Path to Destination</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>设置自动寻路到终点</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>SET_AUTO_PATH_TO_DESTINATION_DESC</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Pathfind an actor to the target map cell. Started continues immediately; Finished continues after movement ends.</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>让 actor 自动寻路到指定地图格。Started 立即继续，Finished 在移动结束后继续。</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>FREEZE_TRANSITION_BACKGROUND</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Freeze Transition Background</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>冻结转场背景</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>FREEZE_TRANSITION_BACKGROUND_DESC</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Capture the current frame as the next transition background, then continue when ready.</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>捕获当前帧作为下一次转场背景，并在捕获完成后继续。</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>REQUEST_TRANSITION</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Request Transition</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>请求转场</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>REQUEST_TRANSITION_DESC</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Start a screen transition (empty transitionName uses a plain fade), then continue when it finishes.</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>启动屏幕转场（transitionName 为空时为普通淡入），并在转场结束后继续。</t>
         </is>
       </c>
     </row>

--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="280" yWindow="4710" windowWidth="28800" windowHeight="15370" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Items" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemies" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equips" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classes" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="States" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MapNames" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="System" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="UI" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Items" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Enemies" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Equips" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Classes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="States" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="MapNames" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_1" localSheetId="0">System!$A$6:$C$249</definedName>
@@ -7268,7 +7268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="25.75" customWidth="1" min="1" max="1"/>
@@ -7528,6 +7528,74 @@
       <c r="C15" t="inlineStr">
         <is>
           <t>可以清除当前地图所有墙壁</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BREAK_LAVA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>冰冻徽章</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BREAK_LAVA_DESC</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>You can use it to destroy a lava in front of you.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>可以破坏面前的一块熔岩</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BREAK_ICE</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ice Axe</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>破冰镐</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BREAK_ICE_DESC</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>You can use it to destroy an ice wall in front of you.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>可以破坏面前的一块冰墙</t>
         </is>
       </c>
     </row>

--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -14,6 +14,7 @@
     <sheet name="Classes" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="States" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="MapNames" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Specials" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_1" localSheetId="0">System!$A$6:$C$249</definedName>
@@ -414,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C380"/>
+  <dimension ref="A1:C382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="38.75" customWidth="1" min="1" max="1"/>
@@ -6877,6 +6878,40 @@
       <c r="C380" t="inlineStr">
         <is>
           <t>启动屏幕转场（transitionName 为空时为普通淡入），并在转场结束后继续。</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>GAME_OVER</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Game Over</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>游戏结束</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>GAME_OVER_DESC</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Switch to the game over scene.</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>进入游戏结束场景。</t>
         </is>
       </c>
     </row>
@@ -7879,7 +7914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <sheetData>
     <row r="1">
@@ -7902,32 +7937,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>POISONED</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Poisoned</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>中毒</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>POISONED</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Poisoned</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>中毒</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>POISONED_DESC</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Once afflicted with the Poisoned status, the affected entity loses additional HP equal to the number of Poison stacks at the end of each turn.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>陷入中毒状态后每回合会多损失中毒层数数值的生命值</t>
         </is>
@@ -8001,4 +8053,69 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>en_GB</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>zh_CN</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>S_POISOING</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Poisoning</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>中毒</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>S_POISOING_DESC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Player will be poisoned after this battle.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>战斗后会使我方陷入中毒状态</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C382"/>
+  <dimension ref="A1:C384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="38.75" customWidth="1" min="1" max="1"/>
@@ -681,6235 +681,6269 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GET_ANIM_LENGTH</t>
+          <t>ADD_ANIM_ON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Get Animation Length</t>
+          <t>Add Animation On Actor</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>获取动画时长</t>
+          <t>在 Actor 上添加动画</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GET_ANIM_LENGTH_DESC</t>
+          <t>ADD_ANIM_ON_DESC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Get the duration of an animation (seconds).</t>
+          <t>Create and add an animation at the position of the actor with the given tag.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>获取指定动画的持续时间（秒）。</t>
+          <t>在指定 tag 的 Actor 位置创建并添加动画。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SUPER</t>
+          <t>GET_ANIM_LENGTH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Call Super</t>
+          <t>Get Animation Length</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>调用父类</t>
+          <t>获取动画时长</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SUPER_DESC</t>
+          <t>GET_ANIM_LENGTH_DESC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Call the parent implementation for the current method.</t>
+          <t>Get the duration of an animation (seconds).</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>在蓝图/生成类中调用父类同名方法。</t>
+          <t>获取指定动画的持续时间（秒）。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SELF</t>
+          <t>SUPER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Self</t>
+          <t>Call Super</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>自身对象</t>
+          <t>调用父类</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SELF_DESC</t>
+          <t>SUPER_DESC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Get the object instance that owns the current graph.</t>
+          <t>Call the parent implementation for the current method.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>获取当前图所属的对象实例。</t>
+          <t>在蓝图/生成类中调用父类同名方法。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GET_ATTR_REF</t>
+          <t>SELF</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Get Attribute Ref</t>
+          <t>Self</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>获取属性引用</t>
+          <t>自身对象</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GET_ATTR_REF_DESC</t>
+          <t>SELF_DESC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Get a readable/writable reference to an object attribute.</t>
+          <t>Get the object instance that owns the current graph.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>获取一个可读写的对象属性引用。</t>
+          <t>获取当前图所属的对象实例。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GET_ATTR</t>
+          <t>GET_ATTR_REF</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Get Attribute</t>
+          <t>Get Attribute Ref</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>获取属性</t>
+          <t>获取属性引用</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GET_ATTR_DESC</t>
+          <t>GET_ATTR_REF_DESC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Read an attribute value from an object.</t>
+          <t>Get a readable/writable reference to an object attribute.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>读取对象的指定属性值。</t>
+          <t>获取一个可读写的对象属性引用。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SET_ATTR</t>
+          <t>GET_ATTR</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Set Attribute</t>
+          <t>Get Attribute</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>设置属性</t>
+          <t>获取属性</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SET_ATTR_DESC</t>
+          <t>GET_ATTR_DESC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Set an attribute value on an object.</t>
+          <t>Read an attribute value from an object.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>设置对象的指定属性值。</t>
+          <t>读取对象的指定属性值。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GET_SCENE</t>
+          <t>SET_ATTR</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Get Scene</t>
+          <t>Set Attribute</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>获取场景</t>
+          <t>设置属性</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GET_SCENE_DESC</t>
+          <t>SET_ATTR_DESC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Get the current running scene.</t>
+          <t>Set an attribute value on an object.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>获取当前运行中的场景对象。</t>
+          <t>设置对象的指定属性值。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IS_VALID_VALUE</t>
+          <t>GET_SCENE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Is Valid Value</t>
+          <t>Get Scene</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>值有效</t>
+          <t>获取场景</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IS_VALID_VALUE_DESC</t>
+          <t>GET_SCENE_DESC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Check whether the value is not None.</t>
+          <t>Get the current running scene.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>判断值是否为非空（None）。</t>
+          <t>获取当前运行中的场景对象。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RUN_COMMON_FUNCTION</t>
+          <t>IS_VALID_VALUE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Run Common Function</t>
+          <t>Is Valid Value</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>运行公共函数</t>
+          <t>值有效</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>RUN_COMMON_FUNCTION_DESC</t>
+          <t>IS_VALID_VALUE_DESC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Execute a common function graph by name.</t>
+          <t>Check whether the value is not None.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>执行指定名称的公共函数图。</t>
+          <t>判断值是否为非空（None）。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DICT_GET</t>
+          <t>RUN_COMMON_FUNCTION</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Dict Get</t>
+          <t>Run Common Function</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>字典获取</t>
+          <t>运行公共函数</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DICT_GET_DESC</t>
+          <t>RUN_COMMON_FUNCTION_DESC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Get a value from a dict by key.</t>
+          <t>Execute a common function graph by name.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>按 key 获取字典中的 value。</t>
+          <t>执行指定名称的公共函数图。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DICT_ADD</t>
+          <t>DICT_GET</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Dict Set</t>
+          <t>Dict Get</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>字典设置</t>
+          <t>字典获取</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DICT_ADD_DESC</t>
+          <t>DICT_GET_DESC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Set a dict value by key.</t>
+          <t>Get a value from a dict by key.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>按 key 写入字典的 value。</t>
+          <t>按 key 获取字典中的 value。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DICT_REMOVE</t>
+          <t>DICT_ADD</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Dict Remove</t>
+          <t>Dict Set</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>字典移除</t>
+          <t>字典设置</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DICT_REMOVE_DESC</t>
+          <t>DICT_ADD_DESC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Remove a key from a dict.</t>
+          <t>Set a dict value by key.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>移除字典中的指定 key。</t>
+          <t>按 key 写入字典的 value。</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DICT_CLEAR</t>
+          <t>DICT_REMOVE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Dict Clear</t>
+          <t>Dict Remove</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>字典清空</t>
+          <t>字典移除</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DICT_CLEAR_DESC</t>
+          <t>DICT_REMOVE_DESC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Clear all entries in a dict.</t>
+          <t>Remove a key from a dict.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>清空字典的所有内容。</t>
+          <t>移除字典中的指定 key。</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DICT_CONTAINS</t>
+          <t>DICT_CLEAR</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Dict Contains</t>
+          <t>Dict Clear</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>字典包含</t>
+          <t>字典清空</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DICT_CONTAINS_DESC</t>
+          <t>DICT_CLEAR_DESC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Check whether a dict contains a key.</t>
+          <t>Clear all entries in a dict.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>判断字典是否包含指定 key。</t>
+          <t>清空字典的所有内容。</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LIST_GET</t>
+          <t>DICT_CONTAINS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>List Get</t>
+          <t>Dict Contains</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>列表获取</t>
+          <t>字典包含</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LIST_GET_DESC</t>
+          <t>DICT_CONTAINS_DESC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Get a list item by index.</t>
+          <t>Check whether a dict contains a key.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>按索引获取列表元素。</t>
+          <t>判断字典是否包含指定 key。</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>LIST_APPEND</t>
+          <t>LIST_GET</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>List Append</t>
+          <t>List Get</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>列表追加</t>
+          <t>列表获取</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>LIST_APPEND_DESC</t>
+          <t>LIST_GET_DESC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Append an item to a list.</t>
+          <t>Get a list item by index.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>向列表尾部追加一个元素。</t>
+          <t>按索引获取列表元素。</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>LIST_REMOVE</t>
+          <t>LIST_APPEND</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>List Remove</t>
+          <t>List Append</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>列表移除</t>
+          <t>列表追加</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>LIST_REMOVE_DESC</t>
+          <t>LIST_APPEND_DESC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Remove a list item by index.</t>
+          <t>Append an item to a list.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>按索引移除列表元素。</t>
+          <t>向列表尾部追加一个元素。</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>LIST_FIND</t>
+          <t>LIST_REMOVE</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>List Find</t>
+          <t>List Remove</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>列表查找</t>
+          <t>列表移除</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>LIST_FIND_DESC</t>
+          <t>LIST_REMOVE_DESC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Find the index of a value in a list.</t>
+          <t>Remove a list item by index.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>查找元素在列表中的索引。</t>
+          <t>按索引移除列表元素。</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>LIST_CLEAR</t>
+          <t>LIST_FIND</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>List Clear</t>
+          <t>List Find</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>列表清空</t>
+          <t>列表查找</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>LIST_CLEAR_DESC</t>
+          <t>LIST_FIND_DESC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Clear all items in a list.</t>
+          <t>Find the index of a value in a list.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>清空列表的所有元素。</t>
+          <t>查找元素在列表中的索引。</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>LIST_CONTAINS</t>
+          <t>LIST_CLEAR</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>List Contains</t>
+          <t>List Clear</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>列表包含</t>
+          <t>列表清空</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>LIST_CONTAINS_DESC</t>
+          <t>LIST_CLEAR_DESC</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Check whether a list contains a value.</t>
+          <t>Clear all items in a list.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>判断列表是否包含指定元素。</t>
+          <t>清空列表的所有元素。</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TO_STRING</t>
+          <t>LIST_CONTAINS</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>To String</t>
+          <t>List Contains</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>转字符串</t>
+          <t>列表包含</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TO_STRING_DESC</t>
+          <t>LIST_CONTAINS_DESC</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Convert a value to string.</t>
+          <t>Check whether a list contains a value.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>将任意值转换为字符串。</t>
+          <t>判断列表是否包含指定元素。</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>GET_INT_FROM_STR</t>
+          <t>TO_STRING</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>String To Int</t>
+          <t>To String</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>字符串转整数</t>
+          <t>转字符串</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>GET_INT_FROM_STR_DESC</t>
+          <t>TO_STRING_DESC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Parse a string as int.</t>
+          <t>Convert a value to string.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>将字符串解析为整数。</t>
+          <t>将任意值转换为字符串。</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>GET_FLOAT_FROM_STR</t>
+          <t>GET_INT_FROM_STR</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>String To Float</t>
+          <t>String To Int</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>字符串转浮点</t>
+          <t>字符串转整数</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>GET_FLOAT_FROM_STR_DESC</t>
+          <t>GET_INT_FROM_STR_DESC</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Parse a string as float.</t>
+          <t>Parse a string as int.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>将字符串解析为浮点数。</t>
+          <t>将字符串解析为整数。</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STRING_CONCAT</t>
+          <t>GET_FLOAT_FROM_STR</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>String Concat</t>
+          <t>String To Float</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>字符串拼接</t>
+          <t>字符串转浮点</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STRING_CONCAT_DESC</t>
+          <t>GET_FLOAT_FROM_STR_DESC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Concatenate two strings.</t>
+          <t>Parse a string as float.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>拼接两个字符串。</t>
+          <t>将字符串解析为浮点数。</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STRING_CONTAINS</t>
+          <t>STRING_CONCAT</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>String Contains</t>
+          <t>String Concat</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>字符串包含</t>
+          <t>字符串拼接</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STRING_CONTAINS_DESC</t>
+          <t>STRING_CONCAT_DESC</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Check whether a string contains a substring.</t>
+          <t>Concatenate two strings.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>判断字符串是否包含子串。</t>
+          <t>拼接两个字符串。</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STRING_LENGTH</t>
+          <t>STRING_CONTAINS</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>String Length</t>
+          <t>String Contains</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>字符串长度</t>
+          <t>字符串包含</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STRING_LENGTH_DESC</t>
+          <t>STRING_CONTAINS_DESC</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Get string length.</t>
+          <t>Check whether a string contains a substring.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>获取字符串长度。</t>
+          <t>判断字符串是否包含子串。</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STRING_FIND</t>
+          <t>STRING_LENGTH</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>String Find</t>
+          <t>String Length</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>字符串查找</t>
+          <t>字符串长度</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STRING_FIND_DESC</t>
+          <t>STRING_LENGTH_DESC</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Find the first occurrence index of a substring.</t>
+          <t>Get string length.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>查找子串首次出现的位置。</t>
+          <t>获取字符串长度。</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STRING_REPLACE</t>
+          <t>STRING_FIND</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>String Replace</t>
+          <t>String Find</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>字符串替换</t>
+          <t>字符串查找</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STRING_REPLACE_DESC</t>
+          <t>STRING_FIND_DESC</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Replace occurrences of a substring.</t>
+          <t>Find the first occurrence index of a substring.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>将子串替换为新字符串。</t>
+          <t>查找子串首次出现的位置。</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STRING_SPLIT</t>
+          <t>STRING_REPLACE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>String Split</t>
+          <t>String Replace</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>字符串分割</t>
+          <t>字符串替换</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STRING_SPLIT_DESC</t>
+          <t>STRING_REPLACE_DESC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Split a string by delimiter.</t>
+          <t>Replace occurrences of a substring.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>按分隔符拆分字符串。</t>
+          <t>将子串替换为新字符串。</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STRING_SUBSTRING</t>
+          <t>STRING_SPLIT</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Substring</t>
+          <t>String Split</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>字符串截取</t>
+          <t>字符串分割</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STRING_SUBSTRING_DESC</t>
+          <t>STRING_SPLIT_DESC</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Get a substring by start/end indices.</t>
+          <t>Split a string by delimiter.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>按起止索引截取子串。</t>
+          <t>按分隔符拆分字符串。</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STRING_TO_LOWER</t>
+          <t>STRING_SUBSTRING</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>To Lower</t>
+          <t>Substring</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>转小写</t>
+          <t>字符串截取</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STRING_TO_LOWER_DESC</t>
+          <t>STRING_SUBSTRING_DESC</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Convert a string to lowercase.</t>
+          <t>Get a substring by start/end indices.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>将字符串转换为小写。</t>
+          <t>按起止索引截取子串。</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STRING_TO_UPPER</t>
+          <t>STRING_TO_LOWER</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>To Upper</t>
+          <t>To Lower</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>转大写</t>
+          <t>转小写</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STRING_TO_UPPER_DESC</t>
+          <t>STRING_TO_LOWER_DESC</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Convert a string to uppercase.</t>
+          <t>Convert a string to lowercase.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>将字符串转换为大写。</t>
+          <t>将字符串转换为小写。</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STRING_STRIP</t>
+          <t>STRING_TO_UPPER</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Trim</t>
+          <t>To Upper</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>去首尾空白</t>
+          <t>转大写</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STRING_STRIP_DESC</t>
+          <t>STRING_TO_UPPER_DESC</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Trim leading/trailing whitespace.</t>
+          <t>Convert a string to uppercase.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>移除字符串首尾空白字符。</t>
+          <t>将字符串转换为大写。</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EDIT_SOUND_FILTER</t>
+          <t>STRING_STRIP</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Edit Sound Filter</t>
+          <t>Trim</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>编辑音效滤镜</t>
+          <t>去首尾空白</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EDIT_SOUND_FILTER_DESC</t>
+          <t>STRING_STRIP_DESC</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Set a property on the sound filter.</t>
+          <t>Trim leading/trailing whitespace.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>设置音效滤镜的指定属性。</t>
+          <t>移除字符串首尾空白字符。</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EDIT_MUSIC_FILTER</t>
+          <t>EDIT_SOUND_FILTER</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Edit Music Filter</t>
+          <t>Edit Sound Filter</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>编辑音乐滤镜</t>
+          <t>编辑音效滤镜</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EDIT_MUSIC_FILTER_DESC</t>
+          <t>EDIT_SOUND_FILTER_DESC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Set a property on the music filter.</t>
+          <t>Set a property on the sound filter.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>设置音乐滤镜的指定属性。</t>
+          <t>设置音效滤镜的指定属性。</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>PLAY_SOUND</t>
+          <t>EDIT_MUSIC_FILTER</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Play Sound</t>
+          <t>Edit Music Filter</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>播放音效</t>
+          <t>编辑音乐滤镜</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PLAY_SOUND_DESC</t>
+          <t>EDIT_MUSIC_FILTER_DESC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Play a sound effect, optionally with filter.</t>
+          <t>Set a property on the music filter.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>播放音效，可选择是否应用滤镜。</t>
+          <t>设置音乐滤镜的指定属性。</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PLAY_MUSIC</t>
+          <t>PLAY_SOUND</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Play Music</t>
+          <t>Play Sound</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>播放音乐</t>
+          <t>播放音效</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PLAY_MUSIC_DESC</t>
+          <t>PLAY_SOUND_DESC</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Play background music, optionally with filter.</t>
+          <t>Play a sound effect, optionally with filter.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>播放背景音乐，可选择是否应用滤镜。</t>
+          <t>播放音效，可选择是否应用滤镜。</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PLAY_VIDEO</t>
+          <t>PLAY_MUSIC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Play Video</t>
+          <t>Play Music</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>播放视频</t>
+          <t>播放音乐</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PLAY_VIDEO_DESC</t>
+          <t>PLAY_MUSIC_DESC</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Play a video file with mute and skippable options.</t>
+          <t>Play background music, optionally with filter.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>播放视频文件，可设置静音与可跳过。</t>
+          <t>播放背景音乐，可选择是否应用滤镜。</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BUILD_VECTOR2F</t>
+          <t>PLAY_VIDEO</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Build Vector2f</t>
+          <t>Play Video</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>构建 Vector2f</t>
+          <t>播放视频</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BUILD_VECTOR2F_DESC</t>
+          <t>PLAY_VIDEO_DESC</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Build a Vector2f from x and y.</t>
+          <t>Play a video file with mute and skippable options.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>从 x、y 构建 Vector2f。</t>
+          <t>播放视频文件，可设置静音与可跳过。</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BUILD_VECTOR2I</t>
+          <t>BUILD_VECTOR2F</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Build Vector2i</t>
+          <t>Build Vector2f</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>构建 Vector2i</t>
+          <t>构建 Vector2f</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BUILD_VECTOR2I_DESC</t>
+          <t>BUILD_VECTOR2F_DESC</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Build a Vector2i from x and y.</t>
+          <t>Build a Vector2f from x and y.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>从 x、y 构建 Vector2i。</t>
+          <t>从 x、y 构建 Vector2f。</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BUILD_VECTOR2U</t>
+          <t>BUILD_VECTOR2I</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Build Vector2u</t>
+          <t>Build Vector2i</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>构建 Vector2u</t>
+          <t>构建 Vector2i</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BUILD_VECTOR2U_DESC</t>
+          <t>BUILD_VECTOR2I_DESC</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Build a Vector2u from x and y.</t>
+          <t>Build a Vector2i from x and y.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>从 x、y 构建 Vector2u。</t>
+          <t>从 x、y 构建 Vector2i。</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BUILD_VECTOR3F</t>
+          <t>BUILD_VECTOR2U</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Build Vector3f</t>
+          <t>Build Vector2u</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>构建 Vector3f</t>
+          <t>构建 Vector2u</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BUILD_VECTOR3F_DESC</t>
+          <t>BUILD_VECTOR2U_DESC</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Build a Vector3f from x, y, z.</t>
+          <t>Build a Vector2u from x and y.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>从 x、y、z 构建 Vector3f。</t>
+          <t>从 x、y 构建 Vector2u。</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BUILD_VECTOR3I</t>
+          <t>BUILD_VECTOR3F</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Build Vector3i</t>
+          <t>Build Vector3f</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>构建 Vector3i</t>
+          <t>构建 Vector3f</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BUILD_VECTOR3I_DESC</t>
+          <t>BUILD_VECTOR3F_DESC</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Build a Vector3i from x, y, z.</t>
+          <t>Build a Vector3f from x, y, z.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>从 x、y、z 构建 Vector3i。</t>
+          <t>从 x、y、z 构建 Vector3f。</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>IS_NEAR_ZERO</t>
+          <t>BUILD_VECTOR3I</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Is Near Zero</t>
+          <t>Build Vector3i</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>是否接近零</t>
+          <t>构建 Vector3i</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>IS_NEAR_ZERO_DESC</t>
+          <t>BUILD_VECTOR3I_DESC</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Check whether a number is near 0 (epsilon).</t>
+          <t>Build a Vector3i from x, y, z.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>判断数值是否接近 0（epsilon）。</t>
+          <t>从 x、y、z 构建 Vector3i。</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>IS_VECTOR2_NEAR_ZERO</t>
+          <t>IS_NEAR_ZERO</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Is Vector2 Near Zero</t>
+          <t>Is Near Zero</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>二维向量接近零</t>
+          <t>是否接近零</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>IS_VECTOR2_NEAR_ZERO_DESC</t>
+          <t>IS_NEAR_ZERO_DESC</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Check whether a Vector2 is near zero (epsilon).</t>
+          <t>Check whether a number is near 0 (epsilon).</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>判断 Vector2 是否接近零向量（epsilon）。</t>
+          <t>判断数值是否接近 0（epsilon）。</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>IS_VECTOR3_NEAR_ZERO</t>
+          <t>IS_VECTOR2_NEAR_ZERO</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Is Vector3 Near Zero</t>
+          <t>Is Vector2 Near Zero</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>三维向量接近零</t>
+          <t>二维向量接近零</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>IS_VECTOR3_NEAR_ZERO_DESC</t>
+          <t>IS_VECTOR2_NEAR_ZERO_DESC</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Check whether a Vector3 is near zero (epsilon).</t>
+          <t>Check whether a Vector2 is near zero (epsilon).</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>判断 Vector3 是否接近零向量（epsilon）。</t>
+          <t>判断 Vector2 是否接近零向量（epsilon）。</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>VECTOR2F_ROUND</t>
+          <t>IS_VECTOR3_NEAR_ZERO</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Vector2 Round</t>
+          <t>Is Vector3 Near Zero</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>二维向量四舍五入</t>
+          <t>三维向量接近零</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>VECTOR2F_ROUND_DESC</t>
+          <t>IS_VECTOR3_NEAR_ZERO_DESC</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Round each component of a Vector2.</t>
+          <t>Check whether a Vector3 is near zero (epsilon).</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>对 Vector2 的各分量进行四舍五入。</t>
+          <t>判断 Vector3 是否接近零向量（epsilon）。</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>VECTOR2F_FLOOR</t>
+          <t>VECTOR2F_ROUND</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Vector2 Floor</t>
+          <t>Vector2 Round</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>二维向量向下取整</t>
+          <t>二维向量四舍五入</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>VECTOR2F_FLOOR_DESC</t>
+          <t>VECTOR2F_ROUND_DESC</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Floor each component of a Vector2.</t>
+          <t>Round each component of a Vector2.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>对 Vector2 的各分量向下取整。</t>
+          <t>对 Vector2 的各分量进行四舍五入。</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>VECTOR2F_CEIL</t>
+          <t>VECTOR2F_FLOOR</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Vector2 Ceil</t>
+          <t>Vector2 Floor</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>二维向量向上取整</t>
+          <t>二维向量向下取整</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>VECTOR2F_CEIL_DESC</t>
+          <t>VECTOR2F_FLOOR_DESC</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Ceil each component of a Vector2.</t>
+          <t>Floor each component of a Vector2.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>对 Vector2 的各分量向上取整。</t>
+          <t>对 Vector2 的各分量向下取整。</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>TO_VECTOR2F</t>
+          <t>VECTOR2F_CEIL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>To Vector2f</t>
+          <t>Vector2 Ceil</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>转 Vector2f</t>
+          <t>二维向量向上取整</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>TO_VECTOR2F_DESC</t>
+          <t>VECTOR2F_CEIL_DESC</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Convert Vector2i/Vector2u to Vector2f.</t>
+          <t>Ceil each component of a Vector2.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>将 Vector2i/Vector2u 转换为 Vector2f。</t>
+          <t>对 Vector2 的各分量向上取整。</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>TO_VECTOR2I</t>
+          <t>TO_VECTOR2F</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>To Vector2i</t>
+          <t>To Vector2f</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>转 Vector2i</t>
+          <t>转 Vector2f</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>TO_VECTOR2I_DESC</t>
+          <t>TO_VECTOR2F_DESC</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Convert Vector2f/Vector2u to Vector2i.</t>
+          <t>Convert Vector2i/Vector2u to Vector2f.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>将 Vector2f/Vector2u 转换为 Vector2i。</t>
+          <t>将 Vector2i/Vector2u 转换为 Vector2f。</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>TO_VECTOR2U</t>
+          <t>TO_VECTOR2I</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>To Vector2u</t>
+          <t>To Vector2i</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>转 Vector2u</t>
+          <t>转 Vector2i</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>TO_VECTOR2U_DESC</t>
+          <t>TO_VECTOR2I_DESC</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Convert Vector2f/Vector2i to Vector2u.</t>
+          <t>Convert Vector2f/Vector2u to Vector2i.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>将 Vector2f/Vector2i 转换为 Vector2u。</t>
+          <t>将 Vector2f/Vector2u 转换为 Vector2i。</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>TO_VECTOR3F</t>
+          <t>TO_VECTOR2U</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>To Vector3f</t>
+          <t>To Vector2u</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>转 Vector3f</t>
+          <t>转 Vector2u</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>TO_VECTOR3F_DESC</t>
+          <t>TO_VECTOR2U_DESC</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Convert Vector3i to Vector3f.</t>
+          <t>Convert Vector2f/Vector2i to Vector2u.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>将 Vector3i 转换为 Vector3f。</t>
+          <t>将 Vector2f/Vector2i 转换为 Vector2u。</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>TO_VECTOR3I</t>
+          <t>TO_VECTOR3F</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>To Vector3i</t>
+          <t>To Vector3f</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>转 Vector3i</t>
+          <t>转 Vector3f</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>TO_VECTOR3I_DESC</t>
+          <t>TO_VECTOR3F_DESC</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Convert Vector3f to Vector3i.</t>
+          <t>Convert Vector3i to Vector3f.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>将 Vector3f 转换为 Vector3i。</t>
+          <t>将 Vector3i 转换为 Vector3f。</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>TO_INT_RECT</t>
+          <t>TO_VECTOR3I</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Build IntRect</t>
+          <t>To Vector3i</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>构建 IntRect</t>
+          <t>转 Vector3i</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>TO_INT_RECT_DESC</t>
+          <t>TO_VECTOR3I_DESC</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Build an IntRect from x, y, width, height.</t>
+          <t>Convert Vector3f to Vector3i.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>从 x、y、width、height 构建 IntRect。</t>
+          <t>将 Vector3f 转换为 Vector3i。</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>TO_FLOAT_RECT</t>
+          <t>TO_INT_RECT</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Build FloatRect</t>
+          <t>Build IntRect</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>构建 FloatRect</t>
+          <t>构建 IntRect</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>TO_FLOAT_RECT_DESC</t>
+          <t>TO_INT_RECT_DESC</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Build a FloatRect from x, y, width, height.</t>
+          <t>Build an IntRect from x, y, width, height.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>从 x、y、width、height 构建 FloatRect。</t>
+          <t>从 x、y、width、height 构建 IntRect。</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CLAMP</t>
+          <t>TO_FLOAT_RECT</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Clamp</t>
+          <t>Build FloatRect</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>限制范围</t>
+          <t>构建 FloatRect</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CLAMP_DESC</t>
+          <t>TO_FLOAT_RECT_DESC</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Clamp a value between min and max.</t>
+          <t>Build a FloatRect from x, y, width, height.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>将值限制在最小值与最大值之间。</t>
+          <t>从 x、y、width、height 构建 FloatRect。</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>LERP</t>
+          <t>CLAMP</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Lerp</t>
+          <t>Clamp</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>线性插值</t>
+          <t>限制范围</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>LERP_DESC</t>
+          <t>CLAMP_DESC</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Linear interpolation between a and b by t.</t>
+          <t>Clamp a value between min and max.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>在 a 与 b 之间进行线性插值（t）。</t>
+          <t>将值限制在最小值与最大值之间。</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>LERP</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Abs</t>
+          <t>Lerp</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>绝对值</t>
+          <t>线性插值</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ABS_DESC</t>
+          <t>LERP_DESC</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Get the absolute value.</t>
+          <t>Linear interpolation between a and b by t.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>返回数值的绝对值。</t>
+          <t>在 a 与 b 之间进行线性插值（t）。</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>TO_INT</t>
+          <t>ABS</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>To Int</t>
+          <t>Abs</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>转整数</t>
+          <t>绝对值</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>TO_INT_DESC</t>
+          <t>ABS_DESC</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Convert a number to int.</t>
+          <t>Get the absolute value.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>将数值转换为整数。</t>
+          <t>返回数值的绝对值。</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>TO_FLOAT</t>
+          <t>TO_INT</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>To Float</t>
+          <t>To Int</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>转浮点</t>
+          <t>转整数</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>TO_FLOAT_DESC</t>
+          <t>TO_INT_DESC</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Convert a number to float.</t>
+          <t>Convert a number to int.</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>将数值转换为浮点数。</t>
+          <t>将数值转换为整数。</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>MAX</t>
+          <t>TO_FLOAT</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>To Float</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>最大值</t>
+          <t>转浮点</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>MAX_DESC</t>
+          <t>TO_FLOAT_DESC</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Get the maximum value in a list.</t>
+          <t>Convert a number to float.</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>返回列表中的最大值。</t>
+          <t>将数值转换为浮点数。</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MAX</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Min</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>最小值</t>
+          <t>最大值</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>MIN_DESC</t>
+          <t>MAX_DESC</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Get the minimum value in a list.</t>
+          <t>Get the maximum value in a list.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>返回列表中的最小值。</t>
+          <t>返回列表中的最大值。</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>SQRT</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Sqrt</t>
+          <t>Min</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>平方根</t>
+          <t>最小值</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>SQRT_DESC</t>
+          <t>MIN_DESC</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Compute the square root.</t>
+          <t>Get the minimum value in a list.</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>计算平方根。</t>
+          <t>返回列表中的最小值。</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>POW</t>
+          <t>SQRT</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Pow</t>
+          <t>Sqrt</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>幂运算</t>
+          <t>平方根</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>POW_DESC</t>
+          <t>SQRT_DESC</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Compute base raised to exp.</t>
+          <t>Compute the square root.</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>计算 base 的 exp 次幂。</t>
+          <t>计算平方根。</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>VECTOR2_DISTANCE</t>
+          <t>POW</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Vector2 Distance</t>
+          <t>Pow</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>二维距离</t>
+          <t>幂运算</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>VECTOR2_DISTANCE_DESC</t>
+          <t>POW_DESC</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Compute distance between two 2D vectors.</t>
+          <t>Compute base raised to exp.</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>计算两个二维向量之间的距离。</t>
+          <t>计算 base 的 exp 次幂。</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>VECTOR3_DISTANCE</t>
+          <t>VECTOR2_DISTANCE</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Vector3 Distance</t>
+          <t>Vector2 Distance</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>三维距离</t>
+          <t>二维距离</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>VECTOR3_DISTANCE_DESC</t>
+          <t>VECTOR2_DISTANCE_DESC</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Compute distance between two 3D vectors.</t>
+          <t>Compute distance between two 2D vectors.</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>计算两个三维向量之间的距离。</t>
+          <t>计算两个二维向量之间的距离。</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>VECTOR2_DOT</t>
+          <t>VECTOR3_DISTANCE</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Vector2 Dot</t>
+          <t>Vector3 Distance</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>二维点积</t>
+          <t>三维距离</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>VECTOR2_DOT_DESC</t>
+          <t>VECTOR3_DISTANCE_DESC</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Compute dot product for 2D vectors.</t>
+          <t>Compute distance between two 3D vectors.</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>计算二维向量点积。</t>
+          <t>计算两个三维向量之间的距离。</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>VECTOR3_DOT</t>
+          <t>VECTOR2_DOT</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Vector3 Dot</t>
+          <t>Vector2 Dot</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>三维点积</t>
+          <t>二维点积</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>VECTOR3_DOT_DESC</t>
+          <t>VECTOR2_DOT_DESC</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Compute dot product for 3D vectors.</t>
+          <t>Compute dot product for 2D vectors.</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>计算三维向量点积。</t>
+          <t>计算二维向量点积。</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>VECTOR2_CROSS</t>
+          <t>VECTOR3_DOT</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Vector2 Cross</t>
+          <t>Vector3 Dot</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>二维叉积</t>
+          <t>三维点积</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>VECTOR2_CROSS_DESC</t>
+          <t>VECTOR3_DOT_DESC</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Compute cross product for 2D vectors.</t>
+          <t>Compute dot product for 3D vectors.</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>计算二维向量叉积。</t>
+          <t>计算三维向量点积。</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>VECTOR3_CROSS</t>
+          <t>VECTOR2_CROSS</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Vector3 Cross</t>
+          <t>Vector2 Cross</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>三维叉积</t>
+          <t>二维叉积</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>VECTOR3_CROSS_DESC</t>
+          <t>VECTOR2_CROSS_DESC</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Compute cross product for 3D vectors.</t>
+          <t>Compute cross product for 2D vectors.</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>计算三维向量叉积。</t>
+          <t>计算二维向量叉积。</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>VECTOR2_LENGTH</t>
+          <t>VECTOR3_CROSS</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Vector2 Length</t>
+          <t>Vector3 Cross</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>二维长度</t>
+          <t>三维叉积</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>VECTOR2_LENGTH_DESC</t>
+          <t>VECTOR3_CROSS_DESC</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Compute length of a 2D vector.</t>
+          <t>Compute cross product for 3D vectors.</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>计算二维向量长度。</t>
+          <t>计算三维向量叉积。</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>VECTOR3_LENGTH</t>
+          <t>VECTOR2_LENGTH</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Vector3 Length</t>
+          <t>Vector2 Length</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>三维长度</t>
+          <t>二维长度</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>VECTOR3_LENGTH_DESC</t>
+          <t>VECTOR2_LENGTH_DESC</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Compute length of a 3D vector.</t>
+          <t>Compute length of a 2D vector.</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>计算三维向量长度。</t>
+          <t>计算二维向量长度。</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>VECTOR2_LENGTH_SQUARED</t>
+          <t>VECTOR3_LENGTH</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Vector2 Length Squared</t>
+          <t>Vector3 Length</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>二维长度平方</t>
+          <t>三维长度</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>VECTOR2_LENGTH_SQUARED_DESC</t>
+          <t>VECTOR3_LENGTH_DESC</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Compute squared length of a 2D vector.</t>
+          <t>Compute length of a 3D vector.</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>计算二维向量长度的平方。</t>
+          <t>计算三维向量长度。</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>VECTOR3_LENGTH_SQUARED</t>
+          <t>VECTOR2_LENGTH_SQUARED</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Vector3 Length Squared</t>
+          <t>Vector2 Length Squared</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>三维长度平方</t>
+          <t>二维长度平方</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>VECTOR3_LENGTH_SQUARED_DESC</t>
+          <t>VECTOR2_LENGTH_SQUARED_DESC</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Compute squared length of a 3D vector.</t>
+          <t>Compute squared length of a 2D vector.</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>计算三维向量长度的平方。</t>
+          <t>计算二维向量长度的平方。</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>VECTOR2_NORMALIZED</t>
+          <t>VECTOR3_LENGTH_SQUARED</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Vector2 Normalize</t>
+          <t>Vector3 Length Squared</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>二维归一化</t>
+          <t>三维长度平方</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>VECTOR2_NORMALIZED_DESC</t>
+          <t>VECTOR3_LENGTH_SQUARED_DESC</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Normalize a 2D vector.</t>
+          <t>Compute squared length of a 3D vector.</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>将二维向量归一化。</t>
+          <t>计算三维向量长度的平方。</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>VECTOR3_NORMALIZED</t>
+          <t>VECTOR2_NORMALIZED</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Vector3 Normalize</t>
+          <t>Vector2 Normalize</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>三维归一化</t>
+          <t>二维归一化</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>VECTOR3_NORMALIZED_DESC</t>
+          <t>VECTOR2_NORMALIZED_DESC</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Normalize a 3D vector.</t>
+          <t>Normalize a 2D vector.</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>将三维向量归一化。</t>
+          <t>将二维向量归一化。</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>GET_ANGLE</t>
+          <t>VECTOR3_NORMALIZED</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Get Angle</t>
+          <t>Vector3 Normalize</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>获取角度</t>
+          <t>三维归一化</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>GET_ANGLE_DESC</t>
+          <t>VECTOR3_NORMALIZED_DESC</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Get the angle of a 2D vector.</t>
+          <t>Normalize a 3D vector.</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>获取二维向量的角度。</t>
+          <t>将三维向量归一化。</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>GET_ANGLE_TO</t>
+          <t>GET_ANGLE</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Get Angle To</t>
+          <t>Get Angle</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>获取指向角度</t>
+          <t>获取角度</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>GET_ANGLE_TO_DESC</t>
+          <t>GET_ANGLE_DESC</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Get the angle from v1 to v2.</t>
+          <t>Get the angle of a 2D vector.</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>获取从 v1 指向 v2 的角度。</t>
+          <t>获取二维向量的角度。</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>AS_DEGREES</t>
+          <t>GET_ANGLE_TO</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>As Degrees</t>
+          <t>Get Angle To</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>角度转度</t>
+          <t>获取指向角度</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>AS_DEGREES_DESC</t>
+          <t>GET_ANGLE_TO_DESC</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Convert an Angle to degrees.</t>
+          <t>Get the angle from v1 to v2.</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>将角度对象转换为度数值。</t>
+          <t>获取从 v1 指向 v2 的角度。</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>AS_RADIANS</t>
+          <t>AS_DEGREES</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>As Radians</t>
+          <t>As Degrees</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>角度转弧度</t>
+          <t>角度转度</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>AS_RADIANS_DESC</t>
+          <t>AS_DEGREES_DESC</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Convert an Angle to radians.</t>
+          <t>Convert an Angle to degrees.</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>将角度对象转换为弧度值。</t>
+          <t>将角度对象转换为度数值。</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>VECTOR2_COMPONENT_WISE_DIV</t>
+          <t>AS_RADIANS</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Component-wise Div</t>
+          <t>As Radians</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>按分量相除</t>
+          <t>角度转弧度</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>VECTOR2_COMPONENT_WISE_DIV_DESC</t>
+          <t>AS_RADIANS_DESC</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Divide vectors component-wise.</t>
+          <t>Convert an Angle to radians.</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>对向量的每个分量分别相除。</t>
+          <t>将角度对象转换为弧度值。</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>VECTOR2_COMPONENT_WISE_MUL</t>
+          <t>VECTOR2_COMPONENT_WISE_DIV</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Component-wise Mul</t>
+          <t>Component-wise Div</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>按分量相乘</t>
+          <t>按分量相除</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>VECTOR2_COMPONENT_WISE_MUL_DESC</t>
+          <t>VECTOR2_COMPONENT_WISE_DIV_DESC</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Multiply vectors component-wise.</t>
+          <t>Divide vectors component-wise.</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>对向量的每个分量分别相乘。</t>
+          <t>对向量的每个分量分别相除。</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>VECTOR2_PERPENDICULAR</t>
+          <t>VECTOR2_COMPONENT_WISE_MUL</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Perpendicular</t>
+          <t>Component-wise Mul</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>垂直向量</t>
+          <t>按分量相乘</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>VECTOR2_PERPENDICULAR_DESC</t>
+          <t>VECTOR2_COMPONENT_WISE_MUL_DESC</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Get a perpendicular vector.</t>
+          <t>Multiply vectors component-wise.</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>获取与二维向量垂直的向量。</t>
+          <t>对向量的每个分量分别相乘。</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>VECTOR2_PROJECTED_ONTO</t>
+          <t>VECTOR2_PERPENDICULAR</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Project Onto</t>
+          <t>Perpendicular</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>投影到轴</t>
+          <t>垂直向量</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>VECTOR2_PROJECTED_ONTO_DESC</t>
+          <t>VECTOR2_PERPENDICULAR_DESC</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Project a vector onto an axis.</t>
+          <t>Get a perpendicular vector.</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>将二维向量投影到指定轴向量上。</t>
+          <t>获取与二维向量垂直的向量。</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>VECTOR2_ROTATED_BY</t>
+          <t>VECTOR2_PROJECTED_ONTO</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Rotate Vector</t>
+          <t>Project Onto</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>旋转向量</t>
+          <t>投影到轴</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>VECTOR2_ROTATED_BY_DESC</t>
+          <t>VECTOR2_PROJECTED_ONTO_DESC</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Rotate a 2D vector by an angle.</t>
+          <t>Project a vector onto an axis.</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>按指定角度旋转二维向量。</t>
+          <t>将二维向量投影到指定轴向量上。</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>DEGREES_TO_ANGLE</t>
+          <t>VECTOR2_ROTATED_BY</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Degrees To Angle</t>
+          <t>Rotate Vector</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>度转角度对象</t>
+          <t>旋转向量</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>DEGREES_TO_ANGLE_DESC</t>
+          <t>VECTOR2_ROTATED_BY_DESC</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Convert degrees value to Angle.</t>
+          <t>Rotate a 2D vector by an angle.</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>将度数值转换为 Angle。</t>
+          <t>按指定角度旋转二维向量。</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>RADIANS_TO_ANGLE</t>
+          <t>DEGREES_TO_ANGLE</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Radians To Angle</t>
+          <t>Degrees To Angle</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>弧度转角度对象</t>
+          <t>度转角度对象</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>RADIANS_TO_ANGLE_DESC</t>
+          <t>DEGREES_TO_ANGLE_DESC</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Convert radians value to Angle.</t>
+          <t>Convert degrees value to Angle.</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>将弧度值转换为 Angle。</t>
+          <t>将度数值转换为 Angle。</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>RANDOM_INT</t>
+          <t>RADIANS_TO_ANGLE</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Random Int</t>
+          <t>Radians To Angle</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>随机整数</t>
+          <t>弧度转角度对象</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>RANDOM_INT_DESC</t>
+          <t>RADIANS_TO_ANGLE_DESC</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Generate a random int in range.</t>
+          <t>Convert radians value to Angle.</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>生成指定范围内的随机整数。</t>
+          <t>将弧度值转换为 Angle。</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>RANDOM_FLOAT</t>
+          <t>RANDOM_INT</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Random Float</t>
+          <t>Random Int</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>随机浮点</t>
+          <t>随机整数</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>RANDOM_FLOAT_DESC</t>
+          <t>RANDOM_INT_DESC</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Generate a random float in range.</t>
+          <t>Generate a random int in range.</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>生成指定范围内的随机浮点数。</t>
+          <t>生成指定范围内的随机整数。</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>GCD</t>
+          <t>RANDOM_FLOAT</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>GCD</t>
+          <t>Random Float</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>最大公约数</t>
+          <t>随机浮点</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>GCD_DESC</t>
+          <t>RANDOM_FLOAT_DESC</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Compute greatest common divisor.</t>
+          <t>Generate a random float in range.</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>计算最大公约数。</t>
+          <t>生成指定范围内的随机浮点数。</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>LCM</t>
+          <t>GCD</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>LCM</t>
+          <t>GCD</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>最小公倍数</t>
+          <t>最大公约数</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>LCM_DESC</t>
+          <t>GCD_DESC</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Compute least common multiple.</t>
+          <t>Compute greatest common divisor.</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>计算最小公倍数。</t>
+          <t>计算最大公约数。</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>LCM</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>LCM</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>最小公倍数</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ADD_DESC</t>
+          <t>LCM_DESC</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Compute a + b.</t>
+          <t>Compute least common multiple.</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>计算 a + b。</t>
+          <t>计算最小公倍数。</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SUB</t>
+          <t>ADD</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SUB_DESC</t>
+          <t>ADD_DESC</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Compute a - b.</t>
+          <t>Compute a + b.</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>计算 a - b。</t>
+          <t>计算 a + b。</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>MUL</t>
+          <t>SUB</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>MUL_DESC</t>
+          <t>SUB_DESC</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Compute a * b.</t>
+          <t>Compute a - b.</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>计算 a * b。</t>
+          <t>计算 a - b。</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>DIV</t>
+          <t>MUL</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>*</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>*</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>DIV_DESC</t>
+          <t>MUL_DESC</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Compute a / b.</t>
+          <t>Compute a * b.</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>计算 a / b。</t>
+          <t>计算 a * b。</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>MOD</t>
+          <t>DIV</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Modulo</t>
+          <t>/</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>取模</t>
+          <t>/</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>MOD_DESC</t>
+          <t>DIV_DESC</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Compute a % b.</t>
+          <t>Compute a / b.</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>计算 a % b。</t>
+          <t>计算 a / b。</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>POW_OP</t>
+          <t>MOD</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>**</t>
+          <t>Modulo</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>**</t>
+          <t>取模</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>POW_OP_DESC</t>
+          <t>MOD_DESC</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Compute a ** b.</t>
+          <t>Compute a % b.</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>计算 a ** b。</t>
+          <t>计算 a % b。</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
+          <t>POW_OP</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>POW_OP_DESC</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Compute a ** b.</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>计算 a ** b。</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
           <t>EQUALS</t>
         </is>
       </c>
-      <c r="B212" s="1">
+      <c r="B214" s="1">
         <f>=</f>
         <v/>
       </c>
-      <c r="C212" s="1">
+      <c r="C214" s="1">
         <f>=</f>
         <v/>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>EQUALS_DESC</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Check whether a equals b.</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>判断 a 是否等于 b。</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>NOT_EQUALS</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>!=</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>!=</t>
-        </is>
-      </c>
-    </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>NOT_EQUALS_DESC</t>
+          <t>EQUALS_DESC</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Check whether a does not equal b.</t>
+          <t>Check whether a equals b.</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>判断 a 是否不等于 b。</t>
+          <t>判断 a 是否等于 b。</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>LESS</t>
+          <t>NOT_EQUALS</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>!=</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>!=</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>LESS_DESC</t>
+          <t>NOT_EQUALS_DESC</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Check whether a is less than b.</t>
+          <t>Check whether a does not equal b.</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>判断 a 是否小于 b。</t>
+          <t>判断 a 是否不等于 b。</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>LESS_EQUALS</t>
+          <t>LESS</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>&lt;=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>&lt;=</t>
+          <t>&lt;</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>LESS_EQUALS_DESC</t>
+          <t>LESS_DESC</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Check whether a is less than or equal to b.</t>
+          <t>Check whether a is less than b.</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>判断 a 是否小于等于 b。</t>
+          <t>判断 a 是否小于 b。</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>GREATER</t>
+          <t>LESS_EQUALS</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>&gt;</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>&gt;</t>
+          <t>&lt;=</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>GREATER_DESC</t>
+          <t>LESS_EQUALS_DESC</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Check whether a is greater than b.</t>
+          <t>Check whether a is less than or equal to b.</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>判断 a 是否大于 b。</t>
+          <t>判断 a 是否小于等于 b。</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>GREATER_EQUALS</t>
+          <t>GREATER</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>&gt;=</t>
+          <t>&gt;</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>&gt;=</t>
+          <t>&gt;</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>GREATER_EQUALS_DESC</t>
+          <t>GREATER_DESC</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Check whether a is greater than or equal to b.</t>
+          <t>Check whether a is greater than b.</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>判断 a 是否大于等于 b。</t>
+          <t>判断 a 是否大于 b。</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>AND</t>
+          <t>GREATER_EQUALS</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>And</t>
+          <t>&gt;=</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>与</t>
+          <t>&gt;=</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>AND_DESC</t>
+          <t>GREATER_EQUALS_DESC</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Boolean AND.</t>
+          <t>Check whether a is greater than or equal to b.</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>布尔与运算。</t>
+          <t>判断 a 是否大于等于 b。</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>AND</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Or</t>
+          <t>And</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>或</t>
+          <t>与</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>OR_DESC</t>
+          <t>AND_DESC</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Boolean OR.</t>
+          <t>Boolean AND.</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>布尔或运算。</t>
+          <t>布尔与运算。</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>NOT</t>
+          <t>OR</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Not</t>
+          <t>Or</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>非</t>
+          <t>或</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>NOT_DESC</t>
+          <t>OR_DESC</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Boolean NOT.</t>
+          <t>Boolean OR.</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>布尔非运算。</t>
+          <t>布尔或运算。</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>XOR</t>
+          <t>NOT</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Xor</t>
+          <t>Not</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>异或</t>
+          <t>非</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>XOR_DESC</t>
+          <t>NOT_DESC</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Boolean XOR.</t>
+          <t>Boolean NOT.</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>布尔异或运算。</t>
+          <t>布尔非运算。</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>NAND</t>
+          <t>XOR</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Nand</t>
+          <t>Xor</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>与非</t>
+          <t>异或</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>NAND_DESC</t>
+          <t>XOR_DESC</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Boolean NAND.</t>
+          <t>Boolean XOR.</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>布尔与非运算。</t>
+          <t>布尔异或运算。</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>NOR</t>
+          <t>NAND</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Nor</t>
+          <t>Nand</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>或非</t>
+          <t>与非</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>NOR_DESC</t>
+          <t>NAND_DESC</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Boolean NOR.</t>
+          <t>Boolean NAND.</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>布尔或非运算。</t>
+          <t>布尔与非运算。</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>XNOR</t>
+          <t>NOR</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Xnor</t>
+          <t>Nor</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>同或</t>
+          <t>或非</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>XNOR_DESC</t>
+          <t>NOR_DESC</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Boolean XNOR.</t>
+          <t>Boolean NOR.</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>布尔同或运算。</t>
+          <t>布尔或非运算。</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>IADD</t>
-        </is>
-      </c>
-      <c r="B238" s="1" t="inlineStr">
-        <is>
-          <t>+=</t>
-        </is>
-      </c>
-      <c r="C238" s="1" t="inlineStr">
-        <is>
-          <t>+=</t>
+          <t>XNOR</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Xnor</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>同或</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>IADD_DESC</t>
+          <t>XNOR_DESC</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Apply += to a reference/variable.</t>
+          <t>Boolean XNOR.</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>对引用/变量执行 += 运算。</t>
+          <t>布尔同或运算。</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>ISUB</t>
+          <t>IADD</t>
         </is>
       </c>
       <c r="B240" s="1" t="inlineStr">
         <is>
-          <t>-=</t>
+          <t>+=</t>
         </is>
       </c>
       <c r="C240" s="1" t="inlineStr">
         <is>
-          <t>-=</t>
+          <t>+=</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>ISUB_DESC</t>
+          <t>IADD_DESC</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Apply -= to a reference/variable.</t>
+          <t>Apply += to a reference/variable.</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>对引用/变量执行 -= 运算。</t>
+          <t>对引用/变量执行 += 运算。</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>IMUL</t>
+          <t>ISUB</t>
         </is>
       </c>
       <c r="B242" s="1" t="inlineStr">
         <is>
-          <t>*=</t>
+          <t>-=</t>
         </is>
       </c>
       <c r="C242" s="1" t="inlineStr">
         <is>
-          <t>*=</t>
+          <t>-=</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>IMUL_DESC</t>
+          <t>ISUB_DESC</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Apply *= to a reference/variable.</t>
+          <t>Apply -= to a reference/variable.</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>对引用/变量执行 *= 运算。</t>
+          <t>对引用/变量执行 -= 运算。</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>IDIV</t>
+          <t>IMUL</t>
         </is>
       </c>
       <c r="B244" s="1" t="inlineStr">
         <is>
-          <t>/=</t>
+          <t>*=</t>
         </is>
       </c>
       <c r="C244" s="1" t="inlineStr">
         <is>
-          <t>/=</t>
+          <t>*=</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>IDIV_DESC</t>
+          <t>IMUL_DESC</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Apply /= to a reference/variable.</t>
+          <t>Apply *= to a reference/variable.</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>对引用/变量执行 /= 运算。</t>
+          <t>对引用/变量执行 *= 运算。</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>IMOD</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>Mod Assign</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>取模并赋值</t>
+          <t>IDIV</t>
+        </is>
+      </c>
+      <c r="B246" s="1" t="inlineStr">
+        <is>
+          <t>/=</t>
+        </is>
+      </c>
+      <c r="C246" s="1" t="inlineStr">
+        <is>
+          <t>/=</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>IMOD_DESC</t>
+          <t>IDIV_DESC</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Apply %= to a reference/variable.</t>
+          <t>Apply /= to a reference/variable.</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>对引用/变量执行 %= 运算。</t>
+          <t>对引用/变量执行 /= 运算。</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>IPOW</t>
-        </is>
-      </c>
-      <c r="B248" s="1" t="inlineStr">
-        <is>
-          <t>**=</t>
-        </is>
-      </c>
-      <c r="C248" s="1" t="inlineStr">
-        <is>
-          <t>**=</t>
+          <t>IMOD</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Mod Assign</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>取模并赋值</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>IPOW_DESC</t>
+          <t>IMOD_DESC</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Apply **= to a reference/variable.</t>
+          <t>Apply %= to a reference/variable.</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>对引用/变量执行 **= 运算。</t>
+          <t>对引用/变量执行 %= 运算。</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>BACK_TO_TITLE</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>Go Back To Title</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>回到标题界面</t>
+          <t>IPOW</t>
+        </is>
+      </c>
+      <c r="B250" s="1" t="inlineStr">
+        <is>
+          <t>**=</t>
+        </is>
+      </c>
+      <c r="C250" s="1" t="inlineStr">
+        <is>
+          <t>**=</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>BACK_TO_TITLE_DESC</t>
+          <t>IPOW_DESC</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>After this command, you will get back to the title scene.</t>
+          <t>Apply **= to a reference/variable.</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>本次操作后，将会回到标题界面</t>
+          <t>对引用/变量执行 **= 运算。</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>SET_GAME_VARIABLE</t>
+          <t>BACK_TO_TITLE</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Set Game Variable</t>
+          <t>Go Back To Title</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>设置游戏变量</t>
+          <t>回到标题界面</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>SET_GAME_VARIABLE_DESC</t>
+          <t>BACK_TO_TITLE_DESC</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Set a persistent game variable (survives across scenes).</t>
+          <t>After this command, you will get back to the title scene.</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>设置一个持久化游戏变量（跨场景保存）。</t>
+          <t>本次操作后，将会回到标题界面</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>GET_GAME_VARIABLE</t>
+          <t>SET_GAME_VARIABLE</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Get Game Variable</t>
+          <t>Set Game Variable</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>获取游戏变量</t>
+          <t>设置游戏变量</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>GET_GAME_VARIABLE_DESC</t>
+          <t>SET_GAME_VARIABLE_DESC</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Get a persistent game variable value.</t>
+          <t>Set a persistent game variable (survives across scenes).</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>获取一个持久化游戏变量的值。</t>
+          <t>设置一个持久化游戏变量（跨场景保存）。</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>ADD_PLAYER_BY_CLASS</t>
+          <t>GET_GAME_VARIABLE</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Add Party Member</t>
+          <t>Get Game Variable</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>添加队员</t>
+          <t>获取游戏变量</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>ADD_PLAYER_BY_CLASS_DESC</t>
+          <t>GET_GAME_VARIABLE_DESC</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Add a player to the party by class path.</t>
+          <t>Get a persistent game variable value.</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>根据角色类路径向队伍中添加一名队员。</t>
+          <t>获取一个持久化游戏变量的值。</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>REMOVE_PLAYER_BY_CLASS</t>
+          <t>ADD_PLAYER_BY_CLASS</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Remove Party Member</t>
+          <t>Add Party Member</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>移除队员</t>
+          <t>添加队员</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>REMOVE_PLAYER_BY_CLASS_DESC</t>
+          <t>ADD_PLAYER_BY_CLASS_DESC</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Remove a player from the party by class path (at least one member remains).</t>
+          <t>Add a player to the party by class path.</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>根据角色类路径从队伍中移除一名队员（至少保留一人）。</t>
+          <t>根据角色类路径向队伍中添加一名队员。</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>SET_BGM_FILTER</t>
+          <t>REMOVE_PLAYER_BY_CLASS</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Set BGM Filter</t>
+          <t>Remove Party Member</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>设置BGM滤镜</t>
+          <t>移除队员</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>SET_BGM_FILTER_DESC</t>
+          <t>REMOVE_PLAYER_BY_CLASS_DESC</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Apply filter properties to the currently playing BGM on the current map scene.</t>
+          <t>Remove a player from the party by class path (at least one member remains).</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>对当前地图场景正在播放的BGM应用滤镜属性。</t>
+          <t>根据角色类路径从队伍中移除一名队员（至少保留一人）。</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>SET_BGS_FILTER</t>
+          <t>SET_BGM_FILTER</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Set BGS Filter</t>
+          <t>Set BGM Filter</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>设置BGS滤镜</t>
+          <t>设置BGM滤镜</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>SET_BGS_FILTER_DESC</t>
+          <t>SET_BGM_FILTER_DESC</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Apply filter properties to the currently playing BGS on the current map scene.</t>
+          <t>Apply filter properties to the currently playing BGM on the current map scene.</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>对当前地图场景正在播放的BGS应用滤镜属性。</t>
+          <t>对当前地图场景正在播放的BGM应用滤镜属性。</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>FLASH_SHADER_LOAD_FAILED</t>
+          <t>SET_BGS_FILTER</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Failed to load screen flash shader</t>
+          <t>Set BGS Filter</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>加载画面闪烁着色器失败</t>
+          <t>设置BGS滤镜</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>FLASH_SCREEN</t>
+          <t>SET_BGS_FILTER_DESC</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Flash Screen</t>
+          <t>Apply filter properties to the currently playing BGS on the current map scene.</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>画面闪烁</t>
+          <t>对当前地图场景正在播放的BGS应用滤镜属性。</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>FLASH_DURATION</t>
+          <t>FLASH_SHADER_LOAD_FAILED</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Duration (s)</t>
+          <t>Failed to load screen flash shader</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>持续时间（秒）</t>
+          <t>加载画面闪烁着色器失败</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>FLASH_SCREEN_DESC</t>
+          <t>FLASH_SCREEN</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Trigger a screen flash with given color and duration (red/green/blue/alpha 0-255, duration in seconds)</t>
+          <t>Flash Screen</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>以指定颜色和持续时间触发画面闪烁效果（参数：红、绿、蓝、透明度 0-255，持续时间秒）</t>
+          <t>画面闪烁</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>STOP_FLASH_SCREEN</t>
+          <t>FLASH_DURATION</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Stop Flash Screen</t>
+          <t>Duration (s)</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>停止画面闪烁</t>
+          <t>持续时间（秒）</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>STOP_FLASH_SCREEN_DESC</t>
+          <t>FLASH_SCREEN_DESC</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Immediately stop any in-progress screen flash effect</t>
+          <t>Trigger a screen flash with given color and duration (red/green/blue/alpha 0-255, duration in seconds)</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>立即停止当前正在进行的画面闪烁效果</t>
+          <t>以指定颜色和持续时间触发画面闪烁效果（参数：红、绿、蓝、透明度 0-255，持续时间秒）</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>SCREEN_SHAKE</t>
+          <t>STOP_FLASH_SCREEN</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Screen Shake</t>
+          <t>Stop Flash Screen</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>画面抖动</t>
+          <t>停止画面闪烁</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>SCREEN_SHAKE_DESC</t>
+          <t>STOP_FLASH_SCREEN_DESC</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Start an RMXP-style screen shake with power, speed, and duration.</t>
+          <t>Immediately stop any in-progress screen flash effect</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>以指定的振幅、速度和持续时间开始 RMXP 风格的画面抖动效果。</t>
+          <t>立即停止当前正在进行的画面闪烁效果</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>STOP_SCREEN_SHAKE</t>
+          <t>SCREEN_SHAKE</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Stop Screen Shake</t>
+          <t>Screen Shake</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>停止画面抖动</t>
+          <t>画面抖动</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>STOP_SCREEN_SHAKE_DESC</t>
+          <t>SCREEN_SHAKE_DESC</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Immediately stop any in-progress screen shake effect.</t>
+          <t>Start an RMXP-style screen shake with power, speed, and duration.</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>立即停止正在进行的画面抖动效果。</t>
+          <t>以指定的振幅、速度和持续时间开始 RMXP 风格的画面抖动效果。</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>ITEM_NEW</t>
+          <t>STOP_SCREEN_SHAKE</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Got #FFD966#{name}#default#!\n{desc}</t>
+          <t>Stop Screen Shake</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>获得了#FFD966#{name}#default#！\n{desc}</t>
+          <t>停止画面抖动</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>GET_PLAYER</t>
+          <t>STOP_SCREEN_SHAKE_DESC</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Get Player</t>
+          <t>Immediately stop any in-progress screen shake effect.</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>获取玩家</t>
+          <t>立即停止正在进行的画面抖动效果。</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>GET_PLAYER_DESC</t>
+          <t>ITEM_NEW</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Get the primary player from the current scene.</t>
+          <t>Got #FFD966#{name}#default#!\n{desc}</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>获取当前场景的主角实例</t>
+          <t>获得了#FFD966#{name}#default#！\n{desc}</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>ADD_ITEM</t>
+          <t>GET_PLAYER</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Add Item</t>
+          <t>Get Player</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>添加道具</t>
+          <t>获取玩家</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>ADD_ITEM_DESC</t>
+          <t>GET_PLAYER_DESC</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Add item(s) to the player inventory.</t>
+          <t>Get the primary player from the current scene.</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>将道具添加到玩家背包</t>
+          <t>获取当前场景的主角实例</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>REMOVE_ITEM</t>
+          <t>ADD_ITEM</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Remove Item</t>
+          <t>Add Item</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>移除道具</t>
+          <t>添加道具</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>REMOVE_ITEM_DESC</t>
+          <t>ADD_ITEM_DESC</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Remove item(s) from the player inventory. Fails if count is insufficient.</t>
+          <t>Add item(s) to the player inventory.</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>从玩家背包移除道具，数量不足则失败</t>
+          <t>将道具添加到玩家背包</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>HAS_ITEM</t>
+          <t>REMOVE_ITEM</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Has Item</t>
+          <t>Remove Item</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>是否持有道具</t>
+          <t>移除道具</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>HAS_ITEM_DESC</t>
+          <t>REMOVE_ITEM_DESC</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Check whether the player owns at least one of the specified item.</t>
+          <t>Remove item(s) from the player inventory. Fails if count is insufficient.</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>检查玩家是否持有至少一个指定道具</t>
+          <t>从玩家背包移除道具，数量不足则失败</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>GET_ITEM_COUNT</t>
+          <t>HAS_ITEM</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Get Item Count</t>
+          <t>Has Item</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>获取道具数量</t>
+          <t>是否持有道具</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>GET_ITEM_COUNT_DESC</t>
+          <t>HAS_ITEM_DESC</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Get the quantity of a specific item in the player inventory.</t>
+          <t>Check whether the player owns at least one of the specified item.</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>获取玩家背包中指定道具的数量</t>
+          <t>检查玩家是否持有至少一个指定道具</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>ADD_EQUIP</t>
+          <t>GET_ITEM_COUNT</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Add Equip</t>
+          <t>Get Item Count</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>添加装备</t>
+          <t>获取道具数量</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>ADD_EQUIP_DESC</t>
+          <t>GET_ITEM_COUNT_DESC</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Add equip(s) to the player equipment bag.</t>
+          <t>Get the quantity of a specific item in the player inventory.</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>将装备添加到玩家装备包</t>
+          <t>获取玩家背包中指定道具的数量</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>REMOVE_EQUIP</t>
+          <t>ADD_EQUIP</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Remove Equip</t>
+          <t>Add Equip</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>移除装备</t>
+          <t>添加装备</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>REMOVE_EQUIP_DESC</t>
+          <t>ADD_EQUIP_DESC</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Remove equip(s) from the player equipment bag. Fails if count is insufficient.</t>
+          <t>Add equip(s) to the player equipment bag.</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>从玩家装备包移除装备，数量不足则失败</t>
+          <t>将装备添加到玩家装备包</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>HAS_EQUIP</t>
+          <t>REMOVE_EQUIP</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Has Equip</t>
+          <t>Remove Equip</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>是否持有装备</t>
+          <t>移除装备</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>HAS_EQUIP_DESC</t>
+          <t>REMOVE_EQUIP_DESC</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Check whether the player owns at least one of the specified equip.</t>
+          <t>Remove equip(s) from the player equipment bag. Fails if count is insufficient.</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>检查玩家是否持有至少一个指定装备</t>
+          <t>从玩家装备包移除装备，数量不足则失败</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>EQUIP_ITEM</t>
+          <t>HAS_EQUIP</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Equip Item</t>
+          <t>Has Equip</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>装备物品</t>
+          <t>是否持有装备</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>EQUIP_ITEM_DESC</t>
+          <t>HAS_EQUIP_DESC</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Equip a piece of equipment onto the player.</t>
+          <t>Check whether the player owns at least one of the specified equip.</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>将装备穿戴到玩家身上</t>
+          <t>检查玩家是否持有至少一个指定装备</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>UNEQUIP_SLOT</t>
+          <t>EQUIP_ITEM</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Unequip Slot</t>
+          <t>Equip Item</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>卸下装备栏</t>
+          <t>装备物品</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>UNEQUIP_SLOT_DESC</t>
+          <t>EQUIP_ITEM_DESC</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Unequip the item occupying the given equipment slot.</t>
+          <t>Equip a piece of equipment onto the player.</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>卸下指定装备栏中的装备</t>
+          <t>将装备穿戴到玩家身上</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>GET_EQUIP_IN_SLOT</t>
+          <t>UNEQUIP_SLOT</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Get Equip In Slot</t>
+          <t>Unequip Slot</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>获取装备栏中的装备</t>
+          <t>卸下装备栏</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>GET_EQUIP_IN_SLOT_DESC</t>
+          <t>UNEQUIP_SLOT_DESC</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Get the equip ID in the specified slot, or empty string if the slot is empty.</t>
+          <t>Unequip the item occupying the given equipment slot.</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>获取指定装备栏中当前装备的ID，空栏返回空字符串</t>
+          <t>卸下指定装备栏中的装备</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>GET_PLAYER_ATTR</t>
+          <t>GET_EQUIP_IN_SLOT</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Get Player Attribute</t>
+          <t>Get Equip In Slot</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>获取玩家属性</t>
+          <t>获取装备栏中的装备</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>GET_PLAYER_ATTR_DESC</t>
+          <t>GET_EQUIP_IN_SLOT_DESC</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Get a named attribute from the player (e.g. HP, MAXHP, ATK, DEF, GOLD, EXP, LEVEL).</t>
+          <t>Get the equip ID in the specified slot, or empty string if the slot is empty.</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>获取玩家指定属性值（如 HP/MAXHP/ATK/DEF/GOLD/EXP/LEVEL）</t>
+          <t>获取指定装备栏中当前装备的ID，空栏返回空字符串</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>SET_PLAYER_ATTR</t>
+          <t>GET_PLAYER_ATTR</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Set Player Attribute</t>
+          <t>Get Player Attribute</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>设置玩家属性</t>
+          <t>获取玩家属性</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>SET_PLAYER_ATTR_DESC</t>
+          <t>GET_PLAYER_ATTR_DESC</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Set a named attribute on the player (e.g. HP, MAXHP, ATK, DEF, GOLD, EXP, LEVEL).</t>
+          <t>Get a named attribute from the player (e.g. HP, MAXHP, ATK, DEF, GOLD, EXP, LEVEL).</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>设置玩家指定属性值（如 HP/MAXHP/ATK/DEF/GOLD/EXP/LEVEL）</t>
+          <t>获取玩家指定属性值（如 HP/MAXHP/ATK/DEF/GOLD/EXP/LEVEL）</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>HEAL_PLAYER</t>
+          <t>SET_PLAYER_ATTR</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Heal Player</t>
+          <t>Set Player Attribute</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>回复玩家HP</t>
+          <t>设置玩家属性</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>HEAL_PLAYER_DESC</t>
+          <t>SET_PLAYER_ATTR_DESC</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Restore HP to the player, capped at MAXHP.</t>
+          <t>Set a named attribute on the player (e.g. HP, MAXHP, ATK, DEF, GOLD, EXP, LEVEL).</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>恢复玩家生命值，上限为最大生命值</t>
+          <t>设置玩家指定属性值（如 HP/MAXHP/ATK/DEF/GOLD/EXP/LEVEL）</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>DAMAGE_PLAYER</t>
+          <t>HEAL_PLAYER</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Damage Player</t>
+          <t>Heal Player</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>对玩家造成伤害</t>
+          <t>回复玩家HP</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>DAMAGE_PLAYER_DESC</t>
+          <t>HEAL_PLAYER_DESC</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Deal damage to the player, floored at 0.</t>
+          <t>Restore HP to the player, capped at MAXHP.</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>减少玩家生命值，下限为0</t>
+          <t>恢复玩家生命值，上限为最大生命值</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>ADD_GOLD</t>
+          <t>DAMAGE_PLAYER</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Add Gold</t>
+          <t>Damage Player</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>增加金币</t>
+          <t>对玩家造成伤害</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>ADD_GOLD_DESC</t>
+          <t>DAMAGE_PLAYER_DESC</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Add gold to the player (can be negative to subtract).</t>
+          <t>Deal damage to the player, floored at 0.</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>为玩家增加（或减少）金币</t>
+          <t>减少玩家生命值，下限为0</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>ADD_EXP</t>
+          <t>ADD_GOLD</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Add EXP</t>
+          <t>Add Gold</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>增加经验值</t>
+          <t>增加金币</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>ADD_EXP_DESC</t>
+          <t>ADD_GOLD_DESC</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Add experience points to the player.</t>
+          <t>Add gold to the player (can be negative to subtract).</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>为玩家增加经验值</t>
+          <t>为玩家增加（或减少）金币</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>SAVE_GAME</t>
+          <t>ADD_EXP</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Save Game</t>
+          <t>Add EXP</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>保存游戏</t>
+          <t>增加经验值</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>SAVE_GAME_DESC</t>
+          <t>ADD_EXP_DESC</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Save the current game state to a file (.json or .dat).</t>
+          <t>Add experience points to the player.</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>将当前游戏状态保存至文件（.json 或 .dat）</t>
+          <t>为玩家增加经验值</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>LOAD_GAME</t>
+          <t>SAVE_GAME</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Load Game</t>
+          <t>Save Game</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>读取游戏</t>
+          <t>保存游戏</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>LOAD_GAME_DESC</t>
+          <t>SAVE_GAME_DESC</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Load game state from a file and apply it to the current scene.</t>
+          <t>Save the current game state to a file (.json or .dat).</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>从文件读取游戏状态并应用到当前场景</t>
+          <t>将当前游戏状态保存至文件（.json 或 .dat）</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>GET_SAVE_PATH</t>
+          <t>LOAD_GAME</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Get Save Path</t>
+          <t>Load Game</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>获取存档路径</t>
+          <t>读取游戏</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>GET_SAVE_PATH_DESC</t>
+          <t>LOAD_GAME_DESC</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Get the platform-specific save file path for a given slot.</t>
+          <t>Load game state from a file and apply it to the current scene.</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>获取指定存档槽的平台存储路径</t>
+          <t>从文件读取游戏状态并应用到当前场景</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>GOTO_MAP</t>
+          <t>GET_SAVE_PATH</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Go to Map</t>
+          <t>Get Save Path</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>跳转地图</t>
+          <t>获取存档路径</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>GOTO_MAP_DESC</t>
+          <t>GET_SAVE_PATH_DESC</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Transition to a map and optionally place the player at (x, y).</t>
+          <t>Get the platform-specific save file path for a given slot.</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>切换到指定地图，并可选择设置玩家位置</t>
+          <t>获取指定存档槽的平台存储路径</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>SET_WEATHER</t>
+          <t>GOTO_MAP</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Set Weather</t>
+          <t>Go to Map</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>设置天气</t>
+          <t>跳转地图</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>SET_WEATHER_DESC</t>
+          <t>GOTO_MAP_DESC</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Set screen weather (0=None, 1=Rain, 2=Storm, 3=Snow). Power and max density range from 0 to 100. iOS uses particle fallback.</t>
+          <t>Transition to a map and optionally place the player at (x, y).</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>设置屏幕天气效果（0=无，1=雨，2=暴风雨，3=雪）。强度与密度范围为 0–100。iOS 使用粒子回退。</t>
+          <t>切换到指定地图，并可选择设置玩家位置</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>CLEAR_WEATHER</t>
+          <t>SET_WEATHER</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Clear Weather</t>
+          <t>Set Weather</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>清除天气</t>
+          <t>设置天气</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>CLEAR_WEATHER_DESC</t>
+          <t>SET_WEATHER_DESC</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Stop the active weather effect.</t>
+          <t>Set screen weather (0=None, 1=Rain, 2=Storm, 3=Snow). Power and max density range from 0 to 100. iOS uses particle fallback.</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>停止当前天气效果。</t>
+          <t>设置屏幕天气效果（0=无，1=雨，2=暴风雨，3=雪）。强度与密度范围为 0–100。iOS 使用粒子回退。</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>WEATHER_TYPE_NONE</t>
+          <t>CLEAR_WEATHER</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Clear Weather</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>清除天气</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>WEATHER_TYPE_RAIN</t>
+          <t>CLEAR_WEATHER_DESC</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Stop the active weather effect.</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>雨</t>
+          <t>停止当前天气效果。</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>WEATHER_TYPE_STORM</t>
+          <t>WEATHER_TYPE_NONE</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Storm</t>
+          <t>None</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>暴风雨</t>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>WEATHER_TYPE_SNOW</t>
+          <t>WEATHER_TYPE_RAIN</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Snow</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>雪</t>
+          <t>雨</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>GET_STATE_OWNER</t>
+          <t>WEATHER_TYPE_STORM</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Get State Owner</t>
+          <t>Storm</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>获取状态宿主</t>
+          <t>暴风雨</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>GET_STATE_OWNER_DESC</t>
+          <t>WEATHER_TYPE_SNOW</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Return the battler currently hosting this state.</t>
+          <t>Snow</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>返回当前承载该状态的战斗者。</t>
+          <t>雪</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>GET_EVENT_ARG</t>
+          <t>GET_STATE_OWNER</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Get Event Arg</t>
+          <t>Get State Owner</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>获取事件参数</t>
+          <t>获取状态宿主</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>GET_EVENT_ARG_DESC</t>
+          <t>GET_STATE_OWNER_DESC</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Read a keyword argument injected into the current blueprint event (e.g. battler, context, opponent, won).</t>
+          <t>Return the battler currently hosting this state.</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>读取注入到当前蓝图事件的关键字参数（如 battler、context、opponent、won 等）。</t>
+          <t>返回当前承载该状态的战斗者。</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>GET_DAMAGE_CONTEXT</t>
+          <t>GET_EVENT_ARG</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Get Damage Context</t>
+          <t>Get Event Arg</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>获取伤害上下文</t>
+          <t>获取事件参数</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>GET_DAMAGE_CONTEXT_DESC</t>
+          <t>GET_EVENT_ARG_DESC</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Get the active DamageContext for the current event.</t>
+          <t>Read a keyword argument injected into the current blueprint event (e.g. battler, context, opponent, won).</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>获取当前事件下活动的 DamageContext。</t>
+          <t>读取注入到当前蓝图事件的关键字参数（如 battler、context、opponent、won 等）。</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>GET_CTX_FIELD</t>
+          <t>GET_DAMAGE_CONTEXT</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Get Ctx Field</t>
+          <t>Get Damage Context</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>读取上下文字段</t>
+          <t>获取伤害上下文</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>GET_CTX_FIELD_DESC</t>
+          <t>GET_DAMAGE_CONTEXT_DESC</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Read a field from a DamageContext (atk, deF, damagePerRound, rounds, totalDamage, …).</t>
+          <t>Get the active DamageContext for the current event.</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>从 DamageContext 读取字段（atk、deF、damagePerRound、rounds、totalDamage 等）。</t>
+          <t>获取当前事件下活动的 DamageContext。</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>SET_CTX_FIELD</t>
+          <t>GET_CTX_FIELD</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Set Ctx Field</t>
+          <t>Get Ctx Field</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>写入上下文字段</t>
+          <t>读取上下文字段</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>SET_CTX_FIELD_DESC</t>
+          <t>GET_CTX_FIELD_DESC</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Write a field on a DamageContext to alter damage resolution.</t>
+          <t>Read a field from a DamageContext (atk, deF, damagePerRound, rounds, totalDamage, …).</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>向 DamageContext 写入字段以影响伤害结算。</t>
+          <t>从 DamageContext 读取字段（atk、deF、damagePerRound、rounds、totalDamage 等）。</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>ADD_CTX_FIELD</t>
+          <t>SET_CTX_FIELD</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Add Ctx Field</t>
+          <t>Set Ctx Field</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>累加上下文字段</t>
+          <t>写入上下文字段</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>ADD_CTX_FIELD_DESC</t>
+          <t>SET_CTX_FIELD_DESC</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Add a numeric delta to a field on the DamageContext (totalDamage, damagePerRound, atk, deF, …).</t>
+          <t>Write a field on a DamageContext to alter damage resolution.</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>在 DamageContext 字段上累加数值（totalDamage、damagePerRound、atk、deF 等）。</t>
+          <t>向 DamageContext 写入字段以影响伤害结算。</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>GET_BATTLER_ATTR</t>
+          <t>ADD_CTX_FIELD</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Get Battler Attr</t>
+          <t>Add Ctx Field</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>读取战斗者属性</t>
+          <t>累加上下文字段</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>GET_BATTLER_ATTR_DESC</t>
+          <t>ADD_CTX_FIELD_DESC</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Read a named attribute from any battler (HP, MAXHP, ATK, DEF, …).</t>
+          <t>Add a numeric delta to a field on the DamageContext (totalDamage, damagePerRound, atk, deF, …).</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>从任意战斗者读取命名属性（HP、MAXHP、ATK、DEF 等）。</t>
+          <t>在 DamageContext 字段上累加数值（totalDamage、damagePerRound、atk、deF 等）。</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>SET_BATTLER_ATTR</t>
+          <t>GET_BATTLER_ATTR</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Set Battler Attr</t>
+          <t>Get Battler Attr</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>写入战斗者属性</t>
+          <t>读取战斗者属性</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>SET_BATTLER_ATTR_DESC</t>
+          <t>GET_BATTLER_ATTR_DESC</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Write a named attribute on any battler.</t>
+          <t>Read a named attribute from any battler (HP, MAXHP, ATK, DEF, …).</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>向任意战斗者写入命名属性。</t>
+          <t>从任意战斗者读取命名属性（HP、MAXHP、ATK、DEF 等）。</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>DAMAGE_BATTLER</t>
+          <t>SET_BATTLER_ATTR</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Damage Battler</t>
+          <t>Set Battler Attr</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>扣除战斗者血量</t>
+          <t>写入战斗者属性</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>DAMAGE_BATTLER_DESC</t>
+          <t>SET_BATTLER_ATTR_DESC</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Subtract HP from any battler (floored at 0).</t>
+          <t>Write a named attribute on any battler.</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>从任意战斗者扣除生命值（下限为 0）。</t>
+          <t>向任意战斗者写入命名属性。</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>HEAL_BATTLER</t>
+          <t>DAMAGE_BATTLER</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Heal Battler</t>
+          <t>Damage Battler</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>治疗战斗者</t>
+          <t>扣除战斗者血量</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>HEAL_BATTLER_DESC</t>
+          <t>DAMAGE_BATTLER_DESC</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Restore HP on any battler (capped at MAXHP).</t>
+          <t>Subtract HP from any battler (floored at 0).</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>为任意战斗者恢复生命值（上限为 MAXHP）。</t>
+          <t>从任意战斗者扣除生命值（下限为 0）。</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>BATTLER_HAS_STATE</t>
+          <t>HEAL_BATTLER</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Battler Has State</t>
+          <t>Heal Battler</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>战斗者是否拥有状态</t>
+          <t>治疗战斗者</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>BATTLER_HAS_STATE_DESC</t>
+          <t>HEAL_BATTLER_DESC</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Check whether a battler currently carries the given state ID.</t>
+          <t>Restore HP on any battler (capped at MAXHP).</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>检查战斗者当前是否拥有指定状态 ID。</t>
+          <t>为任意战斗者恢复生命值（上限为 MAXHP）。</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>ADD_STATE_TO</t>
+          <t>BATTLER_HAS_STATE</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Add State To</t>
+          <t>Battler Has State</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>为战斗者添加状态</t>
+          <t>战斗者是否拥有状态</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>ADD_STATE_TO_DESC</t>
+          <t>BATTLER_HAS_STATE_DESC</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Apply a state (by ID) to any battler, firing its onAdd blueprint.</t>
+          <t>Check whether a battler currently carries the given state ID.</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>通过 ID 给任意战斗者添加状态，并触发其 onAdd 蓝图。</t>
+          <t>检查战斗者当前是否拥有指定状态 ID。</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>REMOVE_STATE_FROM</t>
+          <t>ADD_STATE_TO</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Remove State From</t>
+          <t>Add State To</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>从战斗者移除状态</t>
+          <t>为战斗者添加状态</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>REMOVE_STATE_FROM_DESC</t>
+          <t>ADD_STATE_TO_DESC</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Remove a state (by ID) from any battler, firing its onRemove blueprint.</t>
+          <t>Apply a state (by ID) to any battler, firing its onAdd blueprint.</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>通过 ID 从任意战斗者移除状态，并触发其 onRemove 蓝图。</t>
+          <t>通过 ID 给任意战斗者添加状态，并触发其 onAdd 蓝图。</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>OPEN_SHOP</t>
+          <t>REMOVE_STATE_FROM</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Open Shop</t>
+          <t>Remove State From</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>打开商店</t>
+          <t>从战斗者移除状态</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>OPEN_SHOP_DESC</t>
+          <t>REMOVE_STATE_FROM_DESC</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Open the map shop with purchasable item IDs and whether selling is allowed.</t>
+          <t>Remove a state (by ID) from any battler, firing its onRemove blueprint.</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>打开地图场景商店，参数为可购买道具ID数组和是否允许出售。</t>
+          <t>通过 ID 从任意战斗者移除状态，并触发其 onRemove 蓝图。</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>RECORD_TELEPOINT</t>
+          <t>OPEN_SHOP</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Record Telepoint</t>
+          <t>Open Shop</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>记录传送点</t>
+          <t>打开商店</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>RECORD_TELEPOINT_DESC</t>
+          <t>OPEN_SHOP_DESC</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Record a telepoint for a map so it can be used by teleport items.</t>
+          <t>Open the map shop with purchasable item IDs and whether selling is allowed.</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>记录地图传送点，供传送道具使用。</t>
+          <t>打开地图场景商店，参数为可购买道具ID数组和是否允许出售。</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>OPEN_MONSTER_BOOK</t>
+          <t>RECORD_TELEPOINT</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Open Monster Book</t>
+          <t>Record Telepoint</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>打开怪物手册</t>
+          <t>记录传送点</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>OPEN_MONSTER_BOOK_DESC</t>
+          <t>RECORD_TELEPOINT_DESC</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Open the monster handbook for the current map.</t>
+          <t>Record a telepoint for a map so it can be used by teleport items.</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>打开当前地图的怪物手册。</t>
+          <t>记录地图传送点，供传送道具使用。</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>GET_CURRENT_REGION</t>
+          <t>OPEN_MONSTER_BOOK</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Get Current Region</t>
+          <t>Open Monster Book</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>获取当前区域</t>
+          <t>打开怪物手册</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>GET_CURRENT_REGION_DESC</t>
+          <t>OPEN_MONSTER_BOOK_DESC</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Get the current mota region name.</t>
+          <t>Open the monster handbook for the current map.</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>获取当前魔塔区域名。</t>
+          <t>打开当前地图的怪物手册。</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>SET_CURRENT_REGION</t>
+          <t>GET_CURRENT_REGION</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Set Current Region</t>
+          <t>Get Current Region</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>设置当前区域</t>
+          <t>获取当前区域</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>SET_CURRENT_REGION_DESC</t>
+          <t>GET_CURRENT_REGION_DESC</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Set the current mota region name.</t>
+          <t>Get the current mota region name.</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>设置当前魔塔区域名。</t>
+          <t>获取当前魔塔区域名。</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>OPEN_FLOOR_TELEPORTER</t>
+          <t>SET_CURRENT_REGION</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Open Floor Teleporter</t>
+          <t>Set Current Region</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>打开楼层传送器</t>
+          <t>设置当前区域</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>OPEN_FLOOR_TELEPORTER_DESC</t>
+          <t>SET_CURRENT_REGION_DESC</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Open the visited-floor teleporter preview window.</t>
+          <t>Set the current mota region name.</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>打开已去过楼层的传送器预览窗口。</t>
+          <t>设置当前魔塔区域名。</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>DESTROY_TERRAIN</t>
+          <t>OPEN_FLOOR_TELEPORTER</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Destroy Terrain</t>
+          <t>Open Floor Teleporter</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>破坏地形</t>
+          <t>打开楼层传送器</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>DESTROY_TERRAIN_DESC</t>
+          <t>OPEN_FLOOR_TELEPORTER_DESC</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Replace one tile on a layer of the current map with the specified tile ID.</t>
+          <t>Open the visited-floor teleporter preview window.</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>将当前地图指定图层上的一个格子替换为指定 tileID。</t>
+          <t>打开已去过楼层的传送器预览窗口。</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>GET_TERRAIN_TILE</t>
+          <t>DESTROY_TERRAIN</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Get Terrain Tile</t>
+          <t>Destroy Terrain</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>获取地形 Tile</t>
+          <t>破坏地形</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>GET_TERRAIN_TILE_DESC</t>
+          <t>DESTROY_TERRAIN_DESC</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Get the tile ID at a layer position on the current map.</t>
+          <t>Replace one tile on a layer of the current map with the specified tile ID.</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>获取当前地图指定图层和坐标上的 tileID。</t>
+          <t>将当前地图指定图层上的一个格子替换为指定 tileID。</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>GET_PLAYER_FRONT_POSITION</t>
+          <t>GET_TERRAIN_TILE</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Get Player Front Position</t>
+          <t>Get Terrain Tile</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>获取玩家面前坐标</t>
+          <t>获取地形 Tile</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>GET_PLAYER_FRONT_POSITION_DESC</t>
+          <t>GET_TERRAIN_TILE_DESC</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Get the tile coordinate in front of the player based on the current facing direction.</t>
+          <t>Get the tile ID at a layer position on the current map.</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>根据玩家当前朝向获取面前一格的地图坐标。</t>
+          <t>获取当前地图指定图层和坐标上的 tileID。</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>DESTROY_TERRAIN_LIST</t>
+          <t>GET_PLAYER_FRONT_POSITION</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Destroy Terrain List</t>
+          <t>Get Player Front Position</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>批量破坏地形</t>
+          <t>获取玩家面前坐标</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>DESTROY_TERRAIN_LIST_DESC</t>
+          <t>GET_PLAYER_FRONT_POSITION_DESC</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Replace multiple tiles on a layer of the current map with the specified tile ID.</t>
+          <t>Get the tile coordinate in front of the player based on the current facing direction.</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>将当前地图指定图层上的多个格子替换为指定 tileID。</t>
+          <t>根据玩家当前朝向获取面前一格的地图坐标。</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>GET_TERRAIN_TILE_POSITIONS</t>
+          <t>DESTROY_TERRAIN_LIST</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Get Terrain Tile Positions</t>
+          <t>Destroy Terrain List</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>获取地形 Tile 坐标列表</t>
+          <t>批量破坏地形</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>GET_TERRAIN_TILE_POSITIONS_DESC</t>
+          <t>DESTROY_TERRAIN_LIST_DESC</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Get all coordinates matching a tile ID on a layer of the current map.</t>
+          <t>Replace multiple tiles on a layer of the current map with the specified tile ID.</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>获取当前地图指定图层中所有匹配 tileID 的坐标。</t>
+          <t>将当前地图指定图层上的多个格子替换为指定 tileID。</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>SET_MOVE_ROUTE</t>
+          <t>GET_TERRAIN_TILE_POSITIONS</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Set Move Route</t>
+          <t>Get Terrain Tile Positions</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>设置移动路线</t>
+          <t>获取地形 Tile 坐标列表</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>SET_MOVE_ROUTE_DESC</t>
+          <t>GET_TERRAIN_TILE_POSITIONS_DESC</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Set an actor movement route. Started continues immediately; Finished continues after movement ends.</t>
+          <t>Get all coordinates matching a tile ID on a layer of the current map.</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>设置 actor 的移动路线。Started 立即继续，Finished 在移动结束后继续。</t>
+          <t>获取当前地图指定图层中所有匹配 tileID 的坐标。</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>SET_AUTO_PATH_TO_DESTINATION</t>
+          <t>SET_MOVE_ROUTE</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Set Auto Path to Destination</t>
+          <t>Set Move Route</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>设置自动寻路到终点</t>
+          <t>设置移动路线</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>SET_AUTO_PATH_TO_DESTINATION_DESC</t>
+          <t>SET_MOVE_ROUTE_DESC</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Pathfind an actor to the target map cell. Started continues immediately; Finished continues after movement ends.</t>
+          <t>Set an actor movement route. Started continues immediately; Finished continues after movement ends.</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>让 actor 自动寻路到指定地图格。Started 立即继续，Finished 在移动结束后继续。</t>
+          <t>设置 actor 的移动路线。Started 立即继续，Finished 在移动结束后继续。</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>FREEZE_TRANSITION_BACKGROUND</t>
+          <t>SET_AUTO_PATH_TO_DESTINATION</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Freeze Transition Background</t>
+          <t>Set Auto Path to Destination</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>冻结转场背景</t>
+          <t>设置自动寻路到终点</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>FREEZE_TRANSITION_BACKGROUND_DESC</t>
+          <t>SET_AUTO_PATH_TO_DESTINATION_DESC</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Capture the current frame as the next transition background, then continue when ready.</t>
+          <t>Pathfind an actor to the target map cell. Started continues immediately; Finished continues after movement ends.</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>捕获当前帧作为下一次转场背景，并在捕获完成后继续。</t>
+          <t>让 actor 自动寻路到指定地图格。Started 立即继续，Finished 在移动结束后继续。</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>REQUEST_TRANSITION</t>
+          <t>FREEZE_TRANSITION_BACKGROUND</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Request Transition</t>
+          <t>Freeze Transition Background</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>请求转场</t>
+          <t>冻结转场背景</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>REQUEST_TRANSITION_DESC</t>
+          <t>FREEZE_TRANSITION_BACKGROUND_DESC</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Start a screen transition (empty transitionName uses a plain fade), then continue when it finishes.</t>
+          <t>Capture the current frame as the next transition background, then continue when ready.</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>启动屏幕转场（transitionName 为空时为普通淡入），并在转场结束后继续。</t>
+          <t>捕获当前帧作为下一次转场背景，并在捕获完成后继续。</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>GAME_OVER</t>
+          <t>REQUEST_TRANSITION</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Game Over</t>
+          <t>Request Transition</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>游戏结束</t>
+          <t>请求转场</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
+          <t>REQUEST_TRANSITION_DESC</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Start a screen transition (empty transitionName uses a plain fade), then continue when it finishes.</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>启动屏幕转场（transitionName 为空时为普通淡入），并在转场结束后继续。</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>GAME_OVER</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Game Over</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>游戏结束</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
           <t>GAME_OVER_DESC</t>
         </is>
       </c>
-      <c r="B382" t="inlineStr">
+      <c r="B384" t="inlineStr">
         <is>
           <t>Switch to the game over scene.</t>
         </is>
       </c>
-      <c r="C382" t="inlineStr">
+      <c r="C384" t="inlineStr">
         <is>
           <t>进入游戏结束场景。</t>
         </is>

--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -7392,7 +7392,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>可以打开一扇黄门</t>
+          <t>可以打开一扇黄门。</t>
         </is>
       </c>
     </row>
@@ -7426,7 +7426,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>可以打开一扇蓝门</t>
+          <t>可以打开一扇蓝门。</t>
         </is>
       </c>
     </row>
@@ -7460,7 +7460,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>可以打开一扇红门</t>
+          <t>可以打开一扇红门。</t>
         </is>
       </c>
     </row>
@@ -7494,7 +7494,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>持有后可以查看敌人信息（快捷键D）</t>
+          <t>持有后可以查看敌人信息（快捷键D）。</t>
         </is>
       </c>
     </row>
@@ -7528,7 +7528,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>持有后可以在前往过的传送点（快捷键F）</t>
+          <t>持有后可以在前往过的传送点（快捷键F）。</t>
         </is>
       </c>
     </row>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>可以破坏面前的一堵墙壁</t>
+          <t>可以破坏面前的一堵墙壁。</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>可以清除当前地图所有墙壁</t>
+          <t>可以清除当前地图所有墙壁。</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7630,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>可以破坏面前的一块熔岩</t>
+          <t>可以破坏面前的一块熔岩。</t>
         </is>
       </c>
     </row>
@@ -7664,7 +7664,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>可以破坏面前的一块冰墙</t>
+          <t>可以破坏面前的一块冰墙。</t>
         </is>
       </c>
     </row>
@@ -7735,7 +7735,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>这是一个骷髅</t>
+          <t>这是一个骷髅。</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>这是一个史莱姆</t>
+          <t>这是一个史莱姆。</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>铁制造的剑，装备后可提升10攻击力</t>
+          <t>铁制造的剑，装备后可提升10攻击力。</t>
         </is>
       </c>
     </row>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>铁制造的盾，装备后可提升10防御力</t>
+          <t>铁制造的盾，装备后可提升10防御力。</t>
         </is>
       </c>
     </row>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>勇猛的战士，具有比较均衡的能力</t>
+          <t>勇猛的战士，具有比较均衡的能力。</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <sheetData>
     <row r="1">
@@ -8015,7 +8015,41 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>陷入中毒状态后每回合会多损失中毒层数数值的生命值</t>
+          <t>陷入中毒状态后，每回合会多损失中毒层数数值的生命值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>WEAK</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>衰弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>WEAK_DESC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When weakened, the attack and defense capabilities will be reduced based on the corresponding stack value during combat.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>陷入衰弱状态后，会在战斗时少发挥响应层数数值的攻击力和防御力。</t>
         </is>
       </c>
     </row>
@@ -8095,7 +8129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8145,7 +8179,41 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>战斗后会使我方陷入中毒状态</t>
+          <t>战斗后会使我方陷入中毒状态。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>S_WEAKEN</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Weaken</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>衰弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>S_WEAKEN_DESC</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Player will be weak after this battle.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>战斗后会使我方陷入衰弱状态。</t>
         </is>
       </c>
     </row>

--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -7680,7 +7680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="29.58203125" customWidth="1" min="1" max="1"/>
@@ -7770,6 +7770,142 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>这是一个史莱姆。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ROCK</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rock</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>石头人</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ROCK_DESC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>This is a rock.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>这是一个石头人。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MAGE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mage</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>魔法师</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MAGE_DESC</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>This is a mage.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>这是一个魔法师。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BAT</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bat</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>大蝙蝠</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BAT_DESC</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>This is a bat.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>这是一个大蝙蝠。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>KNIGHT</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Knight</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>骑士</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>KNIGHT_DESC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>This is a knight.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>这是一位骑士。</t>
         </is>
       </c>
     </row>
@@ -8129,7 +8265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8217,6 +8353,142 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>S_HARD</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>坚固</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S_HARD_DESC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>The holder's DEF is treated as at least the opponent's ATK minus 1 during damage calculation.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>计算伤害时，持有者的防御力视为不低于对方攻击力-1。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>S_MAGIC</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>魔攻</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>S_MAGIC_DESC</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>During battle, the holder treats the opponent's DEF as 0 when calculating damage.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>战斗中计算伤害时，持有者将对方防御力视为0。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>S_MULTIHIT</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MultiHit</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>连击</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>S_MULTIHIT_DESC</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>During battle, each round's base damage is multiplied by the holder's hit count. Missing or invalid values count as 1, with a minimum of 1.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>战斗中，持有者每回合基础伤害会按连击数倍计算。未设置或无效值视为1，最低为1。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>S_COMPETE</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>争斗</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>S_COMPETE_DESC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>The holder's ATK is treated as at least the opponent's ATK.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>持有者的攻击力视为不低于对方攻击力。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="280" yWindow="4710" windowWidth="28800" windowHeight="15370" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="System" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="UI" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Items" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Enemies" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Equips" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Classes" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="States" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="MapNames" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Specials" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Items" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemies" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equips" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="States" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MapNames" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Specials" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_1" localSheetId="0">System!$A$6:$C$249</definedName>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C384"/>
+  <dimension ref="A1:C388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="38.75" customWidth="1" min="1" max="1"/>
@@ -6946,6 +6946,74 @@
       <c r="C384" t="inlineStr">
         <is>
           <t>进入游戏结束场景。</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>LOCK_CAMERA</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Lock Camera</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>锁定镜头</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>LOCK_CAMERA_DESC</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Lock the current map camera to the player.</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>将当前地图镜头锁定到玩家身上。</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>UNLOCK_CAMERA</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Unlock Camera</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>解除镜头锁定</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>UNLOCK_CAMERA_DESC</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Stop the current map camera from following the player.</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>停止当前地图镜头跟随玩家。</t>
         </is>
       </c>
     </row>

--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="280" yWindow="4710" windowWidth="28800" windowHeight="15370" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Items" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemies" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equips" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classes" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="States" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MapNames" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Specials" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="System" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="UI" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Items" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Enemies" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Equips" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Classes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="States" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="MapNames" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Specials" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_1" localSheetId="0">System!$A$6:$C$249</definedName>
@@ -416,7 +416,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C388"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14" outlineLevelCol="0"/>
   <cols>
     <col width="38.75" customWidth="1" min="1" max="1"/>
     <col width="61.83203125" customWidth="1" min="2" max="2"/>
@@ -7030,7 +7030,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14" outlineLevelCol="0"/>
   <cols>
     <col width="17.4140625" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -7406,7 +7406,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14" outlineLevelCol="0"/>
   <cols>
     <col width="25.75" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
@@ -7749,7 +7749,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14" outlineLevelCol="0"/>
   <cols>
     <col width="29.58203125" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
@@ -8333,7 +8333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8356,202 +8356,236 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S_POISOING</t>
+          <t>NORMAL_SPECIAL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Poisoning</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>中毒</t>
+          <t>普通</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S_POISOING_DESC</t>
+          <t>MORE_SPECIAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Player will be poisoned after this battle.</t>
+          <t>More...</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>战斗后会使我方陷入中毒状态。</t>
+          <t>更多...</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S_WEAKEN</t>
+          <t>S_POISONING</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Weaken</t>
+          <t>Poisoning</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>衰弱</t>
+          <t>中毒</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S_WEAKEN_DESC</t>
+          <t>S_POISONING_DESC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Player will be weak after this battle.</t>
+          <t>Player will be poisoned after this battle.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>战斗后会使我方陷入衰弱状态。</t>
+          <t>战斗后会使我方陷入中毒状态。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S_HARD</t>
+          <t>S_WEAKEN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Weaken</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>坚固</t>
+          <t>衰弱</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S_HARD_DESC</t>
+          <t>S_WEAKEN_DESC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The holder's DEF is treated as at least the opponent's ATK minus 1 during damage calculation.</t>
+          <t>Player will be weak after this battle.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>计算伤害时，持有者的防御力视为不低于对方攻击力-1。</t>
+          <t>战斗后会使我方陷入衰弱状态。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S_MAGIC</t>
+          <t>S_HARD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>魔攻</t>
+          <t>坚固</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S_MAGIC_DESC</t>
+          <t>S_HARD_DESC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>During battle, the holder treats the opponent's DEF as 0 when calculating damage.</t>
+          <t>The holder's DEF is treated as at least the opponent's ATK minus 1 during damage calculation.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>战斗中计算伤害时，持有者将对方防御力视为0。</t>
+          <t>计算伤害时，持有者的防御力视为不低于对方攻击力-1。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S_MULTIHIT</t>
+          <t>S_MAGIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MultiHit</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>连击</t>
+          <t>魔攻</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S_MULTIHIT_DESC</t>
+          <t>S_MAGIC_DESC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>During battle, each round's base damage is multiplied by the holder's hit count. Missing or invalid values count as 1, with a minimum of 1.</t>
+          <t>During battle, the holder treats the opponent's DEF as 0 when calculating damage.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>战斗中，持有者每回合基础伤害会按连击数倍计算。未设置或无效值视为1，最低为1。</t>
+          <t>战斗中计算伤害时，持有者将对方防御力视为0。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S_COMPETE</t>
+          <t>S_MULTIHIT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Compete</t>
+          <t>MultiHit</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>争斗</t>
+          <t>连击</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>S_MULTIHIT_DESC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>During battle, each round's base damage is multiplied by the holder's hit count. Missing or invalid values count as 1, with a minimum of 1.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>战斗中，持有者每回合基础伤害会按连击数倍计算。未设置或无效值视为1，最低为1。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>S_COMPETE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>争斗</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>S_COMPETE_DESC</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>The holder's ATK is treated as at least the opponent's ATK.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>持有者的攻击力视为不低于对方攻击力。</t>
         </is>

--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -415,8 +415,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C388"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14" outlineLevelCol="0"/>
+  <dimension ref="A1:C402"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="38.75" customWidth="1" min="1" max="1"/>
     <col width="61.83203125" customWidth="1" min="2" max="2"/>
@@ -4050,13 +4050,15 @@
           <t>EQUALS</t>
         </is>
       </c>
-      <c r="B214" s="1">
-        <f>=</f>
-        <v/>
-      </c>
-      <c r="C214" s="1">
-        <f>=</f>
-        <v/>
+      <c r="B214" s="1" t="inlineStr">
+        <is>
+          <t>==</t>
+        </is>
+      </c>
+      <c r="C214" s="1" t="inlineStr">
+        <is>
+          <t>==</t>
+        </is>
       </c>
     </row>
     <row r="215">
@@ -7014,6 +7016,244 @@
       <c r="C388" t="inlineStr">
         <is>
           <t>停止当前地图镜头跟随玩家。</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>REGISTER_EVENT_BUS</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Register EventBus</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>注册 EventBus</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>REGISTER_EVENT_BUS_DESC</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Subscribe an object event or method to an EventBus key.</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>将对象的事件或方法注册到 EventBus key。</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>TRIGGER_EVENT_BUS</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Trigger EventBus</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>触发 EventBus</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>TRIGGER_EVENT_BUS_DESC</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Post kwargs to an EventBus key; registered object events run on a later logic frame.</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>向指定 EventBus key 发送参数，已注册的对象事件会在后续逻辑帧执行。</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>REGISTER_EVENT_BUS_EVENT</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Register EventBus Event</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>注册 EventBus 事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>REGISTER_EVENT_BUS_EVENT_DESC</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Subscribe an object blueprint event to an EventBus key. Event payload is ignored.</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>将对象的蓝图事件注册到 EventBus key，忽略事件参数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>TRIGGER_BLUEPRINT_EVENT</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Trigger Blueprint Event</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>触发蓝图事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>TRIGGER_BLUEPRINT_EVENT_DESC</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Trigger a blueprint event on an object without arguments.</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>不带参数地触发对象上的蓝图事件。</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>GET_GAME_VARIABLE_REF</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Get Game Variable Ref</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>获取游戏变量引用</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>GET_GAME_VARIABLE_REF_DESC</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Get a readable/writable reference to a game variable.</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>获取一个可读写的游戏变量引用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>UNREGISTER_EVENT_BUS</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Unregister EventBus</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>取消 EventBus 注册</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>UNREGISTER_EVENT_BUS_DESC</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Unsubscribe an object event or method from an EventBus key.</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>取消对象事件或方法对 EventBus key 的注册。</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>UNREGISTER_EVENT_BUS_EVENT</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Unregister EventBus Event</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>取消 EventBus 蓝图事件注册</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>UNREGISTER_EVENT_BUS_EVENT_DESC</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Unsubscribe an object blueprint event from an EventBus key.</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>取消对象蓝图事件对 EventBus key 的注册。</t>
         </is>
       </c>
     </row>
@@ -7029,8 +7269,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14" outlineLevelCol="0"/>
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="17.4140625" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -7391,6 +7631,210 @@
       <c r="C21" t="inlineStr">
         <is>
           <t>点位 {index}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>语言</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>scale</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>缩放</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>framerate</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Frame Rate</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>帧率</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>verticalsync</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Vertical Sync</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>垂直同步</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>musicon</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>音乐</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>musicvolume</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Music Volume</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>音乐音量</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>soundon</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>音效</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>soundvolume</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Sound Volume</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>音效音量</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voiceon</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Voice</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>语音</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>voicevolume</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Voice Volume</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>语音音量</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>en_GB</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>zh_CN</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Simplified Chinese</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>简体中文</t>
         </is>
       </c>
     </row>
@@ -7406,7 +7850,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="25.75" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
@@ -7749,7 +8193,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="29.58203125" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>

--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -15,6 +15,7 @@
     <sheet name="States" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="MapNames" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Specials" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Player" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_1" localSheetId="0">System!$A$6:$C$249</definedName>
@@ -415,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C402"/>
+  <dimension ref="A1:C404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="38.75" customWidth="1" min="1" max="1"/>
@@ -4050,15 +4051,13 @@
           <t>EQUALS</t>
         </is>
       </c>
-      <c r="B214" s="1" t="inlineStr">
-        <is>
-          <t>==</t>
-        </is>
-      </c>
-      <c r="C214" s="1" t="inlineStr">
-        <is>
-          <t>==</t>
-        </is>
+      <c r="B214" s="1">
+        <f>=</f>
+        <v/>
+      </c>
+      <c r="C214" s="1">
+        <f>=</f>
+        <v/>
       </c>
     </row>
     <row r="215">
@@ -7254,12 +7253,111 @@
       <c r="C402" t="inlineStr">
         <is>
           <t>取消对象蓝图事件对 EventBus key 的注册。</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>GET_ANIM_VISUAL_LENGTH</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Get Animation Visual Length</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>获取动画视觉时长</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>GET_ANIM_VISUAL_LENGTH_DESC</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Get the visual duration of an animation, excluding sound track length (seconds).</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>获取指定动画的视觉时长（秒），不包含音轨长度。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>en_GB</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>zh_CN</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BRAVOR</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bravor</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>勇士</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BRAVOR_DESC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>This is a bravor player pawn.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>这是一个勇士形式角色。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -7269,7 +7367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="17.4140625" customWidth="1" min="1" max="1"/>
@@ -7835,6 +7933,159 @@
       <c r="C33" t="inlineStr">
         <is>
           <t>简体中文</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>STAT_HP</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>HP:</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>生命:</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>STAT_MAXHP</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>MAXHP:</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>最大生命:</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>STAT_ATK</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ATK:</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>攻击:</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>STAT_DEF</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>DEF:</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>防御:</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>STAT_EXP</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>EXP:</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>经验:</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>STAT_GOLD</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>GOLD:</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>金币:</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>STAT_DMG</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>DMG:</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>伤害:</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>STAT_HIT</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>HIT:</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>连击:</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>STAT_CRIT</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CRIT:</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>临界:</t>
         </is>
       </c>
     </row>
@@ -8992,12 +9243,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>During battle, each round's base damage is multiplied by the holder's hit count. Missing or invalid values count as 1, with a minimum of 1.</t>
+          <t>During battle, each round's base damage is multiplied by the holder's hit count.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>战斗中，持有者每回合基础伤害会按连击数倍计算。未设置或无效值视为1，最低为1。</t>
+          <t>战斗中，持有者每回合基础伤害会按连击数倍计算。</t>
         </is>
       </c>
     </row>

--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="280" yWindow="4710" windowWidth="28800" windowHeight="15370" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="System" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="UI" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Items" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Enemies" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Equips" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Classes" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="States" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="MapNames" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Specials" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Player" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Items" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemies" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equips" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="States" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MapNames" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Specials" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_1" localSheetId="0">System!$A$6:$C$249</definedName>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C404"/>
+  <dimension ref="A1:C406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="38.75" customWidth="1" min="1" max="1"/>
@@ -7287,6 +7287,40 @@
       <c r="C404" t="inlineStr">
         <is>
           <t>获取指定动画的视觉时长（秒），不包含音轨长度。</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>TO_SHORT_NUMBER</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Short Number</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>数值缩写</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>TO_SHORT_NUMBER_DESC</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Shorten large numbers with k/m/b suffixes.</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>将较大的数字显示为 k/m/b 缩写。</t>
         </is>
       </c>
     </row>

--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C406"/>
+  <dimension ref="A1:C412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="38.75" customWidth="1" min="1" max="1"/>
@@ -7321,6 +7321,108 @@
       <c r="C406" t="inlineStr">
         <is>
           <t>将较大的数字显示为 k/m/b 缩写。</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>SHOW_VOICE_MESSAGE</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Show Voice Message</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>语音对话</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>SHOW_VOICE_MESSAGE_DESC</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Play a voice clip and show dialogue on the current map scene. refActorTag controls dialogue-window placement; refActor controls spatial voice position.</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>在当前地图场景中播放语音并显示对话。refActorTag 控制对话窗口位置；refActor 控制空间语音位置。</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>SHOW_MESSAGE</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Show Message</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>显示对话</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>SHOW_MESSAGE_DESC</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Show dialogue on the current map scene. refActorTag controls dialogue-window placement.</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>在当前地图场景中显示对话。refActorTag 用于控制对话窗口位置。</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>SHOW_SELECTION</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Show Selection</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>显示选项</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>SHOW_SELECTION_DESC</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Show a selection window on the current map scene. refActorTag controls selection-window placement.</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>在当前地图场景中显示选项窗口。refActorTag 用于控制选项窗口位置。</t>
         </is>
       </c>
     </row>

--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="280" yWindow="4710" windowWidth="28800" windowHeight="15370" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-35050" yWindow="4360" windowWidth="28800" windowHeight="15370" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Items" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemies" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equips" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classes" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="States" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MapNames" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Specials" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="System" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="UI" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Items" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Enemies" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Equips" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Classes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="States" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="MapNames" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Specials" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Player" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_1" localSheetId="0">System!$A$6:$C$249</definedName>
@@ -69,10 +69,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -416,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C412"/>
+  <dimension ref="A1:C420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="38.75" customWidth="1" min="1" max="1"/>
@@ -4051,13 +4052,15 @@
           <t>EQUALS</t>
         </is>
       </c>
-      <c r="B214" s="1">
-        <f>=</f>
-        <v/>
-      </c>
-      <c r="C214" s="1">
-        <f>=</f>
-        <v/>
+      <c r="B214" s="3" t="inlineStr">
+        <is>
+          <t>==</t>
+        </is>
+      </c>
+      <c r="C214" s="3" t="inlineStr">
+        <is>
+          <t>==</t>
+        </is>
       </c>
     </row>
     <row r="215">
@@ -7423,6 +7426,142 @@
       <c r="C412" t="inlineStr">
         <is>
           <t>在当前地图场景中显示选项窗口。refActorTag 用于控制选项窗口位置。</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>GET_PLAYER_ATTR_REF</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Get Player Attribute Ref</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>获取玩家属性引用</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>GET_PLAYER_ATTR_REF_DESC</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Get a readable/writable reference to a player attribute (e.g. HP, ATK, DEF, GOLD).</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>获取玩家指定属性的可读写引用（如 HP/ATK/DEF/GOLD）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>ADD_HP</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Add HP</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>增加HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>ADD_HP_DESC</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Add HP to the player (can be negative to subtract).</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>为玩家增加（或减少）HP。</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>ADD_ATK</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Add ATK</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>增加攻击力</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>ADD_ATK_DESC</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Add ATK to the player (can be negative to subtract).</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>为玩家增加（或减少）攻击力。</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>ADD_DEF</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Add DEF</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>增加防御力</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>ADD_DEF_DESC</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Add DEF to the player (can be negative to subtract).</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>为玩家增加（或减少）防御力。</t>
         </is>
       </c>
     </row>
@@ -7439,7 +7578,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -9100,7 +9239,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -9165,7 +9304,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">

--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C420"/>
+  <dimension ref="A1:C437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="38.75" customWidth="1" min="1" max="1"/>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>==</t>
+          <t>'==</t>
         </is>
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>==</t>
+          <t>'==</t>
         </is>
       </c>
     </row>
@@ -7562,6 +7562,295 @@
       <c r="C420" t="inlineStr">
         <is>
           <t>为玩家增加（或减少）防御力。</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>TONE_SHADER_LOAD_FAILED</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Failed to load screen tone shader</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>画面色调着色器加载失败</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>CHANGE_SCREEN_TONE</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Change Screen Tone</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>更改画面色调</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>CHANGE_SCREEN_TONE_DESC</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Change the screen tone over time. Red, green, and blue range from -255 to 255; gray ranges from 0 to 255; duration is in seconds.</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>在指定时间内更改画面色调。红、绿、蓝范围为 -255 到 255；灰度范围为 0 到 255；持续时间单位为秒。</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>CLEAR_SCREEN_TONE</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Clear Screen Tone</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>清除画面色调</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>CLEAR_SCREEN_TONE_DESC</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Fade the screen tone back to normal over the given duration in seconds.</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>在指定秒数内将画面色调恢复为正常。</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>CREATE_ACTOR_FROM_BP_PATH</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Create Actor From BP Path</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>从蓝图路径创建 Actor</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>CREATE_ACTOR_FROM_BP_PATH_DESC</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Create an actor from a blueprint class path and spawn it on the current map.</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>根据蓝图类路径创建 Actor，并生成到当前地图。</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>ADD_TIMER</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Add Timer</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>添加计时器</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>ADD_TIMER_DESC</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Wait for a scene timer. If blocking is enabled, player movement and scene hotkeys are disabled until TimeUp.</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>等待场景计时器。如果启用阻塞，TimeUp 前玩家移动和场景快捷键不可用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>RECORD_DESTROYED_ACTOR</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Record Destroyed Actor</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>记录已销毁 Actor</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>RECORD_DESTROYED_ACTOR_DESC</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Record a destroyed actor for persistence on the current map scene.</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>在当前地图场景中记录一个已销毁 Actor，用于存档持久化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>SELF_RECORD_DESTROYED</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Self Record Destroyed</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>自身记录已销毁</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>SELF_RECORD_DESTROYED_DESC</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Record the blueprint owner as a destroyed actor for persistence on the current map scene.</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>将蓝图所有者记录为已销毁 Actor，用于在当前地图场景中持久化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>RECORD_AND_DESTROY_ACTOR</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Record And Destroy Actor</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>记录并销毁 Actor</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>RECORD_AND_DESTROY_ACTOR_DESC</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Record a destroyed actor for persistence and destroy it on the current map scene.</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>在当前地图场景中记录一个已销毁 Actor 并销毁它。</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>SELF_RECORD_AND_DESTROY</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Self Record And Destroy</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>自身记录并销毁</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>SELF_RECORD_AND_DESTROY_DESC</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Record the blueprint owner as destroyed for persistence and destroy it on the current map scene.</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>将蓝图所有者记录为已销毁并销毁它，用于在当前地图场景中持久化。</t>
         </is>
       </c>
     </row>

--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C437"/>
+  <dimension ref="A1:C453"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="38.75" customWidth="1" min="1" max="1"/>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Play a voice clip and show dialogue on the current map scene. refActorTag controls dialogue-window placement; refActor controls spatial voice position.</t>
+          <t>Play a non-spatial voice clip and show a dialogue message on the current map scene. refActorTag controls dialogue-window placement.</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>在当前地图场景中播放语音并显示对话。refActorTag 控制对话窗口位置；refActor 控制空间语音位置。</t>
+          <t>在当前地图场景中播放非空间语音并显示对话。refActorTag 控制对话窗口位置。</t>
         </is>
       </c>
     </row>
@@ -7851,6 +7851,278 @@
       <c r="C437" t="inlineStr">
         <is>
           <t>将蓝图所有者记录为已销毁并销毁它，用于在当前地图场景中持久化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>SHOW_REF_MESSAGE</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Show Ref Message</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>显示引用消息</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>SHOW_REF_MESSAGE_DESC</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Show a dialogue message on the current map scene. Uses a direct actor reference for window placement.</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>在当前地图场景中显示对话，通过直接 Actor 引用进行窗口定位。</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>SHOW_VOICE_REF_MESSAGE</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Show Voice Ref Message</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>显示引用语音消息</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>SHOW_VOICE_REF_MESSAGE_DESC</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Play a spatial voice clip and show a dialogue message on the current map scene. Uses a direct actor reference for voice positioning.</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>在当前地图场景中播放空间语音并显示对话。通过直接 Actor 引用进行语音定位。</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>GET_SELF_ATTR</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Get Self Attr</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>获取自身属性</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>GET_SELF_ATTR_DESC</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Read an attribute value from the blueprint owner</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>读取蓝图拥有者的属性值</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>SET_SELF_ATTR</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Set Self Attr</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>设置自身属性</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>SET_SELF_ATTR_DESC</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Set an attribute value on the blueprint owner</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>设置蓝图拥有者的属性值</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>IF_PLAYER_OVERLAPS</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>If Player Overlaps</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>玩家是否重叠</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>IF_PLAYER_OVERLAPS_DESC</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Check if the player shares the same cell as the blueprint owner</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>判断玩家是否与蓝图拥有者处于同一格子</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>IF_GAME_VAR</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>If Game Var</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>判断游戏变量</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>IF_GAME_VAR_DESC</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Compare a game variable with a given value, returning a true/false branch</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>将游戏变量与给定值进行比较，返回真假分支</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>GET_ACTOR_BY_TAG</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Get Actor By Tag</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>按标签查找角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>GET_ACTOR_BY_TAG_DESC</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Find an actor by tag on the current map</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>在当前地图上按标签查找角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>GET_ALL_ACTORS</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Get All Actors</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>获取全部角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>GET_ALL_ACTORS_DESC</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Get a list of all actors on the current map</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>获取当前地图上的所有角色列表</t>
         </is>
       </c>
     </row>

--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-35050" yWindow="4360" windowWidth="28800" windowHeight="15370" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="System" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="UI" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Items" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Enemies" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Equips" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Classes" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="States" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="MapNames" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Specials" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Player" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Items" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemies" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equips" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="States" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MapNames" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Specials" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_1" localSheetId="0">System!$A$6:$C$249</definedName>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C453"/>
+  <dimension ref="A1:C465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="38.75" customWidth="1" min="1" max="1"/>
@@ -7024,1105 +7024,1309 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>REGISTER_EVENT_BUS</t>
+          <t>ATTACH_CAMERA</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Register EventBus</t>
+          <t>Attach Camera</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>注册 EventBus</t>
+          <t>附着镜头</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>REGISTER_EVENT_BUS_DESC</t>
+          <t>ATTACH_CAMERA_DESC</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Subscribe an object event or method to an EventBus key.</t>
+          <t>Attach the current map camera to the specified actor. Pass None to detach and stop following.</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>将对象的事件或方法注册到 EventBus key。</t>
+          <t>将当前地图镜头附着到指定 Actor；传入 None 可取消附着并停止跟随。</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>TRIGGER_EVENT_BUS</t>
+          <t>MOVE_CAMERA</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Trigger EventBus</t>
+          <t>Move Camera</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>触发 EventBus</t>
+          <t>移动镜头</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>TRIGGER_EVENT_BUS_DESC</t>
+          <t>MOVE_CAMERA_DESC</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Post kwargs to an EventBus key; registered object events run on a later logic frame.</t>
+          <t>Move the current map camera by the given viewport offset and clamp it to the map bounds.</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>向指定 EventBus key 发送参数，已注册的对象事件会在后续逻辑帧执行。</t>
+          <t>按给定视口偏移移动当前地图镜头，并将结果自动钳制到地图范围内。</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>REGISTER_EVENT_BUS_EVENT</t>
+          <t>REGISTER_EVENT_BUS</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Register EventBus Event</t>
+          <t>Register EventBus</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>注册 EventBus 事件</t>
+          <t>注册 EventBus</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>REGISTER_EVENT_BUS_EVENT_DESC</t>
+          <t>REGISTER_EVENT_BUS_DESC</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Subscribe an object blueprint event to an EventBus key. Event payload is ignored.</t>
+          <t>Subscribe an object event or method to an EventBus key.</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>将对象的蓝图事件注册到 EventBus key，忽略事件参数。</t>
+          <t>将对象的事件或方法注册到 EventBus key。</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>TRIGGER_BLUEPRINT_EVENT</t>
+          <t>TRIGGER_EVENT_BUS</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Trigger Blueprint Event</t>
+          <t>Trigger EventBus</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>触发蓝图事件</t>
+          <t>触发 EventBus</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>TRIGGER_BLUEPRINT_EVENT_DESC</t>
+          <t>TRIGGER_EVENT_BUS_DESC</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Trigger a blueprint event on an object without arguments.</t>
+          <t>Post kwargs to an EventBus key; registered object events run on a later logic frame.</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>不带参数地触发对象上的蓝图事件。</t>
+          <t>向指定 EventBus key 发送参数，已注册的对象事件会在后续逻辑帧执行。</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>GET_GAME_VARIABLE_REF</t>
+          <t>REGISTER_EVENT_BUS_EVENT</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Get Game Variable Ref</t>
+          <t>Register EventBus Event</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>获取游戏变量引用</t>
+          <t>注册 EventBus 事件</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>GET_GAME_VARIABLE_REF_DESC</t>
+          <t>REGISTER_EVENT_BUS_EVENT_DESC</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Get a readable/writable reference to a game variable.</t>
+          <t>Subscribe an object blueprint event to an EventBus key. Event payload is ignored.</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>获取一个可读写的游戏变量引用。</t>
+          <t>将对象的蓝图事件注册到 EventBus key，忽略事件参数。</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>UNREGISTER_EVENT_BUS</t>
+          <t>TRIGGER_BLUEPRINT_EVENT</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Unregister EventBus</t>
+          <t>Trigger Blueprint Event</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>取消 EventBus 注册</t>
+          <t>触发蓝图事件</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>UNREGISTER_EVENT_BUS_DESC</t>
+          <t>TRIGGER_BLUEPRINT_EVENT_DESC</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Unsubscribe an object event or method from an EventBus key.</t>
+          <t>Trigger a blueprint event on an object without arguments.</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>取消对象事件或方法对 EventBus key 的注册。</t>
+          <t>不带参数地触发对象上的蓝图事件。</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>UNREGISTER_EVENT_BUS_EVENT</t>
+          <t>GET_GAME_VARIABLE_REF</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Unregister EventBus Event</t>
+          <t>Get Game Variable Ref</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>取消 EventBus 蓝图事件注册</t>
+          <t>获取游戏变量引用</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>UNREGISTER_EVENT_BUS_EVENT_DESC</t>
+          <t>GET_GAME_VARIABLE_REF_DESC</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Unsubscribe an object blueprint event from an EventBus key.</t>
+          <t>Get a readable/writable reference to a game variable.</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>取消对象蓝图事件对 EventBus key 的注册。</t>
+          <t>获取一个可读写的游戏变量引用。</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>GET_ANIM_VISUAL_LENGTH</t>
+          <t>UNREGISTER_EVENT_BUS</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Get Animation Visual Length</t>
+          <t>Unregister EventBus</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>获取动画视觉时长</t>
+          <t>取消 EventBus 注册</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>GET_ANIM_VISUAL_LENGTH_DESC</t>
+          <t>UNREGISTER_EVENT_BUS_DESC</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Get the visual duration of an animation, excluding sound track length (seconds).</t>
+          <t>Unsubscribe an object event or method from an EventBus key.</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>获取指定动画的视觉时长（秒），不包含音轨长度。</t>
+          <t>取消对象事件或方法对 EventBus key 的注册。</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>TO_SHORT_NUMBER</t>
+          <t>UNREGISTER_EVENT_BUS_EVENT</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Short Number</t>
+          <t>Unregister EventBus Event</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>数值缩写</t>
+          <t>取消 EventBus 蓝图事件注册</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>TO_SHORT_NUMBER_DESC</t>
+          <t>UNREGISTER_EVENT_BUS_EVENT_DESC</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Shorten large numbers with k/m/b suffixes.</t>
+          <t>Unsubscribe an object blueprint event from an EventBus key.</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>将较大的数字显示为 k/m/b 缩写。</t>
+          <t>取消对象蓝图事件对 EventBus key 的注册。</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>SHOW_VOICE_MESSAGE</t>
+          <t>GET_ANIM_VISUAL_LENGTH</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Show Voice Message</t>
+          <t>Get Animation Visual Length</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>语音对话</t>
+          <t>获取动画视觉时长</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>SHOW_VOICE_MESSAGE_DESC</t>
+          <t>GET_ANIM_VISUAL_LENGTH_DESC</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Play a non-spatial voice clip and show a dialogue message on the current map scene. refActorTag controls dialogue-window placement.</t>
+          <t>Get the visual duration of an animation, excluding sound track length (seconds).</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>在当前地图场景中播放非空间语音并显示对话。refActorTag 控制对话窗口位置。</t>
+          <t>获取指定动画的视觉时长（秒），不包含音轨长度。</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>SHOW_MESSAGE</t>
+          <t>TO_SHORT_NUMBER</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Show Message</t>
+          <t>Short Number</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>显示对话</t>
+          <t>数值缩写</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>SHOW_MESSAGE_DESC</t>
+          <t>TO_SHORT_NUMBER_DESC</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Show dialogue on the current map scene. refActorTag controls dialogue-window placement.</t>
+          <t>Shorten large numbers with k/m/b suffixes.</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>在当前地图场景中显示对话。refActorTag 用于控制对话窗口位置。</t>
+          <t>将较大的数字显示为 k/m/b 缩写。</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>SHOW_SELECTION</t>
+          <t>SHOW_VOICE_MESSAGE</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Show Selection</t>
+          <t>Show Voice Message</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>显示选项</t>
+          <t>语音对话</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>SHOW_SELECTION_DESC</t>
+          <t>SHOW_VOICE_MESSAGE_DESC</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Show a selection window on the current map scene. refActorTag controls selection-window placement.</t>
+          <t>Play a non-spatial voice clip and show a dialogue message on the current map scene. refActorTag controls dialogue-window placement.</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>在当前地图场景中显示选项窗口。refActorTag 用于控制选项窗口位置。</t>
+          <t>在当前地图场景中播放非空间语音并显示对话。refActorTag 控制对话窗口位置。</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>GET_PLAYER_ATTR_REF</t>
+          <t>SHOW_MESSAGE</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Get Player Attribute Ref</t>
+          <t>Show Message</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>获取玩家属性引用</t>
+          <t>显示对话</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>GET_PLAYER_ATTR_REF_DESC</t>
+          <t>SHOW_MESSAGE_DESC</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Get a readable/writable reference to a player attribute (e.g. HP, ATK, DEF, GOLD).</t>
+          <t>Show dialogue on the current map scene. refActorTag controls dialogue-window placement.</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>获取玩家指定属性的可读写引用（如 HP/ATK/DEF/GOLD）。</t>
+          <t>在当前地图场景中显示对话。refActorTag 用于控制对话窗口位置。</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>ADD_HP</t>
+          <t>SHOW_SELECTION</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Add HP</t>
+          <t>Show Selection</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>增加HP</t>
+          <t>显示选项</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>ADD_HP_DESC</t>
+          <t>SHOW_SELECTION_DESC</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Add HP to the player (can be negative to subtract).</t>
+          <t>Show a selection window on the current map scene. refActorTag controls selection-window placement.</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>为玩家增加（或减少）HP。</t>
+          <t>在当前地图场景中显示选项窗口。refActorTag 用于控制选项窗口位置。</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>ADD_ATK</t>
+          <t>SHOW_REF_SELECTION</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Add ATK</t>
+          <t>Show Ref Selection</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>增加攻击力</t>
+          <t>显示引用选项</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>ADD_ATK_DESC</t>
+          <t>SHOW_REF_SELECTION_DESC</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Add ATK to the player (can be negative to subtract).</t>
+          <t>Show a selection window on the current map scene. Uses a direct actor reference for selection-window placement.</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>为玩家增加（或减少）攻击力。</t>
+          <t>在当前地图场景中显示选项窗口。通过直接 Actor 引用进行选项窗口定位。</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>ADD_DEF</t>
+          <t>GET_PLAYER_ATTR_REF</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Add DEF</t>
+          <t>Get Player Attribute Ref</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>增加防御力</t>
+          <t>获取玩家属性引用</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>ADD_DEF_DESC</t>
+          <t>GET_PLAYER_ATTR_REF_DESC</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Add DEF to the player (can be negative to subtract).</t>
+          <t>Get a readable/writable reference to a player attribute (e.g. HP, ATK, DEF, GOLD).</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>为玩家增加（或减少）防御力。</t>
+          <t>获取玩家指定属性的可读写引用（如 HP/ATK/DEF/GOLD）。</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>TONE_SHADER_LOAD_FAILED</t>
+          <t>ADD_HP</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Failed to load screen tone shader</t>
+          <t>Add HP</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>画面色调着色器加载失败</t>
+          <t>增加HP</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>CHANGE_SCREEN_TONE</t>
+          <t>ADD_HP_DESC</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Change Screen Tone</t>
+          <t>Add HP to the player (can be negative to subtract).</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>更改画面色调</t>
+          <t>为玩家增加（或减少）HP。</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>CHANGE_SCREEN_TONE_DESC</t>
+          <t>ADD_ATK</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Change the screen tone over time. Red, green, and blue range from -255 to 255; gray ranges from 0 to 255; duration is in seconds.</t>
+          <t>Add ATK</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>在指定时间内更改画面色调。红、绿、蓝范围为 -255 到 255；灰度范围为 0 到 255；持续时间单位为秒。</t>
+          <t>增加攻击力</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>CLEAR_SCREEN_TONE</t>
+          <t>ADD_ATK_DESC</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Clear Screen Tone</t>
+          <t>Add ATK to the player (can be negative to subtract).</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>清除画面色调</t>
+          <t>为玩家增加（或减少）攻击力。</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>CLEAR_SCREEN_TONE_DESC</t>
+          <t>ADD_DEF</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Fade the screen tone back to normal over the given duration in seconds.</t>
+          <t>Add DEF</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>在指定秒数内将画面色调恢复为正常。</t>
+          <t>增加防御力</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>CREATE_ACTOR_FROM_BP_PATH</t>
+          <t>ADD_DEF_DESC</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Create Actor From BP Path</t>
+          <t>Add DEF to the player (can be negative to subtract).</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>从蓝图路径创建 Actor</t>
+          <t>为玩家增加（或减少）防御力。</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>CREATE_ACTOR_FROM_BP_PATH_DESC</t>
+          <t>TONE_SHADER_LOAD_FAILED</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Create an actor from a blueprint class path and spawn it on the current map.</t>
+          <t>Failed to load screen tone shader</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>根据蓝图类路径创建 Actor，并生成到当前地图。</t>
+          <t>画面色调着色器加载失败</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>ADD_TIMER</t>
+          <t>CHANGE_SCREEN_TONE</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Add Timer</t>
+          <t>Change Screen Tone</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>添加计时器</t>
+          <t>更改画面色调</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>ADD_TIMER_DESC</t>
+          <t>CHANGE_SCREEN_TONE_DESC</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Wait for a scene timer. If blocking is enabled, player movement and scene hotkeys are disabled until TimeUp.</t>
+          <t>Change the screen tone over time. Red, green, and blue range from -255 to 255; gray ranges from 0 to 255; duration is in seconds.</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>等待场景计时器。如果启用阻塞，TimeUp 前玩家移动和场景快捷键不可用。</t>
+          <t>在指定时间内更改画面色调。红、绿、蓝范围为 -255 到 255；灰度范围为 0 到 255；持续时间单位为秒。</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>RECORD_DESTROYED_ACTOR</t>
+          <t>CLEAR_SCREEN_TONE</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Record Destroyed Actor</t>
+          <t>Clear Screen Tone</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>记录已销毁 Actor</t>
+          <t>清除画面色调</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>RECORD_DESTROYED_ACTOR_DESC</t>
+          <t>CLEAR_SCREEN_TONE_DESC</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Record a destroyed actor for persistence on the current map scene.</t>
+          <t>Fade the screen tone back to normal over the given duration in seconds.</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>在当前地图场景中记录一个已销毁 Actor，用于存档持久化。</t>
+          <t>在指定秒数内将画面色调恢复为正常。</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>SELF_RECORD_DESTROYED</t>
+          <t>CREATE_ACTOR_FROM_BP_PATH</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Self Record Destroyed</t>
+          <t>Create Actor From BP Path</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>自身记录已销毁</t>
+          <t>从蓝图路径创建 Actor</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>SELF_RECORD_DESTROYED_DESC</t>
+          <t>CREATE_ACTOR_FROM_BP_PATH_DESC</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Record the blueprint owner as a destroyed actor for persistence on the current map scene.</t>
+          <t>Create an actor from a blueprint class path and spawn it on the current map.</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>将蓝图所有者记录为已销毁 Actor，用于在当前地图场景中持久化。</t>
+          <t>根据蓝图类路径创建 Actor，并生成到当前地图。</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>RECORD_AND_DESTROY_ACTOR</t>
+          <t>ADD_TIMER</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Record And Destroy Actor</t>
+          <t>Add Timer</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>记录并销毁 Actor</t>
+          <t>添加计时器</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>RECORD_AND_DESTROY_ACTOR_DESC</t>
+          <t>ADD_TIMER_DESC</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Record a destroyed actor for persistence and destroy it on the current map scene.</t>
+          <t>Wait for a scene timer. If blocking is enabled, player movement and scene hotkeys are disabled until TimeUp.</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>在当前地图场景中记录一个已销毁 Actor 并销毁它。</t>
+          <t>等待场景计时器。如果启用阻塞，TimeUp 前玩家移动和场景快捷键不可用。</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>SELF_RECORD_AND_DESTROY</t>
+          <t>RECORD_DESTROYED_ACTOR</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Self Record And Destroy</t>
+          <t>Record Destroyed Actor</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>自身记录并销毁</t>
+          <t>记录已销毁 Actor</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>SELF_RECORD_AND_DESTROY_DESC</t>
+          <t>RECORD_DESTROYED_ACTOR_DESC</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Record the blueprint owner as destroyed for persistence and destroy it on the current map scene.</t>
+          <t>Record a destroyed actor for persistence on the current map scene.</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>将蓝图所有者记录为已销毁并销毁它，用于在当前地图场景中持久化。</t>
+          <t>在当前地图场景中记录一个已销毁 Actor，用于存档持久化。</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>SHOW_REF_MESSAGE</t>
+          <t>SELF_RECORD_DESTROYED</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Show Ref Message</t>
+          <t>Self Record Destroyed</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>显示引用消息</t>
+          <t>自身记录已销毁</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>SHOW_REF_MESSAGE_DESC</t>
+          <t>SELF_RECORD_DESTROYED_DESC</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Show a dialogue message on the current map scene. Uses a direct actor reference for window placement.</t>
+          <t>Record the blueprint owner as a destroyed actor for persistence on the current map scene.</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>在当前地图场景中显示对话，通过直接 Actor 引用进行窗口定位。</t>
+          <t>将蓝图所有者记录为已销毁 Actor，用于在当前地图场景中持久化。</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>SHOW_VOICE_REF_MESSAGE</t>
+          <t>RECORD_AND_DESTROY_ACTOR</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Show Voice Ref Message</t>
+          <t>Record And Destroy Actor</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>显示引用语音消息</t>
+          <t>记录并销毁 Actor</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>SHOW_VOICE_REF_MESSAGE_DESC</t>
+          <t>RECORD_AND_DESTROY_ACTOR_DESC</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Play a spatial voice clip and show a dialogue message on the current map scene. Uses a direct actor reference for voice positioning.</t>
+          <t>Record a destroyed actor for persistence and destroy it on the current map scene.</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>在当前地图场景中播放空间语音并显示对话。通过直接 Actor 引用进行语音定位。</t>
+          <t>在当前地图场景中记录一个已销毁 Actor 并销毁它。</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>GET_SELF_ATTR</t>
+          <t>SELF_RECORD_AND_DESTROY</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Get Self Attr</t>
+          <t>Self Record And Destroy</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>获取自身属性</t>
+          <t>自身记录并销毁</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>GET_SELF_ATTR_DESC</t>
+          <t>SELF_RECORD_AND_DESTROY_DESC</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Read an attribute value from the blueprint owner</t>
+          <t>Record the blueprint owner as destroyed for persistence and destroy it on the current map scene.</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>读取蓝图拥有者的属性值</t>
+          <t>将蓝图所有者记录为已销毁并销毁它，用于在当前地图场景中持久化。</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>SET_SELF_ATTR</t>
+          <t>SHOW_REF_MESSAGE</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Set Self Attr</t>
+          <t>Show Ref Message</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>设置自身属性</t>
+          <t>显示引用消息</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>SET_SELF_ATTR_DESC</t>
+          <t>SHOW_REF_MESSAGE_DESC</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Set an attribute value on the blueprint owner</t>
+          <t>Show a dialogue message on the current map scene. Uses a direct actor reference for window placement.</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>设置蓝图拥有者的属性值</t>
+          <t>在当前地图场景中显示对话，通过直接 Actor 引用进行窗口定位。</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>IF_PLAYER_OVERLAPS</t>
+          <t>SHOW_VOICE_REF_MESSAGE</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>If Player Overlaps</t>
+          <t>Show Voice Ref Message</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>玩家是否重叠</t>
+          <t>显示引用语音消息</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>IF_PLAYER_OVERLAPS_DESC</t>
+          <t>SHOW_VOICE_REF_MESSAGE_DESC</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Check if the player shares the same cell as the blueprint owner</t>
+          <t>Play a spatial voice clip and show a dialogue message on the current map scene. Uses a direct actor reference for voice positioning.</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>判断玩家是否与蓝图拥有者处于同一格子</t>
+          <t>在当前地图场景中播放空间语音并显示对话。通过直接 Actor 引用进行语音定位。</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>IF_GAME_VAR</t>
+          <t>GET_SELF_ATTR</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>If Game Var</t>
+          <t>Get Self Attr</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>判断游戏变量</t>
+          <t>获取自身属性</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>IF_GAME_VAR_DESC</t>
+          <t>GET_SELF_ATTR_DESC</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Compare a game variable with a given value, returning a true/false branch</t>
+          <t>Read an attribute value from the blueprint owner</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>将游戏变量与给定值进行比较，返回真假分支</t>
+          <t>读取蓝图拥有者的属性值</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>GET_ACTOR_BY_TAG</t>
+          <t>SET_SELF_ATTR</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Get Actor By Tag</t>
+          <t>Set Self Attr</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>按标签查找角色</t>
+          <t>设置自身属性</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>GET_ACTOR_BY_TAG_DESC</t>
+          <t>SET_SELF_ATTR_DESC</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Find an actor by tag on the current map</t>
+          <t>Set an attribute value on the blueprint owner</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>在当前地图上按标签查找角色</t>
+          <t>设置蓝图拥有者的属性值</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>GET_ALL_ACTORS</t>
+          <t>IF_PLAYER_OVERLAPS</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Get All Actors</t>
+          <t>If Player Overlaps</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>获取全部角色</t>
+          <t>玩家是否重叠</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
+          <t>IF_PLAYER_OVERLAPS_DESC</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Check if the player shares the same cell as the blueprint owner</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>判断玩家是否与蓝图拥有者处于同一格子</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>IF_GAME_VAR</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>If Game Var</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>判断游戏变量</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>IF_GAME_VAR_DESC</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Compare a game variable with a given value, returning a true/false branch</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>将游戏变量与给定值进行比较，返回真假分支</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>GET_ACTOR_BY_TAG</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Get Actor By Tag</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>按标签查找角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>GET_ACTOR_BY_TAG_DESC</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Find an actor by tag on the current map</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>在当前地图上按标签查找角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>GET_ALL_ACTORS</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Get All Actors</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>获取全部角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
           <t>GET_ALL_ACTORS_DESC</t>
         </is>
       </c>
-      <c r="B453" t="inlineStr">
+      <c r="B459" t="inlineStr">
         <is>
           <t>Get a list of all actors on the current map</t>
         </is>
       </c>
-      <c r="C453" t="inlineStr">
+      <c r="C459" t="inlineStr">
         <is>
           <t>获取当前地图上的所有角色列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>REDUCE_STATE_FROM</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Reduce State From</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>减少战斗者状态层数</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>REDUCE_STATE_FROM_DESC</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Reduce a state stack count on any battler. Remove the state when stacks reach zero.</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>减少任意战斗者身上的状态层数，层数归零时移除状态。</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>REDUCE_PLAYER_STATE</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Reduce Player State</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>减少玩家状态层数</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>REDUCE_PLAYER_STATE_DESC</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Reduce a state stack count on the player. Remove the state when stacks reach zero.</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>减少玩家身上的状态层数，层数归零时移除状态。</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>REMOVE_PLAYER_STATE</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Remove Player State</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>移除玩家状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>REMOVE_PLAYER_STATE_DESC</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Remove a state from the player.</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>移除玩家身上的指定状态。</t>
         </is>
       </c>
     </row>
@@ -8936,7 +9140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="25.75" customWidth="1" min="1" max="1"/>
@@ -9264,6 +9468,142 @@
       <c r="C19" t="inlineStr">
         <is>
           <t>可以破坏面前的一块冰墙。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>POISONED_EASE</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Antidote</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>解毒剂</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>POISONED_EASE_DESC</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>It can reduce the accumulation of poison layers by 5 points.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>可以减少5点中毒层数累积。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>POISONED_RELEASE</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Antitoxic</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>解毒药水</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>POISONED_RELEASE_DESC</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>It can completely cure the poisoning state.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>可以完全解除中毒状态。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>WEAK_EASE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Adrenaline</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>解衰剂</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>WEAK_EASE_DESC</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>It can reduce the accumulation of 5 points of weakened layers.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>可以减少5点衰弱层数累积。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>WEAK_RELEASE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Aqua-vitae</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>解衰药水</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>WEAK_RELEASE_DESC</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>It can completely relieve the weakened state.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>可以完全解除衰弱状态。</t>
         </is>
       </c>
     </row>

--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -1,26 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Items" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemies" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equips" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classes" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="States" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MapNames" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Specials" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="System" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="UI" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Items" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Enemies" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Equips" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Classes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="States" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="MapNames" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Specials" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Player" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_1" localSheetId="0">System!$A$6:$C$249</definedName>
   </definedNames>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -30,17 +26,12 @@
   <fonts count="2">
     <font>
       <name val="等线"/>
-      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="等线"/>
-      <charset val="134"/>
-      <family val="3"/>
       <sz val="9"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -53,32 +44,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -151,7 +134,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -193,74 +176,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -272,23 +195,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
-                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="103000"/>
-                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="109000"/>
-                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -298,23 +221,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
                 <a:satMod val="120000"/>
-                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -322,26 +245,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -376,17 +296,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -401,13 +321,6 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -417,12 +330,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C465"/>
+  <dimension ref="A1:C469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col width="38.75" customWidth="1" min="1" max="1"/>
-    <col width="61.83203125" customWidth="1" min="2" max="2"/>
-    <col width="52.33203125" customWidth="1" min="3" max="3"/>
+    <col width="38.75" customWidth="1" style="1" min="1" max="1"/>
+    <col width="61.83203125" customWidth="1" style="1" min="2" max="2"/>
+    <col width="52.33203125" customWidth="1" style="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4494,12 +4407,12 @@
           <t>IADD</t>
         </is>
       </c>
-      <c r="B240" s="1" t="inlineStr">
+      <c r="B240" t="inlineStr">
         <is>
           <t>+=</t>
         </is>
       </c>
-      <c r="C240" s="1" t="inlineStr">
+      <c r="C240" t="inlineStr">
         <is>
           <t>+=</t>
         </is>
@@ -4528,12 +4441,12 @@
           <t>ISUB</t>
         </is>
       </c>
-      <c r="B242" s="1" t="inlineStr">
+      <c r="B242" t="inlineStr">
         <is>
           <t>-=</t>
         </is>
       </c>
-      <c r="C242" s="1" t="inlineStr">
+      <c r="C242" t="inlineStr">
         <is>
           <t>-=</t>
         </is>
@@ -4562,12 +4475,12 @@
           <t>IMUL</t>
         </is>
       </c>
-      <c r="B244" s="1" t="inlineStr">
+      <c r="B244" t="inlineStr">
         <is>
           <t>*=</t>
         </is>
       </c>
-      <c r="C244" s="1" t="inlineStr">
+      <c r="C244" t="inlineStr">
         <is>
           <t>*=</t>
         </is>
@@ -4596,12 +4509,12 @@
           <t>IDIV</t>
         </is>
       </c>
-      <c r="B246" s="1" t="inlineStr">
+      <c r="B246" t="inlineStr">
         <is>
           <t>/=</t>
         </is>
       </c>
-      <c r="C246" s="1" t="inlineStr">
+      <c r="C246" t="inlineStr">
         <is>
           <t>/=</t>
         </is>
@@ -4664,12 +4577,12 @@
           <t>IPOW</t>
         </is>
       </c>
-      <c r="B250" s="1" t="inlineStr">
+      <c r="B250" t="inlineStr">
         <is>
           <t>**=</t>
         </is>
       </c>
-      <c r="C250" s="1" t="inlineStr">
+      <c r="C250" t="inlineStr">
         <is>
           <t>**=</t>
         </is>
@@ -8330,9 +8243,76 @@
         </is>
       </c>
     </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>OPEN_ATTR_SHOP</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Open Attribute Shop</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>打开数值商店</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>OPEN_ATTR_SHOP_DESC</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Opens an attribute shop using an Actor reference for the shop avatar.</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>使用 Actor 引用作为商店头像，打开数值商店。</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>OPEN_ATTR_SHOP_BY_TAG</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Open Attribute Shop By Tag</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>按标签打开数值商店</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>OPEN_ATTR_SHOP_BY_TAG_DESC</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Finds a map Actor by tag and opens an attribute shop using it as the shop avatar.</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>按标签查找地图 Actor，并将其作为商店头像打开数值商店。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -8397,7 +8377,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -8407,12 +8387,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col width="17.4140625" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="17.25" customWidth="1" min="3" max="3"/>
+    <col width="17.4140625" customWidth="1" style="1" min="1" max="1"/>
+    <col width="18" customWidth="1" style="1" min="2" max="2"/>
+    <col width="17.25" customWidth="1" style="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8979,153 +8959,68 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STAT_HP</t>
+          <t>SHOP_ATTR_LEAVE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HP:</t>
+          <t>Leave</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>生命:</t>
+          <t>离开</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STAT_MAXHP</t>
+          <t>SHOP_ATTR_PRICE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MAXHP:</t>
+          <t>Current Price ({gold})</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>最大生命:</t>
+          <t>当前价格（{gold}）</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STAT_ATK</t>
+          <t>SHOP_NAME</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ATK:</t>
+          <t>The Gold of Avarice</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>攻击:</t>
+          <t>贪婪之神</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STAT_DEF</t>
+          <t>SHOP_DESC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DEF:</t>
+          <t>How insignificant are humankind! \nIf you offer me enough wealth, \nI will grant you a certain amount of power!</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>防御:</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>STAT_EXP</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>EXP:</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>经验:</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>STAT_GOLD</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>GOLD:</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>金币:</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>STAT_DMG</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>DMG:</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>伤害:</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>STAT_HIT</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>HIT:</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>连击:</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>STAT_CRIT</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>CRIT:</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>临界:</t>
+          <t>渺小的人类啊。\n如果你向我献上财富，\n我会给予你一定的力量！</t>
         </is>
       </c>
     </row>
@@ -9143,9 +9038,9 @@
   <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col width="25.75" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="24.83203125" customWidth="1" min="3" max="3"/>
+    <col width="25.75" customWidth="1" style="1" min="1" max="1"/>
+    <col width="29" customWidth="1" style="1" min="2" max="2"/>
+    <col width="24.83203125" customWidth="1" style="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9609,7 +9504,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -9622,9 +9516,9 @@
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col width="29.58203125" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="32.33203125" customWidth="1" min="3" max="3"/>
+    <col width="29.58203125" customWidth="1" style="1" min="1" max="1"/>
+    <col width="29" customWidth="1" style="1" min="2" max="2"/>
+    <col width="32.33203125" customWidth="1" style="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9948,7 +9842,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -10013,7 +9907,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -10129,7 +10023,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -10194,7 +10088,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -10463,6 +10357,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -331,7 +331,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C469"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14" outlineLevelCol="0"/>
   <cols>
     <col width="38.75" customWidth="1" style="1" min="1" max="1"/>
     <col width="61.83203125" customWidth="1" style="1" min="2" max="2"/>
@@ -8387,8 +8387,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
+  <dimension ref="A1:C39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14" outlineLevelCol="0"/>
   <cols>
     <col width="17.4140625" customWidth="1" style="1" min="1" max="1"/>
     <col width="18" customWidth="1" style="1" min="2" max="2"/>
@@ -9021,6 +9021,40 @@
       <c r="C37" t="inlineStr">
         <is>
           <t>渺小的人类啊。\n如果你向我献上财富，\n我会给予你一定的力量！</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>EXP_SHOP_NAME</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>The Gold of War</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>战斗之神</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>EXP_SHOP_DESC</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Offer thy hard-won essence, O hero of mortality! \nAnd I shall transform it into thy strength.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>献上经验吧，英雄的人类！\n我会将经验转换成你的力量！</t>
         </is>
       </c>
     </row>
@@ -9036,7 +9070,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14" outlineLevelCol="0"/>
   <cols>
     <col width="25.75" customWidth="1" style="1" min="1" max="1"/>
     <col width="29" customWidth="1" style="1" min="2" max="2"/>
@@ -9514,7 +9548,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14" outlineLevelCol="0"/>
   <cols>
     <col width="29.58203125" customWidth="1" style="1" min="1" max="1"/>
     <col width="29" customWidth="1" style="1" min="2" max="2"/>

--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -330,8 +330,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C469"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14" outlineLevelCol="0"/>
+  <dimension ref="A1:C471"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="38.75" customWidth="1" style="1" min="1" max="1"/>
     <col width="61.83203125" customWidth="1" style="1" min="2" max="2"/>
@@ -8308,6 +8308,40 @@
       <c r="C469" t="inlineStr">
         <is>
           <t>按标签查找地图 Actor，并将其作为商店头像打开数值商店。</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>SET_MOVE_ENABLED_BY_TAG</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Set Move Enabled By Tag</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>按标签设置移动启用</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>SET_MOVE_ENABLED_BY_TAG_DESC</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Finds a map Actor by tag and enables or disables its movement.</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>按标签查找到地图Actor，并启用或禁用其移动。</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8422,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="17.4140625" customWidth="1" style="1" min="1" max="1"/>
     <col width="18" customWidth="1" style="1" min="2" max="2"/>
@@ -9070,7 +9104,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="25.75" customWidth="1" style="1" min="1" max="1"/>
     <col width="29" customWidth="1" style="1" min="2" max="2"/>
@@ -9548,7 +9582,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="29.58203125" customWidth="1" style="1" min="1" max="1"/>
     <col width="29" customWidth="1" style="1" min="2" max="2"/>

--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -330,7 +330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C471"/>
+  <dimension ref="A1:C477"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="38.75" customWidth="1" style="1" min="1" max="1"/>
@@ -8342,6 +8342,108 @@
       <c r="C471" t="inlineStr">
         <is>
           <t>按标签查找到地图Actor，并启用或禁用其移动。</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>CREATE_DICT</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Create Dict</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>创建字典</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>CREATE_DICT_DESC</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Create a new empty dict.</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>创建一个新的空字典。</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>CREATE_LIST</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Create List</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>创建列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>CREATE_LIST_DESC</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Create a new empty list.</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>创建一个新的空列表。</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>SET_AUTO_PATH_TO_DESTINATION_BY_TAG</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>按标签自动寻路到终点</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Set Auto Path to Destination By Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>SET_AUTO_PATH_TO_DESTINATION_BY_TAG_DESC</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>按标签找到地图 Actor 并自动寻路到指定地图格。Started 出口立即继续；Finished 在移动结束后继续。</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Finds a map Actor by tag and pathfinds it to the target map cell. Started continues immediately; Finished continues after movement ends.</t>
         </is>
       </c>
     </row>
@@ -9289,12 +9391,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>You can teleport to the map you had been to with it(Hotkey: F).</t>
+          <t>You can teleport to the map you had been to with it(Hotkey: G).</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>持有后可以在前往过的传送点（快捷键F）。</t>
+          <t>持有后可以在前往过的传送点（快捷键G）。</t>
         </is>
       </c>
     </row>

--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -330,7 +330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C477"/>
+  <dimension ref="A1:C585"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="38.75" customWidth="1" style="1" min="1" max="1"/>
@@ -8444,6 +8444,1842 @@
       <c r="C477" t="inlineStr">
         <is>
           <t>Finds a map Actor by tag and pathfinds it to the target map cell. Started continues immediately; Finished continues after movement ends.</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>CREATE_ACTOR_FROM_BP_PATH_WITH_DEFAULTS</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Create Actor From BP Path With Defaults</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>按蓝图路径创建 Actor（带默认值）</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>CREATE_ACTOR_FROM_BP_PATH_WITH_DEFAULTS_DESC</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Create an actor from a blueprint class path, apply defaults overrides, and spawn it on the current map.</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>按蓝图类路径创建 Actor，先应用 defaults 字典中的类默认属性覆盖，再生成到当前地图。</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_TAG</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_TAG_DESC</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Identifier used to find this actor on a map.</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>用于在地图上查找该 Actor 的标识。</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_SWITCH_INTERVAL</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Frame Interval</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>帧切换间隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_SWITCH_INTERVAL_DESC</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Sprite animation frame interval in seconds.</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>精灵动画帧切换间隔，单位为秒。</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_ANIMATABLE</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Animatable</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>启用动画</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_ANIMATABLE_DESC</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Whether sprite-sheet animation is enabled.</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>是否启用精灵表动画。</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_MATERIAL</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>材质</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_MATERIAL_DESC</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Surface material settings used by movement, opacity, and lighting.</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>用于移动、透明度和光照的表面材质设置。</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_SHADER_PATH</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Shader Path</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>着色器路径</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_SHADER_PATH_DESC</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Fragment shader path under Assets/Shaders.</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Assets/Shaders 下的片段着色器路径。</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_COLLISION_ENABLED</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Collision Enabled</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>启用碰撞</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_COLLISION_ENABLED_DESC</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Whether this actor blocks movement.</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>该 Actor 是否阻挡移动。</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_TICKABLE</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Tickable</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>启用 Tick</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_TICKABLE_DESC</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Whether tick events are dispatched every frame.</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>是否每帧分发 Tick 事件。</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_SPEED</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Move Speed</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>移动速度</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_SPEED_DESC</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Movement speed in pixels per second.</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>移动速度，单位为像素/秒。</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_AUTO_SOUND</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Auto Sound</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>自动音效</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_AUTO_SOUND_DESC</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Sound asset under Assets/Sounds played automatically as spatial audio.</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Assets/Sounds 下自动播放的音效素材，会作为空间音频播放。</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_AUTO_SOUND_INTERVAL</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Auto Sound Interval</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>自动音效间隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_AUTO_SOUND_INTERVAL_DESC</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Delay from one automatic sound ending to the next playback start.</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>一次自动音效播放结束后，到下一次开始播放前的等待时间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_AUTO_SOUND_PARAMS</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Auto Sound Params</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>自动音效参数</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_AUTO_SOUND_PARAMS_DESC</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Nested spatial sound parameters used by the automatic sound.</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>自动音效使用的嵌套空间音频参数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_TEXTURE_PATH</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Texture Path</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>纹理路径</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_TEXTURE_PATH_DESC</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Character texture asset path under Assets/Characters.</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Assets/Characters 下的角色纹理素材路径。</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_DEFAULT_RECT</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Default Rect</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>默认矩形</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_DEFAULT_RECT_DESC</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Default texture rectangle stored as origin and size.</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>默认贴图矩形，以起点和尺寸保存。</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_DEFAULT_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Default Translation</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>默认偏移</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_DEFAULT_TRANSLATION_DESC</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Default position offset on the actor sprite.</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Actor 精灵的默认位置偏移。</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_DEFAULT_ROTATION</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Default Rotation</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>默认旋转</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_DEFAULT_ROTATION_DESC</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Default rotation in degrees.</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>默认旋转角度，单位为度。</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_DEFAULT_SCALE</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Default Scale</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>默认缩放</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_DEFAULT_SCALE_DESC</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Default x/y scale factors.</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>默认 x/y 缩放比例。</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_DEFAULT_ORIGIN</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Default Origin</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>默认原点</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_DEFAULT_ORIGIN_DESC</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Default origin point for transformations.</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>用于变换的默认原点。</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_LIGHT_COMP</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Light Component</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>光照组件</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_LIGHT_COMP_DESC</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Optional self-light settings attached to this actor.</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>附加到该 Actor 的可选自发光设置。</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_CHILD_ACTOR_COMP</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Child Actor Component</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>子 Actor 组件</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_CHILD_ACTOR_COMP_DESC</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Optional child actor spawned relative to this actor.</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>相对该 Actor 生成的可选子 Actor。</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>AUTO_SOUND_VAR_VOLUME</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>音量</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>AUTO_SOUND_VAR_VOLUME_DESC</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Base sound volume before global sound-volume scaling.</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>应用全局音效音量前的基础音量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>AUTO_SOUND_VAR_MIN_DISTANCE</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Min Distance</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>最小距离</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>AUTO_SOUND_VAR_MIN_DISTANCE_DESC</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Distance where the sound remains at full volume.</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>声音保持最大音量的距离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>AUTO_SOUND_VAR_ATTENUATION</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Attenuation</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>衰减</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>AUTO_SOUND_VAR_ATTENUATION_DESC</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Distance fade factor for the automatic sound.</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>自动音效的距离衰减系数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>CHARACTER_VAR_DIRECTION</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>朝向</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>CHARACTER_VAR_DIRECTION_DESC</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Current facing direction.</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>当前面向的方向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>CHARACTER_VAR_DIRECTION_FIX</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Direction Fix</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>固定朝向</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>CHARACTER_VAR_DIRECTION_FIX_DESC</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>If enabled, movement will not update the facing direction.</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>启用后，移动不会更新朝向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>CHARACTER_VAR_ANIMATE_WITHOUT_MOVING</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Animate While Idle</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>静止时播放动画</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>CHARACTER_VAR_ANIMATE_WITHOUT_MOVING_DESC</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>If enabled, the character animation plays even when idle.</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>启用后，即使角色静止也会播放动画。</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>CHILD_ACTOR_COMP_VAR_CLASS_NAME</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Class Name</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>类名</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>CHILD_ACTOR_COMP_VAR_CLASS_NAME_DESC</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Actor class path or generated blueprint class name to spawn.</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>要生成的 Actor 类路径或生成的蓝图类名。</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>CHILD_ACTOR_COMP_VAR_RELATIVE_POSITION</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Relative Position</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>相对位置</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>CHILD_ACTOR_COMP_VAR_RELATIVE_POSITION_DESC</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Spawn offset relative to the parent actor.</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>相对父 Actor 的生成偏移。</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>LIGHT_COMP_VAR_LIGHT_COLOUR</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Light Colour</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>光照颜色</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>LIGHT_COMP_VAR_LIGHT_COLOUR_DESC</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Self-light colour stored as RGBA.</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>以 RGBA 保存的自发光颜色。</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>LIGHT_COMP_VAR_LIGHT_RADIUS</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Light Radius</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>光照半径</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>LIGHT_COMP_VAR_LIGHT_RADIUS_DESC</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Self-light radius in pixels.</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>自发光半径，单位为像素。</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>INFO_VAR_ID</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>INFO_VAR_ID_DESC</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Unique identifier for this info object.</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>该信息对象的唯一标识。</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>GAME_MAP_VAR_DEFAULT_COVER_ALPHA</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Default Cover Alpha</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>默认遮罩透明度</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>GAME_MAP_VAR_DEFAULT_COVER_ALPHA_DESC</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Default alpha used by cover and occlusion rendering.</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>遮罩和遮挡渲染使用的默认透明度。</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>GAME_MAP_VAR_MAP_VIEW_OFFSET</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Map View Offset</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>地图视图偏移</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>GAME_MAP_VAR_MAP_VIEW_OFFSET_DESC</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Default camera/view offset for map presentation.</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>地图显示使用的默认镜头/视图偏移。</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_LOOP</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Loop</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>循环</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_LOOP_DESC</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Whether to loop playback.</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>是否循环播放。</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_OFFSET</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>播放偏移</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_OFFSET_DESC</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Playback offset in seconds or a Time value.</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>播放偏移，可为秒数或 Time 值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_NEED_EFFECT</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Need Effect</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>需要效果器</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_NEED_EFFECT_DESC</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Whether a sound effect processor is required.</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>是否需要音效处理器。</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_SOUND_EFFECT</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Sound Effect</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>音效处理器</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_SOUND_EFFECT_DESC</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Custom effect processor callback.</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>自定义音效处理回调。</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_PITCH</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Pitch</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>音调</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_PITCH_DESC</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Pitch multiplier, where 1.0 is normal.</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>音调倍率，1.0 为正常。</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_PAN</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Pan</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>声像</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_PAN_DESC</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Stereo pan from -1.0 left to 1.0 right.</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>立体声声像，-1.0 为左，1.0 为右。</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_VOLUME</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>音量</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_VOLUME_DESC</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Volume from 0.0 mute to 100.0 maximum.</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>音量，0.0 为静音，100.0 为最大。</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_SPATIAL</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Spatial</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>空间音频</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_SPATIAL_DESC</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Whether spatialisation is enabled.</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>是否启用空间化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_POSITION</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_POSITION_DESC</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Sound position in 3D space.</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>声音在 3D 空间中的位置。</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_DIRECTION</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>方向</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_DIRECTION_DESC</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Sound direction in 3D space.</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>声音在 3D 空间中的方向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_CONE</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Cone</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>声锥</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_CONE_DESC</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Attenuation cone settings.</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>声源方向衰减锥设置。</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_VELOCITY</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>速度</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_VELOCITY_DESC</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Sound source velocity used for Doppler.</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>用于多普勒效果的声源速度。</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_DOPPLER_FACTOR</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Doppler Factor</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>多普勒系数</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_DOPPLER_FACTOR_DESC</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Doppler effect factor.</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>多普勒效果系数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_DIRECTIONAL_ATTENUATION_FACTOR</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Directional Attenuation</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>方向衰减</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_DIRECTIONAL_ATTENUATION_FACTOR_DESC</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Directional attenuation factor.</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>方向性衰减系数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_RELATIVE_TO_LISTENER</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Relative To Listener</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>相对监听者</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_RELATIVE_TO_LISTENER_DESC</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Whether the position is relative to the listener.</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>位置是否相对监听者。</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_MIN_DISTANCE</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Min Distance</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>最小距离</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_MIN_DISTANCE_DESC</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Minimum attenuation distance.</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>开始衰减前的最小距离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_MAX_DISTANCE</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Max Distance</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>最大距离</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_MAX_DISTANCE_DESC</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Maximum attenuation distance.</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>最大衰减距离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_MIN_GAIN</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Min Gain</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>最小增益</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_MIN_GAIN_DESC</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Minimum gain after attenuation.</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>衰减后的最小增益。</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_MAX_GAIN</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Max Gain</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>最大增益</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_MAX_GAIN_DESC</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Maximum gain after attenuation.</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>衰减后的最大增益。</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_ATTENUATION</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Attenuation</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>衰减</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>SOUND_FILTER_VAR_ATTENUATION_DESC</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Distance attenuation factor.</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>距离衰减系数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>MUSIC_FILTER_VAR_LOOP_POINT</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Loop Point</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>循环点</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>MUSIC_FILTER_VAR_LOOP_POINT_DESC</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Optional loop time range for music.</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>音乐可选的循环时间范围。</t>
         </is>
       </c>
     </row>

--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C585"/>
+  <dimension ref="A1:C589"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="38.75" customWidth="1" min="1" max="1"/>
@@ -10303,6 +10303,74 @@
       <c r="C585" t="inlineStr">
         <is>
           <t>音乐可选的循环时间范围。</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>FOR_LOOP</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>For Loop</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>For 循环</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>FOR_LOOP_DESC</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Loop from firstIndex to lastIndex inclusively by step. LoopBody continues for each iteration, and Completed continues after the loop. Latent nodes are not currently supported inside the loop body.</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>从 firstIndex 到 lastIndex 按 step 闭区间循环。LoopBody 每轮继续，Completed 在循环结束后继续。循环体暂不支持 latent 节点。</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>FOR_EACH</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>For Each</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>For Each</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>FOR_EACH_DESC</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Iterate over a list. LoopBody continues once for each element and outputs element and index; Completed continues after iteration. Latent nodes are not currently supported inside the loop body.</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>遍历列表。LoopBody 每个元素继续一次，并输出 element 与 index；Completed 在遍历结束后继续。循环体暂不支持 latent 节点。</t>
         </is>
       </c>
     </row>

--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -10385,7 +10385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <sheetData>
     <row r="1">
@@ -10640,6 +10640,108 @@
       <c r="C15" t="inlineStr">
         <is>
           <t>持有者的攻击力视为不低于对方攻击力。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S_DOMAIN</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>领域</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S_DOMAIN_DESC</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>After each player move, the holder deals one-round damage while the player is within its Manhattan range.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>玩家每次移动后，若处于持有者的曼哈顿领域范围内，持有者造成一次单回合伤害。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>S_FLANK</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Flank</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>夹击</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>S_FLANK_DESC</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>After each player move, two opposite adjacent holders both deal one-round damage.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>玩家每次移动后，若被两个正对相邻的持有者夹在中间，二者各造成一次单回合伤害。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>S_BLOCKADE</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Blockade</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>阻击</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>S_BLOCKADE_DESC</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>After each player move, an adjacent holder deals one-round damage, retreats one cell away, and records its map position.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>玩家每次移动后，相邻的持有者造成一次单回合伤害，向远离玩家方向后退一格，并记录地图坐标。</t>
         </is>
       </c>
     </row>
@@ -10719,7 +10821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="17.4140625" customWidth="1" min="1" max="1"/>
@@ -11002,389 +11104,372 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MENU_LOAD</t>
+          <t>CONFIG_MIND_RESTART</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Load File</t>
+          <t>The configuration will take effect after a restart.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>读档</t>
+          <t>配置将在重启后生效</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CONFIG_MIND_RESTART</t>
+          <t>SHOP_BUY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The configuration will take effect after a restart.</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>配置将在重启后生效</t>
+          <t>购买</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SHOP_BUY</t>
+          <t>SHOP_SELL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>购买</t>
+          <t>出售</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SHOP_SELL</t>
+          <t>POINT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>P {index}</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>出售</t>
+          <t>点位 {index}</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>POINT</t>
+          <t>language</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>P {index}</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>点位 {index}</t>
+          <t>语言</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>scale</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>语言</t>
+          <t>缩放</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>scale</t>
+          <t>framerate</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Frame Rate</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>缩放</t>
+          <t>帧率</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>framerate</t>
+          <t>verticalsync</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Frame Rate</t>
+          <t>Vertical Sync</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>帧率</t>
+          <t>垂直同步</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>verticalsync</t>
+          <t>musicon</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vertical Sync</t>
+          <t>Music</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>垂直同步</t>
+          <t>音乐</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>musicon</t>
+          <t>musicvolume</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Music</t>
+          <t>Music Volume</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>音乐</t>
+          <t>音乐音量</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>musicvolume</t>
+          <t>soundon</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Music Volume</t>
+          <t>Sound</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>音乐音量</t>
+          <t>音效</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>soundon</t>
+          <t>soundvolume</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Sound Volume</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>音效</t>
+          <t>音效音量</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>soundvolume</t>
+          <t>voiceon</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sound Volume</t>
+          <t>Voice</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>音效音量</t>
+          <t>语音</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>voiceon</t>
+          <t>voicevolume</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Voice</t>
+          <t>Voice Volume</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>语音</t>
+          <t>语音音量</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>voicevolume</t>
+          <t>en_GB</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Voice Volume</t>
+          <t>English</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>语音音量</t>
+          <t>英语</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>en_GB</t>
+          <t>zh_CN</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Simplified Chinese</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>英语</t>
+          <t>简体中文</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>zh_CN</t>
+          <t>SHOP_ATTR_LEAVE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Simplified Chinese</t>
+          <t>Leave</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>简体中文</t>
+          <t>离开</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SHOP_ATTR_LEAVE</t>
+          <t>SHOP_ATTR_PRICE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Leave</t>
+          <t>Current Price ({gold})</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>离开</t>
+          <t>当前价格（{gold}）</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SHOP_ATTR_PRICE</t>
+          <t>SHOP_NAME</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Current Price ({gold})</t>
+          <t>The Gold of Avarice</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>当前价格（{gold}）</t>
+          <t>贪婪之神</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SHOP_NAME</t>
+          <t>SHOP_DESC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The Gold of Avarice</t>
+          <t>How insignificant are humankind! \nIf you offer me enough wealth, \nI will grant you a certain amount of power!</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>贪婪之神</t>
+          <t>渺小的人类啊。\n如果你向我献上财富，\n我会给予你一定的力量！</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SHOP_DESC</t>
+          <t>EXP_SHOP_NAME</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>How insignificant are humankind! \nIf you offer me enough wealth, \nI will grant you a certain amount of power!</t>
+          <t>The Gold of War</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>渺小的人类啊。\n如果你向我献上财富，\n我会给予你一定的力量！</t>
+          <t>战斗之神</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>EXP_SHOP_NAME</t>
+          <t>EXP_SHOP_DESC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Gold of War</t>
+          <t>Offer thy hard-won essence, O hero of mortality! \nAnd I shall transform it into thy strength.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
-        <is>
-          <t>战斗之神</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>EXP_SHOP_DESC</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Offer thy hard-won essence, O hero of mortality! \nAnd I shall transform it into thy strength.</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
         <is>
           <t>献上经验吧，英雄的人类！\n我会将经验转换成你的力量！</t>
         </is>

--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-31630" yWindow="2260" windowWidth="28800" windowHeight="15370" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="System" sheetId="1" state="visible" r:id="rId1"/>
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C589"/>
+  <dimension ref="A1:C591"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="38.75" customWidth="1" min="1" max="1"/>
@@ -10371,6 +10371,40 @@
       <c r="C589" t="inlineStr">
         <is>
           <t>遍历列表。LoopBody 每个元素继续一次，并输出 element 与 index；Completed 在遍历结束后继续。循环体暂不支持 latent 节点。</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_HUE</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Hue</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>色相</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>ACTOR_VAR_HUE_DESC</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Hue rotation in degrees applied to this actor sprite. 0 keeps the original colour; values wrap every 360 degrees.</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>应用到该 Actor 精灵的色相旋转角度。0 保持原色；数值每 360 度循环。</t>
         </is>
       </c>
     </row>
@@ -12165,7 +12199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="29.58203125" customWidth="1" min="1" max="1"/>
@@ -12391,6 +12425,108 @@
       <c r="C13" t="inlineStr">
         <is>
           <t>这是一位骑士。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>WIZARD</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Wizard</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>巫师</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>WIZARD_DESC</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>This is a wizard.</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>这是一个巫师。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>WHITE_KING</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>White King</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>魔法警卫</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>WHITE_KING_DESC</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>This is a white king.</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>这是一个魔法警卫。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BIG_WIZARD</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Big Wizard</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>大法师</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>BIG_WIZARD_DESC</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>This is a big wizard.</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>这是一个大法师。</t>
         </is>
       </c>
     </row>

--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Other\Ludork\Sample\Data\Locale\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB00EE6F-51BC-4338-829C-0EF8C53AB637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB3AF306-5407-46E7-88F6-865206C82966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5150" yWindow="3810" windowWidth="25260" windowHeight="14150" firstSheet="5" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5150" yWindow="3810" windowWidth="25260" windowHeight="14150" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="2" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="456">
   <si>
     <t>ID</t>
   </si>
@@ -1378,6 +1378,90 @@
   </si>
   <si>
     <t>本条消息会携带水下特效的语音。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CENTREFLY</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>UPFLY</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DOWNFLY</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>FLY_FAIL</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Failed to transport to target position. </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>传送失败</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>中心对称飞行器</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>上楼器</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>下楼器</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CenterSymmetricTeleport</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>UpstairsTransportation</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DownstairsTransportation</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CENTREFLY_DESC</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>UPFLY_DESC</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DOWNFLY_DESC</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以传送到中心对称位置。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>It can teleport you to a centrally symmetric position.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以传送到下一楼层。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以传送到上一楼层。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>You can teleport to the upper floor with it.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>You can teleport to the lower floor with it.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1660,7 +1744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.4140625" customWidth="1"/>
@@ -2095,6 +2179,17 @@
       </c>
       <c r="C39" s="3" t="s">
         <v>108</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>440</v>
       </c>
     </row>
   </sheetData>
@@ -2793,7 +2888,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.75" customWidth="1"/>
@@ -3096,6 +3191,72 @@
       </c>
       <c r="C27" t="s">
         <v>217</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>452</v>
       </c>
     </row>
   </sheetData>

--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Other\Ludork\Sample\Data\Locale\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB3AF306-5407-46E7-88F6-865206C82966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B02A8BF-1E70-4343-B9E8-65FC89320410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5150" yWindow="3810" windowWidth="25260" windowHeight="14150" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="940" yWindow="890" windowWidth="38420" windowHeight="19620" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="2" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="468">
   <si>
     <t>ID</t>
   </si>
@@ -1060,12 +1060,6 @@
     <t>S_HARD_DESC</t>
   </si>
   <si>
-    <t>The holder's DEF is treated as at least the opponent's ATK minus 1 during damage calculation.</t>
-  </si>
-  <si>
-    <t>计算伤害时，持有者的防御力视为不低于对方攻击力-1。</t>
-  </si>
-  <si>
     <t>S_MAGIC</t>
   </si>
   <si>
@@ -1078,12 +1072,6 @@
     <t>S_MAGIC_DESC</t>
   </si>
   <si>
-    <t>During battle, the holder treats the opponent's DEF as 0 when calculating damage.</t>
-  </si>
-  <si>
-    <t>战斗中计算伤害时，持有者将对方防御力视为0。</t>
-  </si>
-  <si>
     <t>S_MULTIHIT</t>
   </si>
   <si>
@@ -1096,12 +1084,6 @@
     <t>S_MULTIHIT_DESC</t>
   </si>
   <si>
-    <t>During battle, each round's base damage is multiplied by the holder's hit count.</t>
-  </si>
-  <si>
-    <t>战斗中，持有者每回合基础伤害会按连击数倍计算。</t>
-  </si>
-  <si>
     <t>S_COMPETE</t>
   </si>
   <si>
@@ -1114,12 +1096,6 @@
     <t>S_COMPETE_DESC</t>
   </si>
   <si>
-    <t>The holder's ATK is treated as at least the opponent's ATK.</t>
-  </si>
-  <si>
-    <t>持有者的攻击力视为不低于对方攻击力。</t>
-  </si>
-  <si>
     <t>S_DOMAIN</t>
   </si>
   <si>
@@ -1132,12 +1108,6 @@
     <t>S_DOMAIN_DESC</t>
   </si>
   <si>
-    <t>After each player move, the holder deals one-round damage while the player is within its Manhattan range.</t>
-  </si>
-  <si>
-    <t>玩家每次移动后，若处于持有者的曼哈顿领域范围内，持有者造成一次单回合伤害。</t>
-  </si>
-  <si>
     <t>S_FLANK</t>
   </si>
   <si>
@@ -1150,12 +1120,6 @@
     <t>S_FLANK_DESC</t>
   </si>
   <si>
-    <t>After each player move, two opposite adjacent holders both deal one-round damage.</t>
-  </si>
-  <si>
-    <t>玩家每次移动后，若被两个正对相邻的持有者夹在中间，二者各造成一次单回合伤害。</t>
-  </si>
-  <si>
     <t>S_BLOCKADE</t>
   </si>
   <si>
@@ -1168,12 +1132,6 @@
     <t>S_BLOCKADE_DESC</t>
   </si>
   <si>
-    <t>After each player move, an adjacent holder deals one-round damage, retreats one cell away, and records its map position.</t>
-  </si>
-  <si>
-    <t>玩家每次移动后，相邻的持有者造成一次单回合伤害，向远离玩家方向后退一格，并记录地图坐标。</t>
-  </si>
-  <si>
     <t>BRAVOR</t>
   </si>
   <si>
@@ -1462,6 +1420,96 @@
   </si>
   <si>
     <t>You can teleport to the lower floor with it.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>S_REBORN</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>重生</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reborn</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>S_REBORN_DESC</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>The enemy's DEF is treated as at least the opponent's ATK minus 1 during damage calculation.</t>
+  </si>
+  <si>
+    <t>During battle, the enemy treats the opponent's DEF as 0 when calculating damage.</t>
+  </si>
+  <si>
+    <t>During battle, each round's base damage is multiplied by the enemy's hit count.</t>
+  </si>
+  <si>
+    <t>The enemy's ATK is treated as at least the opponent's ATK.</t>
+  </si>
+  <si>
+    <t>After each player move, the enemy deals one-round damage while the player is within its Manhattan range.</t>
+  </si>
+  <si>
+    <t>After each player move, two opposite adjacent enemys both deal one-round damage.</t>
+  </si>
+  <si>
+    <t>After each player move, an adjacent enemy deals one-round damage, retreats one cell away, and records its map position.</t>
+  </si>
+  <si>
+    <t>计算伤害时，敌人的防御力视为不低于对方攻击力-1。</t>
+  </si>
+  <si>
+    <t>战斗中计算伤害时，敌人将对方防御力视为0。</t>
+  </si>
+  <si>
+    <t>战斗中，敌人每回合基础伤害会按连击数倍计算。</t>
+  </si>
+  <si>
+    <t>敌人的攻击力视为不低于对方攻击力。</t>
+  </si>
+  <si>
+    <t>玩家每次移动后，若处于敌人的曼哈顿领域范围内，敌人造成一次单回合伤害。</t>
+  </si>
+  <si>
+    <t>玩家每次移动后，若被两个正对相邻的敌人夹在中间，二者各造成一次单回合伤害。</t>
+  </si>
+  <si>
+    <t>玩家每次移动后，相邻的敌人造成一次单回合伤害，向远离玩家方向后退一格，并记录地图坐标。</t>
+  </si>
+  <si>
+    <t>敌人在战败后会变身为另一敌人。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>The enemy will turn to another kind after this battle.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>GHOST_SOLDIER</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>GHOST_SOLDIER_DESC</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ghost Soldier</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>This is a ghost soldier.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这是一个鬼战士。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>鬼战士</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1842,7 +1890,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
@@ -1941,13 +1989,13 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="B18" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="C18" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -2183,13 +2231,13 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>438</v>
+        <v>424</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>439</v>
+        <v>425</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>440</v>
+        <v>426</v>
       </c>
     </row>
   </sheetData>
@@ -2200,7 +2248,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="43.1640625" customWidth="1"/>
@@ -2299,143 +2347,165 @@
       <c r="A9" t="s">
         <v>341</v>
       </c>
-      <c r="B9" t="s">
-        <v>342</v>
+      <c r="B9" s="4" t="s">
+        <v>446</v>
       </c>
       <c r="C9" t="s">
-        <v>343</v>
+        <v>453</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>342</v>
+      </c>
+      <c r="B10" t="s">
+        <v>343</v>
+      </c>
+      <c r="C10" t="s">
         <v>344</v>
-      </c>
-      <c r="B10" t="s">
-        <v>345</v>
-      </c>
-      <c r="C10" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B11" t="s">
-        <v>348</v>
-      </c>
-      <c r="C11" t="s">
-        <v>349</v>
+        <v>447</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B12" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C12" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B13" t="s">
-        <v>354</v>
+        <v>448</v>
       </c>
       <c r="C13" t="s">
-        <v>355</v>
+        <v>455</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="B14" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="C14" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="B15" t="s">
-        <v>360</v>
+        <v>449</v>
       </c>
       <c r="C15" t="s">
-        <v>361</v>
+        <v>456</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="B16" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="C16" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B17" t="s">
-        <v>366</v>
+        <v>450</v>
       </c>
       <c r="C17" t="s">
-        <v>367</v>
+        <v>457</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="B18" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="C18" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="B19" t="s">
-        <v>372</v>
+        <v>451</v>
       </c>
       <c r="C19" t="s">
-        <v>373</v>
+        <v>458</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="B20" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="C20" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="B21" t="s">
-        <v>378</v>
+        <v>452</v>
       </c>
       <c r="C21" t="s">
-        <v>379</v>
+        <v>459</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -2466,24 +2536,24 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="B2" t="s">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="C2" t="s">
-        <v>382</v>
+        <v>368</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="B3" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="C3" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -2515,35 +2585,35 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>390</v>
+        <v>376</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>391</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>420</v>
+        <v>406</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>400</v>
+        <v>386</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>421</v>
+        <v>407</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>423</v>
+        <v>409</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>422</v>
+        <v>408</v>
       </c>
     </row>
   </sheetData>
@@ -2574,134 +2644,134 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>394</v>
+        <v>380</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>395</v>
+        <v>381</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>396</v>
+        <v>382</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>397</v>
+        <v>383</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>398</v>
+        <v>384</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>401</v>
+        <v>387</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>407</v>
+        <v>393</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>414</v>
+        <v>400</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>402</v>
+        <v>388</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>408</v>
+        <v>394</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>415</v>
+        <v>401</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>409</v>
+        <v>395</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>416</v>
+        <v>402</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>410</v>
+        <v>396</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>417</v>
+        <v>403</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>411</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>418</v>
+        <v>404</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>406</v>
+        <v>392</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>412</v>
+        <v>398</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>419</v>
+        <v>405</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>430</v>
+        <v>416</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>431</v>
+        <v>417</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>432</v>
+        <v>418</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>434</v>
+        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -3195,68 +3265,68 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>435</v>
+        <v>421</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>444</v>
+        <v>430</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>441</v>
+        <v>427</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>451</v>
+        <v>437</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>450</v>
+        <v>436</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>445</v>
+        <v>431</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>442</v>
+        <v>428</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>454</v>
+        <v>440</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>453</v>
+        <v>439</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>437</v>
+        <v>423</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>446</v>
+        <v>432</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>443</v>
+        <v>429</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>449</v>
+        <v>435</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>452</v>
+        <v>438</v>
       </c>
     </row>
   </sheetData>
@@ -3267,7 +3337,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.58203125" customWidth="1"/>
@@ -3504,6 +3574,28 @@
       </c>
       <c r="C21" s="3" t="s">
         <v>277</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>466</v>
       </c>
     </row>
   </sheetData>

--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Other\Ludork\Sample\Data\Locale\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fengmingliu/Dev/Ludork/Sample/Data/Locale/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B02A8BF-1E70-4343-B9E8-65FC89320410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69E8AA3F-1D5D-D64C-BF06-843CDA960A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="940" yWindow="890" windowWidth="38420" windowHeight="19620" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="2" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="471">
   <si>
     <t>ID</t>
   </si>
@@ -1511,13 +1511,22 @@
   <si>
     <t>鬼战士</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>antialiasinglevel</t>
+  </si>
+  <si>
+    <t>Antialiasing Level</t>
+  </si>
+  <si>
+    <t>抗锯齿等级</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1527,12 +1536,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="4"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="4"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1582,7 +1593,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1792,15 +1803,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C40"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C41"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.4140625" customWidth="1"/>
+    <col min="1" max="1" width="17.33203125" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="17.25" customWidth="1"/>
+    <col min="3" max="3" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1811,7 +1822,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1822,7 +1833,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1833,7 +1844,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1844,7 +1855,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1855,7 +1866,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -1866,7 +1877,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1877,7 +1888,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -1888,7 +1899,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" s="4" t="s">
         <v>375</v>
       </c>
@@ -1899,7 +1910,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -1910,7 +1921,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -1921,7 +1932,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -1932,7 +1943,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -1943,7 +1954,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -1954,7 +1965,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -1965,7 +1976,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -1976,7 +1987,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>43</v>
       </c>
@@ -1987,7 +1998,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>372</v>
       </c>
@@ -1998,7 +2009,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>46</v>
       </c>
@@ -2009,7 +2020,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>49</v>
       </c>
@@ -2020,7 +2031,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>52</v>
       </c>
@@ -2031,7 +2042,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -2042,7 +2053,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -2053,7 +2064,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>61</v>
       </c>
@@ -2064,179 +2075,190 @@
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+    <row r="25" spans="1:3">
+      <c r="A25" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B26" t="s">
         <v>65</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C26" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
         <v>67</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B27" t="s">
         <v>68</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C27" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
         <v>70</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B28" t="s">
         <v>71</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C28" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
         <v>73</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B29" t="s">
         <v>74</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C29" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
         <v>76</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B30" t="s">
         <v>77</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C30" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
         <v>79</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B31" t="s">
         <v>80</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C31" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
         <v>82</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B32" t="s">
         <v>83</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C32" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
         <v>85</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B33" t="s">
         <v>86</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C33" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
         <v>88</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B34" t="s">
         <v>89</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C34" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
         <v>91</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B35" t="s">
         <v>92</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C35" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
         <v>94</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B36" t="s">
         <v>95</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C36" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
         <v>97</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B37" t="s">
         <v>98</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C37" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
         <v>100</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B38" t="s">
         <v>101</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C38" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
         <v>103</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B39" t="s">
         <v>104</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C39" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="3" t="s">
+    <row r="40" spans="1:3">
+      <c r="A40" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B40" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="4" t="s">
+    <row r="41" spans="1:3">
+      <c r="A41" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B41" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C41" s="4" t="s">
         <v>426</v>
       </c>
     </row>
@@ -2249,13 +2271,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="43.1640625" customWidth="1"/>
-    <col min="3" max="3" width="43.58203125" customWidth="1"/>
+    <col min="3" max="3" width="43.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2266,7 +2288,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>323</v>
       </c>
@@ -2277,7 +2299,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>325</v>
       </c>
@@ -2288,7 +2310,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>328</v>
       </c>
@@ -2299,7 +2321,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>330</v>
       </c>
@@ -2310,7 +2332,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>333</v>
       </c>
@@ -2321,7 +2343,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>335</v>
       </c>
@@ -2332,7 +2354,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>338</v>
       </c>
@@ -2343,7 +2365,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>341</v>
       </c>
@@ -2354,7 +2376,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>342</v>
       </c>
@@ -2365,7 +2387,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>345</v>
       </c>
@@ -2376,7 +2398,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>346</v>
       </c>
@@ -2387,7 +2409,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>349</v>
       </c>
@@ -2398,7 +2420,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>350</v>
       </c>
@@ -2409,7 +2431,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>353</v>
       </c>
@@ -2420,7 +2442,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>354</v>
       </c>
@@ -2431,7 +2453,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>357</v>
       </c>
@@ -2442,7 +2464,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>358</v>
       </c>
@@ -2453,7 +2475,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>361</v>
       </c>
@@ -2464,7 +2486,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>362</v>
       </c>
@@ -2475,7 +2497,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>365</v>
       </c>
@@ -2486,7 +2508,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3">
       <c r="A22" s="4" t="s">
         <v>442</v>
       </c>
@@ -2497,7 +2519,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3">
       <c r="A23" s="4" t="s">
         <v>445</v>
       </c>
@@ -2517,13 +2539,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="25.75" customWidth="1"/>
+    <col min="3" max="3" width="25.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2534,7 +2556,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>366</v>
       </c>
@@ -2545,7 +2567,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>369</v>
       </c>
@@ -2565,14 +2587,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FA4E9DF-B4C0-496C-83E9-11467FE432C9}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.4140625" customWidth="1"/>
+    <col min="1" max="1" width="17.33203125" customWidth="1"/>
     <col min="2" max="2" width="17.6640625" customWidth="1"/>
-    <col min="3" max="3" width="17.25" customWidth="1"/>
+    <col min="3" max="3" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2583,7 +2605,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" s="4" t="s">
         <v>378</v>
       </c>
@@ -2594,7 +2616,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" s="4" t="s">
         <v>406</v>
       </c>
@@ -2605,7 +2627,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
         <v>407</v>
       </c>
@@ -2625,13 +2647,12 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18A9F10C-3E5E-41A2-9938-5DC7A61B6D47}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="34.58203125" customWidth="1"/>
-    <col min="3" max="3" width="34.5" customWidth="1"/>
+    <col min="2" max="3" width="34.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2642,7 +2663,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" s="4" t="s">
         <v>379</v>
       </c>
@@ -2653,7 +2674,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" s="4" t="s">
         <v>382</v>
       </c>
@@ -2664,7 +2685,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
         <v>399</v>
       </c>
@@ -2675,7 +2696,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
         <v>400</v>
       </c>
@@ -2686,7 +2707,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
         <v>401</v>
       </c>
@@ -2697,7 +2718,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
         <v>402</v>
       </c>
@@ -2708,7 +2729,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
         <v>403</v>
       </c>
@@ -2719,7 +2740,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" s="4" t="s">
         <v>404</v>
       </c>
@@ -2730,7 +2751,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" s="4" t="s">
         <v>405</v>
       </c>
@@ -2741,7 +2762,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" s="4" t="s">
         <v>412</v>
       </c>
@@ -2752,7 +2773,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
         <v>413</v>
       </c>
@@ -2763,7 +2784,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
         <v>414</v>
       </c>
@@ -2783,9 +2804,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2796,7 +2817,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2807,7 +2828,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2827,9 +2848,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2840,7 +2861,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
         <v>113</v>
       </c>
@@ -2851,7 +2872,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
         <v>116</v>
       </c>
@@ -2862,7 +2883,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
         <v>119</v>
       </c>
@@ -2873,7 +2894,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
         <v>121</v>
       </c>
@@ -2884,7 +2905,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
         <v>123</v>
       </c>
@@ -2895,7 +2916,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
         <v>125</v>
       </c>
@@ -2906,7 +2927,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
         <v>128</v>
       </c>
@@ -2917,7 +2938,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
         <v>131</v>
       </c>
@@ -2928,7 +2949,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
         <v>134</v>
       </c>
@@ -2939,7 +2960,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
         <v>137</v>
       </c>
@@ -2959,14 +2980,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C33"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="25.75" customWidth="1"/>
+    <col min="1" max="1" width="25.6640625" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="24.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2977,7 +2998,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>140</v>
       </c>
@@ -2988,7 +3009,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>143</v>
       </c>
@@ -2999,7 +3020,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>146</v>
       </c>
@@ -3010,7 +3031,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>149</v>
       </c>
@@ -3021,7 +3042,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>152</v>
       </c>
@@ -3032,7 +3053,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>155</v>
       </c>
@@ -3043,7 +3064,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>158</v>
       </c>
@@ -3054,7 +3075,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>161</v>
       </c>
@@ -3065,7 +3086,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>164</v>
       </c>
@@ -3076,7 +3097,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>167</v>
       </c>
@@ -3087,7 +3108,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>170</v>
       </c>
@@ -3098,7 +3119,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>173</v>
       </c>
@@ -3109,7 +3130,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>176</v>
       </c>
@@ -3120,7 +3141,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>179</v>
       </c>
@@ -3131,7 +3152,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>182</v>
       </c>
@@ -3142,7 +3163,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>185</v>
       </c>
@@ -3153,7 +3174,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>188</v>
       </c>
@@ -3164,7 +3185,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>191</v>
       </c>
@@ -3175,7 +3196,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>194</v>
       </c>
@@ -3186,7 +3207,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>197</v>
       </c>
@@ -3197,7 +3218,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>200</v>
       </c>
@@ -3208,7 +3229,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>203</v>
       </c>
@@ -3219,7 +3240,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>206</v>
       </c>
@@ -3230,7 +3251,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>209</v>
       </c>
@@ -3241,7 +3262,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>212</v>
       </c>
@@ -3252,7 +3273,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>215</v>
       </c>
@@ -3263,7 +3284,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3">
       <c r="A28" s="4" t="s">
         <v>421</v>
       </c>
@@ -3274,7 +3295,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3">
       <c r="A29" s="4" t="s">
         <v>433</v>
       </c>
@@ -3285,7 +3306,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3">
       <c r="A30" s="4" t="s">
         <v>422</v>
       </c>
@@ -3296,7 +3317,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3">
       <c r="A31" s="4" t="s">
         <v>434</v>
       </c>
@@ -3307,7 +3328,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
         <v>423</v>
       </c>
@@ -3318,7 +3339,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3">
       <c r="A33" s="4" t="s">
         <v>435</v>
       </c>
@@ -3338,14 +3359,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="29.58203125" customWidth="1"/>
+    <col min="1" max="1" width="29.5" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="32.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3356,7 +3377,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>218</v>
       </c>
@@ -3367,7 +3388,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>221</v>
       </c>
@@ -3378,7 +3399,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>224</v>
       </c>
@@ -3389,7 +3410,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>227</v>
       </c>
@@ -3400,7 +3421,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>230</v>
       </c>
@@ -3411,7 +3432,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>233</v>
       </c>
@@ -3422,7 +3443,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>236</v>
       </c>
@@ -3433,7 +3454,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>239</v>
       </c>
@@ -3444,7 +3465,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>242</v>
       </c>
@@ -3455,7 +3476,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>245</v>
       </c>
@@ -3466,7 +3487,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>248</v>
       </c>
@@ -3477,7 +3498,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>251</v>
       </c>
@@ -3488,7 +3509,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
         <v>254</v>
       </c>
@@ -3499,7 +3520,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
         <v>257</v>
       </c>
@@ -3510,7 +3531,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
         <v>260</v>
       </c>
@@ -3521,7 +3542,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
         <v>263</v>
       </c>
@@ -3532,7 +3553,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>266</v>
       </c>
@@ -3543,7 +3564,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
         <v>269</v>
       </c>
@@ -3554,7 +3575,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>272</v>
       </c>
@@ -3565,7 +3586,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3">
       <c r="A21" s="3" t="s">
         <v>275</v>
       </c>
@@ -3576,7 +3597,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3">
       <c r="A22" s="4" t="s">
         <v>462</v>
       </c>
@@ -3587,7 +3608,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3">
       <c r="A23" s="4" t="s">
         <v>463</v>
       </c>
@@ -3607,13 +3628,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="52.9140625" customWidth="1"/>
+    <col min="2" max="2" width="52.83203125" customWidth="1"/>
     <col min="3" max="3" width="42.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3624,7 +3645,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>278</v>
       </c>
@@ -3635,7 +3656,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>281</v>
       </c>
@@ -3646,7 +3667,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>284</v>
       </c>
@@ -3657,7 +3678,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>287</v>
       </c>
@@ -3677,13 +3698,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="40" customWidth="1"/>
     <col min="3" max="3" width="35.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3694,7 +3715,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>290</v>
       </c>
@@ -3705,7 +3726,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>293</v>
       </c>
@@ -3725,13 +3746,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="43.25" customWidth="1"/>
-    <col min="3" max="3" width="44.08203125" customWidth="1"/>
+    <col min="2" max="2" width="43.1640625" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3742,7 +3763,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>296</v>
       </c>
@@ -3753,7 +3774,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>299</v>
       </c>
@@ -3764,7 +3785,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>302</v>
       </c>
@@ -3775,7 +3796,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>305</v>
       </c>
@@ -3786,7 +3807,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>308</v>
       </c>
@@ -3806,14 +3827,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
-    <col min="2" max="2" width="16.08203125" customWidth="1"/>
-    <col min="3" max="3" width="17.25" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3824,7 +3845,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>311</v>
       </c>
@@ -3835,7 +3856,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>314</v>
       </c>
@@ -3846,7 +3867,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>317</v>
       </c>
@@ -3857,7 +3878,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>320</v>
       </c>

--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI" sheetId="2" r:id="Rf5f2439c2c6a494b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Languages" sheetId="12" r:id="R31d6cf3603b1447d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Attrs" sheetId="3" r:id="Rc9cb65dc915d48bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Items" sheetId="4" r:id="Rfee6b8b610aa417b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemies" sheetId="5" r:id="R04f2e8968b2a4f00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equips" sheetId="6" r:id="R0b82220b445c4e4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classes" sheetId="7" r:id="R4c750b0eeefe4a74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="States" sheetId="8" r:id="Re2c048a7cba74a2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MapNames" sheetId="9" r:id="R30f8ba25fd8546fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Specials" sheetId="10" r:id="Refb195a68d734154"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player" sheetId="11" r:id="R404a114adbc64d77"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DialogueNames" sheetId="13" r:id="R8ab02f9dde6d4ad9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DialogueContents" sheetId="14" r:id="R87fe3329e03845ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI" sheetId="2" r:id="R7c6102095ac046a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Languages" sheetId="12" r:id="R6fd3ba9604ce46dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Attrs" sheetId="3" r:id="Rcb16155260ca416a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Items" sheetId="4" r:id="R08593f07489048da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemies" sheetId="5" r:id="Ra38e1412645541fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equips" sheetId="6" r:id="R82ae3d75aafe4b0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classes" sheetId="7" r:id="R7c8a05caf61f437e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="States" sheetId="8" r:id="Rb73ecf821f834d99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MapNames" sheetId="9" r:id="R7f29443a380e4d13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Specials" sheetId="10" r:id="R57fb59fdebbe49aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player" sheetId="11" r:id="R10ede87ac49b4a7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DialogueNames" sheetId="13" r:id="R90c33be79393461e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DialogueContents" sheetId="14" r:id="Rce66ef665e1d48a1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2153,10 +2153,10 @@
         <x:v>maxrenderscale</x:v>
       </x:c>
       <x:c r="B42" t="str">
-        <x:v>Maximum Render Scale</x:v>
+        <x:v>Render Limit</x:v>
       </x:c>
       <x:c r="C42" t="str">
-        <x:v>最大渲染倍率</x:v>
+        <x:v>渲染上限</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -2168,6 +2168,116 @@
       </x:c>
       <x:c r="C43" t="str">
         <x:v>不限</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>graphics</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>Graphics</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>画质</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>audio</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>Audio</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>音量</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>graphicspreset</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>Quality Preset</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>画质档位</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>lightingrenderscale</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>Lighting Resolution</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>光照分辨率</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="str">
+        <x:v>low</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>Low</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>低</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" t="str">
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="B50" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="C50" t="str">
+        <x:v>高</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" t="str">
+        <x:v>extrahigh</x:v>
+      </x:c>
+      <x:c r="B51" t="str">
+        <x:v>Extra High</x:v>
+      </x:c>
+      <x:c r="C51" t="str">
+        <x:v>超高</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" t="str">
+        <x:v>original</x:v>
+      </x:c>
+      <x:c r="B52" t="str">
+        <x:v>Original</x:v>
+      </x:c>
+      <x:c r="C52" t="str">
+        <x:v>原画</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" t="str">
+        <x:v>custom</x:v>
+      </x:c>
+      <x:c r="B53" t="str">
+        <x:v>Custom</x:v>
+      </x:c>
+      <x:c r="C53" t="str">
+        <x:v>自定义</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI" sheetId="2" r:id="R7c6102095ac046a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Languages" sheetId="12" r:id="R6fd3ba9604ce46dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Attrs" sheetId="3" r:id="Rcb16155260ca416a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Items" sheetId="4" r:id="R08593f07489048da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemies" sheetId="5" r:id="Ra38e1412645541fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equips" sheetId="6" r:id="R82ae3d75aafe4b0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classes" sheetId="7" r:id="R7c8a05caf61f437e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="States" sheetId="8" r:id="Rb73ecf821f834d99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MapNames" sheetId="9" r:id="R7f29443a380e4d13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Specials" sheetId="10" r:id="R57fb59fdebbe49aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player" sheetId="11" r:id="R10ede87ac49b4a7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DialogueNames" sheetId="13" r:id="R90c33be79393461e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DialogueContents" sheetId="14" r:id="Rce66ef665e1d48a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI" sheetId="2" r:id="R936406ca3ca44419"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Languages" sheetId="12" r:id="Rb13e3c717c6a43ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Attrs" sheetId="3" r:id="R635c17cf092a4ae1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Items" sheetId="4" r:id="R250cb1b3caee42e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemies" sheetId="5" r:id="Re8421290e5f442c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equips" sheetId="6" r:id="R41d10fce622c4250"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classes" sheetId="7" r:id="R0731ea360ed241ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="States" sheetId="8" r:id="R5c2bf0bc8836409c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MapNames" sheetId="9" r:id="R63e35b6cb46d445d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Specials" sheetId="10" r:id="R8d4000e61aeb4aed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player" sheetId="11" r:id="R2805da4dc25c4cd9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DialogueNames" sheetId="13" r:id="Rc1fe707b5fcb4790"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DialogueContents" sheetId="14" r:id="Reffa9329b2e84c09"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2280,6 +2280,17 @@
         <x:v>自定义</x:v>
       </x:c>
     </x:row>
+    <x:row r="54">
+      <x:c r="A54" t="str">
+        <x:v>other</x:v>
+      </x:c>
+      <x:c r="B54" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="C54" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Sample/Data/Locale/Locale.xlsx
+++ b/Sample/Data/Locale/Locale.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Other\Ludork\Sample\Data\Locale\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fengmingliu/Dev/Ludork/Sample/Data/Locale/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC10B104-5CE7-4EC7-95E2-D22AD613D81E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC7FE2FF-B907-DB4A-AC68-1409E7096AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="2" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="513">
   <si>
     <t>ID</t>
   </si>
@@ -1564,77 +1564,26 @@
     <t>其他</t>
   </si>
   <si>
-    <t>MAP_W01_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>Tower 3F R1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MAP_W01_02</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MAP_W01_03</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MAP_W01_04</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MAP_W01_05</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tower 3F R2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tower 3F R3</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tower 3F R4</t>
-  </si>
-  <si>
-    <t>Tower 3F R5</t>
-  </si>
-  <si>
-    <t>魔塔 3 层 2 区</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>魔塔 3 层 1 区</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>魔塔 3 层 3 区</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>魔塔 3 层 4 区</t>
-  </si>
-  <si>
-    <t>魔塔 3 层 5 区</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>WORLD_01</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1690,21 +1639,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1915,14 +1862,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C54"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1933,7 +1880,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1944,7 +1891,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1955,7 +1902,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1966,7 +1913,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1977,7 +1924,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -1988,7 +1935,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1999,7 +1946,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -2010,7 +1957,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" s="4" t="s">
         <v>24</v>
       </c>
@@ -2021,7 +1968,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -2032,7 +1979,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -2043,7 +1990,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -2054,7 +2001,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -2065,7 +2012,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -2076,7 +2023,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>39</v>
       </c>
@@ -2087,7 +2034,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -2098,7 +2045,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -2109,7 +2056,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -2120,7 +2067,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -2131,7 +2078,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>53</v>
       </c>
@@ -2142,7 +2089,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>56</v>
       </c>
@@ -2153,7 +2100,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>59</v>
       </c>
@@ -2164,7 +2111,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>62</v>
       </c>
@@ -2175,7 +2122,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>65</v>
       </c>
@@ -2186,7 +2133,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3">
       <c r="A25" s="2" t="s">
         <v>68</v>
       </c>
@@ -2197,7 +2144,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3">
       <c r="A26" s="2" t="s">
         <v>71</v>
       </c>
@@ -2208,7 +2155,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>74</v>
       </c>
@@ -2219,7 +2166,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>77</v>
       </c>
@@ -2230,7 +2177,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>80</v>
       </c>
@@ -2241,7 +2188,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>83</v>
       </c>
@@ -2252,7 +2199,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>86</v>
       </c>
@@ -2263,7 +2210,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>89</v>
       </c>
@@ -2274,7 +2221,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>92</v>
       </c>
@@ -2285,7 +2232,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>95</v>
       </c>
@@ -2296,7 +2243,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>98</v>
       </c>
@@ -2307,7 +2254,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>101</v>
       </c>
@@ -2318,7 +2265,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>104</v>
       </c>
@@ -2329,7 +2276,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>107</v>
       </c>
@@ -2340,7 +2287,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>110</v>
       </c>
@@ -2351,7 +2298,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3">
       <c r="A40" s="3" t="s">
         <v>113</v>
       </c>
@@ -2362,7 +2309,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3">
       <c r="A41" s="4" t="s">
         <v>116</v>
       </c>
@@ -2373,7 +2320,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
         <v>471</v>
       </c>
@@ -2384,7 +2331,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3">
       <c r="A43" t="s">
         <v>474</v>
       </c>
@@ -2395,7 +2342,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
         <v>477</v>
       </c>
@@ -2406,7 +2353,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3">
       <c r="A45" t="s">
         <v>480</v>
       </c>
@@ -2417,7 +2364,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3">
       <c r="A46" t="s">
         <v>483</v>
       </c>
@@ -2428,7 +2375,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3">
       <c r="A47" t="s">
         <v>486</v>
       </c>
@@ -2439,7 +2386,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3">
       <c r="A48" t="s">
         <v>489</v>
       </c>
@@ -2450,7 +2397,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3">
       <c r="A49" t="s">
         <v>492</v>
       </c>
@@ -2461,7 +2408,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3">
       <c r="A50" t="s">
         <v>495</v>
       </c>
@@ -2472,7 +2419,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3">
       <c r="A51" t="s">
         <v>498</v>
       </c>
@@ -2483,7 +2430,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3">
       <c r="A52" t="s">
         <v>501</v>
       </c>
@@ -2494,7 +2441,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3">
       <c r="A53" t="s">
         <v>504</v>
       </c>
@@ -2505,7 +2452,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3">
       <c r="A54" t="s">
         <v>507</v>
       </c>
@@ -2517,7 +2464,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2525,13 +2472,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="43.1640625" customWidth="1"/>
     <col min="3" max="3" width="43.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2542,7 +2489,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>357</v>
       </c>
@@ -2553,7 +2500,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>359</v>
       </c>
@@ -2564,7 +2511,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>362</v>
       </c>
@@ -2575,7 +2522,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>364</v>
       </c>
@@ -2586,7 +2533,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>367</v>
       </c>
@@ -2597,7 +2544,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>369</v>
       </c>
@@ -2608,7 +2555,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>372</v>
       </c>
@@ -2619,7 +2566,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>375</v>
       </c>
@@ -2630,7 +2577,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>378</v>
       </c>
@@ -2641,7 +2588,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>381</v>
       </c>
@@ -2652,7 +2599,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>384</v>
       </c>
@@ -2663,7 +2610,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>387</v>
       </c>
@@ -2674,7 +2621,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>390</v>
       </c>
@@ -2685,7 +2632,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>393</v>
       </c>
@@ -2696,7 +2643,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>396</v>
       </c>
@@ -2707,7 +2654,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>399</v>
       </c>
@@ -2718,7 +2665,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>402</v>
       </c>
@@ -2729,7 +2676,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>405</v>
       </c>
@@ -2740,7 +2687,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>408</v>
       </c>
@@ -2751,7 +2698,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>411</v>
       </c>
@@ -2762,7 +2709,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3">
       <c r="A22" s="4" t="s">
         <v>414</v>
       </c>
@@ -2773,7 +2720,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3">
       <c r="A23" s="4" t="s">
         <v>417</v>
       </c>
@@ -2785,7 +2732,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2793,13 +2740,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="25.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2810,7 +2757,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>420</v>
       </c>
@@ -2821,7 +2768,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>423</v>
       </c>
@@ -2833,7 +2780,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2841,14 +2788,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
     <col min="2" max="2" width="17.6640625" customWidth="1"/>
     <col min="3" max="3" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2859,7 +2806,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" s="4" t="s">
         <v>426</v>
       </c>
@@ -2870,7 +2817,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" s="4" t="s">
         <v>429</v>
       </c>
@@ -2881,7 +2828,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
         <v>432</v>
       </c>
@@ -2893,7 +2840,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2901,12 +2848,12 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="3" width="34.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2917,7 +2864,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" s="4" t="s">
         <v>435</v>
       </c>
@@ -2928,7 +2875,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" s="4" t="s">
         <v>438</v>
       </c>
@@ -2939,7 +2886,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
         <v>441</v>
       </c>
@@ -2950,7 +2897,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
         <v>444</v>
       </c>
@@ -2961,7 +2908,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
         <v>447</v>
       </c>
@@ -2972,7 +2919,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
         <v>450</v>
       </c>
@@ -2983,7 +2930,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
         <v>453</v>
       </c>
@@ -2994,7 +2941,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" s="4" t="s">
         <v>456</v>
       </c>
@@ -3005,7 +2952,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" s="4" t="s">
         <v>459</v>
       </c>
@@ -3016,7 +2963,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" s="4" t="s">
         <v>462</v>
       </c>
@@ -3027,7 +2974,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
         <v>465</v>
       </c>
@@ -3038,7 +2985,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
         <v>468</v>
       </c>
@@ -3050,7 +2997,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3058,9 +3005,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3071,7 +3018,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3082,7 +3029,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -3094,7 +3041,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3102,9 +3049,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3115,7 +3062,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
         <v>123</v>
       </c>
@@ -3126,7 +3073,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
         <v>126</v>
       </c>
@@ -3137,7 +3084,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
         <v>129</v>
       </c>
@@ -3148,7 +3095,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
         <v>131</v>
       </c>
@@ -3159,7 +3106,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
         <v>133</v>
       </c>
@@ -3170,7 +3117,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
         <v>135</v>
       </c>
@@ -3181,7 +3128,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
         <v>138</v>
       </c>
@@ -3192,7 +3139,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
         <v>141</v>
       </c>
@@ -3203,7 +3150,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
         <v>144</v>
       </c>
@@ -3214,7 +3161,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
         <v>147</v>
       </c>
@@ -3226,7 +3173,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3234,14 +3181,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C33"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.6640625" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="24.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3252,7 +3199,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>150</v>
       </c>
@@ -3263,7 +3210,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>153</v>
       </c>
@@ -3274,7 +3221,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>156</v>
       </c>
@@ -3285,7 +3232,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>159</v>
       </c>
@@ -3296,7 +3243,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>162</v>
       </c>
@@ -3307,7 +3254,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>165</v>
       </c>
@@ -3318,7 +3265,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>168</v>
       </c>
@@ -3329,7 +3276,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>171</v>
       </c>
@@ -3340,7 +3287,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>174</v>
       </c>
@@ -3351,7 +3298,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>177</v>
       </c>
@@ -3362,7 +3309,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>180</v>
       </c>
@@ -3373,7 +3320,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>183</v>
       </c>
@@ -3384,7 +3331,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>186</v>
       </c>
@@ -3395,7 +3342,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>189</v>
       </c>
@@ -3406,7 +3353,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>192</v>
       </c>
@@ -3417,7 +3364,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>195</v>
       </c>
@@ -3428,7 +3375,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>198</v>
       </c>
@@ -3439,7 +3386,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>201</v>
       </c>
@@ -3450,7 +3397,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>204</v>
       </c>
@@ -3461,7 +3408,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>207</v>
       </c>
@@ -3472,7 +3419,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>210</v>
       </c>
@@ -3483,7 +3430,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>213</v>
       </c>
@@ -3494,7 +3441,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>216</v>
       </c>
@@ -3505,7 +3452,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>219</v>
       </c>
@@ -3516,7 +3463,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>222</v>
       </c>
@@ -3527,7 +3474,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>225</v>
       </c>
@@ -3538,7 +3485,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3">
       <c r="A28" s="4" t="s">
         <v>228</v>
       </c>
@@ -3549,7 +3496,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3">
       <c r="A29" s="4" t="s">
         <v>231</v>
       </c>
@@ -3560,7 +3507,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3">
       <c r="A30" s="4" t="s">
         <v>234</v>
       </c>
@@ -3571,7 +3518,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3">
       <c r="A31" s="4" t="s">
         <v>237</v>
       </c>
@@ -3582,7 +3529,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
         <v>240</v>
       </c>
@@ -3593,7 +3540,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3">
       <c r="A33" s="4" t="s">
         <v>243</v>
       </c>
@@ -3605,7 +3552,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3613,14 +3560,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29.5" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="32.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3631,7 +3578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>246</v>
       </c>
@@ -3642,7 +3589,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>249</v>
       </c>
@@ -3653,7 +3600,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>252</v>
       </c>
@@ -3664,7 +3611,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>255</v>
       </c>
@@ -3675,7 +3622,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>258</v>
       </c>
@@ -3686,7 +3633,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>261</v>
       </c>
@@ -3697,7 +3644,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>264</v>
       </c>
@@ -3708,7 +3655,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>267</v>
       </c>
@@ -3719,7 +3666,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>270</v>
       </c>
@@ -3730,7 +3677,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>273</v>
       </c>
@@ -3741,7 +3688,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>276</v>
       </c>
@@ -3752,7 +3699,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>279</v>
       </c>
@@ -3763,7 +3710,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
         <v>282</v>
       </c>
@@ -3774,7 +3721,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
         <v>285</v>
       </c>
@@ -3785,7 +3732,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
         <v>288</v>
       </c>
@@ -3796,7 +3743,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
         <v>291</v>
       </c>
@@ -3807,7 +3754,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>294</v>
       </c>
@@ -3818,7 +3765,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
         <v>297</v>
       </c>
@@ -3829,7 +3776,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>300</v>
       </c>
@@ -3840,7 +3787,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3">
       <c r="A21" s="3" t="s">
         <v>303</v>
       </c>
@@ -3851,7 +3798,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3">
       <c r="A22" s="4" t="s">
         <v>306</v>
       </c>
@@ -3862,7 +3809,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3">
       <c r="A23" s="4" t="s">
         <v>309</v>
       </c>
@@ -3874,7 +3821,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3882,13 +3829,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
     <col min="3" max="3" width="42.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3899,7 +3846,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>312</v>
       </c>
@@ -3910,7 +3857,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>315</v>
       </c>
@@ -3921,7 +3868,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>318</v>
       </c>
@@ -3932,7 +3879,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>321</v>
       </c>
@@ -3944,7 +3891,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3952,13 +3899,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="40" customWidth="1"/>
     <col min="3" max="3" width="35.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3969,7 +3916,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>324</v>
       </c>
@@ -3980,7 +3927,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>327</v>
       </c>
@@ -3992,7 +3939,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4000,13 +3947,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="43.1640625" customWidth="1"/>
     <col min="3" max="3" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4017,7 +3964,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>330</v>
       </c>
@@ -4028,7 +3975,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>333</v>
       </c>
@@ -4039,7 +3986,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>336</v>
       </c>
@@ -4050,7 +3997,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>339</v>
       </c>
@@ -4061,7 +4008,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>342</v>
       </c>
@@ -4073,7 +4020,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4081,14 +4028,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4099,7 +4046,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>345</v>
       </c>
@@ -4110,7 +4057,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>348</v>
       </c>
@@ -4121,7 +4068,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>351</v>
       </c>
@@ -4132,7 +4079,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>354</v>
       </c>
@@ -4143,63 +4090,39 @@
         <v>356</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" s="5" t="s">
+        <v>512</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>510</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>511</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
-        <v>512</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>516</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>513</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>517</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>518</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
-        <v>515</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>519</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>524</v>
-      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>